--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4479E847-A1A8-4627-BB18-F74E2AB6A3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C06ED55-A508-489C-86EF-8B6D630DB2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -17427,7 +17427,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I477" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="16" priority="67"/>
   </conditionalFormatting>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804C7222-F2CC-4777-8B44-59C7D18A6658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF45B70-8626-4E22-B6DB-5BA58E9F8F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$481</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$480</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3167" uniqueCount="1649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3166" uniqueCount="1649">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -5651,7 +5651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:I481"/>
+  <dimension ref="A1:I480"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -18234,11 +18234,6 @@
       <c r="H480" s="13"/>
       <c r="I480" s="15">
         <v>0</v>
-      </c>
-    </row>
-    <row r="481" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A481" s="1" t="s">
-        <v>1220</v>
       </c>
     </row>
   </sheetData>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96846BD0-0833-4351-873C-A2D1866AE3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE0A5A5-82A7-44C6-8382-0F27E7283452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3167" uniqueCount="1644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4922" uniqueCount="2699">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -4969,6 +4969,3171 @@
   </si>
   <si>
     <t>B0FHVWHQHR</t>
+  </si>
+  <si>
+    <t>FBA80093</t>
+  </si>
+  <si>
+    <t>FBA75260</t>
+  </si>
+  <si>
+    <t>FBA74728</t>
+  </si>
+  <si>
+    <t>FBA66963</t>
+  </si>
+  <si>
+    <t>FBA66974</t>
+  </si>
+  <si>
+    <t>FBA66636</t>
+  </si>
+  <si>
+    <t>FBA69595</t>
+  </si>
+  <si>
+    <t>FBA74721</t>
+  </si>
+  <si>
+    <t>FBA66640</t>
+  </si>
+  <si>
+    <t>FBA66964</t>
+  </si>
+  <si>
+    <t>FBA79748</t>
+  </si>
+  <si>
+    <t>FBA70527</t>
+  </si>
+  <si>
+    <t>FBA71628</t>
+  </si>
+  <si>
+    <t>FBA79633</t>
+  </si>
+  <si>
+    <t>FBA75077</t>
+  </si>
+  <si>
+    <t>FBA67811</t>
+  </si>
+  <si>
+    <t>FBA66627</t>
+  </si>
+  <si>
+    <t>FBA79514</t>
+  </si>
+  <si>
+    <t>FBA74257</t>
+  </si>
+  <si>
+    <t>FBA79627</t>
+  </si>
+  <si>
+    <t>FBA66648</t>
+  </si>
+  <si>
+    <t>FBA79753</t>
+  </si>
+  <si>
+    <t>FBA79539</t>
+  </si>
+  <si>
+    <t>FBA79289</t>
+  </si>
+  <si>
+    <t>FBA70774</t>
+  </si>
+  <si>
+    <t>FBA76941</t>
+  </si>
+  <si>
+    <t>FBA70769</t>
+  </si>
+  <si>
+    <t>FBA79731</t>
+  </si>
+  <si>
+    <t>FBA67266</t>
+  </si>
+  <si>
+    <t>FBA79735</t>
+  </si>
+  <si>
+    <t>FBA70827</t>
+  </si>
+  <si>
+    <t>FBA79530</t>
+  </si>
+  <si>
+    <t>FBA79755</t>
+  </si>
+  <si>
+    <t>FBA79148</t>
+  </si>
+  <si>
+    <t>FBA79920</t>
+  </si>
+  <si>
+    <t>FBA79512</t>
+  </si>
+  <si>
+    <t>FBA79526</t>
+  </si>
+  <si>
+    <t>FBA67803</t>
+  </si>
+  <si>
+    <t>FBA79018</t>
+  </si>
+  <si>
+    <t>FBA79334</t>
+  </si>
+  <si>
+    <t>FBA79515</t>
+  </si>
+  <si>
+    <t>FBA79421</t>
+  </si>
+  <si>
+    <t>FBA79640</t>
+  </si>
+  <si>
+    <t>FBA79224</t>
+  </si>
+  <si>
+    <t>FBA79335</t>
+  </si>
+  <si>
+    <t>FBA74927</t>
+  </si>
+  <si>
+    <t>FBA66633</t>
+  </si>
+  <si>
+    <t>FBA79754</t>
+  </si>
+  <si>
+    <t>FBA74251</t>
+  </si>
+  <si>
+    <t>FBA79324</t>
+  </si>
+  <si>
+    <t>FBA79527</t>
+  </si>
+  <si>
+    <t>FBA79143</t>
+  </si>
+  <si>
+    <t>FBA79223</t>
+  </si>
+  <si>
+    <t>FBA79933</t>
+  </si>
+  <si>
+    <t>FBA79030</t>
+  </si>
+  <si>
+    <t>FBA79637</t>
+  </si>
+  <si>
+    <t>FBA79879</t>
+  </si>
+  <si>
+    <t>FBA79921</t>
+  </si>
+  <si>
+    <t>FBA79935</t>
+  </si>
+  <si>
+    <t>FBA79529</t>
+  </si>
+  <si>
+    <t>FBA79144</t>
+  </si>
+  <si>
+    <t>FBA79222</t>
+  </si>
+  <si>
+    <t>FBA79733</t>
+  </si>
+  <si>
+    <t>FBA79875</t>
+  </si>
+  <si>
+    <t>FBA79554</t>
+  </si>
+  <si>
+    <t>FBA79876</t>
+  </si>
+  <si>
+    <t>FBA79934</t>
+  </si>
+  <si>
+    <t>FBA79145</t>
+  </si>
+  <si>
+    <t>FBA67928</t>
+  </si>
+  <si>
+    <t>FBA75320</t>
+  </si>
+  <si>
+    <t>FBA79319</t>
+  </si>
+  <si>
+    <t>FBA79638</t>
+  </si>
+  <si>
+    <t>FBA79556</t>
+  </si>
+  <si>
+    <t>FBA79801</t>
+  </si>
+  <si>
+    <t>FBA79867</t>
+  </si>
+  <si>
+    <t>FBA79880</t>
+  </si>
+  <si>
+    <t>FBA79883</t>
+  </si>
+  <si>
+    <t>FBA74952</t>
+  </si>
+  <si>
+    <t>FBA79926</t>
+  </si>
+  <si>
+    <t>FBA76772</t>
+  </si>
+  <si>
+    <t>FBA79048</t>
+  </si>
+  <si>
+    <t>FBA79495</t>
+  </si>
+  <si>
+    <t>FBA79625</t>
+  </si>
+  <si>
+    <t>FBA79651</t>
+  </si>
+  <si>
+    <t>FBA75326</t>
+  </si>
+  <si>
+    <t>FBA79800</t>
+  </si>
+  <si>
+    <t>FBA78013</t>
+  </si>
+  <si>
+    <t>FBA79641</t>
+  </si>
+  <si>
+    <t>FBA79634</t>
+  </si>
+  <si>
+    <t>FBA79877</t>
+  </si>
+  <si>
+    <t>FBA79881</t>
+  </si>
+  <si>
+    <t>FBA79925</t>
+  </si>
+  <si>
+    <t>FBA79937</t>
+  </si>
+  <si>
+    <t>FBA79632</t>
+  </si>
+  <si>
+    <t>FBA79152</t>
+  </si>
+  <si>
+    <t>FBA69614</t>
+  </si>
+  <si>
+    <t>FBA79432</t>
+  </si>
+  <si>
+    <t>FBA72002</t>
+  </si>
+  <si>
+    <t>FBA79723</t>
+  </si>
+  <si>
+    <t>FBA79504</t>
+  </si>
+  <si>
+    <t>FBA79558</t>
+  </si>
+  <si>
+    <t>FBA75346</t>
+  </si>
+  <si>
+    <t>FBA76771</t>
+  </si>
+  <si>
+    <t>FBA79031</t>
+  </si>
+  <si>
+    <t>FBA79497</t>
+  </si>
+  <si>
+    <t>FBA79541</t>
+  </si>
+  <si>
+    <t>FBA79618</t>
+  </si>
+  <si>
+    <t>FBA79730</t>
+  </si>
+  <si>
+    <t>FBA79868</t>
+  </si>
+  <si>
+    <t>FBA79624</t>
+  </si>
+  <si>
+    <t>FBA79882</t>
+  </si>
+  <si>
+    <t>FBA79885</t>
+  </si>
+  <si>
+    <t>FBA79513</t>
+  </si>
+  <si>
+    <t>FBA74758</t>
+  </si>
+  <si>
+    <t>FBA74245</t>
+  </si>
+  <si>
+    <t>FBA79746</t>
+  </si>
+  <si>
+    <t>FBA79628</t>
+  </si>
+  <si>
+    <t>FBA79649</t>
+  </si>
+  <si>
+    <t>FBA77996</t>
+  </si>
+  <si>
+    <t>FBA79305</t>
+  </si>
+  <si>
+    <t>FBA79317</t>
+  </si>
+  <si>
+    <t>FBA79340</t>
+  </si>
+  <si>
+    <t>FBA79302</t>
+  </si>
+  <si>
+    <t>FBA79518</t>
+  </si>
+  <si>
+    <t>FBA69631</t>
+  </si>
+  <si>
+    <t>FBA79630</t>
+  </si>
+  <si>
+    <t>FBA79533</t>
+  </si>
+  <si>
+    <t>FBA79729</t>
+  </si>
+  <si>
+    <t>FBA79525</t>
+  </si>
+  <si>
+    <t>FBA79756</t>
+  </si>
+  <si>
+    <t>FBA79323</t>
+  </si>
+  <si>
+    <t>FBA74972</t>
+  </si>
+  <si>
+    <t>FBA79500</t>
+  </si>
+  <si>
+    <t>FBA76447</t>
+  </si>
+  <si>
+    <t>FBA79557</t>
+  </si>
+  <si>
+    <t>FBA79040</t>
+  </si>
+  <si>
+    <t>FBA79422</t>
+  </si>
+  <si>
+    <t>FBA79496</t>
+  </si>
+  <si>
+    <t>FBA79283</t>
+  </si>
+  <si>
+    <t>FBA79158</t>
+  </si>
+  <si>
+    <t>FBA79288</t>
+  </si>
+  <si>
+    <t>FBA79322</t>
+  </si>
+  <si>
+    <t>FBA79021</t>
+  </si>
+  <si>
+    <t>FBA79312</t>
+  </si>
+  <si>
+    <t>FBA79029</t>
+  </si>
+  <si>
+    <t>FBA79645</t>
+  </si>
+  <si>
+    <t>FBA79724</t>
+  </si>
+  <si>
+    <t>FBA79742</t>
+  </si>
+  <si>
+    <t>FBA79743</t>
+  </si>
+  <si>
+    <t>FBA79796</t>
+  </si>
+  <si>
+    <t>FBA79856</t>
+  </si>
+  <si>
+    <t>FBA77972</t>
+  </si>
+  <si>
+    <t>FBA79857</t>
+  </si>
+  <si>
+    <t>FBA79425</t>
+  </si>
+  <si>
+    <t>FBA79859</t>
+  </si>
+  <si>
+    <t>FBA79377</t>
+  </si>
+  <si>
+    <t>FBA79221</t>
+  </si>
+  <si>
+    <t>FBA79860</t>
+  </si>
+  <si>
+    <t>FBA79861</t>
+  </si>
+  <si>
+    <t>FBA79866</t>
+  </si>
+  <si>
+    <t>FBA79869</t>
+  </si>
+  <si>
+    <t>FBA79521</t>
+  </si>
+  <si>
+    <t>FBA79522</t>
+  </si>
+  <si>
+    <t>FBA79884</t>
+  </si>
+  <si>
+    <t>FBA79890</t>
+  </si>
+  <si>
+    <t>FBA79542</t>
+  </si>
+  <si>
+    <t>FBA79555</t>
+  </si>
+  <si>
+    <t>FBA79414</t>
+  </si>
+  <si>
+    <t>FBA79891</t>
+  </si>
+  <si>
+    <t>FBA79046</t>
+  </si>
+  <si>
+    <t>FBA79341</t>
+  </si>
+  <si>
+    <t>FBA79894</t>
+  </si>
+  <si>
+    <t>FBA79409</t>
+  </si>
+  <si>
+    <t>FBA79545</t>
+  </si>
+  <si>
+    <t>FBA79919</t>
+  </si>
+  <si>
+    <t>FBA79343</t>
+  </si>
+  <si>
+    <t>FBA79938</t>
+  </si>
+  <si>
+    <t>FBA74838</t>
+  </si>
+  <si>
+    <t>FBA79738</t>
+  </si>
+  <si>
+    <t>FBA69544</t>
+  </si>
+  <si>
+    <t>FBA77981</t>
+  </si>
+  <si>
+    <t>FBA79538</t>
+  </si>
+  <si>
+    <t>FBA79426</t>
+  </si>
+  <si>
+    <t>FBA67801</t>
+  </si>
+  <si>
+    <t>FBA66995</t>
+  </si>
+  <si>
+    <t>FBA79540</t>
+  </si>
+  <si>
+    <t>FBA79503</t>
+  </si>
+  <si>
+    <t>FBA66654</t>
+  </si>
+  <si>
+    <t>FBA75146</t>
+  </si>
+  <si>
+    <t>FBA79642</t>
+  </si>
+  <si>
+    <t>FBA76490</t>
+  </si>
+  <si>
+    <t>FBA79650</t>
+  </si>
+  <si>
+    <t>FBA79728</t>
+  </si>
+  <si>
+    <t>FBA79619</t>
+  </si>
+  <si>
+    <t>FBA79622</t>
+  </si>
+  <si>
+    <t>FBA79749</t>
+  </si>
+  <si>
+    <t>FBA79639</t>
+  </si>
+  <si>
+    <t>FBA77995</t>
+  </si>
+  <si>
+    <t>FBA79647</t>
+  </si>
+  <si>
+    <t>FBA79629</t>
+  </si>
+  <si>
+    <t>FBA79524</t>
+  </si>
+  <si>
+    <t>FBA79507</t>
+  </si>
+  <si>
+    <t>FBA79520</t>
+  </si>
+  <si>
+    <t>FBA79523</t>
+  </si>
+  <si>
+    <t>FBA79502</t>
+  </si>
+  <si>
+    <t>FBA67860</t>
+  </si>
+  <si>
+    <t>FBA77066</t>
+  </si>
+  <si>
+    <t>FBA79636</t>
+  </si>
+  <si>
+    <t>FBA79740</t>
+  </si>
+  <si>
+    <t>FBA79741</t>
+  </si>
+  <si>
+    <t>FBA79757</t>
+  </si>
+  <si>
+    <t>FBA79758</t>
+  </si>
+  <si>
+    <t>FBA79759</t>
+  </si>
+  <si>
+    <t>FBA79760</t>
+  </si>
+  <si>
+    <t>FBA79761</t>
+  </si>
+  <si>
+    <t>FBA79795</t>
+  </si>
+  <si>
+    <t>FBA79797</t>
+  </si>
+  <si>
+    <t>FBA79798</t>
+  </si>
+  <si>
+    <t>FBA79805</t>
+  </si>
+  <si>
+    <t>FBA79806</t>
+  </si>
+  <si>
+    <t>FBA79807</t>
+  </si>
+  <si>
+    <t>FBA79862</t>
+  </si>
+  <si>
+    <t>FBA79864</t>
+  </si>
+  <si>
+    <t>FBA79878</t>
+  </si>
+  <si>
+    <t>FBA79893</t>
+  </si>
+  <si>
+    <t>FBA79897</t>
+  </si>
+  <si>
+    <t>FBA79916</t>
+  </si>
+  <si>
+    <t>FBA79917</t>
+  </si>
+  <si>
+    <t>FBA79855</t>
+  </si>
+  <si>
+    <t>FBA79923</t>
+  </si>
+  <si>
+    <t>FBA79643</t>
+  </si>
+  <si>
+    <t>FBA69548</t>
+  </si>
+  <si>
+    <t>FBA79499</t>
+  </si>
+  <si>
+    <t>FBA79311</t>
+  </si>
+  <si>
+    <t>FBA79644</t>
+  </si>
+  <si>
+    <t>FBA79336</t>
+  </si>
+  <si>
+    <t>FBA79310</t>
+  </si>
+  <si>
+    <t>FBA79501</t>
+  </si>
+  <si>
+    <t>FBA79517</t>
+  </si>
+  <si>
+    <t>FBA79423</t>
+  </si>
+  <si>
+    <t>FBA78012</t>
+  </si>
+  <si>
+    <t>FBA79727</t>
+  </si>
+  <si>
+    <t>FBA79808</t>
+  </si>
+  <si>
+    <t>FBA79854</t>
+  </si>
+  <si>
+    <t>FBA79863</t>
+  </si>
+  <si>
+    <t>FBA79865</t>
+  </si>
+  <si>
+    <t>FBA79874</t>
+  </si>
+  <si>
+    <t>FBA79871</t>
+  </si>
+  <si>
+    <t>FBA79873</t>
+  </si>
+  <si>
+    <t>FBA79886</t>
+  </si>
+  <si>
+    <t>FBA79887</t>
+  </si>
+  <si>
+    <t>FBA79888</t>
+  </si>
+  <si>
+    <t>FBA79889</t>
+  </si>
+  <si>
+    <t>FBA79892</t>
+  </si>
+  <si>
+    <t>FBA79895</t>
+  </si>
+  <si>
+    <t>FBA79896</t>
+  </si>
+  <si>
+    <t>FBA79898</t>
+  </si>
+  <si>
+    <t>FBA79918</t>
+  </si>
+  <si>
+    <t>FBA79927</t>
+  </si>
+  <si>
+    <t>FBA79930</t>
+  </si>
+  <si>
+    <t>FBA79931</t>
+  </si>
+  <si>
+    <t>FBA79932</t>
+  </si>
+  <si>
+    <t>FBA79943</t>
+  </si>
+  <si>
+    <t>FBA79944</t>
+  </si>
+  <si>
+    <t>FBA79948</t>
+  </si>
+  <si>
+    <t>FBA79950</t>
+  </si>
+  <si>
+    <t>FBA69556</t>
+  </si>
+  <si>
+    <t>FBA79418</t>
+  </si>
+  <si>
+    <t>FBA69579</t>
+  </si>
+  <si>
+    <t>FBA79413</t>
+  </si>
+  <si>
+    <t>FBA79899</t>
+  </si>
+  <si>
+    <t>FBA79411</t>
+  </si>
+  <si>
+    <t>FBA79412</t>
+  </si>
+  <si>
+    <t>FBA79498</t>
+  </si>
+  <si>
+    <t>FBA79725</t>
+  </si>
+  <si>
+    <t>FBA79737</t>
+  </si>
+  <si>
+    <t>FBA79750</t>
+  </si>
+  <si>
+    <t>FBA79799</t>
+  </si>
+  <si>
+    <t>FBA79803</t>
+  </si>
+  <si>
+    <t>FBA79804</t>
+  </si>
+  <si>
+    <t>FBA79870</t>
+  </si>
+  <si>
+    <t>FBA79928</t>
+  </si>
+  <si>
+    <t>FBA79929</t>
+  </si>
+  <si>
+    <t>FBA79924</t>
+  </si>
+  <si>
+    <t>FBA79939</t>
+  </si>
+  <si>
+    <t>FBA79941</t>
+  </si>
+  <si>
+    <t>FBA79942</t>
+  </si>
+  <si>
+    <t>FBA79945</t>
+  </si>
+  <si>
+    <t>FBA79949</t>
+  </si>
+  <si>
+    <t>FBA79631</t>
+  </si>
+  <si>
+    <t>FBA77988</t>
+  </si>
+  <si>
+    <t>FBA79752</t>
+  </si>
+  <si>
+    <t>FBA79940</t>
+  </si>
+  <si>
+    <t>FBA79506</t>
+  </si>
+  <si>
+    <t>FBA79292</t>
+  </si>
+  <si>
+    <t>FBA79122</t>
+  </si>
+  <si>
+    <t>FBA79946</t>
+  </si>
+  <si>
+    <t>FBA79951</t>
+  </si>
+  <si>
+    <t>FBA80025</t>
+  </si>
+  <si>
+    <t>FBA80026</t>
+  </si>
+  <si>
+    <t>FBA80027</t>
+  </si>
+  <si>
+    <t>FBA80028</t>
+  </si>
+  <si>
+    <t>FBA80029</t>
+  </si>
+  <si>
+    <t>FBA80030</t>
+  </si>
+  <si>
+    <t>FBA80031</t>
+  </si>
+  <si>
+    <t>FBA80032</t>
+  </si>
+  <si>
+    <t>FBA80033</t>
+  </si>
+  <si>
+    <t>FBA80034</t>
+  </si>
+  <si>
+    <t>FBA80036</t>
+  </si>
+  <si>
+    <t>FBA80037</t>
+  </si>
+  <si>
+    <t>FBA80039</t>
+  </si>
+  <si>
+    <t>FBA80040</t>
+  </si>
+  <si>
+    <t>FBA80042</t>
+  </si>
+  <si>
+    <t>FBA80043</t>
+  </si>
+  <si>
+    <t>FBA80044</t>
+  </si>
+  <si>
+    <t>FBA80045</t>
+  </si>
+  <si>
+    <t>FBA80046</t>
+  </si>
+  <si>
+    <t>FBA80047</t>
+  </si>
+  <si>
+    <t>FBA80048</t>
+  </si>
+  <si>
+    <t>FBA80049</t>
+  </si>
+  <si>
+    <t>FBA80050</t>
+  </si>
+  <si>
+    <t>FBA80052</t>
+  </si>
+  <si>
+    <t>FBA80054</t>
+  </si>
+  <si>
+    <t>FBA80055</t>
+  </si>
+  <si>
+    <t>FBA80056</t>
+  </si>
+  <si>
+    <t>FBA80057</t>
+  </si>
+  <si>
+    <t>FBA80058</t>
+  </si>
+  <si>
+    <t>FBA80059</t>
+  </si>
+  <si>
+    <t>FBA80060</t>
+  </si>
+  <si>
+    <t>FBA80061</t>
+  </si>
+  <si>
+    <t>FBA80062</t>
+  </si>
+  <si>
+    <t>FBA80063</t>
+  </si>
+  <si>
+    <t>FBA80064</t>
+  </si>
+  <si>
+    <t>FBA80065</t>
+  </si>
+  <si>
+    <t>FBA80066</t>
+  </si>
+  <si>
+    <t>FBA80067</t>
+  </si>
+  <si>
+    <t>FBA80068</t>
+  </si>
+  <si>
+    <t>FBA80069</t>
+  </si>
+  <si>
+    <t>FBA80070</t>
+  </si>
+  <si>
+    <t>FBA80071</t>
+  </si>
+  <si>
+    <t>FBA80072</t>
+  </si>
+  <si>
+    <t>FBA80073</t>
+  </si>
+  <si>
+    <t>B00H2ZDX00</t>
+  </si>
+  <si>
+    <t>B00DUCIK7U</t>
+  </si>
+  <si>
+    <t>B078Y2PJL4</t>
+  </si>
+  <si>
+    <t>B00AG37H8Y</t>
+  </si>
+  <si>
+    <t>B008AXYWHQ</t>
+  </si>
+  <si>
+    <t>B004D4S7AY</t>
+  </si>
+  <si>
+    <t>B07CSNG8XL</t>
+  </si>
+  <si>
+    <t>B00AMWDOEK</t>
+  </si>
+  <si>
+    <t>B00AFTTQ8I</t>
+  </si>
+  <si>
+    <t>B00WM0CF4A</t>
+  </si>
+  <si>
+    <t>B0DSBSGK17</t>
+  </si>
+  <si>
+    <t>B00NVAWTLY</t>
+  </si>
+  <si>
+    <t>B07RZ1R1HJ</t>
+  </si>
+  <si>
+    <t>B0DJ2XHK2N</t>
+  </si>
+  <si>
+    <t>B08QVCPDVT</t>
+  </si>
+  <si>
+    <t>B06VV5QB6Q</t>
+  </si>
+  <si>
+    <t>B007NM84PQ</t>
+  </si>
+  <si>
+    <t>B0D854LDQM</t>
+  </si>
+  <si>
+    <t>B079XB5RXH</t>
+  </si>
+  <si>
+    <t>B0DKJHSD8R</t>
+  </si>
+  <si>
+    <t>B00AFTTQQ0</t>
+  </si>
+  <si>
+    <t>B0DSBSD26P</t>
+  </si>
+  <si>
+    <t>B0D955L5S7</t>
+  </si>
+  <si>
+    <t>B0CRDG22TQ</t>
+  </si>
+  <si>
+    <t>B07MFZ6S2Q</t>
+  </si>
+  <si>
+    <t>B0BFXL8ZP9</t>
+  </si>
+  <si>
+    <t>B07M7P7VLX</t>
+  </si>
+  <si>
+    <t>B0DSBQCZTK</t>
+  </si>
+  <si>
+    <t>B0058XWUHA</t>
+  </si>
+  <si>
+    <t>B0DSBR8G7Y</t>
+  </si>
+  <si>
+    <t>B07MM5MH6F</t>
+  </si>
+  <si>
+    <t>B0D9369MTM</t>
+  </si>
+  <si>
+    <t>B0DSBRWZ8N</t>
+  </si>
+  <si>
+    <t>B0CF61X2BG</t>
+  </si>
+  <si>
+    <t>B0FRVZCYH9</t>
+  </si>
+  <si>
+    <t>B0D84YY632</t>
+  </si>
+  <si>
+    <t>B0D9574DPS</t>
+  </si>
+  <si>
+    <t>B01487C7CO</t>
+  </si>
+  <si>
+    <t>B0C77PPS9S</t>
+  </si>
+  <si>
+    <t>B0CRCWV9DV</t>
+  </si>
+  <si>
+    <t>B0D8572WTJ</t>
+  </si>
+  <si>
+    <t>B0CZ8ZKPJ9</t>
+  </si>
+  <si>
+    <t>B0DJ2V3TH2</t>
+  </si>
+  <si>
+    <t>B0CFBCTN93</t>
+  </si>
+  <si>
+    <t>B0CRD1DRXG</t>
+  </si>
+  <si>
+    <t>B0846Q1JT5</t>
+  </si>
+  <si>
+    <t>B00AFTT8KE</t>
+  </si>
+  <si>
+    <t>B0DSBQYVSM</t>
+  </si>
+  <si>
+    <t>B01GZZYSRO</t>
+  </si>
+  <si>
+    <t>B0CRCZ8TGK</t>
+  </si>
+  <si>
+    <t>B0D936GPVL</t>
+  </si>
+  <si>
+    <t>B0CJ6ZHK1S</t>
+  </si>
+  <si>
+    <t>B0CFBB587Z</t>
+  </si>
+  <si>
+    <t>B0FTMM455Z</t>
+  </si>
+  <si>
+    <t>B0C7WKTMFC</t>
+  </si>
+  <si>
+    <t>B0DC64BD5R</t>
+  </si>
+  <si>
+    <t>B0FCVBY986</t>
+  </si>
+  <si>
+    <t>B0FRVG8SR6</t>
+  </si>
+  <si>
+    <t>B0FTK3KCY6</t>
+  </si>
+  <si>
+    <t>B0D9362N4Q</t>
+  </si>
+  <si>
+    <t>B0CF5XZR93</t>
+  </si>
+  <si>
+    <t>B0C77Q5TQ5</t>
+  </si>
+  <si>
+    <t>B0DSBS17RY</t>
+  </si>
+  <si>
+    <t>B0FCVLFLGF</t>
+  </si>
+  <si>
+    <t>B0D9568856</t>
+  </si>
+  <si>
+    <t>B0FCVLB3FG</t>
+  </si>
+  <si>
+    <t>B0FTKNBJY4</t>
+  </si>
+  <si>
+    <t>B0CJ6ZW8F6</t>
+  </si>
+  <si>
+    <t>B001J1772I</t>
+  </si>
+  <si>
+    <t>B09NC2NFR9</t>
+  </si>
+  <si>
+    <t>B0CRD2CVZL</t>
+  </si>
+  <si>
+    <t>B0DC674ZNR</t>
+  </si>
+  <si>
+    <t>B0D955YGX7</t>
+  </si>
+  <si>
+    <t>B0DT31Q99D</t>
+  </si>
+  <si>
+    <t>B0FFDM5QJX</t>
+  </si>
+  <si>
+    <t>B0FJ2SQTNR</t>
+  </si>
+  <si>
+    <t>B0FCVRKB8C</t>
+  </si>
+  <si>
+    <t>B09CSXR4TR</t>
+  </si>
+  <si>
+    <t>B0FRWJ5N3P</t>
+  </si>
+  <si>
+    <t>B0BFZRGPJ6</t>
+  </si>
+  <si>
+    <t>B0CCHHGG9B</t>
+  </si>
+  <si>
+    <t>B0DB1J1HST</t>
+  </si>
+  <si>
+    <t>B0DKJH623H</t>
+  </si>
+  <si>
+    <t>B0DJ2WP1M5</t>
+  </si>
+  <si>
+    <t>B09SHQSHBF</t>
+  </si>
+  <si>
+    <t>B0DT2Q1R2H</t>
+  </si>
+  <si>
+    <t>B0BQ34TRDX</t>
+  </si>
+  <si>
+    <t>B0DJ2VFZWN</t>
+  </si>
+  <si>
+    <t>B0DJ2Z6JSW</t>
+  </si>
+  <si>
+    <t>B0FCVHPY4B</t>
+  </si>
+  <si>
+    <t>B0FCVBJX29</t>
+  </si>
+  <si>
+    <t>B0FRVBBDM9</t>
+  </si>
+  <si>
+    <t>B0FTK7KQ1P</t>
+  </si>
+  <si>
+    <t>B0DJ2Y1BG6</t>
+  </si>
+  <si>
+    <t>B0CHXTNMNX</t>
+  </si>
+  <si>
+    <t>B00944CXEY</t>
+  </si>
+  <si>
+    <t>B0CZ8X8CBD</t>
+  </si>
+  <si>
+    <t>B00CMWR0K2</t>
+  </si>
+  <si>
+    <t>B0DT2QDBS3</t>
+  </si>
+  <si>
+    <t>B0D935TWSR</t>
+  </si>
+  <si>
+    <t>B0D9573TBX</t>
+  </si>
+  <si>
+    <t>B08XBYKWW3</t>
+  </si>
+  <si>
+    <t>B0BFZL8NN2</t>
+  </si>
+  <si>
+    <t>B0C89RHY4W</t>
+  </si>
+  <si>
+    <t>B0D936FLK4</t>
+  </si>
+  <si>
+    <t>B0D955BY7N</t>
+  </si>
+  <si>
+    <t>B0DJ2XCDJ1</t>
+  </si>
+  <si>
+    <t>B0DSBN63D1</t>
+  </si>
+  <si>
+    <t>B0FFD4KBM7</t>
+  </si>
+  <si>
+    <t>B0DKJHJV6T</t>
+  </si>
+  <si>
+    <t>B0FCVPBY7Y</t>
+  </si>
+  <si>
+    <t>B0FJ2RND61</t>
+  </si>
+  <si>
+    <t>B0D853Y52R</t>
+  </si>
+  <si>
+    <t>B0846PC77Q</t>
+  </si>
+  <si>
+    <t>B084CG2ZVZ</t>
+  </si>
+  <si>
+    <t>B0DSBQDZNV</t>
+  </si>
+  <si>
+    <t>B0DKJBJBX6</t>
+  </si>
+  <si>
+    <t>B0DJ2W8W79</t>
+  </si>
+  <si>
+    <t>B0BS4BHNVN</t>
+  </si>
+  <si>
+    <t>B0CR5PZRNY</t>
+  </si>
+  <si>
+    <t>B0CR5S175Y</t>
+  </si>
+  <si>
+    <t>B0CRCYMKY8</t>
+  </si>
+  <si>
+    <t>B0CR5QRNQN</t>
+  </si>
+  <si>
+    <t>B0D84YD59Y</t>
+  </si>
+  <si>
+    <t>B077SMJP9Z</t>
+  </si>
+  <si>
+    <t>B0DJ2YM76K</t>
+  </si>
+  <si>
+    <t>B0D933B79H</t>
+  </si>
+  <si>
+    <t>B0DT2Y9HRM</t>
+  </si>
+  <si>
+    <t>B0D954M6YQ</t>
+  </si>
+  <si>
+    <t>B0DP5HM2ZR</t>
+  </si>
+  <si>
+    <t>B0CRD3QWVJ</t>
+  </si>
+  <si>
+    <t>B09GYQ4RS7</t>
+  </si>
+  <si>
+    <t>B0D935TKFD</t>
+  </si>
+  <si>
+    <t>B0B75LLWV6</t>
+  </si>
+  <si>
+    <t>B0D955NZTN</t>
+  </si>
+  <si>
+    <t>B0CCHKHCTD</t>
+  </si>
+  <si>
+    <t>B0CZ91YKMP</t>
+  </si>
+  <si>
+    <t>B0D936CMG1</t>
+  </si>
+  <si>
+    <t>B0CR5RR8Z6</t>
+  </si>
+  <si>
+    <t>B0CHXTV16D</t>
+  </si>
+  <si>
+    <t>B07T655VD8</t>
+  </si>
+  <si>
+    <t>B0CR5NKB4C</t>
+  </si>
+  <si>
+    <t>B0CCHHHGNW</t>
+  </si>
+  <si>
+    <t>B0CRT23BD5</t>
+  </si>
+  <si>
+    <t>B0CBCWGTGR</t>
+  </si>
+  <si>
+    <t>B0DJ2WNH1Y</t>
+  </si>
+  <si>
+    <t>B0DT2ZS8T4</t>
+  </si>
+  <si>
+    <t>B0DSBRQNM8</t>
+  </si>
+  <si>
+    <t>B0DSBQWH32</t>
+  </si>
+  <si>
+    <t>B0DT2ZQV18</t>
+  </si>
+  <si>
+    <t>B0FFJPKHZL</t>
+  </si>
+  <si>
+    <t>B0BQZH3LGP</t>
+  </si>
+  <si>
+    <t>B0FFJG71QJ</t>
+  </si>
+  <si>
+    <t>B0CZ9HTWNC</t>
+  </si>
+  <si>
+    <t>B0FFJQB51R</t>
+  </si>
+  <si>
+    <t>B0CCHLL1ZJ</t>
+  </si>
+  <si>
+    <t>B0CDQHYGLW</t>
+  </si>
+  <si>
+    <t>B0FFHXRJNS</t>
+  </si>
+  <si>
+    <t>B0FFJ2583H</t>
+  </si>
+  <si>
+    <t>B0FFDLZV1H</t>
+  </si>
+  <si>
+    <t>B0FFDJNB8T</t>
+  </si>
+  <si>
+    <t>B07T62VK1C</t>
+  </si>
+  <si>
+    <t>B07SZSVT1F</t>
+  </si>
+  <si>
+    <t>B0FCVFDZP7</t>
+  </si>
+  <si>
+    <t>B0FJZZ6J3R</t>
+  </si>
+  <si>
+    <t>B0D955GP1C</t>
+  </si>
+  <si>
+    <t>B0D9564Z9T</t>
+  </si>
+  <si>
+    <t>B07T63MQ9G</t>
+  </si>
+  <si>
+    <t>B0FJZZ4X7Q</t>
+  </si>
+  <si>
+    <t>B0CBCTFVYL</t>
+  </si>
+  <si>
+    <t>B0CSK4ZCQH</t>
+  </si>
+  <si>
+    <t>B0FK1FC978</t>
+  </si>
+  <si>
+    <t>B0CWRLQ99S</t>
+  </si>
+  <si>
+    <t>B0D955VQ4S</t>
+  </si>
+  <si>
+    <t>B0FTMMBT5P</t>
+  </si>
+  <si>
+    <t>B0CSK63BKG</t>
+  </si>
+  <si>
+    <t>B0FTL6PH2Z</t>
+  </si>
+  <si>
+    <t>B09BBK2LV4</t>
+  </si>
+  <si>
+    <t>B0DSBN62LR</t>
+  </si>
+  <si>
+    <t>B01GZZZ328</t>
+  </si>
+  <si>
+    <t>B0BQZG6C28</t>
+  </si>
+  <si>
+    <t>B0D936P9C1</t>
+  </si>
+  <si>
+    <t>B0CZ93JG5X</t>
+  </si>
+  <si>
+    <t>B00HVBJ6W4</t>
+  </si>
+  <si>
+    <t>B00PW3J8LM</t>
+  </si>
+  <si>
+    <t>B0D955B6SX</t>
+  </si>
+  <si>
+    <t>B0D935S1B3</t>
+  </si>
+  <si>
+    <t>B00FF8CDSO</t>
+  </si>
+  <si>
+    <t>B079DC27J5</t>
+  </si>
+  <si>
+    <t>B0DJ2Y4J4Q</t>
+  </si>
+  <si>
+    <t>B08HGVDKFH</t>
+  </si>
+  <si>
+    <t>B0DJ2XWYX7</t>
+  </si>
+  <si>
+    <t>B0DT2KTXK3</t>
+  </si>
+  <si>
+    <t>B0DJ2Z41C1</t>
+  </si>
+  <si>
+    <t>B0DKJQDKPD</t>
+  </si>
+  <si>
+    <t>B0DSBQN2B9</t>
+  </si>
+  <si>
+    <t>B0DJ2XQB3P</t>
+  </si>
+  <si>
+    <t>B0BS4BFLZW</t>
+  </si>
+  <si>
+    <t>B0DJ2XDV59</t>
+  </si>
+  <si>
+    <t>B0DJ2X1477</t>
+  </si>
+  <si>
+    <t>B07T1X89FZ</t>
+  </si>
+  <si>
+    <t>B0D9345QY7</t>
+  </si>
+  <si>
+    <t>B0D858SPK4</t>
+  </si>
+  <si>
+    <t>B07T1X8TKH</t>
+  </si>
+  <si>
+    <t>B0D935CGMF</t>
+  </si>
+  <si>
+    <t>B077SN2LNP</t>
+  </si>
+  <si>
+    <t>B07QSK7DHR</t>
+  </si>
+  <si>
+    <t>B0D9ZN5NBD</t>
+  </si>
+  <si>
+    <t>B0DSBRPS7R</t>
+  </si>
+  <si>
+    <t>B0DSBPPPJ9</t>
+  </si>
+  <si>
+    <t>B0DSBQ8JV7</t>
+  </si>
+  <si>
+    <t>B0DP5KBJ7H</t>
+  </si>
+  <si>
+    <t>B0DP5J7VF3</t>
+  </si>
+  <si>
+    <t>B0DP5JYG31</t>
+  </si>
+  <si>
+    <t>B0DP5J526J</t>
+  </si>
+  <si>
+    <t>B0DT3F8L97</t>
+  </si>
+  <si>
+    <t>B0DT322B7L</t>
+  </si>
+  <si>
+    <t>B0DT32JDPV</t>
+  </si>
+  <si>
+    <t>B07T3ZPD9X</t>
+  </si>
+  <si>
+    <t>B07T2XYHYD</t>
+  </si>
+  <si>
+    <t>B07T53T1KV</t>
+  </si>
+  <si>
+    <t>B0FFJJM7DS</t>
+  </si>
+  <si>
+    <t>B0FFDJHKR5</t>
+  </si>
+  <si>
+    <t>B0FCVGHVV7</t>
+  </si>
+  <si>
+    <t>B0FKBV4H32</t>
+  </si>
+  <si>
+    <t>B07T2XYGR5</t>
+  </si>
+  <si>
+    <t>B0FTL6QH21</t>
+  </si>
+  <si>
+    <t>B0FTKCRHPQ</t>
+  </si>
+  <si>
+    <t>B0FFJQBHGH</t>
+  </si>
+  <si>
+    <t>B0FRW51FQF</t>
+  </si>
+  <si>
+    <t>B0DJ2XNSD2</t>
+  </si>
+  <si>
+    <t>B012R0UNAW</t>
+  </si>
+  <si>
+    <t>B0D936YHDH</t>
+  </si>
+  <si>
+    <t>B0CRCZYDY6</t>
+  </si>
+  <si>
+    <t>B0DJ2WJ9R7</t>
+  </si>
+  <si>
+    <t>B0CRD7DH79</t>
+  </si>
+  <si>
+    <t>B0CRSQDJJ5</t>
+  </si>
+  <si>
+    <t>B0D935VW9J</t>
+  </si>
+  <si>
+    <t>B0D85171BL</t>
+  </si>
+  <si>
+    <t>B0CZ94B6QL</t>
+  </si>
+  <si>
+    <t>B0BQ35JRM3</t>
+  </si>
+  <si>
+    <t>B0DT381WY9</t>
+  </si>
+  <si>
+    <t>B0DT34RQM2</t>
+  </si>
+  <si>
+    <t>B0FFJ6T8YY</t>
+  </si>
+  <si>
+    <t>B0FFJ939GQ</t>
+  </si>
+  <si>
+    <t>B0FFDSN4S1</t>
+  </si>
+  <si>
+    <t>B0FJ2SSSZR</t>
+  </si>
+  <si>
+    <t>B0FFD8Q4K6</t>
+  </si>
+  <si>
+    <t>B0FCVKH4TS</t>
+  </si>
+  <si>
+    <t>B0FKBW8L5H</t>
+  </si>
+  <si>
+    <t>B0FKBVVZ7P</t>
+  </si>
+  <si>
+    <t>B0FKBWS861</t>
+  </si>
+  <si>
+    <t>B0FKBVB3YH</t>
+  </si>
+  <si>
+    <t>B0FK237HV4</t>
+  </si>
+  <si>
+    <t>B0FKBV3N4Y</t>
+  </si>
+  <si>
+    <t>B0FK1995CB</t>
+  </si>
+  <si>
+    <t>B07T2XY7V5</t>
+  </si>
+  <si>
+    <t>B0FTMKHR8H</t>
+  </si>
+  <si>
+    <t>B0FRVZ29NP</t>
+  </si>
+  <si>
+    <t>B0FS5QZRYB</t>
+  </si>
+  <si>
+    <t>B0FTMMNCK7</t>
+  </si>
+  <si>
+    <t>B0FTML3VHG</t>
+  </si>
+  <si>
+    <t>B0FQ8BFNPN</t>
+  </si>
+  <si>
+    <t>B0FS6JY8XW</t>
+  </si>
+  <si>
+    <t>B0FTL6L4WG</t>
+  </si>
+  <si>
+    <t>B0FQ832739</t>
+  </si>
+  <si>
+    <t>B002LZUAFM</t>
+  </si>
+  <si>
+    <t>B0CYMWQCKL</t>
+  </si>
+  <si>
+    <t>B01MTYS3BW</t>
+  </si>
+  <si>
+    <t>B07T1X96CL</t>
+  </si>
+  <si>
+    <t>B07T62YVHY</t>
+  </si>
+  <si>
+    <t>B07T63ZJTR</t>
+  </si>
+  <si>
+    <t>B07T3ZLNM3</t>
+  </si>
+  <si>
+    <t>B0D9363BB2</t>
+  </si>
+  <si>
+    <t>B0DT36621X</t>
+  </si>
+  <si>
+    <t>B0DSBPGKDR</t>
+  </si>
+  <si>
+    <t>B0DSBPT3J3</t>
+  </si>
+  <si>
+    <t>B0DT2XZNK5</t>
+  </si>
+  <si>
+    <t>B07T62XNWY</t>
+  </si>
+  <si>
+    <t>B07T64HT6R</t>
+  </si>
+  <si>
+    <t>B08BCLYN66</t>
+  </si>
+  <si>
+    <t>B0FTMRC37L</t>
+  </si>
+  <si>
+    <t>B0FTMLYC74</t>
+  </si>
+  <si>
+    <t>B0FRV4KDN4</t>
+  </si>
+  <si>
+    <t>B0FTMNTYMX</t>
+  </si>
+  <si>
+    <t>B0FTKWD4HQ</t>
+  </si>
+  <si>
+    <t>B0FQ7WTM8P</t>
+  </si>
+  <si>
+    <t>B0FTL71V28</t>
+  </si>
+  <si>
+    <t>B0FQ8K147H</t>
+  </si>
+  <si>
+    <t>B0DJ2WKCPD</t>
+  </si>
+  <si>
+    <t>B0BR5DZQSN</t>
+  </si>
+  <si>
+    <t>B0DSBT4S4K</t>
+  </si>
+  <si>
+    <t>B0FTK1RVG8</t>
+  </si>
+  <si>
+    <t>B0D936RRVB</t>
+  </si>
+  <si>
+    <t>B0CRCTQH2C</t>
+  </si>
+  <si>
+    <t>B0CGSQGH17</t>
+  </si>
+  <si>
+    <t>B0FS6M8FSK</t>
+  </si>
+  <si>
+    <t>B0FTMMHDNH</t>
+  </si>
+  <si>
+    <t>B0GDJPJKSG</t>
+  </si>
+  <si>
+    <t>B0GDXN1QGR</t>
+  </si>
+  <si>
+    <t>B0GDJXGF4H</t>
+  </si>
+  <si>
+    <t>B0GDJ5HLRJ</t>
+  </si>
+  <si>
+    <t>B0GDHZ5QH8</t>
+  </si>
+  <si>
+    <t>B0GDWZZD4K</t>
+  </si>
+  <si>
+    <t>B0GF7J5Y4W</t>
+  </si>
+  <si>
+    <t>B0GDXH64ZW</t>
+  </si>
+  <si>
+    <t>B0GDJNRRMD</t>
+  </si>
+  <si>
+    <t>B0GDXBGXH2</t>
+  </si>
+  <si>
+    <t>B07SXDRFK2</t>
+  </si>
+  <si>
+    <t>B07SXFRLZZ</t>
+  </si>
+  <si>
+    <t>B0GDZM3K6W</t>
+  </si>
+  <si>
+    <t>B0GHDHD4B9</t>
+  </si>
+  <si>
+    <t>B0GF715X4M</t>
+  </si>
+  <si>
+    <t>B0GF78NM4J</t>
+  </si>
+  <si>
+    <t>B0GF78441L</t>
+  </si>
+  <si>
+    <t>B0GF7GZ4K7</t>
+  </si>
+  <si>
+    <t>B0GF7BR5NH</t>
+  </si>
+  <si>
+    <t>B0GF74WKKN</t>
+  </si>
+  <si>
+    <t>B0GF71CV69</t>
+  </si>
+  <si>
+    <t>B0GF7KPRXB</t>
+  </si>
+  <si>
+    <t>B0GF6XC1KP</t>
+  </si>
+  <si>
+    <t>B0GF7CZ53H</t>
+  </si>
+  <si>
+    <t>B0GF72W1XQ</t>
+  </si>
+  <si>
+    <t>B0GF7C1MPD</t>
+  </si>
+  <si>
+    <t>B0GF72C48V</t>
+  </si>
+  <si>
+    <t>B07SW9WNP5</t>
+  </si>
+  <si>
+    <t>B0GDJR4K6T</t>
+  </si>
+  <si>
+    <t>B0GDJJBCRP</t>
+  </si>
+  <si>
+    <t>B0GDJNQ5K8</t>
+  </si>
+  <si>
+    <t>B0GFD7N73D</t>
+  </si>
+  <si>
+    <t>B0GDHZ3899</t>
+  </si>
+  <si>
+    <t>B0GDK6QPGC</t>
+  </si>
+  <si>
+    <t>B0GDJ33ZQP</t>
+  </si>
+  <si>
+    <t>B0GDJLX2MP</t>
+  </si>
+  <si>
+    <t>B0GDJ5ZSCZ</t>
+  </si>
+  <si>
+    <t>B0GF7561XM</t>
+  </si>
+  <si>
+    <t>B0GF7JSSRF</t>
+  </si>
+  <si>
+    <t>B0GF72GF8N</t>
+  </si>
+  <si>
+    <t>B0GF7BLQ27</t>
+  </si>
+  <si>
+    <t>B0GF785MMZ</t>
+  </si>
+  <si>
+    <t>B0GF6W4YCD</t>
+  </si>
+  <si>
+    <t>B0GF71BBKV</t>
+  </si>
+  <si>
+    <t>FS4867</t>
+  </si>
+  <si>
+    <t>CH2882</t>
+  </si>
+  <si>
+    <t>BQ3181</t>
+  </si>
+  <si>
+    <t>FS4795</t>
+  </si>
+  <si>
+    <t>JR1401</t>
+  </si>
+  <si>
+    <t>ES2811</t>
+  </si>
+  <si>
+    <t>ES4433</t>
+  </si>
+  <si>
+    <t>FS4735</t>
+  </si>
+  <si>
+    <t>FS4813</t>
+  </si>
+  <si>
+    <t>ES3843</t>
+  </si>
+  <si>
+    <t>FS6106</t>
+  </si>
+  <si>
+    <t>JR1487</t>
+  </si>
+  <si>
+    <t>ES4628</t>
+  </si>
+  <si>
+    <t>ES5388</t>
+  </si>
+  <si>
+    <t>FS5792</t>
+  </si>
+  <si>
+    <t>FS5308</t>
+  </si>
+  <si>
+    <t>ES3020</t>
+  </si>
+  <si>
+    <t>AX4182</t>
+  </si>
+  <si>
+    <t>MK6485</t>
+  </si>
+  <si>
+    <t>AX4184</t>
+  </si>
+  <si>
+    <t>FS4812</t>
+  </si>
+  <si>
+    <t>FS6111</t>
+  </si>
+  <si>
+    <t>MK4842</t>
+  </si>
+  <si>
+    <t>ES5278</t>
+  </si>
+  <si>
+    <t>FS5525</t>
+  </si>
+  <si>
+    <t>FS5963</t>
+  </si>
+  <si>
+    <t>ES4519</t>
+  </si>
+  <si>
+    <t>AX2463</t>
+  </si>
+  <si>
+    <t>MK5491</t>
+  </si>
+  <si>
+    <t>AX5176</t>
+  </si>
+  <si>
+    <t>FS5512</t>
+  </si>
+  <si>
+    <t>ES5364</t>
+  </si>
+  <si>
+    <t>FS6113</t>
+  </si>
+  <si>
+    <t>FS6029</t>
+  </si>
+  <si>
+    <t>AX1769</t>
+  </si>
+  <si>
+    <t>AX4180</t>
+  </si>
+  <si>
+    <t>ES5358</t>
+  </si>
+  <si>
+    <t>ME3098</t>
+  </si>
+  <si>
+    <t>ES5310</t>
+  </si>
+  <si>
+    <t>FS6048</t>
+  </si>
+  <si>
+    <t>AX4183</t>
+  </si>
+  <si>
+    <t>ES5349</t>
+  </si>
+  <si>
+    <t>FS6090</t>
+  </si>
+  <si>
+    <t>ME3254</t>
+  </si>
+  <si>
+    <t>ME3260</t>
+  </si>
+  <si>
+    <t>AX5901</t>
+  </si>
+  <si>
+    <t>ES3284</t>
+  </si>
+  <si>
+    <t>FS6112</t>
+  </si>
+  <si>
+    <t>AR1979</t>
+  </si>
+  <si>
+    <t>ES5329</t>
+  </si>
+  <si>
+    <t>ES5361</t>
+  </si>
+  <si>
+    <t>ES5323</t>
+  </si>
+  <si>
+    <t>ME3253</t>
+  </si>
+  <si>
+    <t>ES5452</t>
+  </si>
+  <si>
+    <t>MK9113</t>
+  </si>
+  <si>
+    <t>FS6086</t>
+  </si>
+  <si>
+    <t>ES5434</t>
+  </si>
+  <si>
+    <t>AX1970</t>
+  </si>
+  <si>
+    <t>FS6140</t>
+  </si>
+  <si>
+    <t>ES5363</t>
+  </si>
+  <si>
+    <t>FS6032</t>
+  </si>
+  <si>
+    <t>ES5303</t>
+  </si>
+  <si>
+    <t>AX4186</t>
+  </si>
+  <si>
+    <t>ES5419</t>
+  </si>
+  <si>
+    <t>MK7506</t>
+  </si>
+  <si>
+    <t>ES5420</t>
+  </si>
+  <si>
+    <t>FS6139</t>
+  </si>
+  <si>
+    <t>ES5319</t>
+  </si>
+  <si>
+    <t>DZ1206</t>
+  </si>
+  <si>
+    <t>FS5901</t>
+  </si>
+  <si>
+    <t>ES5338</t>
+  </si>
+  <si>
+    <t>FS6087</t>
+  </si>
+  <si>
+    <t>MK9177</t>
+  </si>
+  <si>
+    <t>AR11669</t>
+  </si>
+  <si>
+    <t>AX2823</t>
+  </si>
+  <si>
+    <t>FS6128</t>
+  </si>
+  <si>
+    <t>FS6132</t>
+  </si>
+  <si>
+    <t>AX5911</t>
+  </si>
+  <si>
+    <t>AX7175SET</t>
+  </si>
+  <si>
+    <t>AR11500</t>
+  </si>
+  <si>
+    <t>AR11575</t>
+  </si>
+  <si>
+    <t>AR11620</t>
+  </si>
+  <si>
+    <t>AX2461</t>
+  </si>
+  <si>
+    <t>MK9193</t>
+  </si>
+  <si>
+    <t>ME3218</t>
+  </si>
+  <si>
+    <t>AR11666</t>
+  </si>
+  <si>
+    <t>ES5271</t>
+  </si>
+  <si>
+    <t>FS6094</t>
+  </si>
+  <si>
+    <t>FS6081SET</t>
+  </si>
+  <si>
+    <t>ES5421</t>
+  </si>
+  <si>
+    <t>FS6129</t>
+  </si>
+  <si>
+    <t>AX4621</t>
+  </si>
+  <si>
+    <t>FS6144</t>
+  </si>
+  <si>
+    <t>ES5387SET</t>
+  </si>
+  <si>
+    <t>AX7151SET</t>
+  </si>
+  <si>
+    <t>MK3190</t>
+  </si>
+  <si>
+    <t>FS6056</t>
+  </si>
+  <si>
+    <t>AR1676</t>
+  </si>
+  <si>
+    <t>AR11665</t>
+  </si>
+  <si>
+    <t>AR11637</t>
+  </si>
+  <si>
+    <t>MK9179</t>
+  </si>
+  <si>
+    <t>AR11338</t>
+  </si>
+  <si>
+    <t>AR11499</t>
+  </si>
+  <si>
+    <t>ES5306</t>
+  </si>
+  <si>
+    <t>AR11622</t>
+  </si>
+  <si>
+    <t>MK4845</t>
+  </si>
+  <si>
+    <t>AR11639</t>
+  </si>
+  <si>
+    <t>AX1767</t>
+  </si>
+  <si>
+    <t>AX5730</t>
+  </si>
+  <si>
+    <t>AX2460</t>
+  </si>
+  <si>
+    <t>FS6131</t>
+  </si>
+  <si>
+    <t>ME3270</t>
+  </si>
+  <si>
+    <t>AX4181</t>
+  </si>
+  <si>
+    <t>AX2413</t>
+  </si>
+  <si>
+    <t>FS5699</t>
+  </si>
+  <si>
+    <t>FS6104</t>
+  </si>
+  <si>
+    <t>AX7163SET</t>
+  </si>
+  <si>
+    <t>MK9191</t>
+  </si>
+  <si>
+    <t>MK4710</t>
+  </si>
+  <si>
+    <t>AR11582</t>
+  </si>
+  <si>
+    <t>AX2454</t>
+  </si>
+  <si>
+    <t>MK7474</t>
+  </si>
+  <si>
+    <t>AR60076</t>
+  </si>
+  <si>
+    <t>AX5725</t>
+  </si>
+  <si>
+    <t>SKW2694</t>
+  </si>
+  <si>
+    <t>ES5381</t>
+  </si>
+  <si>
+    <t>FS6071</t>
+  </si>
+  <si>
+    <t>AR11677</t>
+  </si>
+  <si>
+    <t>ES5357</t>
+  </si>
+  <si>
+    <t>MK4882</t>
+  </si>
+  <si>
+    <t>ES5331</t>
+  </si>
+  <si>
+    <t>ME3206</t>
+  </si>
+  <si>
+    <t>AR11625</t>
+  </si>
+  <si>
+    <t>AR11484</t>
+  </si>
+  <si>
+    <t>MK9178</t>
+  </si>
+  <si>
+    <t>AR70010</t>
+  </si>
+  <si>
+    <t>ES5350</t>
+  </si>
+  <si>
+    <t>AR11621</t>
+  </si>
+  <si>
+    <t>AR11596</t>
+  </si>
+  <si>
+    <t>AX1956</t>
+  </si>
+  <si>
+    <t>DZ4659</t>
+  </si>
+  <si>
+    <t>AX1962</t>
+  </si>
+  <si>
+    <t>AX1742</t>
+  </si>
+  <si>
+    <t>MK9153</t>
+  </si>
+  <si>
+    <t>DZ2189</t>
+  </si>
+  <si>
+    <t>MK4864</t>
+  </si>
+  <si>
+    <t>AR11671</t>
+  </si>
+  <si>
+    <t>ES5399</t>
+  </si>
+  <si>
+    <t>ES5400</t>
+  </si>
+  <si>
+    <t>AR11661</t>
+  </si>
+  <si>
+    <t>AR11690</t>
+  </si>
+  <si>
+    <t>AX1739</t>
+  </si>
+  <si>
+    <t>AR11691</t>
+  </si>
+  <si>
+    <t>MK4824</t>
+  </si>
+  <si>
+    <t>AR11693</t>
+  </si>
+  <si>
+    <t>AR11568</t>
+  </si>
+  <si>
+    <t>AR11558</t>
+  </si>
+  <si>
+    <t>AR11694</t>
+  </si>
+  <si>
+    <t>AR11706</t>
+  </si>
+  <si>
+    <t>AX2822</t>
+  </si>
+  <si>
+    <t>AX5732</t>
+  </si>
+  <si>
+    <t>DZ2212</t>
+  </si>
+  <si>
+    <t>DZ2213</t>
+  </si>
+  <si>
+    <t>FS6133</t>
+  </si>
+  <si>
+    <t>MK9220</t>
+  </si>
+  <si>
+    <t>MK4847</t>
+  </si>
+  <si>
+    <t>MK9176</t>
+  </si>
+  <si>
+    <t>DZ2210SET</t>
+  </si>
+  <si>
+    <t>MK9221</t>
+  </si>
+  <si>
+    <t>DZ4640</t>
+  </si>
+  <si>
+    <t>MK9163</t>
+  </si>
+  <si>
+    <t>MK4923</t>
+  </si>
+  <si>
+    <t>AX1764</t>
+  </si>
+  <si>
+    <t>MK7488</t>
+  </si>
+  <si>
+    <t>AR80083SET</t>
+  </si>
+  <si>
+    <t>MK9156</t>
+  </si>
+  <si>
+    <t>FS6145SET</t>
+  </si>
+  <si>
+    <t>AR11360</t>
+  </si>
+  <si>
+    <t>AX7165SET</t>
+  </si>
+  <si>
+    <t>AR2502</t>
+  </si>
+  <si>
+    <t>AR80065SET</t>
+  </si>
+  <si>
+    <t>ME3261</t>
+  </si>
+  <si>
+    <t>MK4829</t>
+  </si>
+  <si>
+    <t>ES3466</t>
+  </si>
+  <si>
+    <t>ME3061</t>
+  </si>
+  <si>
+    <t>MK4843</t>
+  </si>
+  <si>
+    <t>AR11636</t>
+  </si>
+  <si>
+    <t>ES3405</t>
+  </si>
+  <si>
+    <t>FS5452</t>
+  </si>
+  <si>
+    <t>ME3265</t>
+  </si>
+  <si>
+    <t>FS5708SET</t>
+  </si>
+  <si>
+    <t>MK9192</t>
+  </si>
+  <si>
+    <t>AR11676</t>
+  </si>
+  <si>
+    <t>AR11640</t>
+  </si>
+  <si>
+    <t>AX1964</t>
+  </si>
+  <si>
+    <t>FS6107</t>
+  </si>
+  <si>
+    <t>FS6089</t>
+  </si>
+  <si>
+    <t>MK4709</t>
+  </si>
+  <si>
+    <t>MK4873</t>
+  </si>
+  <si>
+    <t>ES5380</t>
+  </si>
+  <si>
+    <t>DZ2215</t>
+  </si>
+  <si>
+    <t>AR60080</t>
+  </si>
+  <si>
+    <t>AX7161SET</t>
+  </si>
+  <si>
+    <t>DZ2214</t>
+  </si>
+  <si>
+    <t>AR11635</t>
+  </si>
+  <si>
+    <t>MK8603</t>
+  </si>
+  <si>
+    <t>MK4339</t>
+  </si>
+  <si>
+    <t>FS6085</t>
+  </si>
+  <si>
+    <t>AX7167SET</t>
+  </si>
+  <si>
+    <t>ES5398</t>
+  </si>
+  <si>
+    <t>MK7519LE</t>
+  </si>
+  <si>
+    <t>MK9195</t>
+  </si>
+  <si>
+    <t>MK9196</t>
+  </si>
+  <si>
+    <t>MK9198</t>
+  </si>
+  <si>
+    <t>MK9201</t>
+  </si>
+  <si>
+    <t>AR11660</t>
+  </si>
+  <si>
+    <t>AR11662</t>
+  </si>
+  <si>
+    <t>AR11663</t>
+  </si>
+  <si>
+    <t>DZ5612</t>
+  </si>
+  <si>
+    <t>DZ5613</t>
+  </si>
+  <si>
+    <t>DZ7487</t>
+  </si>
+  <si>
+    <t>AR11707</t>
+  </si>
+  <si>
+    <t>AX2820</t>
+  </si>
+  <si>
+    <t>ES5422</t>
+  </si>
+  <si>
+    <t>MK9223</t>
+  </si>
+  <si>
+    <t>DZ4670</t>
+  </si>
+  <si>
+    <t>AR11713</t>
+  </si>
+  <si>
+    <t>AR11714</t>
+  </si>
+  <si>
+    <t>AR11689</t>
+  </si>
+  <si>
+    <t>AX4173</t>
+  </si>
+  <si>
+    <t>ME3266</t>
+  </si>
+  <si>
+    <t>AR1926</t>
+  </si>
+  <si>
+    <t>AR11624</t>
+  </si>
+  <si>
+    <t>MK4817SET</t>
+  </si>
+  <si>
+    <t>MK4863</t>
+  </si>
+  <si>
+    <t>FS6045</t>
+  </si>
+  <si>
+    <t>MK9152</t>
+  </si>
+  <si>
+    <t>AR11626</t>
+  </si>
+  <si>
+    <t>AX5724</t>
+  </si>
+  <si>
+    <t>MK4822</t>
+  </si>
+  <si>
+    <t>FS5971</t>
+  </si>
+  <si>
+    <t>AR11674</t>
+  </si>
+  <si>
+    <t>MK7528</t>
+  </si>
+  <si>
+    <t>AR11688</t>
+  </si>
+  <si>
+    <t>AR11708</t>
+  </si>
+  <si>
+    <t>AX2821</t>
+  </si>
+  <si>
+    <t>ES5418</t>
+  </si>
+  <si>
+    <t>AX5735</t>
+  </si>
+  <si>
+    <t>ES5417</t>
+  </si>
+  <si>
+    <t>MK4931</t>
+  </si>
+  <si>
+    <t>MK4933</t>
+  </si>
+  <si>
+    <t>MK4934</t>
+  </si>
+  <si>
+    <t>MK4935</t>
+  </si>
+  <si>
+    <t>MK9222</t>
+  </si>
+  <si>
+    <t>MK4932</t>
+  </si>
+  <si>
+    <t>MK7559</t>
+  </si>
+  <si>
+    <t>DZ4671</t>
+  </si>
+  <si>
+    <t>AR11718</t>
+  </si>
+  <si>
+    <t>AX7176SET</t>
+  </si>
+  <si>
+    <t>ES5443</t>
+  </si>
+  <si>
+    <t>ES5444</t>
+  </si>
+  <si>
+    <t>ES5451</t>
+  </si>
+  <si>
+    <t>MK4963</t>
+  </si>
+  <si>
+    <t>MK4964</t>
+  </si>
+  <si>
+    <t>MK9240</t>
+  </si>
+  <si>
+    <t>MK9245SET</t>
+  </si>
+  <si>
+    <t>AR2434</t>
+  </si>
+  <si>
+    <t>AR11610</t>
+  </si>
+  <si>
+    <t>DZ7395</t>
+  </si>
+  <si>
+    <t>DZ4667</t>
+  </si>
+  <si>
+    <t>DZ5618</t>
+  </si>
+  <si>
+    <t>DZ4662</t>
+  </si>
+  <si>
+    <t>DZ4665</t>
+  </si>
+  <si>
+    <t>AR11623</t>
+  </si>
+  <si>
+    <t>AR11672</t>
+  </si>
+  <si>
+    <t>AX5916</t>
+  </si>
+  <si>
+    <t>FS6108</t>
+  </si>
+  <si>
+    <t>AR11664</t>
+  </si>
+  <si>
+    <t>DZ5609</t>
+  </si>
+  <si>
+    <t>DZ5611</t>
+  </si>
+  <si>
+    <t>AX5734</t>
+  </si>
+  <si>
+    <t>ES5438</t>
+  </si>
+  <si>
+    <t>ES5439</t>
+  </si>
+  <si>
+    <t>AX4199</t>
+  </si>
+  <si>
+    <t>FS6149</t>
+  </si>
+  <si>
+    <t>FS6151</t>
+  </si>
+  <si>
+    <t>MK4962</t>
+  </si>
+  <si>
+    <t>MK4965</t>
+  </si>
+  <si>
+    <t>MK9242</t>
+  </si>
+  <si>
+    <t>ES5386</t>
+  </si>
+  <si>
+    <t>DZ4627</t>
+  </si>
+  <si>
+    <t>FS6110</t>
+  </si>
+  <si>
+    <t>FS6150</t>
+  </si>
+  <si>
+    <t>AR60079</t>
+  </si>
+  <si>
+    <t>MK4805</t>
+  </si>
+  <si>
+    <t>SKW3121</t>
+  </si>
+  <si>
+    <t>MK4966</t>
+  </si>
+  <si>
+    <t>MKO1224</t>
+  </si>
+  <si>
+    <t>AX1971</t>
+  </si>
+  <si>
+    <t>AX1972</t>
+  </si>
+  <si>
+    <t>AX1973</t>
+  </si>
+  <si>
+    <t>AX2766</t>
+  </si>
+  <si>
+    <t>AX2767</t>
+  </si>
+  <si>
+    <t>AX4405</t>
+  </si>
+  <si>
+    <t>AX4406</t>
+  </si>
+  <si>
+    <t>AX4407</t>
+  </si>
+  <si>
+    <t>AX4408</t>
+  </si>
+  <si>
+    <t>AX4625</t>
+  </si>
+  <si>
+    <t>DZ4702</t>
+  </si>
+  <si>
+    <t>DZ4709</t>
+  </si>
+  <si>
+    <t>AR11773</t>
+  </si>
+  <si>
+    <t>AR80087SET</t>
+  </si>
+  <si>
+    <t>ES5456</t>
+  </si>
+  <si>
+    <t>ES5472</t>
+  </si>
+  <si>
+    <t>FS6154</t>
+  </si>
+  <si>
+    <t>FS6161</t>
+  </si>
+  <si>
+    <t>FS6163</t>
+  </si>
+  <si>
+    <t>MK4997</t>
+  </si>
+  <si>
+    <t>MK4998</t>
+  </si>
+  <si>
+    <t>MK4999</t>
+  </si>
+  <si>
+    <t>MK7568</t>
+  </si>
+  <si>
+    <t>MK7581</t>
+  </si>
+  <si>
+    <t>MK7583</t>
+  </si>
+  <si>
+    <t>MK7589</t>
+  </si>
+  <si>
+    <t>MK7590</t>
+  </si>
+  <si>
+    <t>DZ4703</t>
+  </si>
+  <si>
+    <t>AR11754</t>
+  </si>
+  <si>
+    <t>AR11756</t>
+  </si>
+  <si>
+    <t>AR11757</t>
+  </si>
+  <si>
+    <t>AR11759</t>
+  </si>
+  <si>
+    <t>AR11770</t>
+  </si>
+  <si>
+    <t>AR11771</t>
+  </si>
+  <si>
+    <t>AR11772</t>
+  </si>
+  <si>
+    <t>AR11774</t>
+  </si>
+  <si>
+    <t>AR11783</t>
+  </si>
+  <si>
+    <t>FS6162</t>
+  </si>
+  <si>
+    <t>FS6164</t>
+  </si>
+  <si>
+    <t>MK7572</t>
+  </si>
+  <si>
+    <t>MK7573</t>
+  </si>
+  <si>
+    <t>MK7574</t>
+  </si>
+  <si>
+    <t>MK7584</t>
+  </si>
+  <si>
+    <t>MK7587</t>
+  </si>
+  <si>
+    <t>Fossil</t>
+  </si>
+  <si>
+    <t>Traditional Watch</t>
+  </si>
+  <si>
+    <t>FBA73952</t>
+  </si>
+  <si>
+    <t>CH2885</t>
+  </si>
+  <si>
+    <t>FBA75262</t>
+  </si>
+  <si>
+    <t>FS5164</t>
+  </si>
+  <si>
+    <t>FBA74358</t>
+  </si>
+  <si>
+    <t>FS5237</t>
+  </si>
+  <si>
+    <t>FBA75372</t>
+  </si>
+  <si>
+    <t>AX1343</t>
+  </si>
+  <si>
+    <t>FBA74415</t>
+  </si>
+  <si>
+    <t>FS5822</t>
+  </si>
+  <si>
+    <t>FBA75153</t>
+  </si>
+  <si>
+    <t>FS5855</t>
+  </si>
+  <si>
+    <t>FBA79745</t>
+  </si>
+  <si>
+    <t>ES5402</t>
+  </si>
+  <si>
+    <t>FBA69567</t>
+  </si>
+  <si>
+    <t>AX2101</t>
+  </si>
+  <si>
+    <t>FBA72073</t>
+  </si>
+  <si>
+    <t>MK2833</t>
+  </si>
+  <si>
+    <t>B00EVZ83J0</t>
+  </si>
+  <si>
+    <t>B0183NW5H6</t>
+  </si>
+  <si>
+    <t>B01KNMEVDG</t>
+  </si>
+  <si>
+    <t>B0846PJPW9</t>
+  </si>
+  <si>
+    <t>B08QTW81S9</t>
+  </si>
+  <si>
+    <t>B0975TDMW6</t>
+  </si>
+  <si>
+    <t>B0DSBSVS4X</t>
+  </si>
+  <si>
+    <t>B00786VY22</t>
+  </si>
+  <si>
+    <t>B07QW9DDGB</t>
   </si>
 </sst>
 </file>
@@ -5087,7 +8252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5133,6 +8298,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5639,7 +8807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:I480"/>
+  <dimension ref="A1:I831"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -18224,6 +21392,5973 @@
       <c r="H480" s="3"/>
       <c r="I480" s="14">
         <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A481" s="16" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C481" s="16" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E481" s="1" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F481" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A482" s="16" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C482" s="16" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F482" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A483" s="16" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C483" s="16" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D483" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E483" s="1" t="s">
+        <v>2330</v>
+      </c>
+      <c r="F483" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A484" s="16" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C484" s="16" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E484" s="1" t="s">
+        <v>2331</v>
+      </c>
+      <c r="F484" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A485" s="16" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C485" s="16" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>2332</v>
+      </c>
+      <c r="F485" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A486" s="16" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C486" s="16" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D486" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="F486" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A487" s="16" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C487" s="16" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D487" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>2334</v>
+      </c>
+      <c r="F487" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A488" s="16" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C488" s="16" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F488" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A489" s="16" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C489" s="16" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D489" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E489" s="1" t="s">
+        <v>2336</v>
+      </c>
+      <c r="F489" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A490" s="16" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C490" s="16" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D490" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>2337</v>
+      </c>
+      <c r="F490" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A491" s="16" t="s">
+        <v>1654</v>
+      </c>
+      <c r="C491" s="16" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D491" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E491" s="1" t="s">
+        <v>2338</v>
+      </c>
+      <c r="F491" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A492" s="16" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C492" s="16" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E492" s="1" t="s">
+        <v>2339</v>
+      </c>
+      <c r="F492" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A493" s="16" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C493" s="16" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D493" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E493" s="1" t="s">
+        <v>2340</v>
+      </c>
+      <c r="F493" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A494" s="16" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C494" s="16" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E494" s="1" t="s">
+        <v>2341</v>
+      </c>
+      <c r="F494" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A495" s="16" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C495" s="16" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D495" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E495" s="1" t="s">
+        <v>2342</v>
+      </c>
+      <c r="F495" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A496" s="16" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C496" s="16" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D496" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="F496" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A497" s="16" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C497" s="16" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D497" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E497" s="1" t="s">
+        <v>2344</v>
+      </c>
+      <c r="F497" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A498" s="16" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C498" s="16" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E498" s="1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="F498" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A499" s="16" t="s">
+        <v>1662</v>
+      </c>
+      <c r="C499" s="16" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>2346</v>
+      </c>
+      <c r="F499" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A500" s="16" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C500" s="16" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E500" s="1" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F500" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A501" s="16" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C501" s="16" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D501" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E501" s="1" t="s">
+        <v>2348</v>
+      </c>
+      <c r="F501" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A502" s="16" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C502" s="16" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E502" s="1" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F502" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A503" s="16" t="s">
+        <v>1666</v>
+      </c>
+      <c r="C503" s="16" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D503" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E503" s="1" t="s">
+        <v>2350</v>
+      </c>
+      <c r="F503" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A504" s="16" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C504" s="16" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E504" s="1" t="s">
+        <v>2351</v>
+      </c>
+      <c r="F504" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A505" s="16" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C505" s="16" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E505" s="1" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F505" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A506" s="16" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C506" s="16" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E506" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F506" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A507" s="16" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C507" s="16" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D507" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E507" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F507" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A508" s="16" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C508" s="16" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E508" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F508" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A509" s="16" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C509" s="16" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D509" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E509" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="F509" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A510" s="16" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C510" s="16" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D510" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E510" s="1" t="s">
+        <v>2357</v>
+      </c>
+      <c r="F510" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A511" s="16" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C511" s="16" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E511" s="1" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F511" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A512" s="16" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C512" s="16" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D512" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E512" s="1" t="s">
+        <v>2359</v>
+      </c>
+      <c r="F512" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A513" s="16" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C513" s="16" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D513" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E513" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="F513" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A514" s="16" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C514" s="16" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E514" s="1" t="s">
+        <v>2361</v>
+      </c>
+      <c r="F514" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A515" s="16" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C515" s="16" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E515" s="1" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F515" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A516" s="16" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C516" s="16" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E516" s="1" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F516" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A517" s="16" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C517" s="16" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>2364</v>
+      </c>
+      <c r="F517" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A518" s="16" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C518" s="16" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E518" s="1" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F518" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A519" s="16" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C519" s="16" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E519" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="F519" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A520" s="16" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C520" s="16" t="s">
+        <v>2025</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E520" s="1" t="s">
+        <v>2367</v>
+      </c>
+      <c r="F520" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A521" s="16" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C521" s="16" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D521" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E521" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="F521" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A522" s="16" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C522" s="16" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E522" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="F522" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A523" s="16" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C523" s="16" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E523" s="1" t="s">
+        <v>2370</v>
+      </c>
+      <c r="F523" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A524" s="16" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C524" s="16" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E524" s="1" t="s">
+        <v>2371</v>
+      </c>
+      <c r="F524" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A525" s="16" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C525" s="16" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E525" s="1" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F525" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A526" s="16" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C526" s="16" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E526" s="1" t="s">
+        <v>2373</v>
+      </c>
+      <c r="F526" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="16" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C527" s="16" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E527" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="F527" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A528" s="16" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C528" s="16" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E528" s="1" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F528" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A529" s="16" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C529" s="16" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E529" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F529" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="16" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C530" s="16" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D530" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E530" s="1" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F530" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A531" s="16" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C531" s="16" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D531" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E531" s="1" t="s">
+        <v>2378</v>
+      </c>
+      <c r="F531" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="16" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C532" s="16" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E532" s="1" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F532" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A533" s="16" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C533" s="16" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D533" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E533" s="1" t="s">
+        <v>2380</v>
+      </c>
+      <c r="F533" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A534" s="16" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C534" s="16" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D534" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E534" s="1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F534" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A535" s="16" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C535" s="16" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E535" s="1" t="s">
+        <v>2382</v>
+      </c>
+      <c r="F535" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A536" s="16" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C536" s="16" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D536" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E536" s="1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="F536" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A537" s="16" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C537" s="16" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D537" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E537" s="1" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F537" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A538" s="16" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C538" s="16" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D538" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E538" s="1" t="s">
+        <v>2385</v>
+      </c>
+      <c r="F538" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A539" s="16" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C539" s="16" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D539" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E539" s="1" t="s">
+        <v>2386</v>
+      </c>
+      <c r="F539" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A540" s="16" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C540" s="16" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E540" s="1" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F540" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A541" s="16" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C541" s="16" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E541" s="1" t="s">
+        <v>2388</v>
+      </c>
+      <c r="F541" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A542" s="16" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C542" s="16" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D542" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E542" s="1" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F542" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A543" s="16" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C543" s="16" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E543" s="1" t="s">
+        <v>2390</v>
+      </c>
+      <c r="F543" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A544" s="16" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C544" s="16" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E544" s="1" t="s">
+        <v>2391</v>
+      </c>
+      <c r="F544" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A545" s="16" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C545" s="16" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E545" s="1" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F545" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A546" s="16" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C546" s="16" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D546" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E546" s="1" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F546" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A547" s="16" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C547" s="16" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E547" s="1" t="s">
+        <v>2394</v>
+      </c>
+      <c r="F547" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A548" s="16" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C548" s="16" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E548" s="1" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F548" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A549" s="16" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C549" s="16" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E549" s="1" t="s">
+        <v>2396</v>
+      </c>
+      <c r="F549" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A550" s="16" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C550" s="16" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D550" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E550" s="1" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F550" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A551" s="16" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C551" s="16" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D551" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E551" s="1" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F551" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A552" s="16" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C552" s="16" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D552" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E552" s="1" t="s">
+        <v>2399</v>
+      </c>
+      <c r="F552" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A553" s="16" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C553" s="16" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D553" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E553" s="1" t="s">
+        <v>2400</v>
+      </c>
+      <c r="F553" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A554" s="16" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C554" s="16" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D554" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E554" s="1" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F554" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A555" s="16" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C555" s="16" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D555" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E555" s="1" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F555" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A556" s="16" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C556" s="16" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D556" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E556" s="1" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F556" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A557" s="16" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C557" s="16" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D557" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E557" s="1" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F557" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A558" s="16" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C558" s="16" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D558" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E558" s="1" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F558" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A559" s="16" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C559" s="16" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D559" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E559" s="1" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F559" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A560" s="16" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C560" s="16" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D560" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E560" s="1" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F560" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A561" s="16" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C561" s="16" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E561" s="1" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F561" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A562" s="16" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C562" s="16" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D562" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E562" s="1" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F562" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A563" s="16" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C563" s="16" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D563" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E563" s="1" t="s">
+        <v>2410</v>
+      </c>
+      <c r="F563" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A564" s="16" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C564" s="16" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D564" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E564" s="1" t="s">
+        <v>2411</v>
+      </c>
+      <c r="F564" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A565" s="16" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C565" s="16" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D565" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E565" s="1" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F565" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A566" s="16" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C566" s="16" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D566" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E566" s="1" t="s">
+        <v>2413</v>
+      </c>
+      <c r="F566" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A567" s="16" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C567" s="16" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D567" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E567" s="1" t="s">
+        <v>2414</v>
+      </c>
+      <c r="F567" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A568" s="16" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C568" s="16" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D568" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E568" s="1" t="s">
+        <v>2415</v>
+      </c>
+      <c r="F568" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A569" s="16" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C569" s="16" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D569" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E569" s="1" t="s">
+        <v>2416</v>
+      </c>
+      <c r="F569" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A570" s="16" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C570" s="16" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D570" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E570" s="1" t="s">
+        <v>2417</v>
+      </c>
+      <c r="F570" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A571" s="16" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C571" s="16" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D571" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E571" s="1" t="s">
+        <v>2418</v>
+      </c>
+      <c r="F571" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A572" s="16" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C572" s="16" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D572" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E572" s="1" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F572" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A573" s="16" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C573" s="16" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D573" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E573" s="1" t="s">
+        <v>2420</v>
+      </c>
+      <c r="F573" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A574" s="16" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C574" s="16" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D574" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E574" s="1" t="s">
+        <v>2421</v>
+      </c>
+      <c r="F574" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A575" s="16" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C575" s="16" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D575" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E575" s="1" t="s">
+        <v>2422</v>
+      </c>
+      <c r="F575" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A576" s="16" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C576" s="16" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D576" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E576" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="F576" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A577" s="16" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C577" s="16" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D577" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E577" s="1" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F577" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A578" s="16" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C578" s="16" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D578" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E578" s="1" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F578" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A579" s="16" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C579" s="16" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D579" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E579" s="1" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F579" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A580" s="16" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C580" s="16" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D580" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E580" s="1" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F580" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A581" s="16" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C581" s="16" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D581" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E581" s="1" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F581" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A582" s="16" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C582" s="16" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D582" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E582" s="1" t="s">
+        <v>2429</v>
+      </c>
+      <c r="F582" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A583" s="16" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C583" s="16" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D583" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E583" s="1" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F583" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A584" s="16" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C584" s="16" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D584" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E584" s="1" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F584" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A585" s="16" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C585" s="16" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D585" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E585" s="1" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F585" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A586" s="16" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C586" s="16" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D586" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E586" s="1" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F586" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A587" s="16" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C587" s="16" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D587" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E587" s="1" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F587" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A588" s="16" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C588" s="16" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F588" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A589" s="16" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C589" s="16" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D589" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E589" s="1" t="s">
+        <v>2436</v>
+      </c>
+      <c r="F589" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A590" s="16" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C590" s="16" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D590" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E590" s="1" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F590" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A591" s="16" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C591" s="16" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D591" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E591" s="1" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F591" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A592" s="16" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C592" s="16" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D592" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E592" s="1" t="s">
+        <v>2439</v>
+      </c>
+      <c r="F592" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A593" s="16" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C593" s="16" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D593" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E593" s="1" t="s">
+        <v>2440</v>
+      </c>
+      <c r="F593" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A594" s="16" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C594" s="16" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D594" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E594" s="1" t="s">
+        <v>2441</v>
+      </c>
+      <c r="F594" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A595" s="16" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C595" s="16" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D595" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E595" s="1" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F595" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A596" s="16" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C596" s="16" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D596" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E596" s="1" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F596" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A597" s="16" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C597" s="16" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D597" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E597" s="1" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F597" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A598" s="16" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C598" s="16" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D598" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E598" s="1" t="s">
+        <v>2445</v>
+      </c>
+      <c r="F598" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A599" s="16" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C599" s="16" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D599" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E599" s="1" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F599" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A600" s="16" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C600" s="16" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D600" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E600" s="1" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F600" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A601" s="16" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C601" s="16" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D601" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E601" s="1" t="s">
+        <v>2448</v>
+      </c>
+      <c r="F601" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A602" s="16" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C602" s="16" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D602" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E602" s="1" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F602" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A603" s="16" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C603" s="16" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D603" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E603" s="1" t="s">
+        <v>2450</v>
+      </c>
+      <c r="F603" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A604" s="16" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C604" s="16" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D604" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E604" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F604" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A605" s="16" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C605" s="16" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E605" s="1" t="s">
+        <v>2452</v>
+      </c>
+      <c r="F605" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A606" s="16" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C606" s="16" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D606" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E606" s="1" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F606" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A607" s="16" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C607" s="16" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D607" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E607" s="1" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F607" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A608" s="16" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C608" s="16" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E608" s="1" t="s">
+        <v>2455</v>
+      </c>
+      <c r="F608" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A609" s="16" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C609" s="16" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D609" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E609" s="1" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F609" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A610" s="16" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C610" s="16" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D610" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E610" s="1" t="s">
+        <v>2457</v>
+      </c>
+      <c r="F610" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A611" s="16" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C611" s="16" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D611" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>2458</v>
+      </c>
+      <c r="F611" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A612" s="16" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C612" s="16" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D612" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E612" s="1" t="s">
+        <v>2459</v>
+      </c>
+      <c r="F612" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A613" s="16" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C613" s="16" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D613" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E613" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F613" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A614" s="16" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C614" s="16" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D614" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E614" s="1" t="s">
+        <v>2461</v>
+      </c>
+      <c r="F614" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A615" s="16" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C615" s="16" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D615" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F615" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A616" s="16" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C616" s="16" t="s">
+        <v>2121</v>
+      </c>
+      <c r="D616" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F616" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A617" s="16" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C617" s="16" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D617" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E617" s="1" t="s">
+        <v>2464</v>
+      </c>
+      <c r="F617" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A618" s="16" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C618" s="16" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D618" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E618" s="1" t="s">
+        <v>2465</v>
+      </c>
+      <c r="F618" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A619" s="16" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C619" s="16" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D619" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E619" s="1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="F619" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A620" s="16" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C620" s="16" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D620" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>2467</v>
+      </c>
+      <c r="F620" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A621" s="16" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C621" s="16" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D621" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E621" s="1" t="s">
+        <v>2468</v>
+      </c>
+      <c r="F621" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A622" s="16" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C622" s="16" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D622" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E622" s="1" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F622" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A623" s="16" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C623" s="16" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D623" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>2470</v>
+      </c>
+      <c r="F623" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A624" s="16" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C624" s="16" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D624" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F624" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A625" s="16" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C625" s="16" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D625" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F625" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A626" s="16" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C626" s="16" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D626" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F626" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A627" s="16" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C627" s="16" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D627" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>2474</v>
+      </c>
+      <c r="F627" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A628" s="16" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C628" s="16" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D628" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>2475</v>
+      </c>
+      <c r="F628" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A629" s="16" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C629" s="16" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D629" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F629" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A630" s="16" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C630" s="16" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D630" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F630" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A631" s="16" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C631" s="16" t="s">
+        <v>2136</v>
+      </c>
+      <c r="D631" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F631" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A632" s="16" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C632" s="16" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D632" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>2479</v>
+      </c>
+      <c r="F632" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A633" s="16" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C633" s="16" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>2480</v>
+      </c>
+      <c r="F633" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A634" s="16" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C634" s="16" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F634" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A635" s="16" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C635" s="16" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D635" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F635" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A636" s="16" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C636" s="16" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D636" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F636" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A637" s="16" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C637" s="16" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D637" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F637" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A638" s="16" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C638" s="16" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D638" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>2485</v>
+      </c>
+      <c r="F638" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A639" s="16" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C639" s="16" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D639" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>2486</v>
+      </c>
+      <c r="F639" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A640" s="16" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C640" s="16" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D640" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F640" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A641" s="16" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C641" s="16" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D641" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F641" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A642" s="16" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C642" s="16" t="s">
+        <v>2147</v>
+      </c>
+      <c r="D642" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F642" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A643" s="16" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C643" s="16" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D643" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>2490</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A644" s="16" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C644" s="16" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D644" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F644" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A645" s="16" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C645" s="16" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D645" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F645" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A646" s="16" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C646" s="16" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D646" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>2493</v>
+      </c>
+      <c r="F646" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A647" s="16" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C647" s="16" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D647" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F647" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A648" s="16" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C648" s="16" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D648" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F648" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A649" s="16" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C649" s="16" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D649" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F649" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A650" s="16" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C650" s="16" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D650" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E650" s="1" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F650" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A651" s="16" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C651" s="16" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D651" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E651" s="1" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F651" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A652" s="16" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C652" s="16" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D652" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E652" s="1" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F652" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A653" s="16" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C653" s="16" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D653" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E653" s="1" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F653" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A654" s="16" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C654" s="16" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D654" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E654" s="1" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F654" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A655" s="16" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C655" s="16" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D655" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E655" s="1" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F655" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A656" s="16" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C656" s="16" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D656" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E656" s="1" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F656" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A657" s="16" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C657" s="16" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D657" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E657" s="1" t="s">
+        <v>2504</v>
+      </c>
+      <c r="F657" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A658" s="16" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C658" s="16" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D658" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E658" s="1" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F658" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A659" s="16" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C659" s="16" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D659" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E659" s="1" t="s">
+        <v>2506</v>
+      </c>
+      <c r="F659" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A660" s="16" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C660" s="16" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D660" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E660" s="1" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F660" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A661" s="16" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C661" s="16" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D661" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E661" s="1" t="s">
+        <v>2508</v>
+      </c>
+      <c r="F661" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A662" s="16" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C662" s="16" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D662" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E662" s="1" t="s">
+        <v>2509</v>
+      </c>
+      <c r="F662" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A663" s="16" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C663" s="16" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D663" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E663" s="1" t="s">
+        <v>2510</v>
+      </c>
+      <c r="F663" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A664" s="16" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C664" s="16" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D664" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E664" s="1" t="s">
+        <v>2511</v>
+      </c>
+      <c r="F664" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="665" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A665" s="16" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C665" s="16" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D665" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E665" s="1" t="s">
+        <v>2512</v>
+      </c>
+      <c r="F665" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A666" s="16" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C666" s="16" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D666" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E666" s="1" t="s">
+        <v>2513</v>
+      </c>
+      <c r="F666" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A667" s="16" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C667" s="16" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D667" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E667" s="1" t="s">
+        <v>2514</v>
+      </c>
+      <c r="F667" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A668" s="16" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C668" s="16" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D668" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E668" s="1" t="s">
+        <v>2515</v>
+      </c>
+      <c r="F668" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A669" s="16" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C669" s="16" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>2516</v>
+      </c>
+      <c r="F669" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A670" s="16" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C670" s="16" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D670" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E670" s="1" t="s">
+        <v>2517</v>
+      </c>
+      <c r="F670" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="671" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A671" s="16" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C671" s="16" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D671" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>2518</v>
+      </c>
+      <c r="F671" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A672" s="16" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C672" s="16" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D672" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F672" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A673" s="16" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C673" s="16" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D673" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>2520</v>
+      </c>
+      <c r="F673" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A674" s="16" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C674" s="16" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D674" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>2521</v>
+      </c>
+      <c r="F674" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A675" s="16" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C675" s="16" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D675" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F675" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A676" s="16" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C676" s="16" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D676" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>2523</v>
+      </c>
+      <c r="F676" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A677" s="16" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C677" s="16" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D677" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>2524</v>
+      </c>
+      <c r="F677" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A678" s="16" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C678" s="16" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D678" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>2525</v>
+      </c>
+      <c r="F678" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A679" s="16" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C679" s="16" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D679" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>2526</v>
+      </c>
+      <c r="F679" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A680" s="16" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C680" s="16" t="s">
+        <v>2185</v>
+      </c>
+      <c r="D680" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>2527</v>
+      </c>
+      <c r="F680" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A681" s="16" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C681" s="16" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D681" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F681" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A682" s="16" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C682" s="16" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D682" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E682" s="1" t="s">
+        <v>2529</v>
+      </c>
+      <c r="F682" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A683" s="16" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C683" s="16" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D683" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E683" s="1" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F683" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A684" s="16" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C684" s="16" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D684" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E684" s="1" t="s">
+        <v>2531</v>
+      </c>
+      <c r="F684" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A685" s="16" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C685" s="16" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D685" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E685" s="1" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F685" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A686" s="16" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C686" s="16" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D686" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E686" s="1" t="s">
+        <v>2533</v>
+      </c>
+      <c r="F686" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A687" s="16" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C687" s="16" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D687" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E687" s="1" t="s">
+        <v>2534</v>
+      </c>
+      <c r="F687" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A688" s="16" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C688" s="16" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D688" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E688" s="1" t="s">
+        <v>2535</v>
+      </c>
+      <c r="F688" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A689" s="16" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C689" s="16" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D689" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F689" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A690" s="16" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C690" s="16" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D690" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>2537</v>
+      </c>
+      <c r="F690" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A691" s="16" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C691" s="16" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D691" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F691" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A692" s="16" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C692" s="16" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F692" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A693" s="16" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C693" s="16" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D693" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>2540</v>
+      </c>
+      <c r="F693" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A694" s="16" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C694" s="16" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D694" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F694" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A695" s="16" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C695" s="16" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>2542</v>
+      </c>
+      <c r="F695" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A696" s="16" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C696" s="16" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F696" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A697" s="16" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C697" s="16" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F697" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A698" s="16" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C698" s="16" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D698" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>2545</v>
+      </c>
+      <c r="F698" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A699" s="16" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C699" s="16" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>2546</v>
+      </c>
+      <c r="F699" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A700" s="16" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C700" s="16" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F700" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A701" s="16" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C701" s="16" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>2548</v>
+      </c>
+      <c r="F701" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A702" s="16" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C702" s="16" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>2549</v>
+      </c>
+      <c r="F702" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A703" s="16" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C703" s="16" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D703" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>2550</v>
+      </c>
+      <c r="F703" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A704" s="16" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C704" s="16" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D704" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>2551</v>
+      </c>
+      <c r="F704" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A705" s="16" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C705" s="16" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D705" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>2552</v>
+      </c>
+      <c r="F705" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A706" s="16" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C706" s="16" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D706" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>2553</v>
+      </c>
+      <c r="F706" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A707" s="16" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C707" s="16" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D707" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>2554</v>
+      </c>
+      <c r="F707" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A708" s="16" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C708" s="16" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D708" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>2555</v>
+      </c>
+      <c r="F708" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A709" s="16" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C709" s="16" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D709" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>2556</v>
+      </c>
+      <c r="F709" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A710" s="16" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C710" s="16" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D710" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>2557</v>
+      </c>
+      <c r="F710" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A711" s="16" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C711" s="16" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D711" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>2558</v>
+      </c>
+      <c r="F711" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A712" s="16" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C712" s="16" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D712" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>2559</v>
+      </c>
+      <c r="F712" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A713" s="16" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C713" s="16" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D713" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F713" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A714" s="16" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C714" s="16" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>2561</v>
+      </c>
+      <c r="F714" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A715" s="16" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C715" s="16" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D715" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>2562</v>
+      </c>
+      <c r="F715" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A716" s="16" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C716" s="16" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D716" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>2563</v>
+      </c>
+      <c r="F716" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A717" s="16" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C717" s="16" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D717" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>2564</v>
+      </c>
+      <c r="F717" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A718" s="16" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C718" s="16" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D718" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>2565</v>
+      </c>
+      <c r="F718" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A719" s="16" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C719" s="16" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D719" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>2566</v>
+      </c>
+      <c r="F719" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A720" s="16" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C720" s="16" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D720" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>2567</v>
+      </c>
+      <c r="F720" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A721" s="16" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C721" s="16" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D721" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>2568</v>
+      </c>
+      <c r="F721" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A722" s="16" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C722" s="16" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D722" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>2569</v>
+      </c>
+      <c r="F722" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A723" s="16" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C723" s="16" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D723" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>2570</v>
+      </c>
+      <c r="F723" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A724" s="16" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C724" s="16" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D724" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>2571</v>
+      </c>
+      <c r="F724" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A725" s="16" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C725" s="16" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D725" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E725" s="1" t="s">
+        <v>2572</v>
+      </c>
+      <c r="F725" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A726" s="16" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C726" s="16" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D726" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E726" s="1" t="s">
+        <v>2573</v>
+      </c>
+      <c r="F726" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A727" s="16" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C727" s="16" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D727" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>2574</v>
+      </c>
+      <c r="F727" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A728" s="16" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C728" s="16" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D728" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E728" s="1" t="s">
+        <v>2575</v>
+      </c>
+      <c r="F728" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A729" s="16" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C729" s="16" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D729" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>2576</v>
+      </c>
+      <c r="F729" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A730" s="16" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C730" s="16" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D730" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E730" s="1" t="s">
+        <v>2577</v>
+      </c>
+      <c r="F730" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A731" s="16" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C731" s="16" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D731" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E731" s="1" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F731" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A732" s="16" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C732" s="16" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D732" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E732" s="1" t="s">
+        <v>2579</v>
+      </c>
+      <c r="F732" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A733" s="16" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C733" s="16" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D733" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E733" s="1" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F733" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A734" s="16" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C734" s="16" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D734" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E734" s="1" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F734" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A735" s="16" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C735" s="16" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D735" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E735" s="1" t="s">
+        <v>2582</v>
+      </c>
+      <c r="F735" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A736" s="16" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C736" s="16" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D736" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E736" s="1" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F736" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A737" s="16" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C737" s="16" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D737" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E737" s="1" t="s">
+        <v>2584</v>
+      </c>
+      <c r="F737" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A738" s="16" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C738" s="16" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D738" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E738" s="1" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F738" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A739" s="16" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C739" s="16" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D739" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E739" s="1" t="s">
+        <v>2586</v>
+      </c>
+      <c r="F739" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A740" s="16" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C740" s="16" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D740" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E740" s="1" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F740" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A741" s="16" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C741" s="16" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D741" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E741" s="1" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F741" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A742" s="16" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C742" s="16" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D742" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E742" s="1" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F742" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A743" s="16" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C743" s="16" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D743" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E743" s="1" t="s">
+        <v>2590</v>
+      </c>
+      <c r="F743" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A744" s="16" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C744" s="16" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D744" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E744" s="1" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F744" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A745" s="16" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C745" s="16" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D745" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E745" s="1" t="s">
+        <v>2592</v>
+      </c>
+      <c r="F745" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A746" s="16" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C746" s="16" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D746" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E746" s="1" t="s">
+        <v>2593</v>
+      </c>
+      <c r="F746" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A747" s="16" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C747" s="16" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D747" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E747" s="1" t="s">
+        <v>2594</v>
+      </c>
+      <c r="F747" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A748" s="16" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C748" s="16" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D748" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E748" s="1" t="s">
+        <v>2595</v>
+      </c>
+      <c r="F748" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A749" s="16" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C749" s="16" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D749" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E749" s="1" t="s">
+        <v>2596</v>
+      </c>
+      <c r="F749" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A750" s="16" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C750" s="16" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D750" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E750" s="1" t="s">
+        <v>2597</v>
+      </c>
+      <c r="F750" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A751" s="16" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C751" s="16" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D751" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E751" s="1" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F751" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A752" s="16" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C752" s="16" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D752" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E752" s="1" t="s">
+        <v>2599</v>
+      </c>
+      <c r="F752" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A753" s="16" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C753" s="16" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D753" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E753" s="1" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F753" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="16" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C754" s="16" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D754" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E754" s="1" t="s">
+        <v>2601</v>
+      </c>
+      <c r="F754" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A755" s="16" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C755" s="16" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D755" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E755" s="1" t="s">
+        <v>2602</v>
+      </c>
+      <c r="F755" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A756" s="16" t="s">
+        <v>1919</v>
+      </c>
+      <c r="C756" s="16" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D756" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E756" s="1" t="s">
+        <v>2603</v>
+      </c>
+      <c r="F756" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A757" s="16" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C757" s="16" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>2604</v>
+      </c>
+      <c r="F757" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A758" s="16" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C758" s="16" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D758" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E758" s="1" t="s">
+        <v>2605</v>
+      </c>
+      <c r="F758" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A759" s="16" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C759" s="16" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D759" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E759" s="1" t="s">
+        <v>2606</v>
+      </c>
+      <c r="F759" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A760" s="16" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C760" s="16" t="s">
+        <v>2265</v>
+      </c>
+      <c r="D760" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E760" s="1" t="s">
+        <v>2607</v>
+      </c>
+      <c r="F760" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A761" s="16" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C761" s="16" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D761" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E761" s="1" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F761" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A762" s="16" t="s">
+        <v>1925</v>
+      </c>
+      <c r="C762" s="16" t="s">
+        <v>2267</v>
+      </c>
+      <c r="D762" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E762" s="1" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F762" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A763" s="16" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C763" s="16" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D763" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E763" s="1" t="s">
+        <v>2610</v>
+      </c>
+      <c r="F763" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A764" s="16" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C764" s="16" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E764" s="1" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F764" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A765" s="16" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C765" s="16" t="s">
+        <v>2270</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E765" s="1" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F765" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A766" s="16" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C766" s="16" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E766" s="1" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F766" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="767" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A767" s="16" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C767" s="16" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D767" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E767" s="1" t="s">
+        <v>2614</v>
+      </c>
+      <c r="F767" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="768" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A768" s="16" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C768" s="16" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D768" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E768" s="1" t="s">
+        <v>2615</v>
+      </c>
+      <c r="F768" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="769" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A769" s="16" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C769" s="16" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E769" s="1" t="s">
+        <v>2616</v>
+      </c>
+      <c r="F769" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A770" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C770" s="16" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D770" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E770" s="1" t="s">
+        <v>2617</v>
+      </c>
+      <c r="F770" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A771" s="16" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C771" s="16" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E771" s="1" t="s">
+        <v>2618</v>
+      </c>
+      <c r="F771" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="772" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A772" s="16" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C772" s="16" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E772" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="F772" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="773" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A773" s="16" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C773" s="16" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D773" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E773" s="1" t="s">
+        <v>2620</v>
+      </c>
+      <c r="F773" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="774" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A774" s="16" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C774" s="16" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D774" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E774" s="1" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F774" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A775" s="16" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C775" s="16" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E775" s="1" t="s">
+        <v>2622</v>
+      </c>
+      <c r="F775" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A776" s="16" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C776" s="16" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E776" s="1" t="s">
+        <v>2623</v>
+      </c>
+      <c r="F776" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A777" s="16" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C777" s="16" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E777" s="1" t="s">
+        <v>2624</v>
+      </c>
+      <c r="F777" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A778" s="16" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C778" s="16" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E778" s="1" t="s">
+        <v>2625</v>
+      </c>
+      <c r="F778" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A779" s="16" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C779" s="16" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E779" s="1" t="s">
+        <v>2626</v>
+      </c>
+      <c r="F779" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A780" s="16" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C780" s="16" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E780" s="1" t="s">
+        <v>2627</v>
+      </c>
+      <c r="F780" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A781" s="16" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C781" s="16" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E781" s="1" t="s">
+        <v>2628</v>
+      </c>
+      <c r="F781" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A782" s="16" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C782" s="16" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E782" s="1" t="s">
+        <v>2629</v>
+      </c>
+      <c r="F782" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A783" s="16" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C783" s="16" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E783" s="1" t="s">
+        <v>2630</v>
+      </c>
+      <c r="F783" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A784" s="16" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C784" s="16" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E784" s="1" t="s">
+        <v>2631</v>
+      </c>
+      <c r="F784" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A785" s="16" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C785" s="16" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E785" s="1" t="s">
+        <v>2632</v>
+      </c>
+      <c r="F785" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A786" s="16" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C786" s="16" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E786" s="1" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F786" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A787" s="16" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C787" s="16" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D787" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E787" s="1" t="s">
+        <v>2634</v>
+      </c>
+      <c r="F787" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A788" s="16" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C788" s="16" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E788" s="1" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F788" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A789" s="16" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C789" s="16" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D789" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E789" s="1" t="s">
+        <v>2636</v>
+      </c>
+      <c r="F789" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A790" s="16" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C790" s="16" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E790" s="1" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F790" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A791" s="16" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C791" s="16" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E791" s="1" t="s">
+        <v>2638</v>
+      </c>
+      <c r="F791" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A792" s="16" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C792" s="16" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D792" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E792" s="1" t="s">
+        <v>2639</v>
+      </c>
+      <c r="F792" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A793" s="16" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C793" s="16" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E793" s="1" t="s">
+        <v>2640</v>
+      </c>
+      <c r="F793" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A794" s="16" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C794" s="16" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D794" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E794" s="1" t="s">
+        <v>2641</v>
+      </c>
+      <c r="F794" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A795" s="16" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C795" s="16" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D795" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E795" s="1" t="s">
+        <v>2642</v>
+      </c>
+      <c r="F795" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A796" s="16" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C796" s="16" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E796" s="1" t="s">
+        <v>2643</v>
+      </c>
+      <c r="F796" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A797" s="16" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C797" s="16" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D797" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E797" s="1" t="s">
+        <v>2644</v>
+      </c>
+      <c r="F797" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A798" s="16" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C798" s="16" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D798" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E798" s="1" t="s">
+        <v>2645</v>
+      </c>
+      <c r="F798" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A799" s="16" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C799" s="16" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D799" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E799" s="1" t="s">
+        <v>2646</v>
+      </c>
+      <c r="F799" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A800" s="16" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C800" s="16" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D800" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E800" s="1" t="s">
+        <v>2647</v>
+      </c>
+      <c r="F800" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A801" s="16" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C801" s="16" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D801" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E801" s="1" t="s">
+        <v>2648</v>
+      </c>
+      <c r="F801" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A802" s="16" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C802" s="16" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D802" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E802" s="1" t="s">
+        <v>2649</v>
+      </c>
+      <c r="F802" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A803" s="16" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C803" s="16" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D803" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E803" s="1" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F803" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A804" s="16" t="s">
+        <v>1967</v>
+      </c>
+      <c r="C804" s="16" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D804" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E804" s="1" t="s">
+        <v>2651</v>
+      </c>
+      <c r="F804" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A805" s="16" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C805" s="16" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D805" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E805" s="1" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F805" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A806" s="16" t="s">
+        <v>1969</v>
+      </c>
+      <c r="C806" s="16" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D806" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E806" s="1" t="s">
+        <v>2653</v>
+      </c>
+      <c r="F806" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="807" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A807" s="16" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C807" s="16" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D807" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E807" s="1" t="s">
+        <v>2654</v>
+      </c>
+      <c r="F807" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="808" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A808" s="16" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C808" s="16" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D808" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E808" s="1" t="s">
+        <v>2655</v>
+      </c>
+      <c r="F808" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="809" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A809" s="16" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C809" s="16" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D809" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E809" s="1" t="s">
+        <v>2656</v>
+      </c>
+      <c r="F809" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="810" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A810" s="16" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C810" s="16" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D810" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E810" s="1" t="s">
+        <v>2657</v>
+      </c>
+      <c r="F810" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="811" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A811" s="16" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C811" s="16" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D811" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E811" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F811" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="812" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A812" s="16" t="s">
+        <v>1975</v>
+      </c>
+      <c r="C812" s="16" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D812" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E812" s="1" t="s">
+        <v>2659</v>
+      </c>
+      <c r="F812" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="813" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A813" s="16" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C813" s="16" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D813" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E813" s="1" t="s">
+        <v>2660</v>
+      </c>
+      <c r="F813" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="814" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A814" s="16" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C814" s="16" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D814" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E814" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="F814" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="815" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A815" s="16" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C815" s="16" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D815" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E815" s="1" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F815" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="816" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A816" s="16" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C816" s="16" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D816" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E816" s="1" t="s">
+        <v>2663</v>
+      </c>
+      <c r="F816" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="817" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A817" s="16" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C817" s="16" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D817" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E817" s="1" t="s">
+        <v>2664</v>
+      </c>
+      <c r="F817" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="818" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A818" s="16" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C818" s="16" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D818" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E818" s="1" t="s">
+        <v>2665</v>
+      </c>
+      <c r="F818" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A819" s="16" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C819" s="16" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D819" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E819" s="1" t="s">
+        <v>2666</v>
+      </c>
+      <c r="F819" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A820" s="16" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C820" s="16" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D820" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E820" s="1" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F820" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A821" s="16" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C821" s="16" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D821" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E821" s="1" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F821" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A822" s="16" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C822" s="16" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D822" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E822" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="F822" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A823" s="1" t="s">
+        <v>2672</v>
+      </c>
+      <c r="C823" s="1" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D823" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E823" s="1" t="s">
+        <v>2673</v>
+      </c>
+      <c r="F823" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A824" s="1" t="s">
+        <v>2674</v>
+      </c>
+      <c r="C824" s="1" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D824" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E824" s="1" t="s">
+        <v>2675</v>
+      </c>
+      <c r="F824" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A825" s="1" t="s">
+        <v>2676</v>
+      </c>
+      <c r="C825" s="1" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D825" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E825" s="1" t="s">
+        <v>2677</v>
+      </c>
+      <c r="F825" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A826" s="1" t="s">
+        <v>2678</v>
+      </c>
+      <c r="C826" s="1" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D826" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E826" s="1" t="s">
+        <v>2679</v>
+      </c>
+      <c r="F826" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A827" s="1" t="s">
+        <v>2680</v>
+      </c>
+      <c r="C827" s="1" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D827" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E827" s="1" t="s">
+        <v>2681</v>
+      </c>
+      <c r="F827" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A828" s="1" t="s">
+        <v>2682</v>
+      </c>
+      <c r="C828" s="1" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D828" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E828" s="1" t="s">
+        <v>2683</v>
+      </c>
+      <c r="F828" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A829" s="1" t="s">
+        <v>2684</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D829" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E829" s="1" t="s">
+        <v>2685</v>
+      </c>
+      <c r="F829" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A830" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="C830" s="1" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D830" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E830" s="1" t="s">
+        <v>2687</v>
+      </c>
+      <c r="F830" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A831" s="1" t="s">
+        <v>2688</v>
+      </c>
+      <c r="C831" s="1" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D831" s="1" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E831" s="1" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F831" s="1" t="s">
+        <v>2671</v>
       </c>
     </row>
   </sheetData>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBF04DD-4E38-4E04-8381-4C3DA5F794B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B0CD71-FEDA-4304-BEFE-356BA27F42F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$837</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$839</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4954" uniqueCount="2706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6742" uniqueCount="2709">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8158,6 +8159,15 @@
   </si>
   <si>
     <t>B0GLHC8CB3</t>
+  </si>
+  <si>
+    <t>B0GN8MMKY1</t>
+  </si>
+  <si>
+    <t>B0GN8MFDGZ</t>
+  </si>
+  <si>
+    <t>B0GN97RFPR</t>
   </si>
 </sst>
 </file>
@@ -8332,7 +8342,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -11046,7 +11076,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -11369,7 +11399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:I837"/>
+  <dimension ref="A1:I843"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
@@ -18169,8 +18199,8 @@
         <v>628</v>
       </c>
       <c r="B249" s="2"/>
-      <c r="C249" s="2" t="s">
-        <v>747</v>
+      <c r="C249" t="s">
+        <v>2708</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>523</v>
@@ -30053,50 +30083,133 @@
         <v>1135</v>
       </c>
     </row>
+    <row r="838" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A838" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="C838" t="s">
+        <v>2706</v>
+      </c>
+      <c r="D838" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E838" s="17" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="839" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A839" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="C839" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D839" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E839" s="17" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="840" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A840" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="C840" s="13" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D840" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E840" s="13" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A841" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="C841" s="13" t="s">
+        <v>2706</v>
+      </c>
+      <c r="D841" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E841" s="13" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="842" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A842" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="C842" s="13" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D842" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E842" s="13" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A843" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="C843" s="13" t="s">
+        <v>2699</v>
+      </c>
+      <c r="D843" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E843" s="13" t="s">
+        <v>931</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I837" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="16" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A92">
-    <cfRule type="duplicateValues" dxfId="15" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A104 A106:A122 A2:A19 A31:A91 A21:A29 B56 B81">
-    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A141:A144">
-    <cfRule type="duplicateValues" dxfId="12" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123:B123">
-    <cfRule type="duplicateValues" dxfId="11" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A124:B140">
-    <cfRule type="duplicateValues" dxfId="10" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="9" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="7" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="6" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95">
-    <cfRule type="duplicateValues" dxfId="4" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="2" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E124:E140">
-    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E141">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="47"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A121" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>
@@ -30104,4 +30217,7420 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64940BF-FA81-488A-8BCB-2334EE5A997C}">
+  <dimension ref="A1:I352"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>2328</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>2329</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="16"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="2" t="s">
+        <v>1988</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>2330</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="16"/>
+    </row>
+    <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>2331</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="16"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>2332</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>2333</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>2334</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>2335</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>2336</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>2337</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>2338</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>2339</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>2340</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>2341</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>2342</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>2343</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>2344</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>2345</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>2346</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="16"/>
+    </row>
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="16"/>
+    </row>
+    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>2348</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="16"/>
+    </row>
+    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>2350</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>2351</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="16"/>
+    </row>
+    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="16"/>
+    </row>
+    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>2353</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="16"/>
+    </row>
+    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="2" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="16"/>
+    </row>
+    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="16"/>
+    </row>
+    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>2356</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="16"/>
+    </row>
+    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>2357</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="16"/>
+    </row>
+    <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="16"/>
+    </row>
+    <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>2359</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="16"/>
+    </row>
+    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>2360</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="16"/>
+    </row>
+    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>2361</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="16"/>
+    </row>
+    <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="16"/>
+    </row>
+    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="16"/>
+    </row>
+    <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>2364</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="16"/>
+    </row>
+    <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>2365</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="16"/>
+    </row>
+    <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>2366</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="16"/>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="2" t="s">
+        <v>2025</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>2367</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="16"/>
+    </row>
+    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>2368</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="16"/>
+    </row>
+    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>2369</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="16"/>
+    </row>
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>2370</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="16"/>
+    </row>
+    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>2371</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="16"/>
+    </row>
+    <row r="46" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="16"/>
+    </row>
+    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>2373</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="16"/>
+    </row>
+    <row r="48" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>2374</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="16"/>
+    </row>
+    <row r="49" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="16"/>
+    </row>
+    <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="16"/>
+    </row>
+    <row r="51" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="16"/>
+    </row>
+    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>2378</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="16"/>
+    </row>
+    <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="16"/>
+    </row>
+    <row r="54" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="2" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>2380</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="16"/>
+    </row>
+    <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="16"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>2382</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="16"/>
+    </row>
+    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>2383</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="16"/>
+    </row>
+    <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="16"/>
+    </row>
+    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="2" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>2385</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="16"/>
+    </row>
+    <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B60" s="13"/>
+      <c r="C60" s="2" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>2386</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="16"/>
+    </row>
+    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="16"/>
+    </row>
+    <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B62" s="13"/>
+      <c r="C62" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>2388</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="16"/>
+    </row>
+    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B63" s="13"/>
+      <c r="C63" s="2" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="16"/>
+    </row>
+    <row r="64" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B64" s="13"/>
+      <c r="C64" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>2390</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="16"/>
+    </row>
+    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B65" s="13"/>
+      <c r="C65" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>2391</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="16"/>
+    </row>
+    <row r="66" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B66" s="13"/>
+      <c r="C66" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>2392</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="16"/>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B67" s="13"/>
+      <c r="C67" s="2" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>2393</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="16"/>
+    </row>
+    <row r="68" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B68" s="13"/>
+      <c r="C68" s="2" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>2394</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="16"/>
+    </row>
+    <row r="69" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B69" s="13"/>
+      <c r="C69" s="2" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="16"/>
+    </row>
+    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B70" s="13"/>
+      <c r="C70" s="2" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>2396</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="16"/>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B71" s="13"/>
+      <c r="C71" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="16"/>
+    </row>
+    <row r="72" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B72" s="13"/>
+      <c r="C72" s="2" t="s">
+        <v>2056</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>2398</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
+      <c r="I72" s="16"/>
+    </row>
+    <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B73" s="13"/>
+      <c r="C73" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>2399</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
+      <c r="I73" s="16"/>
+    </row>
+    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B74" s="13"/>
+      <c r="C74" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>2400</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="16"/>
+    </row>
+    <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B75" s="13"/>
+      <c r="C75" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>2401</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="16"/>
+    </row>
+    <row r="76" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B76" s="13"/>
+      <c r="C76" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="16"/>
+    </row>
+    <row r="77" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B77" s="13"/>
+      <c r="C77" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="16"/>
+    </row>
+    <row r="78" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B78" s="13"/>
+      <c r="C78" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>2404</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="16"/>
+    </row>
+    <row r="79" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B79" s="13"/>
+      <c r="C79" s="2" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="16"/>
+    </row>
+    <row r="80" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B80" s="13"/>
+      <c r="C80" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>2406</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
+      <c r="I80" s="16"/>
+    </row>
+    <row r="81" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B81" s="13"/>
+      <c r="C81" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>2407</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
+      <c r="I81" s="16"/>
+    </row>
+    <row r="82" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="16"/>
+    </row>
+    <row r="83" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>2409</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
+      <c r="I83" s="16"/>
+    </row>
+    <row r="84" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B84" s="13"/>
+      <c r="C84" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>2410</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="16"/>
+    </row>
+    <row r="85" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B85" s="13"/>
+      <c r="C85" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>2411</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
+      <c r="I85" s="16"/>
+    </row>
+    <row r="86" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B86" s="13"/>
+      <c r="C86" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="16"/>
+    </row>
+    <row r="87" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B87" s="13"/>
+      <c r="C87" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>2413</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="16"/>
+    </row>
+    <row r="88" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B88" s="13"/>
+      <c r="C88" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>2414</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
+      <c r="I88" s="16"/>
+    </row>
+    <row r="89" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B89" s="13"/>
+      <c r="C89" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>2415</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="16"/>
+    </row>
+    <row r="90" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B90" s="13"/>
+      <c r="C90" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>2416</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
+      <c r="I90" s="16"/>
+    </row>
+    <row r="91" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B91" s="13"/>
+      <c r="C91" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>2417</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="16"/>
+    </row>
+    <row r="92" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B92" s="13"/>
+      <c r="C92" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>2418</v>
+      </c>
+      <c r="F92" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="16"/>
+    </row>
+    <row r="93" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B93" s="13"/>
+      <c r="C93" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="16"/>
+    </row>
+    <row r="94" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B94" s="13"/>
+      <c r="C94" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>2420</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="16"/>
+    </row>
+    <row r="95" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B95" s="13"/>
+      <c r="C95" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>2421</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="16"/>
+    </row>
+    <row r="96" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B96" s="13"/>
+      <c r="C96" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>2422</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="16"/>
+    </row>
+    <row r="97" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B97" s="13"/>
+      <c r="C97" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>2423</v>
+      </c>
+      <c r="F97" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
+      <c r="I97" s="16"/>
+    </row>
+    <row r="98" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B98" s="13"/>
+      <c r="C98" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>2424</v>
+      </c>
+      <c r="F98" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="16"/>
+    </row>
+    <row r="99" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B99" s="13"/>
+      <c r="C99" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>2425</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
+      <c r="I99" s="16"/>
+    </row>
+    <row r="100" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B100" s="13"/>
+      <c r="C100" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>2426</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
+      <c r="I100" s="16"/>
+    </row>
+    <row r="101" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B101" s="13"/>
+      <c r="C101" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
+      <c r="I101" s="16"/>
+    </row>
+    <row r="102" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B102" s="13"/>
+      <c r="C102" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
+      <c r="I102" s="16"/>
+    </row>
+    <row r="103" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B103" s="13"/>
+      <c r="C103" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>2429</v>
+      </c>
+      <c r="F103" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="16"/>
+    </row>
+    <row r="104" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B104" s="13"/>
+      <c r="C104" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>2430</v>
+      </c>
+      <c r="F104" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13"/>
+      <c r="I104" s="16"/>
+    </row>
+    <row r="105" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B105" s="13"/>
+      <c r="C105" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D105" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E105" s="13" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F105" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="16"/>
+    </row>
+    <row r="106" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B106" s="13"/>
+      <c r="C106" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>2432</v>
+      </c>
+      <c r="F106" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G106" s="13"/>
+      <c r="H106" s="13"/>
+      <c r="I106" s="16"/>
+    </row>
+    <row r="107" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B107" s="13"/>
+      <c r="C107" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>2433</v>
+      </c>
+      <c r="F107" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G107" s="13"/>
+      <c r="H107" s="13"/>
+      <c r="I107" s="16"/>
+    </row>
+    <row r="108" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B108" s="13"/>
+      <c r="C108" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E108" s="13" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F108" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="16"/>
+    </row>
+    <row r="109" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B109" s="13"/>
+      <c r="C109" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>2435</v>
+      </c>
+      <c r="F109" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G109" s="13"/>
+      <c r="H109" s="13"/>
+      <c r="I109" s="16"/>
+    </row>
+    <row r="110" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B110" s="13"/>
+      <c r="C110" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>2436</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
+      <c r="I110" s="16"/>
+    </row>
+    <row r="111" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B111" s="13"/>
+      <c r="C111" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F111" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
+      <c r="I111" s="16"/>
+    </row>
+    <row r="112" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B112" s="13"/>
+      <c r="C112" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>2438</v>
+      </c>
+      <c r="F112" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
+      <c r="I112" s="16"/>
+    </row>
+    <row r="113" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B113" s="13"/>
+      <c r="C113" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>2439</v>
+      </c>
+      <c r="F113" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
+      <c r="I113" s="16"/>
+    </row>
+    <row r="114" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B114" s="13"/>
+      <c r="C114" s="2" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>2440</v>
+      </c>
+      <c r="F114" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
+      <c r="I114" s="16"/>
+    </row>
+    <row r="115" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B115" s="13"/>
+      <c r="C115" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>2441</v>
+      </c>
+      <c r="F115" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
+      <c r="I115" s="16"/>
+    </row>
+    <row r="116" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B116" s="13"/>
+      <c r="C116" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F116" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G116" s="13"/>
+      <c r="H116" s="13"/>
+      <c r="I116" s="16"/>
+    </row>
+    <row r="117" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B117" s="13"/>
+      <c r="C117" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F117" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G117" s="13"/>
+      <c r="H117" s="13"/>
+      <c r="I117" s="16"/>
+    </row>
+    <row r="118" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B118" s="13"/>
+      <c r="C118" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F118" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
+      <c r="I118" s="16"/>
+    </row>
+    <row r="119" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B119" s="13"/>
+      <c r="C119" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>2445</v>
+      </c>
+      <c r="F119" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
+      <c r="I119" s="16"/>
+    </row>
+    <row r="120" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B120" s="13"/>
+      <c r="C120" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>2446</v>
+      </c>
+      <c r="F120" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
+      <c r="I120" s="16"/>
+    </row>
+    <row r="121" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B121" s="13"/>
+      <c r="C121" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>2447</v>
+      </c>
+      <c r="F121" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="16"/>
+    </row>
+    <row r="122" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B122" s="13"/>
+      <c r="C122" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>2448</v>
+      </c>
+      <c r="F122" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="16"/>
+    </row>
+    <row r="123" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B123" s="13"/>
+      <c r="C123" s="2" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F123" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
+      <c r="I123" s="16"/>
+    </row>
+    <row r="124" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B124" s="13"/>
+      <c r="C124" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>2450</v>
+      </c>
+      <c r="F124" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
+      <c r="I124" s="16"/>
+    </row>
+    <row r="125" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B125" s="13"/>
+      <c r="C125" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F125" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
+      <c r="I125" s="16"/>
+    </row>
+    <row r="126" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B126" s="13"/>
+      <c r="C126" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>2452</v>
+      </c>
+      <c r="F126" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
+      <c r="I126" s="16"/>
+    </row>
+    <row r="127" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B127" s="13"/>
+      <c r="C127" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>2453</v>
+      </c>
+      <c r="F127" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G127" s="13"/>
+      <c r="H127" s="13"/>
+      <c r="I127" s="16"/>
+    </row>
+    <row r="128" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B128" s="13"/>
+      <c r="C128" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>2454</v>
+      </c>
+      <c r="F128" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G128" s="13"/>
+      <c r="H128" s="13"/>
+      <c r="I128" s="16"/>
+    </row>
+    <row r="129" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B129" s="13"/>
+      <c r="C129" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>2455</v>
+      </c>
+      <c r="F129" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G129" s="13"/>
+      <c r="H129" s="13"/>
+      <c r="I129" s="16"/>
+    </row>
+    <row r="130" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B130" s="13"/>
+      <c r="C130" s="2" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>2456</v>
+      </c>
+      <c r="F130" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G130" s="13"/>
+      <c r="H130" s="13"/>
+      <c r="I130" s="16"/>
+    </row>
+    <row r="131" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B131" s="13"/>
+      <c r="C131" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>2457</v>
+      </c>
+      <c r="F131" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G131" s="13"/>
+      <c r="H131" s="13"/>
+      <c r="I131" s="16"/>
+    </row>
+    <row r="132" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B132" s="13"/>
+      <c r="C132" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>2458</v>
+      </c>
+      <c r="F132" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G132" s="13"/>
+      <c r="H132" s="13"/>
+      <c r="I132" s="16"/>
+    </row>
+    <row r="133" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B133" s="13"/>
+      <c r="C133" s="2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D133" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E133" s="13" t="s">
+        <v>2459</v>
+      </c>
+      <c r="F133" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13"/>
+      <c r="I133" s="16"/>
+    </row>
+    <row r="134" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B134" s="13"/>
+      <c r="C134" s="2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D134" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>2460</v>
+      </c>
+      <c r="F134" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
+      <c r="I134" s="16"/>
+    </row>
+    <row r="135" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B135" s="13"/>
+      <c r="C135" s="2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D135" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>2461</v>
+      </c>
+      <c r="F135" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G135" s="13"/>
+      <c r="H135" s="13"/>
+      <c r="I135" s="16"/>
+    </row>
+    <row r="136" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B136" s="13"/>
+      <c r="C136" s="2" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F136" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G136" s="13"/>
+      <c r="H136" s="13"/>
+      <c r="I136" s="16"/>
+    </row>
+    <row r="137" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B137" s="13"/>
+      <c r="C137" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="D137" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F137" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G137" s="13"/>
+      <c r="H137" s="13"/>
+      <c r="I137" s="16"/>
+    </row>
+    <row r="138" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B138" s="13"/>
+      <c r="C138" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>2464</v>
+      </c>
+      <c r="F138" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G138" s="13"/>
+      <c r="H138" s="13"/>
+      <c r="I138" s="16"/>
+    </row>
+    <row r="139" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B139" s="13"/>
+      <c r="C139" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E139" s="13" t="s">
+        <v>2465</v>
+      </c>
+      <c r="F139" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G139" s="13"/>
+      <c r="H139" s="13"/>
+      <c r="I139" s="16"/>
+    </row>
+    <row r="140" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B140" s="13"/>
+      <c r="C140" s="2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>2466</v>
+      </c>
+      <c r="F140" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G140" s="13"/>
+      <c r="H140" s="13"/>
+      <c r="I140" s="16"/>
+    </row>
+    <row r="141" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B141" s="13"/>
+      <c r="C141" s="2" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E141" s="13" t="s">
+        <v>2467</v>
+      </c>
+      <c r="F141" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G141" s="13"/>
+      <c r="H141" s="13"/>
+      <c r="I141" s="16"/>
+    </row>
+    <row r="142" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B142" s="13"/>
+      <c r="C142" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E142" s="13" t="s">
+        <v>2468</v>
+      </c>
+      <c r="F142" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G142" s="13"/>
+      <c r="H142" s="13"/>
+      <c r="I142" s="16"/>
+    </row>
+    <row r="143" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B143" s="13"/>
+      <c r="C143" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D143" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E143" s="13" t="s">
+        <v>2469</v>
+      </c>
+      <c r="F143" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G143" s="13"/>
+      <c r="H143" s="13"/>
+      <c r="I143" s="16"/>
+    </row>
+    <row r="144" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B144" s="13"/>
+      <c r="C144" s="2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D144" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>2470</v>
+      </c>
+      <c r="F144" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G144" s="13"/>
+      <c r="H144" s="13"/>
+      <c r="I144" s="16"/>
+    </row>
+    <row r="145" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B145" s="13"/>
+      <c r="C145" s="2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F145" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G145" s="13"/>
+      <c r="H145" s="13"/>
+      <c r="I145" s="16"/>
+    </row>
+    <row r="146" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B146" s="13"/>
+      <c r="C146" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>2472</v>
+      </c>
+      <c r="F146" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G146" s="13"/>
+      <c r="H146" s="13"/>
+      <c r="I146" s="16"/>
+    </row>
+    <row r="147" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B147" s="13"/>
+      <c r="C147" s="2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F147" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G147" s="13"/>
+      <c r="H147" s="13"/>
+      <c r="I147" s="16"/>
+    </row>
+    <row r="148" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B148" s="13"/>
+      <c r="C148" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D148" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>2474</v>
+      </c>
+      <c r="F148" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G148" s="13"/>
+      <c r="H148" s="13"/>
+      <c r="I148" s="16"/>
+    </row>
+    <row r="149" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B149" s="13"/>
+      <c r="C149" s="2" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E149" s="13" t="s">
+        <v>2475</v>
+      </c>
+      <c r="F149" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G149" s="13"/>
+      <c r="H149" s="13"/>
+      <c r="I149" s="16"/>
+    </row>
+    <row r="150" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B150" s="13"/>
+      <c r="C150" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F150" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G150" s="13"/>
+      <c r="H150" s="13"/>
+      <c r="I150" s="16"/>
+    </row>
+    <row r="151" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B151" s="13"/>
+      <c r="C151" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D151" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E151" s="13" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F151" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G151" s="13"/>
+      <c r="H151" s="13"/>
+      <c r="I151" s="16"/>
+    </row>
+    <row r="152" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B152" s="13"/>
+      <c r="C152" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F152" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G152" s="13"/>
+      <c r="H152" s="13"/>
+      <c r="I152" s="16"/>
+    </row>
+    <row r="153" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B153" s="13"/>
+      <c r="C153" s="2" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>2479</v>
+      </c>
+      <c r="F153" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G153" s="13"/>
+      <c r="H153" s="13"/>
+      <c r="I153" s="16"/>
+    </row>
+    <row r="154" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B154" s="13"/>
+      <c r="C154" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D154" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E154" s="13" t="s">
+        <v>2480</v>
+      </c>
+      <c r="F154" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G154" s="13"/>
+      <c r="H154" s="13"/>
+      <c r="I154" s="16"/>
+    </row>
+    <row r="155" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B155" s="13"/>
+      <c r="C155" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G155" s="13"/>
+      <c r="H155" s="13"/>
+      <c r="I155" s="16"/>
+    </row>
+    <row r="156" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B156" s="13"/>
+      <c r="C156" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D156" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F156" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G156" s="13"/>
+      <c r="H156" s="13"/>
+      <c r="I156" s="16"/>
+    </row>
+    <row r="157" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B157" s="13"/>
+      <c r="C157" s="2" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E157" s="13" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F157" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G157" s="13"/>
+      <c r="H157" s="13"/>
+      <c r="I157" s="16"/>
+    </row>
+    <row r="158" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B158" s="13"/>
+      <c r="C158" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D158" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F158" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G158" s="13"/>
+      <c r="H158" s="13"/>
+      <c r="I158" s="16"/>
+    </row>
+    <row r="159" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B159" s="13"/>
+      <c r="C159" s="2" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D159" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>2485</v>
+      </c>
+      <c r="F159" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G159" s="13"/>
+      <c r="H159" s="13"/>
+      <c r="I159" s="16"/>
+    </row>
+    <row r="160" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B160" s="13"/>
+      <c r="C160" s="2" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E160" s="13" t="s">
+        <v>2486</v>
+      </c>
+      <c r="F160" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="16"/>
+    </row>
+    <row r="161" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B161" s="13"/>
+      <c r="C161" s="2" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D161" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E161" s="13" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F161" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G161" s="13"/>
+      <c r="H161" s="13"/>
+      <c r="I161" s="16"/>
+    </row>
+    <row r="162" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B162" s="13"/>
+      <c r="C162" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E162" s="13" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F162" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G162" s="13"/>
+      <c r="H162" s="13"/>
+      <c r="I162" s="16"/>
+    </row>
+    <row r="163" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B163" s="13"/>
+      <c r="C163" s="2" t="s">
+        <v>2147</v>
+      </c>
+      <c r="D163" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E163" s="13" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F163" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G163" s="13"/>
+      <c r="H163" s="13"/>
+      <c r="I163" s="16"/>
+    </row>
+    <row r="164" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B164" s="13"/>
+      <c r="C164" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D164" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E164" s="13" t="s">
+        <v>2490</v>
+      </c>
+      <c r="F164" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G164" s="13"/>
+      <c r="H164" s="13"/>
+      <c r="I164" s="16"/>
+    </row>
+    <row r="165" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B165" s="13"/>
+      <c r="C165" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D165" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E165" s="13" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F165" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G165" s="13"/>
+      <c r="H165" s="13"/>
+      <c r="I165" s="16"/>
+    </row>
+    <row r="166" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B166" s="13"/>
+      <c r="C166" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D166" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E166" s="13" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F166" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G166" s="13"/>
+      <c r="H166" s="13"/>
+      <c r="I166" s="16"/>
+    </row>
+    <row r="167" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B167" s="13"/>
+      <c r="C167" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="D167" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E167" s="13" t="s">
+        <v>2493</v>
+      </c>
+      <c r="F167" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G167" s="13"/>
+      <c r="H167" s="13"/>
+      <c r="I167" s="16"/>
+    </row>
+    <row r="168" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B168" s="13"/>
+      <c r="C168" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D168" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E168" s="13" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F168" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G168" s="13"/>
+      <c r="H168" s="13"/>
+      <c r="I168" s="16"/>
+    </row>
+    <row r="169" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B169" s="13"/>
+      <c r="C169" s="2" t="s">
+        <v>2153</v>
+      </c>
+      <c r="D169" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E169" s="13" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F169" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G169" s="13"/>
+      <c r="H169" s="13"/>
+      <c r="I169" s="16"/>
+    </row>
+    <row r="170" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B170" s="13"/>
+      <c r="C170" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="D170" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E170" s="13" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F170" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G170" s="13"/>
+      <c r="H170" s="13"/>
+      <c r="I170" s="16"/>
+    </row>
+    <row r="171" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B171" s="13"/>
+      <c r="C171" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E171" s="13" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F171" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G171" s="13"/>
+      <c r="H171" s="13"/>
+      <c r="I171" s="16"/>
+    </row>
+    <row r="172" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B172" s="13"/>
+      <c r="C172" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E172" s="13" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F172" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G172" s="13"/>
+      <c r="H172" s="13"/>
+      <c r="I172" s="16"/>
+    </row>
+    <row r="173" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B173" s="13"/>
+      <c r="C173" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D173" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E173" s="13" t="s">
+        <v>2499</v>
+      </c>
+      <c r="F173" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G173" s="13"/>
+      <c r="H173" s="13"/>
+      <c r="I173" s="16"/>
+    </row>
+    <row r="174" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B174" s="13"/>
+      <c r="C174" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="D174" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E174" s="13" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F174" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G174" s="13"/>
+      <c r="H174" s="13"/>
+      <c r="I174" s="16"/>
+    </row>
+    <row r="175" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B175" s="13"/>
+      <c r="C175" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D175" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F175" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G175" s="13"/>
+      <c r="H175" s="13"/>
+      <c r="I175" s="16"/>
+    </row>
+    <row r="176" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B176" s="13"/>
+      <c r="C176" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="D176" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E176" s="13" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F176" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G176" s="13"/>
+      <c r="H176" s="13"/>
+      <c r="I176" s="16"/>
+    </row>
+    <row r="177" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B177" s="13"/>
+      <c r="C177" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D177" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E177" s="13" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F177" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G177" s="13"/>
+      <c r="H177" s="13"/>
+      <c r="I177" s="16"/>
+    </row>
+    <row r="178" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B178" s="13"/>
+      <c r="C178" s="2" t="s">
+        <v>2162</v>
+      </c>
+      <c r="D178" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E178" s="13" t="s">
+        <v>2504</v>
+      </c>
+      <c r="F178" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G178" s="13"/>
+      <c r="H178" s="13"/>
+      <c r="I178" s="16"/>
+    </row>
+    <row r="179" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B179" s="13"/>
+      <c r="C179" s="2" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D179" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E179" s="13" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F179" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G179" s="13"/>
+      <c r="H179" s="13"/>
+      <c r="I179" s="16"/>
+    </row>
+    <row r="180" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B180" s="13"/>
+      <c r="C180" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D180" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E180" s="13" t="s">
+        <v>2506</v>
+      </c>
+      <c r="F180" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G180" s="13"/>
+      <c r="H180" s="13"/>
+      <c r="I180" s="16"/>
+    </row>
+    <row r="181" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B181" s="13"/>
+      <c r="C181" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D181" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E181" s="13" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F181" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G181" s="13"/>
+      <c r="H181" s="13"/>
+      <c r="I181" s="16"/>
+    </row>
+    <row r="182" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B182" s="13"/>
+      <c r="C182" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D182" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E182" s="13" t="s">
+        <v>2508</v>
+      </c>
+      <c r="F182" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G182" s="13"/>
+      <c r="H182" s="13"/>
+      <c r="I182" s="16"/>
+    </row>
+    <row r="183" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A183" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B183" s="13"/>
+      <c r="C183" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="D183" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E183" s="13" t="s">
+        <v>2509</v>
+      </c>
+      <c r="F183" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G183" s="13"/>
+      <c r="H183" s="13"/>
+      <c r="I183" s="16"/>
+    </row>
+    <row r="184" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B184" s="13"/>
+      <c r="C184" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D184" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E184" s="13" t="s">
+        <v>2510</v>
+      </c>
+      <c r="F184" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G184" s="13"/>
+      <c r="H184" s="13"/>
+      <c r="I184" s="16"/>
+    </row>
+    <row r="185" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B185" s="13"/>
+      <c r="C185" s="2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D185" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E185" s="13" t="s">
+        <v>2511</v>
+      </c>
+      <c r="F185" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G185" s="13"/>
+      <c r="H185" s="13"/>
+      <c r="I185" s="16"/>
+    </row>
+    <row r="186" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B186" s="13"/>
+      <c r="C186" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E186" s="13" t="s">
+        <v>2512</v>
+      </c>
+      <c r="F186" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G186" s="13"/>
+      <c r="H186" s="13"/>
+      <c r="I186" s="16"/>
+    </row>
+    <row r="187" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B187" s="13"/>
+      <c r="C187" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E187" s="13" t="s">
+        <v>2513</v>
+      </c>
+      <c r="F187" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G187" s="13"/>
+      <c r="H187" s="13"/>
+      <c r="I187" s="16"/>
+    </row>
+    <row r="188" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B188" s="13"/>
+      <c r="C188" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E188" s="13" t="s">
+        <v>2514</v>
+      </c>
+      <c r="F188" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G188" s="13"/>
+      <c r="H188" s="13"/>
+      <c r="I188" s="16"/>
+    </row>
+    <row r="189" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B189" s="13"/>
+      <c r="C189" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D189" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E189" s="13" t="s">
+        <v>2515</v>
+      </c>
+      <c r="F189" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G189" s="13"/>
+      <c r="H189" s="13"/>
+      <c r="I189" s="16"/>
+    </row>
+    <row r="190" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B190" s="13"/>
+      <c r="C190" s="2" t="s">
+        <v>2174</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E190" s="13" t="s">
+        <v>2516</v>
+      </c>
+      <c r="F190" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G190" s="13"/>
+      <c r="H190" s="13"/>
+      <c r="I190" s="16"/>
+    </row>
+    <row r="191" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B191" s="13"/>
+      <c r="C191" s="2" t="s">
+        <v>2175</v>
+      </c>
+      <c r="D191" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E191" s="13" t="s">
+        <v>2517</v>
+      </c>
+      <c r="F191" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G191" s="13"/>
+      <c r="H191" s="13"/>
+      <c r="I191" s="16"/>
+    </row>
+    <row r="192" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B192" s="13"/>
+      <c r="C192" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="D192" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E192" s="13" t="s">
+        <v>2518</v>
+      </c>
+      <c r="F192" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G192" s="13"/>
+      <c r="H192" s="13"/>
+      <c r="I192" s="16"/>
+    </row>
+    <row r="193" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B193" s="13"/>
+      <c r="C193" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D193" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E193" s="13" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F193" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G193" s="13"/>
+      <c r="H193" s="13"/>
+      <c r="I193" s="16"/>
+    </row>
+    <row r="194" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B194" s="13"/>
+      <c r="C194" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D194" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E194" s="13" t="s">
+        <v>2520</v>
+      </c>
+      <c r="F194" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G194" s="13"/>
+      <c r="H194" s="13"/>
+      <c r="I194" s="16"/>
+    </row>
+    <row r="195" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A195" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B195" s="13"/>
+      <c r="C195" s="2" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D195" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E195" s="13" t="s">
+        <v>2521</v>
+      </c>
+      <c r="F195" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G195" s="13"/>
+      <c r="H195" s="13"/>
+      <c r="I195" s="16"/>
+    </row>
+    <row r="196" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B196" s="13"/>
+      <c r="C196" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D196" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E196" s="13" t="s">
+        <v>2522</v>
+      </c>
+      <c r="F196" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G196" s="13"/>
+      <c r="H196" s="13"/>
+      <c r="I196" s="16"/>
+    </row>
+    <row r="197" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A197" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B197" s="13"/>
+      <c r="C197" s="2" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D197" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E197" s="13" t="s">
+        <v>2523</v>
+      </c>
+      <c r="F197" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G197" s="13"/>
+      <c r="H197" s="13"/>
+      <c r="I197" s="16"/>
+    </row>
+    <row r="198" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B198" s="13"/>
+      <c r="C198" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D198" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E198" s="13" t="s">
+        <v>2524</v>
+      </c>
+      <c r="F198" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G198" s="13"/>
+      <c r="H198" s="13"/>
+      <c r="I198" s="16"/>
+    </row>
+    <row r="199" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B199" s="13"/>
+      <c r="C199" s="2" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D199" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E199" s="13" t="s">
+        <v>2525</v>
+      </c>
+      <c r="F199" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G199" s="13"/>
+      <c r="H199" s="13"/>
+      <c r="I199" s="16"/>
+    </row>
+    <row r="200" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B200" s="13"/>
+      <c r="C200" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D200" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E200" s="13" t="s">
+        <v>2526</v>
+      </c>
+      <c r="F200" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G200" s="13"/>
+      <c r="H200" s="13"/>
+      <c r="I200" s="16"/>
+    </row>
+    <row r="201" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B201" s="13"/>
+      <c r="C201" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E201" s="13" t="s">
+        <v>2527</v>
+      </c>
+      <c r="F201" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G201" s="13"/>
+      <c r="H201" s="13"/>
+      <c r="I201" s="16"/>
+    </row>
+    <row r="202" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B202" s="13"/>
+      <c r="C202" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D202" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E202" s="13" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F202" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G202" s="13"/>
+      <c r="H202" s="13"/>
+      <c r="I202" s="16"/>
+    </row>
+    <row r="203" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B203" s="13"/>
+      <c r="C203" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D203" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E203" s="13" t="s">
+        <v>2529</v>
+      </c>
+      <c r="F203" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G203" s="13"/>
+      <c r="H203" s="13"/>
+      <c r="I203" s="16"/>
+    </row>
+    <row r="204" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B204" s="13"/>
+      <c r="C204" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D204" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E204" s="13" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F204" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G204" s="13"/>
+      <c r="H204" s="13"/>
+      <c r="I204" s="16"/>
+    </row>
+    <row r="205" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B205" s="13"/>
+      <c r="C205" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D205" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E205" s="13" t="s">
+        <v>2531</v>
+      </c>
+      <c r="F205" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G205" s="13"/>
+      <c r="H205" s="13"/>
+      <c r="I205" s="16"/>
+    </row>
+    <row r="206" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B206" s="13"/>
+      <c r="C206" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="D206" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E206" s="13" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F206" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G206" s="13"/>
+      <c r="H206" s="13"/>
+      <c r="I206" s="16"/>
+    </row>
+    <row r="207" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B207" s="13"/>
+      <c r="C207" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="D207" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E207" s="13" t="s">
+        <v>2533</v>
+      </c>
+      <c r="F207" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G207" s="13"/>
+      <c r="H207" s="13"/>
+      <c r="I207" s="16"/>
+    </row>
+    <row r="208" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B208" s="13"/>
+      <c r="C208" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D208" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E208" s="13" t="s">
+        <v>2534</v>
+      </c>
+      <c r="F208" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G208" s="13"/>
+      <c r="H208" s="13"/>
+      <c r="I208" s="16"/>
+    </row>
+    <row r="209" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B209" s="13"/>
+      <c r="C209" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D209" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E209" s="13" t="s">
+        <v>2535</v>
+      </c>
+      <c r="F209" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G209" s="13"/>
+      <c r="H209" s="13"/>
+      <c r="I209" s="16"/>
+    </row>
+    <row r="210" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B210" s="13"/>
+      <c r="C210" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="D210" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E210" s="13" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F210" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G210" s="13"/>
+      <c r="H210" s="13"/>
+      <c r="I210" s="16"/>
+    </row>
+    <row r="211" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A211" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B211" s="13"/>
+      <c r="C211" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="D211" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E211" s="13" t="s">
+        <v>2537</v>
+      </c>
+      <c r="F211" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G211" s="13"/>
+      <c r="H211" s="13"/>
+      <c r="I211" s="16"/>
+    </row>
+    <row r="212" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B212" s="13"/>
+      <c r="C212" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D212" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E212" s="13" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F212" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G212" s="13"/>
+      <c r="H212" s="13"/>
+      <c r="I212" s="16"/>
+    </row>
+    <row r="213" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A213" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B213" s="13"/>
+      <c r="C213" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D213" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E213" s="13" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F213" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G213" s="13"/>
+      <c r="H213" s="13"/>
+      <c r="I213" s="16"/>
+    </row>
+    <row r="214" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B214" s="13"/>
+      <c r="C214" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D214" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E214" s="13" t="s">
+        <v>2540</v>
+      </c>
+      <c r="F214" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G214" s="13"/>
+      <c r="H214" s="13"/>
+      <c r="I214" s="16"/>
+    </row>
+    <row r="215" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B215" s="13"/>
+      <c r="C215" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D215" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E215" s="13" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F215" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G215" s="13"/>
+      <c r="H215" s="13"/>
+      <c r="I215" s="16"/>
+    </row>
+    <row r="216" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B216" s="13"/>
+      <c r="C216" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="D216" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E216" s="13" t="s">
+        <v>2542</v>
+      </c>
+      <c r="F216" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G216" s="13"/>
+      <c r="H216" s="13"/>
+      <c r="I216" s="16"/>
+    </row>
+    <row r="217" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A217" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B217" s="13"/>
+      <c r="C217" s="2" t="s">
+        <v>2201</v>
+      </c>
+      <c r="D217" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E217" s="13" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F217" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G217" s="13"/>
+      <c r="H217" s="13"/>
+      <c r="I217" s="16"/>
+    </row>
+    <row r="218" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B218" s="13"/>
+      <c r="C218" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D218" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E218" s="13" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F218" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G218" s="13"/>
+      <c r="H218" s="13"/>
+      <c r="I218" s="16"/>
+    </row>
+    <row r="219" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A219" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B219" s="13"/>
+      <c r="C219" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D219" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E219" s="13" t="s">
+        <v>2545</v>
+      </c>
+      <c r="F219" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G219" s="13"/>
+      <c r="H219" s="13"/>
+      <c r="I219" s="16"/>
+    </row>
+    <row r="220" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B220" s="13"/>
+      <c r="C220" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D220" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E220" s="13" t="s">
+        <v>2546</v>
+      </c>
+      <c r="F220" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G220" s="13"/>
+      <c r="H220" s="13"/>
+      <c r="I220" s="16"/>
+    </row>
+    <row r="221" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A221" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B221" s="13"/>
+      <c r="C221" s="2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D221" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E221" s="13" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F221" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G221" s="13"/>
+      <c r="H221" s="13"/>
+      <c r="I221" s="16"/>
+    </row>
+    <row r="222" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B222" s="13"/>
+      <c r="C222" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D222" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E222" s="13" t="s">
+        <v>2548</v>
+      </c>
+      <c r="F222" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G222" s="13"/>
+      <c r="H222" s="13"/>
+      <c r="I222" s="16"/>
+    </row>
+    <row r="223" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A223" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B223" s="13"/>
+      <c r="C223" s="2" t="s">
+        <v>2207</v>
+      </c>
+      <c r="D223" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E223" s="13" t="s">
+        <v>2549</v>
+      </c>
+      <c r="F223" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G223" s="13"/>
+      <c r="H223" s="13"/>
+      <c r="I223" s="16"/>
+    </row>
+    <row r="224" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B224" s="13"/>
+      <c r="C224" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D224" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E224" s="13" t="s">
+        <v>2550</v>
+      </c>
+      <c r="F224" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G224" s="13"/>
+      <c r="H224" s="13"/>
+      <c r="I224" s="16"/>
+    </row>
+    <row r="225" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B225" s="13"/>
+      <c r="C225" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D225" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E225" s="13" t="s">
+        <v>2551</v>
+      </c>
+      <c r="F225" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G225" s="13"/>
+      <c r="H225" s="13"/>
+      <c r="I225" s="16"/>
+    </row>
+    <row r="226" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B226" s="13"/>
+      <c r="C226" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="D226" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E226" s="13" t="s">
+        <v>2552</v>
+      </c>
+      <c r="F226" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G226" s="13"/>
+      <c r="H226" s="13"/>
+      <c r="I226" s="16"/>
+    </row>
+    <row r="227" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B227" s="13"/>
+      <c r="C227" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D227" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E227" s="13" t="s">
+        <v>2553</v>
+      </c>
+      <c r="F227" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G227" s="13"/>
+      <c r="H227" s="13"/>
+      <c r="I227" s="16"/>
+    </row>
+    <row r="228" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B228" s="13"/>
+      <c r="C228" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D228" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E228" s="13" t="s">
+        <v>2554</v>
+      </c>
+      <c r="F228" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G228" s="13"/>
+      <c r="H228" s="13"/>
+      <c r="I228" s="16"/>
+    </row>
+    <row r="229" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B229" s="13"/>
+      <c r="C229" s="2" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D229" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E229" s="13" t="s">
+        <v>2555</v>
+      </c>
+      <c r="F229" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G229" s="13"/>
+      <c r="H229" s="13"/>
+      <c r="I229" s="16"/>
+    </row>
+    <row r="230" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B230" s="13"/>
+      <c r="C230" s="2" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D230" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E230" s="13" t="s">
+        <v>2556</v>
+      </c>
+      <c r="F230" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G230" s="13"/>
+      <c r="H230" s="13"/>
+      <c r="I230" s="16"/>
+    </row>
+    <row r="231" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A231" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B231" s="13"/>
+      <c r="C231" s="2" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D231" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E231" s="13" t="s">
+        <v>2557</v>
+      </c>
+      <c r="F231" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G231" s="13"/>
+      <c r="H231" s="13"/>
+      <c r="I231" s="16"/>
+    </row>
+    <row r="232" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B232" s="13"/>
+      <c r="C232" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="D232" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E232" s="13" t="s">
+        <v>2558</v>
+      </c>
+      <c r="F232" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G232" s="13"/>
+      <c r="H232" s="13"/>
+      <c r="I232" s="16"/>
+    </row>
+    <row r="233" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A233" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B233" s="13"/>
+      <c r="C233" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D233" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E233" s="13" t="s">
+        <v>2559</v>
+      </c>
+      <c r="F233" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G233" s="13"/>
+      <c r="H233" s="13"/>
+      <c r="I233" s="16"/>
+    </row>
+    <row r="234" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B234" s="13"/>
+      <c r="C234" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D234" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E234" s="13" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F234" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G234" s="13"/>
+      <c r="H234" s="13"/>
+      <c r="I234" s="16"/>
+    </row>
+    <row r="235" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A235" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B235" s="13"/>
+      <c r="C235" s="2" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D235" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E235" s="13" t="s">
+        <v>2561</v>
+      </c>
+      <c r="F235" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G235" s="13"/>
+      <c r="H235" s="13"/>
+      <c r="I235" s="16"/>
+    </row>
+    <row r="236" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B236" s="13"/>
+      <c r="C236" s="2" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D236" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E236" s="13" t="s">
+        <v>2562</v>
+      </c>
+      <c r="F236" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G236" s="13"/>
+      <c r="H236" s="13"/>
+      <c r="I236" s="16"/>
+    </row>
+    <row r="237" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A237" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B237" s="13"/>
+      <c r="C237" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D237" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E237" s="13" t="s">
+        <v>2563</v>
+      </c>
+      <c r="F237" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G237" s="13"/>
+      <c r="H237" s="13"/>
+      <c r="I237" s="16"/>
+    </row>
+    <row r="238" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B238" s="13"/>
+      <c r="C238" s="2" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D238" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E238" s="13" t="s">
+        <v>2564</v>
+      </c>
+      <c r="F238" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G238" s="13"/>
+      <c r="H238" s="13"/>
+      <c r="I238" s="16"/>
+    </row>
+    <row r="239" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A239" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B239" s="13"/>
+      <c r="C239" s="2" t="s">
+        <v>2223</v>
+      </c>
+      <c r="D239" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E239" s="13" t="s">
+        <v>2565</v>
+      </c>
+      <c r="F239" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G239" s="13"/>
+      <c r="H239" s="13"/>
+      <c r="I239" s="16"/>
+    </row>
+    <row r="240" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A240" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B240" s="13"/>
+      <c r="C240" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D240" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E240" s="13" t="s">
+        <v>2566</v>
+      </c>
+      <c r="F240" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G240" s="13"/>
+      <c r="H240" s="13"/>
+      <c r="I240" s="16"/>
+    </row>
+    <row r="241" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A241" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B241" s="13"/>
+      <c r="C241" s="2" t="s">
+        <v>2225</v>
+      </c>
+      <c r="D241" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E241" s="13" t="s">
+        <v>2567</v>
+      </c>
+      <c r="F241" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G241" s="13"/>
+      <c r="H241" s="13"/>
+      <c r="I241" s="16"/>
+    </row>
+    <row r="242" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B242" s="13"/>
+      <c r="C242" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D242" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E242" s="13" t="s">
+        <v>2568</v>
+      </c>
+      <c r="F242" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G242" s="13"/>
+      <c r="H242" s="13"/>
+      <c r="I242" s="16"/>
+    </row>
+    <row r="243" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A243" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B243" s="13"/>
+      <c r="C243" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="D243" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E243" s="13" t="s">
+        <v>2569</v>
+      </c>
+      <c r="F243" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G243" s="13"/>
+      <c r="H243" s="13"/>
+      <c r="I243" s="16"/>
+    </row>
+    <row r="244" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B244" s="13"/>
+      <c r="C244" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D244" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E244" s="13" t="s">
+        <v>2570</v>
+      </c>
+      <c r="F244" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G244" s="13"/>
+      <c r="H244" s="13"/>
+      <c r="I244" s="16"/>
+    </row>
+    <row r="245" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A245" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B245" s="13"/>
+      <c r="C245" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D245" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E245" s="13" t="s">
+        <v>2571</v>
+      </c>
+      <c r="F245" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G245" s="13"/>
+      <c r="H245" s="13"/>
+      <c r="I245" s="16"/>
+    </row>
+    <row r="246" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A246" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B246" s="13"/>
+      <c r="C246" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D246" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E246" s="13" t="s">
+        <v>2572</v>
+      </c>
+      <c r="F246" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G246" s="13"/>
+      <c r="H246" s="13"/>
+      <c r="I246" s="16"/>
+    </row>
+    <row r="247" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A247" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B247" s="13"/>
+      <c r="C247" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D247" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E247" s="13" t="s">
+        <v>2573</v>
+      </c>
+      <c r="F247" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G247" s="13"/>
+      <c r="H247" s="13"/>
+      <c r="I247" s="16"/>
+    </row>
+    <row r="248" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A248" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B248" s="13"/>
+      <c r="C248" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D248" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E248" s="13" t="s">
+        <v>2574</v>
+      </c>
+      <c r="F248" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G248" s="13"/>
+      <c r="H248" s="13"/>
+      <c r="I248" s="16"/>
+    </row>
+    <row r="249" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A249" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B249" s="13"/>
+      <c r="C249" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D249" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E249" s="13" t="s">
+        <v>2575</v>
+      </c>
+      <c r="F249" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G249" s="13"/>
+      <c r="H249" s="13"/>
+      <c r="I249" s="16"/>
+    </row>
+    <row r="250" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A250" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B250" s="13"/>
+      <c r="C250" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D250" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E250" s="13" t="s">
+        <v>2576</v>
+      </c>
+      <c r="F250" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G250" s="13"/>
+      <c r="H250" s="13"/>
+      <c r="I250" s="16"/>
+    </row>
+    <row r="251" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A251" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B251" s="13"/>
+      <c r="C251" s="2" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D251" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E251" s="13" t="s">
+        <v>2577</v>
+      </c>
+      <c r="F251" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G251" s="13"/>
+      <c r="H251" s="13"/>
+      <c r="I251" s="16"/>
+    </row>
+    <row r="252" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A252" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B252" s="13"/>
+      <c r="C252" s="2" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D252" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E252" s="13" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F252" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G252" s="13"/>
+      <c r="H252" s="13"/>
+      <c r="I252" s="16"/>
+    </row>
+    <row r="253" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A253" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B253" s="13"/>
+      <c r="C253" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="D253" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E253" s="13" t="s">
+        <v>2579</v>
+      </c>
+      <c r="F253" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G253" s="13"/>
+      <c r="H253" s="13"/>
+      <c r="I253" s="16"/>
+    </row>
+    <row r="254" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A254" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B254" s="13"/>
+      <c r="C254" s="2" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D254" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E254" s="13" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F254" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G254" s="13"/>
+      <c r="H254" s="13"/>
+      <c r="I254" s="16"/>
+    </row>
+    <row r="255" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B255" s="13"/>
+      <c r="C255" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D255" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E255" s="13" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F255" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G255" s="13"/>
+      <c r="H255" s="13"/>
+      <c r="I255" s="16"/>
+    </row>
+    <row r="256" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A256" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B256" s="13"/>
+      <c r="C256" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D256" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E256" s="13" t="s">
+        <v>2582</v>
+      </c>
+      <c r="F256" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G256" s="13"/>
+      <c r="H256" s="13"/>
+      <c r="I256" s="16"/>
+    </row>
+    <row r="257" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A257" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B257" s="13"/>
+      <c r="C257" s="2" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D257" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E257" s="13" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F257" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G257" s="13"/>
+      <c r="H257" s="13"/>
+      <c r="I257" s="16"/>
+    </row>
+    <row r="258" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A258" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B258" s="13"/>
+      <c r="C258" s="2" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D258" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E258" s="13" t="s">
+        <v>2584</v>
+      </c>
+      <c r="F258" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G258" s="13"/>
+      <c r="H258" s="13"/>
+      <c r="I258" s="16"/>
+    </row>
+    <row r="259" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A259" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B259" s="13"/>
+      <c r="C259" s="2" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D259" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E259" s="13" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F259" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G259" s="13"/>
+      <c r="H259" s="13"/>
+      <c r="I259" s="16"/>
+    </row>
+    <row r="260" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A260" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B260" s="13"/>
+      <c r="C260" s="2" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D260" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E260" s="13" t="s">
+        <v>2586</v>
+      </c>
+      <c r="F260" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G260" s="13"/>
+      <c r="H260" s="13"/>
+      <c r="I260" s="16"/>
+    </row>
+    <row r="261" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A261" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B261" s="13"/>
+      <c r="C261" s="2" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D261" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E261" s="13" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F261" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G261" s="13"/>
+      <c r="H261" s="13"/>
+      <c r="I261" s="16"/>
+    </row>
+    <row r="262" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A262" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B262" s="13"/>
+      <c r="C262" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D262" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E262" s="13" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F262" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G262" s="13"/>
+      <c r="H262" s="13"/>
+      <c r="I262" s="16"/>
+    </row>
+    <row r="263" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A263" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B263" s="13"/>
+      <c r="C263" s="2" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D263" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E263" s="13" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F263" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G263" s="13"/>
+      <c r="H263" s="13"/>
+      <c r="I263" s="16"/>
+    </row>
+    <row r="264" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B264" s="13"/>
+      <c r="C264" s="2" t="s">
+        <v>2248</v>
+      </c>
+      <c r="D264" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E264" s="13" t="s">
+        <v>2590</v>
+      </c>
+      <c r="F264" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G264" s="13"/>
+      <c r="H264" s="13"/>
+      <c r="I264" s="16"/>
+    </row>
+    <row r="265" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A265" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B265" s="13"/>
+      <c r="C265" s="2" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D265" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E265" s="13" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F265" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G265" s="13"/>
+      <c r="H265" s="13"/>
+      <c r="I265" s="16"/>
+    </row>
+    <row r="266" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A266" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B266" s="13"/>
+      <c r="C266" s="2" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D266" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E266" s="13" t="s">
+        <v>2592</v>
+      </c>
+      <c r="F266" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G266" s="13"/>
+      <c r="H266" s="13"/>
+      <c r="I266" s="16"/>
+    </row>
+    <row r="267" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A267" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B267" s="13"/>
+      <c r="C267" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D267" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E267" s="13" t="s">
+        <v>2593</v>
+      </c>
+      <c r="F267" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G267" s="13"/>
+      <c r="H267" s="13"/>
+      <c r="I267" s="16"/>
+    </row>
+    <row r="268" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A268" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B268" s="13"/>
+      <c r="C268" s="2" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D268" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E268" s="13" t="s">
+        <v>2594</v>
+      </c>
+      <c r="F268" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G268" s="13"/>
+      <c r="H268" s="13"/>
+      <c r="I268" s="16"/>
+    </row>
+    <row r="269" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A269" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B269" s="13"/>
+      <c r="C269" s="2" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D269" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E269" s="13" t="s">
+        <v>2595</v>
+      </c>
+      <c r="F269" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G269" s="13"/>
+      <c r="H269" s="13"/>
+      <c r="I269" s="16"/>
+    </row>
+    <row r="270" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A270" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B270" s="13"/>
+      <c r="C270" s="2" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D270" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E270" s="13" t="s">
+        <v>2596</v>
+      </c>
+      <c r="F270" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G270" s="13"/>
+      <c r="H270" s="13"/>
+      <c r="I270" s="16"/>
+    </row>
+    <row r="271" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A271" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B271" s="13"/>
+      <c r="C271" s="2" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D271" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E271" s="13" t="s">
+        <v>2597</v>
+      </c>
+      <c r="F271" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G271" s="13"/>
+      <c r="H271" s="13"/>
+      <c r="I271" s="16"/>
+    </row>
+    <row r="272" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A272" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B272" s="13"/>
+      <c r="C272" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D272" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E272" s="13" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F272" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G272" s="13"/>
+      <c r="H272" s="13"/>
+      <c r="I272" s="16"/>
+    </row>
+    <row r="273" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A273" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B273" s="13"/>
+      <c r="C273" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="D273" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E273" s="13" t="s">
+        <v>2599</v>
+      </c>
+      <c r="F273" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G273" s="13"/>
+      <c r="H273" s="13"/>
+      <c r="I273" s="16"/>
+    </row>
+    <row r="274" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A274" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B274" s="13"/>
+      <c r="C274" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D274" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E274" s="13" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F274" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G274" s="13"/>
+      <c r="H274" s="13"/>
+      <c r="I274" s="16"/>
+    </row>
+    <row r="275" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A275" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B275" s="13"/>
+      <c r="C275" s="2" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D275" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E275" s="13" t="s">
+        <v>2601</v>
+      </c>
+      <c r="F275" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G275" s="13"/>
+      <c r="H275" s="13"/>
+      <c r="I275" s="16"/>
+    </row>
+    <row r="276" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A276" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B276" s="13"/>
+      <c r="C276" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D276" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E276" s="13" t="s">
+        <v>2602</v>
+      </c>
+      <c r="F276" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G276" s="13"/>
+      <c r="H276" s="13"/>
+      <c r="I276" s="16"/>
+    </row>
+    <row r="277" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A277" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B277" s="13"/>
+      <c r="C277" s="2" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D277" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E277" s="13" t="s">
+        <v>2603</v>
+      </c>
+      <c r="F277" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G277" s="13"/>
+      <c r="H277" s="13"/>
+      <c r="I277" s="16"/>
+    </row>
+    <row r="278" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A278" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B278" s="13"/>
+      <c r="C278" s="2" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D278" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E278" s="13" t="s">
+        <v>2604</v>
+      </c>
+      <c r="F278" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G278" s="13"/>
+      <c r="H278" s="13"/>
+      <c r="I278" s="16"/>
+    </row>
+    <row r="279" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A279" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B279" s="13"/>
+      <c r="C279" s="2" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D279" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E279" s="13" t="s">
+        <v>2605</v>
+      </c>
+      <c r="F279" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G279" s="13"/>
+      <c r="H279" s="13"/>
+      <c r="I279" s="16"/>
+    </row>
+    <row r="280" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A280" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B280" s="13"/>
+      <c r="C280" s="2" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D280" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E280" s="13" t="s">
+        <v>2606</v>
+      </c>
+      <c r="F280" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G280" s="13"/>
+      <c r="H280" s="13"/>
+      <c r="I280" s="16"/>
+    </row>
+    <row r="281" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A281" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B281" s="13"/>
+      <c r="C281" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="D281" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E281" s="13" t="s">
+        <v>2607</v>
+      </c>
+      <c r="F281" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G281" s="13"/>
+      <c r="H281" s="13"/>
+      <c r="I281" s="16"/>
+    </row>
+    <row r="282" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A282" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B282" s="13"/>
+      <c r="C282" s="2" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D282" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E282" s="13" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F282" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G282" s="13"/>
+      <c r="H282" s="13"/>
+      <c r="I282" s="16"/>
+    </row>
+    <row r="283" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A283" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B283" s="13"/>
+      <c r="C283" s="2" t="s">
+        <v>2267</v>
+      </c>
+      <c r="D283" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E283" s="13" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F283" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G283" s="13"/>
+      <c r="H283" s="13"/>
+      <c r="I283" s="16"/>
+    </row>
+    <row r="284" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A284" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B284" s="13"/>
+      <c r="C284" s="2" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D284" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E284" s="13" t="s">
+        <v>2610</v>
+      </c>
+      <c r="F284" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G284" s="13"/>
+      <c r="H284" s="13"/>
+      <c r="I284" s="16"/>
+    </row>
+    <row r="285" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A285" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B285" s="13"/>
+      <c r="C285" s="2" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D285" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E285" s="13" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F285" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G285" s="13"/>
+      <c r="H285" s="13"/>
+      <c r="I285" s="16"/>
+    </row>
+    <row r="286" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A286" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B286" s="13"/>
+      <c r="C286" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="D286" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E286" s="13" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F286" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G286" s="13"/>
+      <c r="H286" s="13"/>
+      <c r="I286" s="16"/>
+    </row>
+    <row r="287" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A287" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B287" s="13"/>
+      <c r="C287" s="2" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D287" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E287" s="13" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F287" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G287" s="13"/>
+      <c r="H287" s="13"/>
+      <c r="I287" s="16"/>
+    </row>
+    <row r="288" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A288" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B288" s="13"/>
+      <c r="C288" s="2" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D288" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E288" s="13" t="s">
+        <v>2614</v>
+      </c>
+      <c r="F288" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G288" s="13"/>
+      <c r="H288" s="13"/>
+      <c r="I288" s="16"/>
+    </row>
+    <row r="289" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A289" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B289" s="13"/>
+      <c r="C289" s="2" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D289" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E289" s="13" t="s">
+        <v>2615</v>
+      </c>
+      <c r="F289" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G289" s="13"/>
+      <c r="H289" s="13"/>
+      <c r="I289" s="16"/>
+    </row>
+    <row r="290" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A290" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B290" s="13"/>
+      <c r="C290" s="2" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D290" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E290" s="13" t="s">
+        <v>2616</v>
+      </c>
+      <c r="F290" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G290" s="13"/>
+      <c r="H290" s="13"/>
+      <c r="I290" s="16"/>
+    </row>
+    <row r="291" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A291" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B291" s="13"/>
+      <c r="C291" s="2" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D291" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E291" s="13" t="s">
+        <v>2617</v>
+      </c>
+      <c r="F291" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G291" s="13"/>
+      <c r="H291" s="13"/>
+      <c r="I291" s="16"/>
+    </row>
+    <row r="292" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A292" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B292" s="13"/>
+      <c r="C292" s="2" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D292" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E292" s="13" t="s">
+        <v>2618</v>
+      </c>
+      <c r="F292" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G292" s="13"/>
+      <c r="H292" s="13"/>
+      <c r="I292" s="16"/>
+    </row>
+    <row r="293" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A293" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B293" s="13"/>
+      <c r="C293" s="2" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D293" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E293" s="13" t="s">
+        <v>2619</v>
+      </c>
+      <c r="F293" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G293" s="13"/>
+      <c r="H293" s="13"/>
+      <c r="I293" s="16"/>
+    </row>
+    <row r="294" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A294" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B294" s="13"/>
+      <c r="C294" s="2" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D294" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E294" s="13" t="s">
+        <v>2620</v>
+      </c>
+      <c r="F294" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G294" s="13"/>
+      <c r="H294" s="13"/>
+      <c r="I294" s="16"/>
+    </row>
+    <row r="295" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A295" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B295" s="13"/>
+      <c r="C295" s="2" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D295" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E295" s="13" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F295" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G295" s="13"/>
+      <c r="H295" s="13"/>
+      <c r="I295" s="16"/>
+    </row>
+    <row r="296" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A296" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B296" s="13"/>
+      <c r="C296" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D296" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E296" s="13" t="s">
+        <v>2622</v>
+      </c>
+      <c r="F296" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G296" s="13"/>
+      <c r="H296" s="13"/>
+      <c r="I296" s="16"/>
+    </row>
+    <row r="297" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A297" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B297" s="13"/>
+      <c r="C297" s="2" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D297" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E297" s="13" t="s">
+        <v>2623</v>
+      </c>
+      <c r="F297" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G297" s="13"/>
+      <c r="H297" s="13"/>
+      <c r="I297" s="16"/>
+    </row>
+    <row r="298" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A298" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B298" s="13"/>
+      <c r="C298" s="2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D298" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E298" s="13" t="s">
+        <v>2624</v>
+      </c>
+      <c r="F298" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G298" s="13"/>
+      <c r="H298" s="13"/>
+      <c r="I298" s="16"/>
+    </row>
+    <row r="299" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A299" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B299" s="13"/>
+      <c r="C299" s="2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D299" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E299" s="13" t="s">
+        <v>2625</v>
+      </c>
+      <c r="F299" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G299" s="13"/>
+      <c r="H299" s="13"/>
+      <c r="I299" s="16"/>
+    </row>
+    <row r="300" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A300" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B300" s="13"/>
+      <c r="C300" s="2" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D300" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E300" s="13" t="s">
+        <v>2626</v>
+      </c>
+      <c r="F300" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G300" s="13"/>
+      <c r="H300" s="13"/>
+      <c r="I300" s="16"/>
+    </row>
+    <row r="301" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A301" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B301" s="13"/>
+      <c r="C301" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D301" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E301" s="13" t="s">
+        <v>2627</v>
+      </c>
+      <c r="F301" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G301" s="13"/>
+      <c r="H301" s="13"/>
+      <c r="I301" s="16"/>
+    </row>
+    <row r="302" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A302" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B302" s="13"/>
+      <c r="C302" s="2" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D302" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E302" s="13" t="s">
+        <v>2628</v>
+      </c>
+      <c r="F302" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G302" s="13"/>
+      <c r="H302" s="13"/>
+      <c r="I302" s="16"/>
+    </row>
+    <row r="303" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A303" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B303" s="13"/>
+      <c r="C303" s="2" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D303" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E303" s="13" t="s">
+        <v>2629</v>
+      </c>
+      <c r="F303" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G303" s="13"/>
+      <c r="H303" s="13"/>
+      <c r="I303" s="16"/>
+    </row>
+    <row r="304" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A304" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B304" s="13"/>
+      <c r="C304" s="2" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D304" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E304" s="13" t="s">
+        <v>2630</v>
+      </c>
+      <c r="F304" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G304" s="13"/>
+      <c r="H304" s="13"/>
+      <c r="I304" s="16"/>
+    </row>
+    <row r="305" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A305" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B305" s="13"/>
+      <c r="C305" s="2" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D305" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E305" s="13" t="s">
+        <v>2631</v>
+      </c>
+      <c r="F305" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G305" s="13"/>
+      <c r="H305" s="13"/>
+      <c r="I305" s="16"/>
+    </row>
+    <row r="306" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A306" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B306" s="13"/>
+      <c r="C306" s="2" t="s">
+        <v>2290</v>
+      </c>
+      <c r="D306" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E306" s="13" t="s">
+        <v>2632</v>
+      </c>
+      <c r="F306" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G306" s="13"/>
+      <c r="H306" s="13"/>
+      <c r="I306" s="16"/>
+    </row>
+    <row r="307" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A307" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B307" s="13"/>
+      <c r="C307" s="2" t="s">
+        <v>2291</v>
+      </c>
+      <c r="D307" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E307" s="13" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F307" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G307" s="13"/>
+      <c r="H307" s="13"/>
+      <c r="I307" s="16"/>
+    </row>
+    <row r="308" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A308" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B308" s="13"/>
+      <c r="C308" s="2" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D308" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E308" s="13" t="s">
+        <v>2634</v>
+      </c>
+      <c r="F308" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G308" s="13"/>
+      <c r="H308" s="13"/>
+      <c r="I308" s="16"/>
+    </row>
+    <row r="309" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A309" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B309" s="13"/>
+      <c r="C309" s="2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D309" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E309" s="13" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F309" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G309" s="13"/>
+      <c r="H309" s="13"/>
+      <c r="I309" s="16"/>
+    </row>
+    <row r="310" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A310" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B310" s="13"/>
+      <c r="C310" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D310" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E310" s="13" t="s">
+        <v>2636</v>
+      </c>
+      <c r="F310" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G310" s="13"/>
+      <c r="H310" s="13"/>
+      <c r="I310" s="16"/>
+    </row>
+    <row r="311" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A311" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B311" s="13"/>
+      <c r="C311" s="2" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D311" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E311" s="13" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F311" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G311" s="13"/>
+      <c r="H311" s="13"/>
+      <c r="I311" s="16"/>
+    </row>
+    <row r="312" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A312" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="B312" s="13"/>
+      <c r="C312" s="2" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D312" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E312" s="13" t="s">
+        <v>2638</v>
+      </c>
+      <c r="F312" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G312" s="13"/>
+      <c r="H312" s="13"/>
+      <c r="I312" s="16"/>
+    </row>
+    <row r="313" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A313" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B313" s="13"/>
+      <c r="C313" s="2" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D313" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E313" s="13" t="s">
+        <v>2639</v>
+      </c>
+      <c r="F313" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G313" s="13"/>
+      <c r="H313" s="13"/>
+      <c r="I313" s="16"/>
+    </row>
+    <row r="314" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A314" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B314" s="13"/>
+      <c r="C314" s="2" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D314" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E314" s="13" t="s">
+        <v>2640</v>
+      </c>
+      <c r="F314" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G314" s="13"/>
+      <c r="H314" s="13"/>
+      <c r="I314" s="16"/>
+    </row>
+    <row r="315" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A315" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B315" s="13"/>
+      <c r="C315" s="2" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D315" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E315" s="13" t="s">
+        <v>2641</v>
+      </c>
+      <c r="F315" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G315" s="13"/>
+      <c r="H315" s="13"/>
+      <c r="I315" s="16"/>
+    </row>
+    <row r="316" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A316" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B316" s="13"/>
+      <c r="C316" s="2" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D316" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E316" s="13" t="s">
+        <v>2642</v>
+      </c>
+      <c r="F316" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G316" s="13"/>
+      <c r="H316" s="13"/>
+      <c r="I316" s="16"/>
+    </row>
+    <row r="317" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A317" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B317" s="13"/>
+      <c r="C317" s="2" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D317" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E317" s="13" t="s">
+        <v>2643</v>
+      </c>
+      <c r="F317" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G317" s="13"/>
+      <c r="H317" s="13"/>
+      <c r="I317" s="16"/>
+    </row>
+    <row r="318" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A318" s="2" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B318" s="13"/>
+      <c r="C318" s="2" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D318" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E318" s="13" t="s">
+        <v>2644</v>
+      </c>
+      <c r="F318" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G318" s="13"/>
+      <c r="H318" s="13"/>
+      <c r="I318" s="16"/>
+    </row>
+    <row r="319" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A319" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B319" s="13"/>
+      <c r="C319" s="2" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D319" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E319" s="13" t="s">
+        <v>2645</v>
+      </c>
+      <c r="F319" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G319" s="13"/>
+      <c r="H319" s="13"/>
+      <c r="I319" s="16"/>
+    </row>
+    <row r="320" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A320" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B320" s="13"/>
+      <c r="C320" s="2" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D320" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E320" s="13" t="s">
+        <v>2646</v>
+      </c>
+      <c r="F320" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G320" s="13"/>
+      <c r="H320" s="13"/>
+      <c r="I320" s="16"/>
+    </row>
+    <row r="321" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A321" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B321" s="13"/>
+      <c r="C321" s="2" t="s">
+        <v>2305</v>
+      </c>
+      <c r="D321" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E321" s="13" t="s">
+        <v>2647</v>
+      </c>
+      <c r="F321" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G321" s="13"/>
+      <c r="H321" s="13"/>
+      <c r="I321" s="16"/>
+    </row>
+    <row r="322" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A322" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B322" s="13"/>
+      <c r="C322" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D322" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E322" s="13" t="s">
+        <v>2648</v>
+      </c>
+      <c r="F322" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G322" s="13"/>
+      <c r="H322" s="13"/>
+      <c r="I322" s="16"/>
+    </row>
+    <row r="323" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A323" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B323" s="13"/>
+      <c r="C323" s="2" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D323" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E323" s="13" t="s">
+        <v>2649</v>
+      </c>
+      <c r="F323" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G323" s="13"/>
+      <c r="H323" s="13"/>
+      <c r="I323" s="16"/>
+    </row>
+    <row r="324" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A324" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B324" s="13"/>
+      <c r="C324" s="2" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D324" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E324" s="13" t="s">
+        <v>2650</v>
+      </c>
+      <c r="F324" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G324" s="13"/>
+      <c r="H324" s="13"/>
+      <c r="I324" s="16"/>
+    </row>
+    <row r="325" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A325" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B325" s="13"/>
+      <c r="C325" s="2" t="s">
+        <v>2309</v>
+      </c>
+      <c r="D325" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E325" s="13" t="s">
+        <v>2651</v>
+      </c>
+      <c r="F325" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G325" s="13"/>
+      <c r="H325" s="13"/>
+      <c r="I325" s="16"/>
+    </row>
+    <row r="326" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A326" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B326" s="13"/>
+      <c r="C326" s="2" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D326" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E326" s="13" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F326" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G326" s="13"/>
+      <c r="H326" s="13"/>
+      <c r="I326" s="16"/>
+    </row>
+    <row r="327" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A327" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B327" s="13"/>
+      <c r="C327" s="2" t="s">
+        <v>2311</v>
+      </c>
+      <c r="D327" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E327" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="F327" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G327" s="13"/>
+      <c r="H327" s="13"/>
+      <c r="I327" s="16"/>
+    </row>
+    <row r="328" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A328" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B328" s="13"/>
+      <c r="C328" s="2" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E328" s="13" t="s">
+        <v>2654</v>
+      </c>
+      <c r="F328" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G328" s="13"/>
+      <c r="H328" s="13"/>
+      <c r="I328" s="16"/>
+    </row>
+    <row r="329" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A329" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B329" s="13"/>
+      <c r="C329" s="2" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D329" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E329" s="13" t="s">
+        <v>2655</v>
+      </c>
+      <c r="F329" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G329" s="13"/>
+      <c r="H329" s="13"/>
+      <c r="I329" s="16"/>
+    </row>
+    <row r="330" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A330" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B330" s="13"/>
+      <c r="C330" s="2" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D330" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E330" s="13" t="s">
+        <v>2656</v>
+      </c>
+      <c r="F330" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G330" s="13"/>
+      <c r="H330" s="13"/>
+      <c r="I330" s="16"/>
+    </row>
+    <row r="331" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A331" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B331" s="13"/>
+      <c r="C331" s="2" t="s">
+        <v>2315</v>
+      </c>
+      <c r="D331" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E331" s="13" t="s">
+        <v>2657</v>
+      </c>
+      <c r="F331" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G331" s="13"/>
+      <c r="H331" s="13"/>
+      <c r="I331" s="16"/>
+    </row>
+    <row r="332" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A332" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B332" s="13"/>
+      <c r="C332" s="2" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D332" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E332" s="13" t="s">
+        <v>2658</v>
+      </c>
+      <c r="F332" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G332" s="13"/>
+      <c r="H332" s="13"/>
+      <c r="I332" s="16"/>
+    </row>
+    <row r="333" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A333" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B333" s="13"/>
+      <c r="C333" s="2" t="s">
+        <v>2317</v>
+      </c>
+      <c r="D333" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E333" s="13" t="s">
+        <v>2659</v>
+      </c>
+      <c r="F333" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G333" s="13"/>
+      <c r="H333" s="13"/>
+      <c r="I333" s="16"/>
+    </row>
+    <row r="334" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A334" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B334" s="13"/>
+      <c r="C334" s="2" t="s">
+        <v>2318</v>
+      </c>
+      <c r="D334" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E334" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="F334" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G334" s="13"/>
+      <c r="H334" s="13"/>
+      <c r="I334" s="16"/>
+    </row>
+    <row r="335" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A335" s="2" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B335" s="13"/>
+      <c r="C335" s="2" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D335" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E335" s="13" t="s">
+        <v>2661</v>
+      </c>
+      <c r="F335" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G335" s="13"/>
+      <c r="H335" s="13"/>
+      <c r="I335" s="16"/>
+    </row>
+    <row r="336" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A336" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B336" s="13"/>
+      <c r="C336" s="2" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D336" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E336" s="13" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F336" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G336" s="13"/>
+      <c r="H336" s="13"/>
+      <c r="I336" s="16"/>
+    </row>
+    <row r="337" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A337" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B337" s="13"/>
+      <c r="C337" s="2" t="s">
+        <v>2321</v>
+      </c>
+      <c r="D337" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E337" s="13" t="s">
+        <v>2663</v>
+      </c>
+      <c r="F337" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G337" s="13"/>
+      <c r="H337" s="13"/>
+      <c r="I337" s="16"/>
+    </row>
+    <row r="338" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A338" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B338" s="13"/>
+      <c r="C338" s="2" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D338" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E338" s="13" t="s">
+        <v>2664</v>
+      </c>
+      <c r="F338" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G338" s="13"/>
+      <c r="H338" s="13"/>
+      <c r="I338" s="16"/>
+    </row>
+    <row r="339" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A339" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B339" s="13"/>
+      <c r="C339" s="2" t="s">
+        <v>2323</v>
+      </c>
+      <c r="D339" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E339" s="13" t="s">
+        <v>2665</v>
+      </c>
+      <c r="F339" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G339" s="13"/>
+      <c r="H339" s="13"/>
+      <c r="I339" s="16"/>
+    </row>
+    <row r="340" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A340" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B340" s="13"/>
+      <c r="C340" s="2" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D340" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E340" s="13" t="s">
+        <v>2666</v>
+      </c>
+      <c r="F340" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G340" s="13"/>
+      <c r="H340" s="13"/>
+      <c r="I340" s="16"/>
+    </row>
+    <row r="341" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A341" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B341" s="13"/>
+      <c r="C341" s="2" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D341" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E341" s="13" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F341" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G341" s="13"/>
+      <c r="H341" s="13"/>
+      <c r="I341" s="16"/>
+    </row>
+    <row r="342" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A342" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B342" s="13"/>
+      <c r="C342" s="2" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D342" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E342" s="13" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F342" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G342" s="13"/>
+      <c r="H342" s="13"/>
+      <c r="I342" s="16"/>
+    </row>
+    <row r="343" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A343" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B343" s="13"/>
+      <c r="C343" s="2" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D343" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E343" s="13" t="s">
+        <v>2669</v>
+      </c>
+      <c r="F343" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G343" s="13"/>
+      <c r="H343" s="13"/>
+      <c r="I343" s="16"/>
+    </row>
+    <row r="344" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A344" s="13" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B344" s="13"/>
+      <c r="C344" s="13" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D344" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E344" s="13" t="s">
+        <v>2673</v>
+      </c>
+      <c r="F344" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G344" s="13"/>
+      <c r="H344" s="13"/>
+      <c r="I344" s="16"/>
+    </row>
+    <row r="345" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A345" s="13" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B345" s="13"/>
+      <c r="C345" s="13" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D345" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E345" s="13" t="s">
+        <v>2675</v>
+      </c>
+      <c r="F345" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G345" s="13"/>
+      <c r="H345" s="13"/>
+      <c r="I345" s="16"/>
+    </row>
+    <row r="346" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A346" s="13" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B346" s="13"/>
+      <c r="C346" s="13" t="s">
+        <v>2692</v>
+      </c>
+      <c r="D346" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E346" s="13" t="s">
+        <v>2677</v>
+      </c>
+      <c r="F346" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G346" s="13"/>
+      <c r="H346" s="13"/>
+      <c r="I346" s="16"/>
+    </row>
+    <row r="347" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A347" s="13" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B347" s="13"/>
+      <c r="C347" s="13" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D347" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E347" s="13" t="s">
+        <v>2679</v>
+      </c>
+      <c r="F347" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G347" s="13"/>
+      <c r="H347" s="13"/>
+      <c r="I347" s="16"/>
+    </row>
+    <row r="348" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A348" s="13" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B348" s="13"/>
+      <c r="C348" s="13" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D348" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E348" s="13" t="s">
+        <v>2681</v>
+      </c>
+      <c r="F348" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G348" s="13"/>
+      <c r="H348" s="13"/>
+      <c r="I348" s="16"/>
+    </row>
+    <row r="349" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A349" s="13" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B349" s="13"/>
+      <c r="C349" s="13" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D349" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E349" s="13" t="s">
+        <v>2683</v>
+      </c>
+      <c r="F349" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G349" s="13"/>
+      <c r="H349" s="13"/>
+      <c r="I349" s="16"/>
+    </row>
+    <row r="350" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A350" s="13" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B350" s="13"/>
+      <c r="C350" s="13" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D350" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E350" s="13" t="s">
+        <v>2685</v>
+      </c>
+      <c r="F350" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G350" s="13"/>
+      <c r="H350" s="13"/>
+      <c r="I350" s="16"/>
+    </row>
+    <row r="351" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A351" s="13" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B351" s="13"/>
+      <c r="C351" s="13" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D351" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E351" s="13" t="s">
+        <v>2687</v>
+      </c>
+      <c r="F351" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G351" s="13"/>
+      <c r="H351" s="13"/>
+      <c r="I351" s="16"/>
+    </row>
+    <row r="352" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A352" s="13" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B352" s="13"/>
+      <c r="C352" s="13" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D352" s="13" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E352" s="13" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F352" s="13" t="s">
+        <v>2671</v>
+      </c>
+      <c r="G352" s="13"/>
+      <c r="H352" s="13"/>
+      <c r="I352" s="16"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B0CD71-FEDA-4304-BEFE-356BA27F42F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2FCAE9-BF71-440F-B5BB-516CA2AC2303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$839</definedName>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6742" uniqueCount="2709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="2709">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8342,27 +8341,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -30169,47 +30148,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="18" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A92">
-    <cfRule type="duplicateValues" dxfId="17" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93:A104 A106:A122 A2:A19 A31:A91 A21:A29 B56 B81">
-    <cfRule type="duplicateValues" dxfId="15" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A141:A144">
-    <cfRule type="duplicateValues" dxfId="14" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123:B123">
-    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A124:B140">
-    <cfRule type="duplicateValues" dxfId="12" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="11" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="9" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="8" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95">
-    <cfRule type="duplicateValues" dxfId="6" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="4" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E124:E140">
-    <cfRule type="duplicateValues" dxfId="3" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E141">
-    <cfRule type="duplicateValues" dxfId="2" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A121" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>
@@ -30217,7420 +30196,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64940BF-FA81-488A-8BCB-2334EE5A997C}">
-  <dimension ref="A1:I352"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1644</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="2" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>2328</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="16"/>
-    </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>1645</v>
-      </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="2" t="s">
-        <v>1987</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>2329</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="16"/>
-    </row>
-    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="2" t="s">
-        <v>1988</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>2330</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="16"/>
-    </row>
-    <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1647</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="2" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>2331</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>1648</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="2" t="s">
-        <v>1990</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>2332</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>1649</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="2" t="s">
-        <v>1991</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>2333</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="2" t="s">
-        <v>1992</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>2334</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>1651</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="2" t="s">
-        <v>1993</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>2335</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="16"/>
-    </row>
-    <row r="10" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1652</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="2" t="s">
-        <v>1994</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>2336</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1653</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="2" t="s">
-        <v>1995</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>2337</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1654</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="2" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>2338</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1655</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="2" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>2339</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="16"/>
-    </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1656</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="2" t="s">
-        <v>1998</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>2340</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="16"/>
-    </row>
-    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1657</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="2" t="s">
-        <v>1999</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>2341</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="16"/>
-    </row>
-    <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1658</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="2" t="s">
-        <v>2000</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>2342</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="16"/>
-    </row>
-    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1659</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="2" t="s">
-        <v>2001</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>2343</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="16"/>
-    </row>
-    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1660</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="2" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>2344</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="16"/>
-    </row>
-    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>1661</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="2" t="s">
-        <v>2003</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>2345</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="16"/>
-    </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>1662</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="2" t="s">
-        <v>2004</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>2346</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="16"/>
-    </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="2" t="s">
-        <v>2005</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>2347</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="16"/>
-    </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>1664</v>
-      </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="2" t="s">
-        <v>2006</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>2348</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="16"/>
-    </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>1665</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="2" t="s">
-        <v>2007</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>2349</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="16"/>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>1666</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="2" t="s">
-        <v>2008</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>2350</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="16"/>
-    </row>
-    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>1667</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="2" t="s">
-        <v>2009</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>2351</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="16"/>
-    </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>1668</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="2" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>2352</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="16"/>
-    </row>
-    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>1669</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="2" t="s">
-        <v>2011</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>2353</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="16"/>
-    </row>
-    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>1670</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="2" t="s">
-        <v>2012</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>2354</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="16"/>
-    </row>
-    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>1671</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="2" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>2355</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="16"/>
-    </row>
-    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>1672</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="2" t="s">
-        <v>2014</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>2356</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="16"/>
-    </row>
-    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="2" t="s">
-        <v>2015</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>2357</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="16"/>
-    </row>
-    <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>1674</v>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="2" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>2358</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="16"/>
-    </row>
-    <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="2" t="s">
-        <v>2017</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>2359</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="16"/>
-    </row>
-    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>1676</v>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="2" t="s">
-        <v>2018</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>2360</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="16"/>
-    </row>
-    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>1677</v>
-      </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="2" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>2361</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="16"/>
-    </row>
-    <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="2" t="s">
-        <v>2020</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>2362</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="16"/>
-    </row>
-    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="2" t="s">
-        <v>2021</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>2363</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="16"/>
-    </row>
-    <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="2" t="s">
-        <v>2022</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>2364</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="16"/>
-    </row>
-    <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>1681</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="2" t="s">
-        <v>2023</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>2365</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="16"/>
-    </row>
-    <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="2" t="s">
-        <v>2024</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>2366</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="16"/>
-    </row>
-    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>1683</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="2" t="s">
-        <v>2025</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>2367</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="16"/>
-    </row>
-    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>1684</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="2" t="s">
-        <v>2026</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>2368</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="16"/>
-    </row>
-    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>1685</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="2" t="s">
-        <v>2027</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>2369</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="16"/>
-    </row>
-    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>1686</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="2" t="s">
-        <v>2028</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>2370</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="16"/>
-    </row>
-    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>1687</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="2" t="s">
-        <v>2029</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>2371</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="16"/>
-    </row>
-    <row r="46" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>1688</v>
-      </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="2" t="s">
-        <v>2030</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>2372</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="16"/>
-    </row>
-    <row r="47" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>1689</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="2" t="s">
-        <v>2031</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>2373</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="16"/>
-    </row>
-    <row r="48" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>1690</v>
-      </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="2" t="s">
-        <v>2032</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>2374</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="16"/>
-    </row>
-    <row r="49" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>1691</v>
-      </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="2" t="s">
-        <v>2033</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>2375</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="16"/>
-    </row>
-    <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>1692</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="2" t="s">
-        <v>2034</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>2376</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="16"/>
-    </row>
-    <row r="51" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>1693</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="2" t="s">
-        <v>2035</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>2377</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="16"/>
-    </row>
-    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>1694</v>
-      </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="2" t="s">
-        <v>2036</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>2378</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="16"/>
-    </row>
-    <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>1695</v>
-      </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="2" t="s">
-        <v>2037</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>2379</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="16"/>
-    </row>
-    <row r="54" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>1696</v>
-      </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="2" t="s">
-        <v>2038</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>2380</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="16"/>
-    </row>
-    <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>1697</v>
-      </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="2" t="s">
-        <v>2039</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>2381</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="16"/>
-    </row>
-    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>1698</v>
-      </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="2" t="s">
-        <v>2040</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>2382</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="16"/>
-    </row>
-    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>1699</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="2" t="s">
-        <v>2041</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>2383</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="16"/>
-    </row>
-    <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>1700</v>
-      </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="2" t="s">
-        <v>2042</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>2384</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="16"/>
-    </row>
-    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>1701</v>
-      </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="2" t="s">
-        <v>2043</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>2385</v>
-      </c>
-      <c r="F59" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="16"/>
-    </row>
-    <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="B60" s="13"/>
-      <c r="C60" s="2" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>2386</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="16"/>
-    </row>
-    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>1703</v>
-      </c>
-      <c r="B61" s="13"/>
-      <c r="C61" s="2" t="s">
-        <v>2045</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>2387</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="16"/>
-    </row>
-    <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>1704</v>
-      </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="2" t="s">
-        <v>2046</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>2388</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="16"/>
-    </row>
-    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>1705</v>
-      </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="2" t="s">
-        <v>2047</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>2389</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="16"/>
-    </row>
-    <row r="64" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>1706</v>
-      </c>
-      <c r="B64" s="13"/>
-      <c r="C64" s="2" t="s">
-        <v>2048</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>2390</v>
-      </c>
-      <c r="F64" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="16"/>
-    </row>
-    <row r="65" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>1707</v>
-      </c>
-      <c r="B65" s="13"/>
-      <c r="C65" s="2" t="s">
-        <v>2049</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>2391</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="16"/>
-    </row>
-    <row r="66" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>1708</v>
-      </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="2" t="s">
-        <v>2050</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>2392</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="16"/>
-    </row>
-    <row r="67" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>1709</v>
-      </c>
-      <c r="B67" s="13"/>
-      <c r="C67" s="2" t="s">
-        <v>2051</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>2393</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="16"/>
-    </row>
-    <row r="68" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>1710</v>
-      </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="2" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>2394</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="16"/>
-    </row>
-    <row r="69" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>1711</v>
-      </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="2" t="s">
-        <v>2053</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>2395</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="16"/>
-    </row>
-    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="B70" s="13"/>
-      <c r="C70" s="2" t="s">
-        <v>2054</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>2396</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="16"/>
-    </row>
-    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>1713</v>
-      </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="2" t="s">
-        <v>2055</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>2397</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="16"/>
-    </row>
-    <row r="72" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="2" t="s">
-        <v>2056</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>2398</v>
-      </c>
-      <c r="F72" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="16"/>
-    </row>
-    <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>1715</v>
-      </c>
-      <c r="B73" s="13"/>
-      <c r="C73" s="2" t="s">
-        <v>2057</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>2399</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="16"/>
-    </row>
-    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>1716</v>
-      </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="2" t="s">
-        <v>2058</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>2400</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="16"/>
-    </row>
-    <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>1717</v>
-      </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="2" t="s">
-        <v>2059</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>2401</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="16"/>
-    </row>
-    <row r="76" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>1718</v>
-      </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="2" t="s">
-        <v>2060</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>2402</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="16"/>
-    </row>
-    <row r="77" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>1719</v>
-      </c>
-      <c r="B77" s="13"/>
-      <c r="C77" s="2" t="s">
-        <v>2061</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>2403</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="16"/>
-    </row>
-    <row r="78" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>1720</v>
-      </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="2" t="s">
-        <v>2062</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>2404</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="16"/>
-    </row>
-    <row r="79" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>1721</v>
-      </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="2" t="s">
-        <v>2063</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>2405</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="16"/>
-    </row>
-    <row r="80" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>1722</v>
-      </c>
-      <c r="B80" s="13"/>
-      <c r="C80" s="2" t="s">
-        <v>2064</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>2406</v>
-      </c>
-      <c r="F80" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="16"/>
-    </row>
-    <row r="81" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="B81" s="13"/>
-      <c r="C81" s="2" t="s">
-        <v>2065</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>2407</v>
-      </c>
-      <c r="F81" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="16"/>
-    </row>
-    <row r="82" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>1724</v>
-      </c>
-      <c r="B82" s="13"/>
-      <c r="C82" s="2" t="s">
-        <v>2066</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>2408</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="16"/>
-    </row>
-    <row r="83" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>1725</v>
-      </c>
-      <c r="B83" s="13"/>
-      <c r="C83" s="2" t="s">
-        <v>2067</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>2409</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="16"/>
-    </row>
-    <row r="84" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>1726</v>
-      </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="2" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>2410</v>
-      </c>
-      <c r="F84" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="16"/>
-    </row>
-    <row r="85" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>1727</v>
-      </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="2" t="s">
-        <v>2069</v>
-      </c>
-      <c r="D85" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>2411</v>
-      </c>
-      <c r="F85" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="16"/>
-    </row>
-    <row r="86" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>1728</v>
-      </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="2" t="s">
-        <v>2070</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>2412</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="16"/>
-    </row>
-    <row r="87" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>1729</v>
-      </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="2" t="s">
-        <v>2071</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>2413</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="16"/>
-    </row>
-    <row r="88" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>1730</v>
-      </c>
-      <c r="B88" s="13"/>
-      <c r="C88" s="2" t="s">
-        <v>2072</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>2414</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="16"/>
-    </row>
-    <row r="89" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>1731</v>
-      </c>
-      <c r="B89" s="13"/>
-      <c r="C89" s="2" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>2415</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="16"/>
-    </row>
-    <row r="90" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>1732</v>
-      </c>
-      <c r="B90" s="13"/>
-      <c r="C90" s="2" t="s">
-        <v>2074</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>2416</v>
-      </c>
-      <c r="F90" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="16"/>
-    </row>
-    <row r="91" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B91" s="13"/>
-      <c r="C91" s="2" t="s">
-        <v>2075</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>2417</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="16"/>
-    </row>
-    <row r="92" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>1734</v>
-      </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="2" t="s">
-        <v>2076</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>2418</v>
-      </c>
-      <c r="F92" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="16"/>
-    </row>
-    <row r="93" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>1735</v>
-      </c>
-      <c r="B93" s="13"/>
-      <c r="C93" s="2" t="s">
-        <v>2077</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>2419</v>
-      </c>
-      <c r="F93" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="16"/>
-    </row>
-    <row r="94" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>1736</v>
-      </c>
-      <c r="B94" s="13"/>
-      <c r="C94" s="2" t="s">
-        <v>2078</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E94" s="13" t="s">
-        <v>2420</v>
-      </c>
-      <c r="F94" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="16"/>
-    </row>
-    <row r="95" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>1737</v>
-      </c>
-      <c r="B95" s="13"/>
-      <c r="C95" s="2" t="s">
-        <v>2079</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>2421</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
-      <c r="I95" s="16"/>
-    </row>
-    <row r="96" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B96" s="13"/>
-      <c r="C96" s="2" t="s">
-        <v>2080</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>2422</v>
-      </c>
-      <c r="F96" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="16"/>
-    </row>
-    <row r="97" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>1739</v>
-      </c>
-      <c r="B97" s="13"/>
-      <c r="C97" s="2" t="s">
-        <v>2081</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>2423</v>
-      </c>
-      <c r="F97" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="16"/>
-    </row>
-    <row r="98" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>1740</v>
-      </c>
-      <c r="B98" s="13"/>
-      <c r="C98" s="2" t="s">
-        <v>2082</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>2424</v>
-      </c>
-      <c r="F98" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="16"/>
-    </row>
-    <row r="99" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>1741</v>
-      </c>
-      <c r="B99" s="13"/>
-      <c r="C99" s="2" t="s">
-        <v>2083</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>2425</v>
-      </c>
-      <c r="F99" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="16"/>
-    </row>
-    <row r="100" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>1742</v>
-      </c>
-      <c r="B100" s="13"/>
-      <c r="C100" s="2" t="s">
-        <v>2084</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>2426</v>
-      </c>
-      <c r="F100" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="16"/>
-    </row>
-    <row r="101" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>1743</v>
-      </c>
-      <c r="B101" s="13"/>
-      <c r="C101" s="2" t="s">
-        <v>2085</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>2427</v>
-      </c>
-      <c r="F101" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="16"/>
-    </row>
-    <row r="102" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>1744</v>
-      </c>
-      <c r="B102" s="13"/>
-      <c r="C102" s="2" t="s">
-        <v>2086</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E102" s="13" t="s">
-        <v>2428</v>
-      </c>
-      <c r="F102" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="16"/>
-    </row>
-    <row r="103" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>1745</v>
-      </c>
-      <c r="B103" s="13"/>
-      <c r="C103" s="2" t="s">
-        <v>2087</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>2429</v>
-      </c>
-      <c r="F103" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="16"/>
-    </row>
-    <row r="104" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>1746</v>
-      </c>
-      <c r="B104" s="13"/>
-      <c r="C104" s="2" t="s">
-        <v>2088</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>2430</v>
-      </c>
-      <c r="F104" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G104" s="13"/>
-      <c r="H104" s="13"/>
-      <c r="I104" s="16"/>
-    </row>
-    <row r="105" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B105" s="13"/>
-      <c r="C105" s="2" t="s">
-        <v>2089</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>2431</v>
-      </c>
-      <c r="F105" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G105" s="13"/>
-      <c r="H105" s="13"/>
-      <c r="I105" s="16"/>
-    </row>
-    <row r="106" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>1748</v>
-      </c>
-      <c r="B106" s="13"/>
-      <c r="C106" s="2" t="s">
-        <v>2090</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>2432</v>
-      </c>
-      <c r="F106" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
-      <c r="I106" s="16"/>
-    </row>
-    <row r="107" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>1749</v>
-      </c>
-      <c r="B107" s="13"/>
-      <c r="C107" s="2" t="s">
-        <v>2091</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>2433</v>
-      </c>
-      <c r="F107" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G107" s="13"/>
-      <c r="H107" s="13"/>
-      <c r="I107" s="16"/>
-    </row>
-    <row r="108" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B108" s="13"/>
-      <c r="C108" s="2" t="s">
-        <v>2092</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E108" s="13" t="s">
-        <v>2434</v>
-      </c>
-      <c r="F108" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="16"/>
-    </row>
-    <row r="109" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>1751</v>
-      </c>
-      <c r="B109" s="13"/>
-      <c r="C109" s="2" t="s">
-        <v>2093</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>2435</v>
-      </c>
-      <c r="F109" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
-      <c r="I109" s="16"/>
-    </row>
-    <row r="110" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>1752</v>
-      </c>
-      <c r="B110" s="13"/>
-      <c r="C110" s="2" t="s">
-        <v>2094</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>2436</v>
-      </c>
-      <c r="F110" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G110" s="13"/>
-      <c r="H110" s="13"/>
-      <c r="I110" s="16"/>
-    </row>
-    <row r="111" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>1753</v>
-      </c>
-      <c r="B111" s="13"/>
-      <c r="C111" s="2" t="s">
-        <v>2095</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>2437</v>
-      </c>
-      <c r="F111" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="16"/>
-    </row>
-    <row r="112" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>1754</v>
-      </c>
-      <c r="B112" s="13"/>
-      <c r="C112" s="2" t="s">
-        <v>2096</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>2438</v>
-      </c>
-      <c r="F112" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
-      <c r="I112" s="16"/>
-    </row>
-    <row r="113" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>1755</v>
-      </c>
-      <c r="B113" s="13"/>
-      <c r="C113" s="2" t="s">
-        <v>2097</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>2439</v>
-      </c>
-      <c r="F113" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="16"/>
-    </row>
-    <row r="114" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>1756</v>
-      </c>
-      <c r="B114" s="13"/>
-      <c r="C114" s="2" t="s">
-        <v>2098</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E114" s="13" t="s">
-        <v>2440</v>
-      </c>
-      <c r="F114" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="16"/>
-    </row>
-    <row r="115" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>1757</v>
-      </c>
-      <c r="B115" s="13"/>
-      <c r="C115" s="2" t="s">
-        <v>2099</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>2441</v>
-      </c>
-      <c r="F115" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G115" s="13"/>
-      <c r="H115" s="13"/>
-      <c r="I115" s="16"/>
-    </row>
-    <row r="116" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>1758</v>
-      </c>
-      <c r="B116" s="13"/>
-      <c r="C116" s="2" t="s">
-        <v>2100</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>2442</v>
-      </c>
-      <c r="F116" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G116" s="13"/>
-      <c r="H116" s="13"/>
-      <c r="I116" s="16"/>
-    </row>
-    <row r="117" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>1759</v>
-      </c>
-      <c r="B117" s="13"/>
-      <c r="C117" s="2" t="s">
-        <v>2101</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F117" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G117" s="13"/>
-      <c r="H117" s="13"/>
-      <c r="I117" s="16"/>
-    </row>
-    <row r="118" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>1760</v>
-      </c>
-      <c r="B118" s="13"/>
-      <c r="C118" s="2" t="s">
-        <v>2102</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>2444</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G118" s="13"/>
-      <c r="H118" s="13"/>
-      <c r="I118" s="16"/>
-    </row>
-    <row r="119" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>1761</v>
-      </c>
-      <c r="B119" s="13"/>
-      <c r="C119" s="2" t="s">
-        <v>2103</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E119" s="13" t="s">
-        <v>2445</v>
-      </c>
-      <c r="F119" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="16"/>
-    </row>
-    <row r="120" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>1762</v>
-      </c>
-      <c r="B120" s="13"/>
-      <c r="C120" s="2" t="s">
-        <v>2104</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F120" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="16"/>
-    </row>
-    <row r="121" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>1763</v>
-      </c>
-      <c r="B121" s="13"/>
-      <c r="C121" s="2" t="s">
-        <v>2105</v>
-      </c>
-      <c r="D121" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>2447</v>
-      </c>
-      <c r="F121" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="16"/>
-    </row>
-    <row r="122" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="B122" s="13"/>
-      <c r="C122" s="2" t="s">
-        <v>2106</v>
-      </c>
-      <c r="D122" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>2448</v>
-      </c>
-      <c r="F122" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="16"/>
-    </row>
-    <row r="123" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
-        <v>1765</v>
-      </c>
-      <c r="B123" s="13"/>
-      <c r="C123" s="2" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D123" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>2449</v>
-      </c>
-      <c r="F123" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G123" s="13"/>
-      <c r="H123" s="13"/>
-      <c r="I123" s="16"/>
-    </row>
-    <row r="124" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
-        <v>1766</v>
-      </c>
-      <c r="B124" s="13"/>
-      <c r="C124" s="2" t="s">
-        <v>2108</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>2450</v>
-      </c>
-      <c r="F124" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="16"/>
-    </row>
-    <row r="125" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
-        <v>1767</v>
-      </c>
-      <c r="B125" s="13"/>
-      <c r="C125" s="2" t="s">
-        <v>2109</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E125" s="13" t="s">
-        <v>2451</v>
-      </c>
-      <c r="F125" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G125" s="13"/>
-      <c r="H125" s="13"/>
-      <c r="I125" s="16"/>
-    </row>
-    <row r="126" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>1768</v>
-      </c>
-      <c r="B126" s="13"/>
-      <c r="C126" s="2" t="s">
-        <v>2110</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>2452</v>
-      </c>
-      <c r="F126" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G126" s="13"/>
-      <c r="H126" s="13"/>
-      <c r="I126" s="16"/>
-    </row>
-    <row r="127" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
-        <v>1769</v>
-      </c>
-      <c r="B127" s="13"/>
-      <c r="C127" s="2" t="s">
-        <v>2111</v>
-      </c>
-      <c r="D127" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E127" s="13" t="s">
-        <v>2453</v>
-      </c>
-      <c r="F127" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G127" s="13"/>
-      <c r="H127" s="13"/>
-      <c r="I127" s="16"/>
-    </row>
-    <row r="128" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
-        <v>1770</v>
-      </c>
-      <c r="B128" s="13"/>
-      <c r="C128" s="2" t="s">
-        <v>2112</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>2454</v>
-      </c>
-      <c r="F128" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G128" s="13"/>
-      <c r="H128" s="13"/>
-      <c r="I128" s="16"/>
-    </row>
-    <row r="129" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
-        <v>1771</v>
-      </c>
-      <c r="B129" s="13"/>
-      <c r="C129" s="2" t="s">
-        <v>2113</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E129" s="13" t="s">
-        <v>2455</v>
-      </c>
-      <c r="F129" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G129" s="13"/>
-      <c r="H129" s="13"/>
-      <c r="I129" s="16"/>
-    </row>
-    <row r="130" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
-        <v>1772</v>
-      </c>
-      <c r="B130" s="13"/>
-      <c r="C130" s="2" t="s">
-        <v>2114</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E130" s="13" t="s">
-        <v>2456</v>
-      </c>
-      <c r="F130" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G130" s="13"/>
-      <c r="H130" s="13"/>
-      <c r="I130" s="16"/>
-    </row>
-    <row r="131" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
-        <v>1773</v>
-      </c>
-      <c r="B131" s="13"/>
-      <c r="C131" s="2" t="s">
-        <v>2115</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E131" s="13" t="s">
-        <v>2457</v>
-      </c>
-      <c r="F131" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G131" s="13"/>
-      <c r="H131" s="13"/>
-      <c r="I131" s="16"/>
-    </row>
-    <row r="132" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
-        <v>1774</v>
-      </c>
-      <c r="B132" s="13"/>
-      <c r="C132" s="2" t="s">
-        <v>2116</v>
-      </c>
-      <c r="D132" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E132" s="13" t="s">
-        <v>2458</v>
-      </c>
-      <c r="F132" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
-      <c r="I132" s="16"/>
-    </row>
-    <row r="133" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
-        <v>1775</v>
-      </c>
-      <c r="B133" s="13"/>
-      <c r="C133" s="2" t="s">
-        <v>2117</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E133" s="13" t="s">
-        <v>2459</v>
-      </c>
-      <c r="F133" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G133" s="13"/>
-      <c r="H133" s="13"/>
-      <c r="I133" s="16"/>
-    </row>
-    <row r="134" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
-        <v>1776</v>
-      </c>
-      <c r="B134" s="13"/>
-      <c r="C134" s="2" t="s">
-        <v>2118</v>
-      </c>
-      <c r="D134" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E134" s="13" t="s">
-        <v>2460</v>
-      </c>
-      <c r="F134" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G134" s="13"/>
-      <c r="H134" s="13"/>
-      <c r="I134" s="16"/>
-    </row>
-    <row r="135" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
-        <v>1777</v>
-      </c>
-      <c r="B135" s="13"/>
-      <c r="C135" s="2" t="s">
-        <v>2119</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E135" s="13" t="s">
-        <v>2461</v>
-      </c>
-      <c r="F135" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G135" s="13"/>
-      <c r="H135" s="13"/>
-      <c r="I135" s="16"/>
-    </row>
-    <row r="136" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A136" s="2" t="s">
-        <v>1778</v>
-      </c>
-      <c r="B136" s="13"/>
-      <c r="C136" s="2" t="s">
-        <v>2120</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E136" s="13" t="s">
-        <v>2462</v>
-      </c>
-      <c r="F136" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G136" s="13"/>
-      <c r="H136" s="13"/>
-      <c r="I136" s="16"/>
-    </row>
-    <row r="137" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B137" s="13"/>
-      <c r="C137" s="2" t="s">
-        <v>2121</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>2463</v>
-      </c>
-      <c r="F137" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G137" s="13"/>
-      <c r="H137" s="13"/>
-      <c r="I137" s="16"/>
-    </row>
-    <row r="138" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="B138" s="13"/>
-      <c r="C138" s="2" t="s">
-        <v>2122</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>2464</v>
-      </c>
-      <c r="F138" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G138" s="13"/>
-      <c r="H138" s="13"/>
-      <c r="I138" s="16"/>
-    </row>
-    <row r="139" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="B139" s="13"/>
-      <c r="C139" s="2" t="s">
-        <v>2123</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E139" s="13" t="s">
-        <v>2465</v>
-      </c>
-      <c r="F139" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G139" s="13"/>
-      <c r="H139" s="13"/>
-      <c r="I139" s="16"/>
-    </row>
-    <row r="140" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
-        <v>1782</v>
-      </c>
-      <c r="B140" s="13"/>
-      <c r="C140" s="2" t="s">
-        <v>2124</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E140" s="13" t="s">
-        <v>2466</v>
-      </c>
-      <c r="F140" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G140" s="13"/>
-      <c r="H140" s="13"/>
-      <c r="I140" s="16"/>
-    </row>
-    <row r="141" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="2" t="s">
-        <v>1783</v>
-      </c>
-      <c r="B141" s="13"/>
-      <c r="C141" s="2" t="s">
-        <v>2125</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E141" s="13" t="s">
-        <v>2467</v>
-      </c>
-      <c r="F141" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G141" s="13"/>
-      <c r="H141" s="13"/>
-      <c r="I141" s="16"/>
-    </row>
-    <row r="142" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A142" s="2" t="s">
-        <v>1784</v>
-      </c>
-      <c r="B142" s="13"/>
-      <c r="C142" s="2" t="s">
-        <v>2126</v>
-      </c>
-      <c r="D142" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E142" s="13" t="s">
-        <v>2468</v>
-      </c>
-      <c r="F142" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G142" s="13"/>
-      <c r="H142" s="13"/>
-      <c r="I142" s="16"/>
-    </row>
-    <row r="143" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
-        <v>1785</v>
-      </c>
-      <c r="B143" s="13"/>
-      <c r="C143" s="2" t="s">
-        <v>2127</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E143" s="13" t="s">
-        <v>2469</v>
-      </c>
-      <c r="F143" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G143" s="13"/>
-      <c r="H143" s="13"/>
-      <c r="I143" s="16"/>
-    </row>
-    <row r="144" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
-        <v>1786</v>
-      </c>
-      <c r="B144" s="13"/>
-      <c r="C144" s="2" t="s">
-        <v>2128</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E144" s="13" t="s">
-        <v>2470</v>
-      </c>
-      <c r="F144" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G144" s="13"/>
-      <c r="H144" s="13"/>
-      <c r="I144" s="16"/>
-    </row>
-    <row r="145" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A145" s="2" t="s">
-        <v>1787</v>
-      </c>
-      <c r="B145" s="13"/>
-      <c r="C145" s="2" t="s">
-        <v>2129</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E145" s="13" t="s">
-        <v>2471</v>
-      </c>
-      <c r="F145" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G145" s="13"/>
-      <c r="H145" s="13"/>
-      <c r="I145" s="16"/>
-    </row>
-    <row r="146" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B146" s="13"/>
-      <c r="C146" s="2" t="s">
-        <v>2130</v>
-      </c>
-      <c r="D146" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E146" s="13" t="s">
-        <v>2472</v>
-      </c>
-      <c r="F146" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G146" s="13"/>
-      <c r="H146" s="13"/>
-      <c r="I146" s="16"/>
-    </row>
-    <row r="147" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B147" s="13"/>
-      <c r="C147" s="2" t="s">
-        <v>2131</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E147" s="13" t="s">
-        <v>2473</v>
-      </c>
-      <c r="F147" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G147" s="13"/>
-      <c r="H147" s="13"/>
-      <c r="I147" s="16"/>
-    </row>
-    <row r="148" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
-        <v>1790</v>
-      </c>
-      <c r="B148" s="13"/>
-      <c r="C148" s="2" t="s">
-        <v>2132</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E148" s="13" t="s">
-        <v>2474</v>
-      </c>
-      <c r="F148" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G148" s="13"/>
-      <c r="H148" s="13"/>
-      <c r="I148" s="16"/>
-    </row>
-    <row r="149" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
-        <v>1791</v>
-      </c>
-      <c r="B149" s="13"/>
-      <c r="C149" s="2" t="s">
-        <v>2133</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E149" s="13" t="s">
-        <v>2475</v>
-      </c>
-      <c r="F149" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G149" s="13"/>
-      <c r="H149" s="13"/>
-      <c r="I149" s="16"/>
-    </row>
-    <row r="150" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>1792</v>
-      </c>
-      <c r="B150" s="13"/>
-      <c r="C150" s="2" t="s">
-        <v>2134</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E150" s="13" t="s">
-        <v>2476</v>
-      </c>
-      <c r="F150" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G150" s="13"/>
-      <c r="H150" s="13"/>
-      <c r="I150" s="16"/>
-    </row>
-    <row r="151" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B151" s="13"/>
-      <c r="C151" s="2" t="s">
-        <v>2135</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E151" s="13" t="s">
-        <v>2477</v>
-      </c>
-      <c r="F151" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G151" s="13"/>
-      <c r="H151" s="13"/>
-      <c r="I151" s="16"/>
-    </row>
-    <row r="152" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
-        <v>1794</v>
-      </c>
-      <c r="B152" s="13"/>
-      <c r="C152" s="2" t="s">
-        <v>2136</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E152" s="13" t="s">
-        <v>2478</v>
-      </c>
-      <c r="F152" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G152" s="13"/>
-      <c r="H152" s="13"/>
-      <c r="I152" s="16"/>
-    </row>
-    <row r="153" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
-        <v>1795</v>
-      </c>
-      <c r="B153" s="13"/>
-      <c r="C153" s="2" t="s">
-        <v>2137</v>
-      </c>
-      <c r="D153" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E153" s="13" t="s">
-        <v>2479</v>
-      </c>
-      <c r="F153" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G153" s="13"/>
-      <c r="H153" s="13"/>
-      <c r="I153" s="16"/>
-    </row>
-    <row r="154" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
-        <v>1796</v>
-      </c>
-      <c r="B154" s="13"/>
-      <c r="C154" s="2" t="s">
-        <v>2138</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E154" s="13" t="s">
-        <v>2480</v>
-      </c>
-      <c r="F154" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G154" s="13"/>
-      <c r="H154" s="13"/>
-      <c r="I154" s="16"/>
-    </row>
-    <row r="155" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
-        <v>1797</v>
-      </c>
-      <c r="B155" s="13"/>
-      <c r="C155" s="2" t="s">
-        <v>2139</v>
-      </c>
-      <c r="D155" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E155" s="13" t="s">
-        <v>2481</v>
-      </c>
-      <c r="F155" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G155" s="13"/>
-      <c r="H155" s="13"/>
-      <c r="I155" s="16"/>
-    </row>
-    <row r="156" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
-        <v>1798</v>
-      </c>
-      <c r="B156" s="13"/>
-      <c r="C156" s="2" t="s">
-        <v>2140</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E156" s="13" t="s">
-        <v>2482</v>
-      </c>
-      <c r="F156" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G156" s="13"/>
-      <c r="H156" s="13"/>
-      <c r="I156" s="16"/>
-    </row>
-    <row r="157" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
-        <v>1799</v>
-      </c>
-      <c r="B157" s="13"/>
-      <c r="C157" s="2" t="s">
-        <v>2141</v>
-      </c>
-      <c r="D157" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E157" s="13" t="s">
-        <v>2483</v>
-      </c>
-      <c r="F157" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G157" s="13"/>
-      <c r="H157" s="13"/>
-      <c r="I157" s="16"/>
-    </row>
-    <row r="158" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
-        <v>1800</v>
-      </c>
-      <c r="B158" s="13"/>
-      <c r="C158" s="2" t="s">
-        <v>2142</v>
-      </c>
-      <c r="D158" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E158" s="13" t="s">
-        <v>2484</v>
-      </c>
-      <c r="F158" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G158" s="13"/>
-      <c r="H158" s="13"/>
-      <c r="I158" s="16"/>
-    </row>
-    <row r="159" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
-        <v>1801</v>
-      </c>
-      <c r="B159" s="13"/>
-      <c r="C159" s="2" t="s">
-        <v>2143</v>
-      </c>
-      <c r="D159" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E159" s="13" t="s">
-        <v>2485</v>
-      </c>
-      <c r="F159" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G159" s="13"/>
-      <c r="H159" s="13"/>
-      <c r="I159" s="16"/>
-    </row>
-    <row r="160" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="2" t="s">
-        <v>1802</v>
-      </c>
-      <c r="B160" s="13"/>
-      <c r="C160" s="2" t="s">
-        <v>2144</v>
-      </c>
-      <c r="D160" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E160" s="13" t="s">
-        <v>2486</v>
-      </c>
-      <c r="F160" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G160" s="13"/>
-      <c r="H160" s="13"/>
-      <c r="I160" s="16"/>
-    </row>
-    <row r="161" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="2" t="s">
-        <v>1803</v>
-      </c>
-      <c r="B161" s="13"/>
-      <c r="C161" s="2" t="s">
-        <v>2145</v>
-      </c>
-      <c r="D161" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E161" s="13" t="s">
-        <v>2487</v>
-      </c>
-      <c r="F161" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G161" s="13"/>
-      <c r="H161" s="13"/>
-      <c r="I161" s="16"/>
-    </row>
-    <row r="162" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A162" s="2" t="s">
-        <v>1804</v>
-      </c>
-      <c r="B162" s="13"/>
-      <c r="C162" s="2" t="s">
-        <v>2146</v>
-      </c>
-      <c r="D162" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E162" s="13" t="s">
-        <v>2488</v>
-      </c>
-      <c r="F162" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G162" s="13"/>
-      <c r="H162" s="13"/>
-      <c r="I162" s="16"/>
-    </row>
-    <row r="163" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
-        <v>1805</v>
-      </c>
-      <c r="B163" s="13"/>
-      <c r="C163" s="2" t="s">
-        <v>2147</v>
-      </c>
-      <c r="D163" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E163" s="13" t="s">
-        <v>2489</v>
-      </c>
-      <c r="F163" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G163" s="13"/>
-      <c r="H163" s="13"/>
-      <c r="I163" s="16"/>
-    </row>
-    <row r="164" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="2" t="s">
-        <v>1806</v>
-      </c>
-      <c r="B164" s="13"/>
-      <c r="C164" s="2" t="s">
-        <v>2148</v>
-      </c>
-      <c r="D164" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E164" s="13" t="s">
-        <v>2490</v>
-      </c>
-      <c r="F164" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G164" s="13"/>
-      <c r="H164" s="13"/>
-      <c r="I164" s="16"/>
-    </row>
-    <row r="165" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A165" s="2" t="s">
-        <v>1807</v>
-      </c>
-      <c r="B165" s="13"/>
-      <c r="C165" s="2" t="s">
-        <v>2149</v>
-      </c>
-      <c r="D165" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E165" s="13" t="s">
-        <v>2491</v>
-      </c>
-      <c r="F165" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G165" s="13"/>
-      <c r="H165" s="13"/>
-      <c r="I165" s="16"/>
-    </row>
-    <row r="166" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="B166" s="13"/>
-      <c r="C166" s="2" t="s">
-        <v>2150</v>
-      </c>
-      <c r="D166" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E166" s="13" t="s">
-        <v>2492</v>
-      </c>
-      <c r="F166" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G166" s="13"/>
-      <c r="H166" s="13"/>
-      <c r="I166" s="16"/>
-    </row>
-    <row r="167" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B167" s="13"/>
-      <c r="C167" s="2" t="s">
-        <v>2151</v>
-      </c>
-      <c r="D167" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E167" s="13" t="s">
-        <v>2493</v>
-      </c>
-      <c r="F167" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G167" s="13"/>
-      <c r="H167" s="13"/>
-      <c r="I167" s="16"/>
-    </row>
-    <row r="168" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
-        <v>1810</v>
-      </c>
-      <c r="B168" s="13"/>
-      <c r="C168" s="2" t="s">
-        <v>2152</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E168" s="13" t="s">
-        <v>2494</v>
-      </c>
-      <c r="F168" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G168" s="13"/>
-      <c r="H168" s="13"/>
-      <c r="I168" s="16"/>
-    </row>
-    <row r="169" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A169" s="2" t="s">
-        <v>1811</v>
-      </c>
-      <c r="B169" s="13"/>
-      <c r="C169" s="2" t="s">
-        <v>2153</v>
-      </c>
-      <c r="D169" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E169" s="13" t="s">
-        <v>2495</v>
-      </c>
-      <c r="F169" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G169" s="13"/>
-      <c r="H169" s="13"/>
-      <c r="I169" s="16"/>
-    </row>
-    <row r="170" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="2" t="s">
-        <v>1812</v>
-      </c>
-      <c r="B170" s="13"/>
-      <c r="C170" s="2" t="s">
-        <v>2154</v>
-      </c>
-      <c r="D170" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E170" s="13" t="s">
-        <v>2496</v>
-      </c>
-      <c r="F170" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G170" s="13"/>
-      <c r="H170" s="13"/>
-      <c r="I170" s="16"/>
-    </row>
-    <row r="171" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A171" s="2" t="s">
-        <v>1813</v>
-      </c>
-      <c r="B171" s="13"/>
-      <c r="C171" s="2" t="s">
-        <v>2155</v>
-      </c>
-      <c r="D171" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E171" s="13" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F171" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G171" s="13"/>
-      <c r="H171" s="13"/>
-      <c r="I171" s="16"/>
-    </row>
-    <row r="172" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A172" s="2" t="s">
-        <v>1814</v>
-      </c>
-      <c r="B172" s="13"/>
-      <c r="C172" s="2" t="s">
-        <v>2156</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E172" s="13" t="s">
-        <v>2498</v>
-      </c>
-      <c r="F172" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G172" s="13"/>
-      <c r="H172" s="13"/>
-      <c r="I172" s="16"/>
-    </row>
-    <row r="173" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A173" s="2" t="s">
-        <v>1815</v>
-      </c>
-      <c r="B173" s="13"/>
-      <c r="C173" s="2" t="s">
-        <v>2157</v>
-      </c>
-      <c r="D173" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E173" s="13" t="s">
-        <v>2499</v>
-      </c>
-      <c r="F173" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G173" s="13"/>
-      <c r="H173" s="13"/>
-      <c r="I173" s="16"/>
-    </row>
-    <row r="174" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A174" s="2" t="s">
-        <v>1816</v>
-      </c>
-      <c r="B174" s="13"/>
-      <c r="C174" s="2" t="s">
-        <v>2158</v>
-      </c>
-      <c r="D174" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E174" s="13" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F174" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G174" s="13"/>
-      <c r="H174" s="13"/>
-      <c r="I174" s="16"/>
-    </row>
-    <row r="175" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A175" s="2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="B175" s="13"/>
-      <c r="C175" s="2" t="s">
-        <v>2159</v>
-      </c>
-      <c r="D175" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E175" s="13" t="s">
-        <v>2501</v>
-      </c>
-      <c r="F175" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G175" s="13"/>
-      <c r="H175" s="13"/>
-      <c r="I175" s="16"/>
-    </row>
-    <row r="176" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B176" s="13"/>
-      <c r="C176" s="2" t="s">
-        <v>2160</v>
-      </c>
-      <c r="D176" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E176" s="13" t="s">
-        <v>2502</v>
-      </c>
-      <c r="F176" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G176" s="13"/>
-      <c r="H176" s="13"/>
-      <c r="I176" s="16"/>
-    </row>
-    <row r="177" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A177" s="2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="B177" s="13"/>
-      <c r="C177" s="2" t="s">
-        <v>2161</v>
-      </c>
-      <c r="D177" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E177" s="13" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F177" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G177" s="13"/>
-      <c r="H177" s="13"/>
-      <c r="I177" s="16"/>
-    </row>
-    <row r="178" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A178" s="2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="B178" s="13"/>
-      <c r="C178" s="2" t="s">
-        <v>2162</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E178" s="13" t="s">
-        <v>2504</v>
-      </c>
-      <c r="F178" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G178" s="13"/>
-      <c r="H178" s="13"/>
-      <c r="I178" s="16"/>
-    </row>
-    <row r="179" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A179" s="2" t="s">
-        <v>1821</v>
-      </c>
-      <c r="B179" s="13"/>
-      <c r="C179" s="2" t="s">
-        <v>2163</v>
-      </c>
-      <c r="D179" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E179" s="13" t="s">
-        <v>2505</v>
-      </c>
-      <c r="F179" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G179" s="13"/>
-      <c r="H179" s="13"/>
-      <c r="I179" s="16"/>
-    </row>
-    <row r="180" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A180" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B180" s="13"/>
-      <c r="C180" s="2" t="s">
-        <v>2164</v>
-      </c>
-      <c r="D180" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E180" s="13" t="s">
-        <v>2506</v>
-      </c>
-      <c r="F180" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G180" s="13"/>
-      <c r="H180" s="13"/>
-      <c r="I180" s="16"/>
-    </row>
-    <row r="181" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
-        <v>1823</v>
-      </c>
-      <c r="B181" s="13"/>
-      <c r="C181" s="2" t="s">
-        <v>2165</v>
-      </c>
-      <c r="D181" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E181" s="13" t="s">
-        <v>2507</v>
-      </c>
-      <c r="F181" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G181" s="13"/>
-      <c r="H181" s="13"/>
-      <c r="I181" s="16"/>
-    </row>
-    <row r="182" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="B182" s="13"/>
-      <c r="C182" s="2" t="s">
-        <v>2166</v>
-      </c>
-      <c r="D182" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E182" s="13" t="s">
-        <v>2508</v>
-      </c>
-      <c r="F182" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G182" s="13"/>
-      <c r="H182" s="13"/>
-      <c r="I182" s="16"/>
-    </row>
-    <row r="183" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="B183" s="13"/>
-      <c r="C183" s="2" t="s">
-        <v>2167</v>
-      </c>
-      <c r="D183" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E183" s="13" t="s">
-        <v>2509</v>
-      </c>
-      <c r="F183" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G183" s="13"/>
-      <c r="H183" s="13"/>
-      <c r="I183" s="16"/>
-    </row>
-    <row r="184" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A184" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B184" s="13"/>
-      <c r="C184" s="2" t="s">
-        <v>2168</v>
-      </c>
-      <c r="D184" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E184" s="13" t="s">
-        <v>2510</v>
-      </c>
-      <c r="F184" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G184" s="13"/>
-      <c r="H184" s="13"/>
-      <c r="I184" s="16"/>
-    </row>
-    <row r="185" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A185" s="2" t="s">
-        <v>1827</v>
-      </c>
-      <c r="B185" s="13"/>
-      <c r="C185" s="2" t="s">
-        <v>2169</v>
-      </c>
-      <c r="D185" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E185" s="13" t="s">
-        <v>2511</v>
-      </c>
-      <c r="F185" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G185" s="13"/>
-      <c r="H185" s="13"/>
-      <c r="I185" s="16"/>
-    </row>
-    <row r="186" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A186" s="2" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B186" s="13"/>
-      <c r="C186" s="2" t="s">
-        <v>2170</v>
-      </c>
-      <c r="D186" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E186" s="13" t="s">
-        <v>2512</v>
-      </c>
-      <c r="F186" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G186" s="13"/>
-      <c r="H186" s="13"/>
-      <c r="I186" s="16"/>
-    </row>
-    <row r="187" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A187" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="B187" s="13"/>
-      <c r="C187" s="2" t="s">
-        <v>2171</v>
-      </c>
-      <c r="D187" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E187" s="13" t="s">
-        <v>2513</v>
-      </c>
-      <c r="F187" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G187" s="13"/>
-      <c r="H187" s="13"/>
-      <c r="I187" s="16"/>
-    </row>
-    <row r="188" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A188" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="B188" s="13"/>
-      <c r="C188" s="2" t="s">
-        <v>2172</v>
-      </c>
-      <c r="D188" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E188" s="13" t="s">
-        <v>2514</v>
-      </c>
-      <c r="F188" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G188" s="13"/>
-      <c r="H188" s="13"/>
-      <c r="I188" s="16"/>
-    </row>
-    <row r="189" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A189" s="2" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B189" s="13"/>
-      <c r="C189" s="2" t="s">
-        <v>2173</v>
-      </c>
-      <c r="D189" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E189" s="13" t="s">
-        <v>2515</v>
-      </c>
-      <c r="F189" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G189" s="13"/>
-      <c r="H189" s="13"/>
-      <c r="I189" s="16"/>
-    </row>
-    <row r="190" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B190" s="13"/>
-      <c r="C190" s="2" t="s">
-        <v>2174</v>
-      </c>
-      <c r="D190" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E190" s="13" t="s">
-        <v>2516</v>
-      </c>
-      <c r="F190" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G190" s="13"/>
-      <c r="H190" s="13"/>
-      <c r="I190" s="16"/>
-    </row>
-    <row r="191" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A191" s="2" t="s">
-        <v>1833</v>
-      </c>
-      <c r="B191" s="13"/>
-      <c r="C191" s="2" t="s">
-        <v>2175</v>
-      </c>
-      <c r="D191" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E191" s="13" t="s">
-        <v>2517</v>
-      </c>
-      <c r="F191" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G191" s="13"/>
-      <c r="H191" s="13"/>
-      <c r="I191" s="16"/>
-    </row>
-    <row r="192" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A192" s="2" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B192" s="13"/>
-      <c r="C192" s="2" t="s">
-        <v>2176</v>
-      </c>
-      <c r="D192" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E192" s="13" t="s">
-        <v>2518</v>
-      </c>
-      <c r="F192" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G192" s="13"/>
-      <c r="H192" s="13"/>
-      <c r="I192" s="16"/>
-    </row>
-    <row r="193" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A193" s="2" t="s">
-        <v>1835</v>
-      </c>
-      <c r="B193" s="13"/>
-      <c r="C193" s="2" t="s">
-        <v>2177</v>
-      </c>
-      <c r="D193" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E193" s="13" t="s">
-        <v>2519</v>
-      </c>
-      <c r="F193" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G193" s="13"/>
-      <c r="H193" s="13"/>
-      <c r="I193" s="16"/>
-    </row>
-    <row r="194" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A194" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B194" s="13"/>
-      <c r="C194" s="2" t="s">
-        <v>2178</v>
-      </c>
-      <c r="D194" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E194" s="13" t="s">
-        <v>2520</v>
-      </c>
-      <c r="F194" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G194" s="13"/>
-      <c r="H194" s="13"/>
-      <c r="I194" s="16"/>
-    </row>
-    <row r="195" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="2" t="s">
-        <v>1837</v>
-      </c>
-      <c r="B195" s="13"/>
-      <c r="C195" s="2" t="s">
-        <v>2179</v>
-      </c>
-      <c r="D195" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E195" s="13" t="s">
-        <v>2521</v>
-      </c>
-      <c r="F195" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G195" s="13"/>
-      <c r="H195" s="13"/>
-      <c r="I195" s="16"/>
-    </row>
-    <row r="196" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A196" s="2" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B196" s="13"/>
-      <c r="C196" s="2" t="s">
-        <v>2180</v>
-      </c>
-      <c r="D196" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E196" s="13" t="s">
-        <v>2522</v>
-      </c>
-      <c r="F196" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G196" s="13"/>
-      <c r="H196" s="13"/>
-      <c r="I196" s="16"/>
-    </row>
-    <row r="197" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A197" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="B197" s="13"/>
-      <c r="C197" s="2" t="s">
-        <v>2181</v>
-      </c>
-      <c r="D197" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E197" s="13" t="s">
-        <v>2523</v>
-      </c>
-      <c r="F197" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G197" s="13"/>
-      <c r="H197" s="13"/>
-      <c r="I197" s="16"/>
-    </row>
-    <row r="198" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A198" s="2" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B198" s="13"/>
-      <c r="C198" s="2" t="s">
-        <v>2182</v>
-      </c>
-      <c r="D198" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E198" s="13" t="s">
-        <v>2524</v>
-      </c>
-      <c r="F198" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G198" s="13"/>
-      <c r="H198" s="13"/>
-      <c r="I198" s="16"/>
-    </row>
-    <row r="199" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A199" s="2" t="s">
-        <v>1841</v>
-      </c>
-      <c r="B199" s="13"/>
-      <c r="C199" s="2" t="s">
-        <v>2183</v>
-      </c>
-      <c r="D199" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E199" s="13" t="s">
-        <v>2525</v>
-      </c>
-      <c r="F199" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G199" s="13"/>
-      <c r="H199" s="13"/>
-      <c r="I199" s="16"/>
-    </row>
-    <row r="200" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A200" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B200" s="13"/>
-      <c r="C200" s="2" t="s">
-        <v>2184</v>
-      </c>
-      <c r="D200" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E200" s="13" t="s">
-        <v>2526</v>
-      </c>
-      <c r="F200" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G200" s="13"/>
-      <c r="H200" s="13"/>
-      <c r="I200" s="16"/>
-    </row>
-    <row r="201" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A201" s="2" t="s">
-        <v>1843</v>
-      </c>
-      <c r="B201" s="13"/>
-      <c r="C201" s="2" t="s">
-        <v>2185</v>
-      </c>
-      <c r="D201" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E201" s="13" t="s">
-        <v>2527</v>
-      </c>
-      <c r="F201" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G201" s="13"/>
-      <c r="H201" s="13"/>
-      <c r="I201" s="16"/>
-    </row>
-    <row r="202" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A202" s="2" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B202" s="13"/>
-      <c r="C202" s="2" t="s">
-        <v>2186</v>
-      </c>
-      <c r="D202" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E202" s="13" t="s">
-        <v>2528</v>
-      </c>
-      <c r="F202" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G202" s="13"/>
-      <c r="H202" s="13"/>
-      <c r="I202" s="16"/>
-    </row>
-    <row r="203" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A203" s="2" t="s">
-        <v>1845</v>
-      </c>
-      <c r="B203" s="13"/>
-      <c r="C203" s="2" t="s">
-        <v>2187</v>
-      </c>
-      <c r="D203" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E203" s="13" t="s">
-        <v>2529</v>
-      </c>
-      <c r="F203" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G203" s="13"/>
-      <c r="H203" s="13"/>
-      <c r="I203" s="16"/>
-    </row>
-    <row r="204" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A204" s="2" t="s">
-        <v>1846</v>
-      </c>
-      <c r="B204" s="13"/>
-      <c r="C204" s="2" t="s">
-        <v>2188</v>
-      </c>
-      <c r="D204" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E204" s="13" t="s">
-        <v>2530</v>
-      </c>
-      <c r="F204" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G204" s="13"/>
-      <c r="H204" s="13"/>
-      <c r="I204" s="16"/>
-    </row>
-    <row r="205" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A205" s="2" t="s">
-        <v>1847</v>
-      </c>
-      <c r="B205" s="13"/>
-      <c r="C205" s="2" t="s">
-        <v>2189</v>
-      </c>
-      <c r="D205" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E205" s="13" t="s">
-        <v>2531</v>
-      </c>
-      <c r="F205" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G205" s="13"/>
-      <c r="H205" s="13"/>
-      <c r="I205" s="16"/>
-    </row>
-    <row r="206" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A206" s="2" t="s">
-        <v>1848</v>
-      </c>
-      <c r="B206" s="13"/>
-      <c r="C206" s="2" t="s">
-        <v>2190</v>
-      </c>
-      <c r="D206" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E206" s="13" t="s">
-        <v>2532</v>
-      </c>
-      <c r="F206" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G206" s="13"/>
-      <c r="H206" s="13"/>
-      <c r="I206" s="16"/>
-    </row>
-    <row r="207" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A207" s="2" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B207" s="13"/>
-      <c r="C207" s="2" t="s">
-        <v>2191</v>
-      </c>
-      <c r="D207" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E207" s="13" t="s">
-        <v>2533</v>
-      </c>
-      <c r="F207" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G207" s="13"/>
-      <c r="H207" s="13"/>
-      <c r="I207" s="16"/>
-    </row>
-    <row r="208" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A208" s="2" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B208" s="13"/>
-      <c r="C208" s="2" t="s">
-        <v>2192</v>
-      </c>
-      <c r="D208" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E208" s="13" t="s">
-        <v>2534</v>
-      </c>
-      <c r="F208" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G208" s="13"/>
-      <c r="H208" s="13"/>
-      <c r="I208" s="16"/>
-    </row>
-    <row r="209" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A209" s="2" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B209" s="13"/>
-      <c r="C209" s="2" t="s">
-        <v>2193</v>
-      </c>
-      <c r="D209" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E209" s="13" t="s">
-        <v>2535</v>
-      </c>
-      <c r="F209" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G209" s="13"/>
-      <c r="H209" s="13"/>
-      <c r="I209" s="16"/>
-    </row>
-    <row r="210" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A210" s="2" t="s">
-        <v>1852</v>
-      </c>
-      <c r="B210" s="13"/>
-      <c r="C210" s="2" t="s">
-        <v>2194</v>
-      </c>
-      <c r="D210" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E210" s="13" t="s">
-        <v>2536</v>
-      </c>
-      <c r="F210" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G210" s="13"/>
-      <c r="H210" s="13"/>
-      <c r="I210" s="16"/>
-    </row>
-    <row r="211" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A211" s="2" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B211" s="13"/>
-      <c r="C211" s="2" t="s">
-        <v>2195</v>
-      </c>
-      <c r="D211" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E211" s="13" t="s">
-        <v>2537</v>
-      </c>
-      <c r="F211" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G211" s="13"/>
-      <c r="H211" s="13"/>
-      <c r="I211" s="16"/>
-    </row>
-    <row r="212" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A212" s="2" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B212" s="13"/>
-      <c r="C212" s="2" t="s">
-        <v>2196</v>
-      </c>
-      <c r="D212" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E212" s="13" t="s">
-        <v>2538</v>
-      </c>
-      <c r="F212" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G212" s="13"/>
-      <c r="H212" s="13"/>
-      <c r="I212" s="16"/>
-    </row>
-    <row r="213" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A213" s="2" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B213" s="13"/>
-      <c r="C213" s="2" t="s">
-        <v>2197</v>
-      </c>
-      <c r="D213" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E213" s="13" t="s">
-        <v>2539</v>
-      </c>
-      <c r="F213" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G213" s="13"/>
-      <c r="H213" s="13"/>
-      <c r="I213" s="16"/>
-    </row>
-    <row r="214" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A214" s="2" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B214" s="13"/>
-      <c r="C214" s="2" t="s">
-        <v>2198</v>
-      </c>
-      <c r="D214" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E214" s="13" t="s">
-        <v>2540</v>
-      </c>
-      <c r="F214" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G214" s="13"/>
-      <c r="H214" s="13"/>
-      <c r="I214" s="16"/>
-    </row>
-    <row r="215" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A215" s="2" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B215" s="13"/>
-      <c r="C215" s="2" t="s">
-        <v>2199</v>
-      </c>
-      <c r="D215" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E215" s="13" t="s">
-        <v>2541</v>
-      </c>
-      <c r="F215" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G215" s="13"/>
-      <c r="H215" s="13"/>
-      <c r="I215" s="16"/>
-    </row>
-    <row r="216" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A216" s="2" t="s">
-        <v>1858</v>
-      </c>
-      <c r="B216" s="13"/>
-      <c r="C216" s="2" t="s">
-        <v>2200</v>
-      </c>
-      <c r="D216" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E216" s="13" t="s">
-        <v>2542</v>
-      </c>
-      <c r="F216" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G216" s="13"/>
-      <c r="H216" s="13"/>
-      <c r="I216" s="16"/>
-    </row>
-    <row r="217" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A217" s="2" t="s">
-        <v>1859</v>
-      </c>
-      <c r="B217" s="13"/>
-      <c r="C217" s="2" t="s">
-        <v>2201</v>
-      </c>
-      <c r="D217" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E217" s="13" t="s">
-        <v>2543</v>
-      </c>
-      <c r="F217" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G217" s="13"/>
-      <c r="H217" s="13"/>
-      <c r="I217" s="16"/>
-    </row>
-    <row r="218" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A218" s="2" t="s">
-        <v>1860</v>
-      </c>
-      <c r="B218" s="13"/>
-      <c r="C218" s="2" t="s">
-        <v>2202</v>
-      </c>
-      <c r="D218" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E218" s="13" t="s">
-        <v>2544</v>
-      </c>
-      <c r="F218" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G218" s="13"/>
-      <c r="H218" s="13"/>
-      <c r="I218" s="16"/>
-    </row>
-    <row r="219" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A219" s="2" t="s">
-        <v>1861</v>
-      </c>
-      <c r="B219" s="13"/>
-      <c r="C219" s="2" t="s">
-        <v>2203</v>
-      </c>
-      <c r="D219" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E219" s="13" t="s">
-        <v>2545</v>
-      </c>
-      <c r="F219" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G219" s="13"/>
-      <c r="H219" s="13"/>
-      <c r="I219" s="16"/>
-    </row>
-    <row r="220" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A220" s="2" t="s">
-        <v>1862</v>
-      </c>
-      <c r="B220" s="13"/>
-      <c r="C220" s="2" t="s">
-        <v>2204</v>
-      </c>
-      <c r="D220" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E220" s="13" t="s">
-        <v>2546</v>
-      </c>
-      <c r="F220" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G220" s="13"/>
-      <c r="H220" s="13"/>
-      <c r="I220" s="16"/>
-    </row>
-    <row r="221" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A221" s="2" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B221" s="13"/>
-      <c r="C221" s="2" t="s">
-        <v>2205</v>
-      </c>
-      <c r="D221" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E221" s="13" t="s">
-        <v>2547</v>
-      </c>
-      <c r="F221" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G221" s="13"/>
-      <c r="H221" s="13"/>
-      <c r="I221" s="16"/>
-    </row>
-    <row r="222" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B222" s="13"/>
-      <c r="C222" s="2" t="s">
-        <v>2206</v>
-      </c>
-      <c r="D222" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E222" s="13" t="s">
-        <v>2548</v>
-      </c>
-      <c r="F222" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G222" s="13"/>
-      <c r="H222" s="13"/>
-      <c r="I222" s="16"/>
-    </row>
-    <row r="223" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A223" s="2" t="s">
-        <v>1865</v>
-      </c>
-      <c r="B223" s="13"/>
-      <c r="C223" s="2" t="s">
-        <v>2207</v>
-      </c>
-      <c r="D223" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E223" s="13" t="s">
-        <v>2549</v>
-      </c>
-      <c r="F223" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G223" s="13"/>
-      <c r="H223" s="13"/>
-      <c r="I223" s="16"/>
-    </row>
-    <row r="224" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A224" s="2" t="s">
-        <v>1866</v>
-      </c>
-      <c r="B224" s="13"/>
-      <c r="C224" s="2" t="s">
-        <v>2208</v>
-      </c>
-      <c r="D224" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E224" s="13" t="s">
-        <v>2550</v>
-      </c>
-      <c r="F224" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G224" s="13"/>
-      <c r="H224" s="13"/>
-      <c r="I224" s="16"/>
-    </row>
-    <row r="225" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A225" s="2" t="s">
-        <v>1867</v>
-      </c>
-      <c r="B225" s="13"/>
-      <c r="C225" s="2" t="s">
-        <v>2209</v>
-      </c>
-      <c r="D225" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E225" s="13" t="s">
-        <v>2551</v>
-      </c>
-      <c r="F225" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G225" s="13"/>
-      <c r="H225" s="13"/>
-      <c r="I225" s="16"/>
-    </row>
-    <row r="226" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="B226" s="13"/>
-      <c r="C226" s="2" t="s">
-        <v>2210</v>
-      </c>
-      <c r="D226" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E226" s="13" t="s">
-        <v>2552</v>
-      </c>
-      <c r="F226" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G226" s="13"/>
-      <c r="H226" s="13"/>
-      <c r="I226" s="16"/>
-    </row>
-    <row r="227" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A227" s="2" t="s">
-        <v>1869</v>
-      </c>
-      <c r="B227" s="13"/>
-      <c r="C227" s="2" t="s">
-        <v>2211</v>
-      </c>
-      <c r="D227" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E227" s="13" t="s">
-        <v>2553</v>
-      </c>
-      <c r="F227" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G227" s="13"/>
-      <c r="H227" s="13"/>
-      <c r="I227" s="16"/>
-    </row>
-    <row r="228" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
-        <v>1870</v>
-      </c>
-      <c r="B228" s="13"/>
-      <c r="C228" s="2" t="s">
-        <v>2212</v>
-      </c>
-      <c r="D228" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E228" s="13" t="s">
-        <v>2554</v>
-      </c>
-      <c r="F228" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G228" s="13"/>
-      <c r="H228" s="13"/>
-      <c r="I228" s="16"/>
-    </row>
-    <row r="229" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A229" s="2" t="s">
-        <v>1871</v>
-      </c>
-      <c r="B229" s="13"/>
-      <c r="C229" s="2" t="s">
-        <v>2213</v>
-      </c>
-      <c r="D229" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E229" s="13" t="s">
-        <v>2555</v>
-      </c>
-      <c r="F229" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G229" s="13"/>
-      <c r="H229" s="13"/>
-      <c r="I229" s="16"/>
-    </row>
-    <row r="230" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
-        <v>1872</v>
-      </c>
-      <c r="B230" s="13"/>
-      <c r="C230" s="2" t="s">
-        <v>2214</v>
-      </c>
-      <c r="D230" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E230" s="13" t="s">
-        <v>2556</v>
-      </c>
-      <c r="F230" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G230" s="13"/>
-      <c r="H230" s="13"/>
-      <c r="I230" s="16"/>
-    </row>
-    <row r="231" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A231" s="2" t="s">
-        <v>1873</v>
-      </c>
-      <c r="B231" s="13"/>
-      <c r="C231" s="2" t="s">
-        <v>2215</v>
-      </c>
-      <c r="D231" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E231" s="13" t="s">
-        <v>2557</v>
-      </c>
-      <c r="F231" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G231" s="13"/>
-      <c r="H231" s="13"/>
-      <c r="I231" s="16"/>
-    </row>
-    <row r="232" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A232" s="2" t="s">
-        <v>1874</v>
-      </c>
-      <c r="B232" s="13"/>
-      <c r="C232" s="2" t="s">
-        <v>2216</v>
-      </c>
-      <c r="D232" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E232" s="13" t="s">
-        <v>2558</v>
-      </c>
-      <c r="F232" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G232" s="13"/>
-      <c r="H232" s="13"/>
-      <c r="I232" s="16"/>
-    </row>
-    <row r="233" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A233" s="2" t="s">
-        <v>1875</v>
-      </c>
-      <c r="B233" s="13"/>
-      <c r="C233" s="2" t="s">
-        <v>2217</v>
-      </c>
-      <c r="D233" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E233" s="13" t="s">
-        <v>2559</v>
-      </c>
-      <c r="F233" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G233" s="13"/>
-      <c r="H233" s="13"/>
-      <c r="I233" s="16"/>
-    </row>
-    <row r="234" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A234" s="2" t="s">
-        <v>1876</v>
-      </c>
-      <c r="B234" s="13"/>
-      <c r="C234" s="2" t="s">
-        <v>2218</v>
-      </c>
-      <c r="D234" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E234" s="13" t="s">
-        <v>2560</v>
-      </c>
-      <c r="F234" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G234" s="13"/>
-      <c r="H234" s="13"/>
-      <c r="I234" s="16"/>
-    </row>
-    <row r="235" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A235" s="2" t="s">
-        <v>1877</v>
-      </c>
-      <c r="B235" s="13"/>
-      <c r="C235" s="2" t="s">
-        <v>2219</v>
-      </c>
-      <c r="D235" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E235" s="13" t="s">
-        <v>2561</v>
-      </c>
-      <c r="F235" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G235" s="13"/>
-      <c r="H235" s="13"/>
-      <c r="I235" s="16"/>
-    </row>
-    <row r="236" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A236" s="2" t="s">
-        <v>1878</v>
-      </c>
-      <c r="B236" s="13"/>
-      <c r="C236" s="2" t="s">
-        <v>2220</v>
-      </c>
-      <c r="D236" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E236" s="13" t="s">
-        <v>2562</v>
-      </c>
-      <c r="F236" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G236" s="13"/>
-      <c r="H236" s="13"/>
-      <c r="I236" s="16"/>
-    </row>
-    <row r="237" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A237" s="2" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B237" s="13"/>
-      <c r="C237" s="2" t="s">
-        <v>2221</v>
-      </c>
-      <c r="D237" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E237" s="13" t="s">
-        <v>2563</v>
-      </c>
-      <c r="F237" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G237" s="13"/>
-      <c r="H237" s="13"/>
-      <c r="I237" s="16"/>
-    </row>
-    <row r="238" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A238" s="2" t="s">
-        <v>1880</v>
-      </c>
-      <c r="B238" s="13"/>
-      <c r="C238" s="2" t="s">
-        <v>2222</v>
-      </c>
-      <c r="D238" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E238" s="13" t="s">
-        <v>2564</v>
-      </c>
-      <c r="F238" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G238" s="13"/>
-      <c r="H238" s="13"/>
-      <c r="I238" s="16"/>
-    </row>
-    <row r="239" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A239" s="2" t="s">
-        <v>1881</v>
-      </c>
-      <c r="B239" s="13"/>
-      <c r="C239" s="2" t="s">
-        <v>2223</v>
-      </c>
-      <c r="D239" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E239" s="13" t="s">
-        <v>2565</v>
-      </c>
-      <c r="F239" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G239" s="13"/>
-      <c r="H239" s="13"/>
-      <c r="I239" s="16"/>
-    </row>
-    <row r="240" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A240" s="2" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B240" s="13"/>
-      <c r="C240" s="2" t="s">
-        <v>2224</v>
-      </c>
-      <c r="D240" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E240" s="13" t="s">
-        <v>2566</v>
-      </c>
-      <c r="F240" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G240" s="13"/>
-      <c r="H240" s="13"/>
-      <c r="I240" s="16"/>
-    </row>
-    <row r="241" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A241" s="2" t="s">
-        <v>1883</v>
-      </c>
-      <c r="B241" s="13"/>
-      <c r="C241" s="2" t="s">
-        <v>2225</v>
-      </c>
-      <c r="D241" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E241" s="13" t="s">
-        <v>2567</v>
-      </c>
-      <c r="F241" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G241" s="13"/>
-      <c r="H241" s="13"/>
-      <c r="I241" s="16"/>
-    </row>
-    <row r="242" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A242" s="2" t="s">
-        <v>1884</v>
-      </c>
-      <c r="B242" s="13"/>
-      <c r="C242" s="2" t="s">
-        <v>2226</v>
-      </c>
-      <c r="D242" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E242" s="13" t="s">
-        <v>2568</v>
-      </c>
-      <c r="F242" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G242" s="13"/>
-      <c r="H242" s="13"/>
-      <c r="I242" s="16"/>
-    </row>
-    <row r="243" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A243" s="2" t="s">
-        <v>1885</v>
-      </c>
-      <c r="B243" s="13"/>
-      <c r="C243" s="2" t="s">
-        <v>2227</v>
-      </c>
-      <c r="D243" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E243" s="13" t="s">
-        <v>2569</v>
-      </c>
-      <c r="F243" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G243" s="13"/>
-      <c r="H243" s="13"/>
-      <c r="I243" s="16"/>
-    </row>
-    <row r="244" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A244" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="B244" s="13"/>
-      <c r="C244" s="2" t="s">
-        <v>2228</v>
-      </c>
-      <c r="D244" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E244" s="13" t="s">
-        <v>2570</v>
-      </c>
-      <c r="F244" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G244" s="13"/>
-      <c r="H244" s="13"/>
-      <c r="I244" s="16"/>
-    </row>
-    <row r="245" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A245" s="2" t="s">
-        <v>1887</v>
-      </c>
-      <c r="B245" s="13"/>
-      <c r="C245" s="2" t="s">
-        <v>2229</v>
-      </c>
-      <c r="D245" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E245" s="13" t="s">
-        <v>2571</v>
-      </c>
-      <c r="F245" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G245" s="13"/>
-      <c r="H245" s="13"/>
-      <c r="I245" s="16"/>
-    </row>
-    <row r="246" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A246" s="2" t="s">
-        <v>1888</v>
-      </c>
-      <c r="B246" s="13"/>
-      <c r="C246" s="2" t="s">
-        <v>2230</v>
-      </c>
-      <c r="D246" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E246" s="13" t="s">
-        <v>2572</v>
-      </c>
-      <c r="F246" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G246" s="13"/>
-      <c r="H246" s="13"/>
-      <c r="I246" s="16"/>
-    </row>
-    <row r="247" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A247" s="2" t="s">
-        <v>1889</v>
-      </c>
-      <c r="B247" s="13"/>
-      <c r="C247" s="2" t="s">
-        <v>2231</v>
-      </c>
-      <c r="D247" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E247" s="13" t="s">
-        <v>2573</v>
-      </c>
-      <c r="F247" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G247" s="13"/>
-      <c r="H247" s="13"/>
-      <c r="I247" s="16"/>
-    </row>
-    <row r="248" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A248" s="2" t="s">
-        <v>1890</v>
-      </c>
-      <c r="B248" s="13"/>
-      <c r="C248" s="2" t="s">
-        <v>2232</v>
-      </c>
-      <c r="D248" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E248" s="13" t="s">
-        <v>2574</v>
-      </c>
-      <c r="F248" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G248" s="13"/>
-      <c r="H248" s="13"/>
-      <c r="I248" s="16"/>
-    </row>
-    <row r="249" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A249" s="2" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B249" s="13"/>
-      <c r="C249" s="2" t="s">
-        <v>2233</v>
-      </c>
-      <c r="D249" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E249" s="13" t="s">
-        <v>2575</v>
-      </c>
-      <c r="F249" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G249" s="13"/>
-      <c r="H249" s="13"/>
-      <c r="I249" s="16"/>
-    </row>
-    <row r="250" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A250" s="2" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B250" s="13"/>
-      <c r="C250" s="2" t="s">
-        <v>2234</v>
-      </c>
-      <c r="D250" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E250" s="13" t="s">
-        <v>2576</v>
-      </c>
-      <c r="F250" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G250" s="13"/>
-      <c r="H250" s="13"/>
-      <c r="I250" s="16"/>
-    </row>
-    <row r="251" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A251" s="2" t="s">
-        <v>1893</v>
-      </c>
-      <c r="B251" s="13"/>
-      <c r="C251" s="2" t="s">
-        <v>2235</v>
-      </c>
-      <c r="D251" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E251" s="13" t="s">
-        <v>2577</v>
-      </c>
-      <c r="F251" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G251" s="13"/>
-      <c r="H251" s="13"/>
-      <c r="I251" s="16"/>
-    </row>
-    <row r="252" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A252" s="2" t="s">
-        <v>1894</v>
-      </c>
-      <c r="B252" s="13"/>
-      <c r="C252" s="2" t="s">
-        <v>2236</v>
-      </c>
-      <c r="D252" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E252" s="13" t="s">
-        <v>2578</v>
-      </c>
-      <c r="F252" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G252" s="13"/>
-      <c r="H252" s="13"/>
-      <c r="I252" s="16"/>
-    </row>
-    <row r="253" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A253" s="2" t="s">
-        <v>1895</v>
-      </c>
-      <c r="B253" s="13"/>
-      <c r="C253" s="2" t="s">
-        <v>2237</v>
-      </c>
-      <c r="D253" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E253" s="13" t="s">
-        <v>2579</v>
-      </c>
-      <c r="F253" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G253" s="13"/>
-      <c r="H253" s="13"/>
-      <c r="I253" s="16"/>
-    </row>
-    <row r="254" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A254" s="2" t="s">
-        <v>1896</v>
-      </c>
-      <c r="B254" s="13"/>
-      <c r="C254" s="2" t="s">
-        <v>2238</v>
-      </c>
-      <c r="D254" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E254" s="13" t="s">
-        <v>2580</v>
-      </c>
-      <c r="F254" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G254" s="13"/>
-      <c r="H254" s="13"/>
-      <c r="I254" s="16"/>
-    </row>
-    <row r="255" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A255" s="2" t="s">
-        <v>1897</v>
-      </c>
-      <c r="B255" s="13"/>
-      <c r="C255" s="2" t="s">
-        <v>2239</v>
-      </c>
-      <c r="D255" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E255" s="13" t="s">
-        <v>2581</v>
-      </c>
-      <c r="F255" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G255" s="13"/>
-      <c r="H255" s="13"/>
-      <c r="I255" s="16"/>
-    </row>
-    <row r="256" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A256" s="2" t="s">
-        <v>1898</v>
-      </c>
-      <c r="B256" s="13"/>
-      <c r="C256" s="2" t="s">
-        <v>2240</v>
-      </c>
-      <c r="D256" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E256" s="13" t="s">
-        <v>2582</v>
-      </c>
-      <c r="F256" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G256" s="13"/>
-      <c r="H256" s="13"/>
-      <c r="I256" s="16"/>
-    </row>
-    <row r="257" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A257" s="2" t="s">
-        <v>1899</v>
-      </c>
-      <c r="B257" s="13"/>
-      <c r="C257" s="2" t="s">
-        <v>2241</v>
-      </c>
-      <c r="D257" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E257" s="13" t="s">
-        <v>2583</v>
-      </c>
-      <c r="F257" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G257" s="13"/>
-      <c r="H257" s="13"/>
-      <c r="I257" s="16"/>
-    </row>
-    <row r="258" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A258" s="2" t="s">
-        <v>1900</v>
-      </c>
-      <c r="B258" s="13"/>
-      <c r="C258" s="2" t="s">
-        <v>2242</v>
-      </c>
-      <c r="D258" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E258" s="13" t="s">
-        <v>2584</v>
-      </c>
-      <c r="F258" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G258" s="13"/>
-      <c r="H258" s="13"/>
-      <c r="I258" s="16"/>
-    </row>
-    <row r="259" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A259" s="2" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B259" s="13"/>
-      <c r="C259" s="2" t="s">
-        <v>2243</v>
-      </c>
-      <c r="D259" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E259" s="13" t="s">
-        <v>2585</v>
-      </c>
-      <c r="F259" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G259" s="13"/>
-      <c r="H259" s="13"/>
-      <c r="I259" s="16"/>
-    </row>
-    <row r="260" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A260" s="2" t="s">
-        <v>1902</v>
-      </c>
-      <c r="B260" s="13"/>
-      <c r="C260" s="2" t="s">
-        <v>2244</v>
-      </c>
-      <c r="D260" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E260" s="13" t="s">
-        <v>2586</v>
-      </c>
-      <c r="F260" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G260" s="13"/>
-      <c r="H260" s="13"/>
-      <c r="I260" s="16"/>
-    </row>
-    <row r="261" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A261" s="2" t="s">
-        <v>1903</v>
-      </c>
-      <c r="B261" s="13"/>
-      <c r="C261" s="2" t="s">
-        <v>2245</v>
-      </c>
-      <c r="D261" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E261" s="13" t="s">
-        <v>2587</v>
-      </c>
-      <c r="F261" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G261" s="13"/>
-      <c r="H261" s="13"/>
-      <c r="I261" s="16"/>
-    </row>
-    <row r="262" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A262" s="2" t="s">
-        <v>1904</v>
-      </c>
-      <c r="B262" s="13"/>
-      <c r="C262" s="2" t="s">
-        <v>2246</v>
-      </c>
-      <c r="D262" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E262" s="13" t="s">
-        <v>2588</v>
-      </c>
-      <c r="F262" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G262" s="13"/>
-      <c r="H262" s="13"/>
-      <c r="I262" s="16"/>
-    </row>
-    <row r="263" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A263" s="2" t="s">
-        <v>1905</v>
-      </c>
-      <c r="B263" s="13"/>
-      <c r="C263" s="2" t="s">
-        <v>2247</v>
-      </c>
-      <c r="D263" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E263" s="13" t="s">
-        <v>2589</v>
-      </c>
-      <c r="F263" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G263" s="13"/>
-      <c r="H263" s="13"/>
-      <c r="I263" s="16"/>
-    </row>
-    <row r="264" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A264" s="2" t="s">
-        <v>1906</v>
-      </c>
-      <c r="B264" s="13"/>
-      <c r="C264" s="2" t="s">
-        <v>2248</v>
-      </c>
-      <c r="D264" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E264" s="13" t="s">
-        <v>2590</v>
-      </c>
-      <c r="F264" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G264" s="13"/>
-      <c r="H264" s="13"/>
-      <c r="I264" s="16"/>
-    </row>
-    <row r="265" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A265" s="2" t="s">
-        <v>1907</v>
-      </c>
-      <c r="B265" s="13"/>
-      <c r="C265" s="2" t="s">
-        <v>2249</v>
-      </c>
-      <c r="D265" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E265" s="13" t="s">
-        <v>2591</v>
-      </c>
-      <c r="F265" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G265" s="13"/>
-      <c r="H265" s="13"/>
-      <c r="I265" s="16"/>
-    </row>
-    <row r="266" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A266" s="2" t="s">
-        <v>1908</v>
-      </c>
-      <c r="B266" s="13"/>
-      <c r="C266" s="2" t="s">
-        <v>2250</v>
-      </c>
-      <c r="D266" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E266" s="13" t="s">
-        <v>2592</v>
-      </c>
-      <c r="F266" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G266" s="13"/>
-      <c r="H266" s="13"/>
-      <c r="I266" s="16"/>
-    </row>
-    <row r="267" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A267" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="B267" s="13"/>
-      <c r="C267" s="2" t="s">
-        <v>2251</v>
-      </c>
-      <c r="D267" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E267" s="13" t="s">
-        <v>2593</v>
-      </c>
-      <c r="F267" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G267" s="13"/>
-      <c r="H267" s="13"/>
-      <c r="I267" s="16"/>
-    </row>
-    <row r="268" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A268" s="2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="B268" s="13"/>
-      <c r="C268" s="2" t="s">
-        <v>2252</v>
-      </c>
-      <c r="D268" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E268" s="13" t="s">
-        <v>2594</v>
-      </c>
-      <c r="F268" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G268" s="13"/>
-      <c r="H268" s="13"/>
-      <c r="I268" s="16"/>
-    </row>
-    <row r="269" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A269" s="2" t="s">
-        <v>1911</v>
-      </c>
-      <c r="B269" s="13"/>
-      <c r="C269" s="2" t="s">
-        <v>2253</v>
-      </c>
-      <c r="D269" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E269" s="13" t="s">
-        <v>2595</v>
-      </c>
-      <c r="F269" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G269" s="13"/>
-      <c r="H269" s="13"/>
-      <c r="I269" s="16"/>
-    </row>
-    <row r="270" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A270" s="2" t="s">
-        <v>1912</v>
-      </c>
-      <c r="B270" s="13"/>
-      <c r="C270" s="2" t="s">
-        <v>2254</v>
-      </c>
-      <c r="D270" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E270" s="13" t="s">
-        <v>2596</v>
-      </c>
-      <c r="F270" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G270" s="13"/>
-      <c r="H270" s="13"/>
-      <c r="I270" s="16"/>
-    </row>
-    <row r="271" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A271" s="2" t="s">
-        <v>1913</v>
-      </c>
-      <c r="B271" s="13"/>
-      <c r="C271" s="2" t="s">
-        <v>2255</v>
-      </c>
-      <c r="D271" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E271" s="13" t="s">
-        <v>2597</v>
-      </c>
-      <c r="F271" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G271" s="13"/>
-      <c r="H271" s="13"/>
-      <c r="I271" s="16"/>
-    </row>
-    <row r="272" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A272" s="2" t="s">
-        <v>1914</v>
-      </c>
-      <c r="B272" s="13"/>
-      <c r="C272" s="2" t="s">
-        <v>2256</v>
-      </c>
-      <c r="D272" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E272" s="13" t="s">
-        <v>2598</v>
-      </c>
-      <c r="F272" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G272" s="13"/>
-      <c r="H272" s="13"/>
-      <c r="I272" s="16"/>
-    </row>
-    <row r="273" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A273" s="2" t="s">
-        <v>1915</v>
-      </c>
-      <c r="B273" s="13"/>
-      <c r="C273" s="2" t="s">
-        <v>2257</v>
-      </c>
-      <c r="D273" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E273" s="13" t="s">
-        <v>2599</v>
-      </c>
-      <c r="F273" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G273" s="13"/>
-      <c r="H273" s="13"/>
-      <c r="I273" s="16"/>
-    </row>
-    <row r="274" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A274" s="2" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B274" s="13"/>
-      <c r="C274" s="2" t="s">
-        <v>2258</v>
-      </c>
-      <c r="D274" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E274" s="13" t="s">
-        <v>2600</v>
-      </c>
-      <c r="F274" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G274" s="13"/>
-      <c r="H274" s="13"/>
-      <c r="I274" s="16"/>
-    </row>
-    <row r="275" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A275" s="2" t="s">
-        <v>1917</v>
-      </c>
-      <c r="B275" s="13"/>
-      <c r="C275" s="2" t="s">
-        <v>2259</v>
-      </c>
-      <c r="D275" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E275" s="13" t="s">
-        <v>2601</v>
-      </c>
-      <c r="F275" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G275" s="13"/>
-      <c r="H275" s="13"/>
-      <c r="I275" s="16"/>
-    </row>
-    <row r="276" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A276" s="2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B276" s="13"/>
-      <c r="C276" s="2" t="s">
-        <v>2260</v>
-      </c>
-      <c r="D276" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E276" s="13" t="s">
-        <v>2602</v>
-      </c>
-      <c r="F276" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G276" s="13"/>
-      <c r="H276" s="13"/>
-      <c r="I276" s="16"/>
-    </row>
-    <row r="277" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A277" s="2" t="s">
-        <v>1919</v>
-      </c>
-      <c r="B277" s="13"/>
-      <c r="C277" s="2" t="s">
-        <v>2261</v>
-      </c>
-      <c r="D277" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E277" s="13" t="s">
-        <v>2603</v>
-      </c>
-      <c r="F277" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G277" s="13"/>
-      <c r="H277" s="13"/>
-      <c r="I277" s="16"/>
-    </row>
-    <row r="278" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A278" s="2" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B278" s="13"/>
-      <c r="C278" s="2" t="s">
-        <v>2262</v>
-      </c>
-      <c r="D278" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E278" s="13" t="s">
-        <v>2604</v>
-      </c>
-      <c r="F278" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G278" s="13"/>
-      <c r="H278" s="13"/>
-      <c r="I278" s="16"/>
-    </row>
-    <row r="279" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A279" s="2" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B279" s="13"/>
-      <c r="C279" s="2" t="s">
-        <v>2263</v>
-      </c>
-      <c r="D279" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E279" s="13" t="s">
-        <v>2605</v>
-      </c>
-      <c r="F279" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G279" s="13"/>
-      <c r="H279" s="13"/>
-      <c r="I279" s="16"/>
-    </row>
-    <row r="280" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A280" s="2" t="s">
-        <v>1922</v>
-      </c>
-      <c r="B280" s="13"/>
-      <c r="C280" s="2" t="s">
-        <v>2264</v>
-      </c>
-      <c r="D280" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E280" s="13" t="s">
-        <v>2606</v>
-      </c>
-      <c r="F280" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G280" s="13"/>
-      <c r="H280" s="13"/>
-      <c r="I280" s="16"/>
-    </row>
-    <row r="281" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A281" s="2" t="s">
-        <v>1923</v>
-      </c>
-      <c r="B281" s="13"/>
-      <c r="C281" s="2" t="s">
-        <v>2265</v>
-      </c>
-      <c r="D281" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E281" s="13" t="s">
-        <v>2607</v>
-      </c>
-      <c r="F281" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G281" s="13"/>
-      <c r="H281" s="13"/>
-      <c r="I281" s="16"/>
-    </row>
-    <row r="282" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A282" s="2" t="s">
-        <v>1924</v>
-      </c>
-      <c r="B282" s="13"/>
-      <c r="C282" s="2" t="s">
-        <v>2266</v>
-      </c>
-      <c r="D282" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E282" s="13" t="s">
-        <v>2608</v>
-      </c>
-      <c r="F282" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G282" s="13"/>
-      <c r="H282" s="13"/>
-      <c r="I282" s="16"/>
-    </row>
-    <row r="283" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A283" s="2" t="s">
-        <v>1925</v>
-      </c>
-      <c r="B283" s="13"/>
-      <c r="C283" s="2" t="s">
-        <v>2267</v>
-      </c>
-      <c r="D283" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E283" s="13" t="s">
-        <v>2609</v>
-      </c>
-      <c r="F283" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G283" s="13"/>
-      <c r="H283" s="13"/>
-      <c r="I283" s="16"/>
-    </row>
-    <row r="284" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A284" s="2" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B284" s="13"/>
-      <c r="C284" s="2" t="s">
-        <v>2268</v>
-      </c>
-      <c r="D284" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E284" s="13" t="s">
-        <v>2610</v>
-      </c>
-      <c r="F284" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G284" s="13"/>
-      <c r="H284" s="13"/>
-      <c r="I284" s="16"/>
-    </row>
-    <row r="285" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A285" s="2" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B285" s="13"/>
-      <c r="C285" s="2" t="s">
-        <v>2269</v>
-      </c>
-      <c r="D285" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E285" s="13" t="s">
-        <v>2611</v>
-      </c>
-      <c r="F285" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G285" s="13"/>
-      <c r="H285" s="13"/>
-      <c r="I285" s="16"/>
-    </row>
-    <row r="286" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A286" s="2" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B286" s="13"/>
-      <c r="C286" s="2" t="s">
-        <v>2270</v>
-      </c>
-      <c r="D286" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E286" s="13" t="s">
-        <v>2612</v>
-      </c>
-      <c r="F286" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G286" s="13"/>
-      <c r="H286" s="13"/>
-      <c r="I286" s="16"/>
-    </row>
-    <row r="287" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A287" s="2" t="s">
-        <v>1929</v>
-      </c>
-      <c r="B287" s="13"/>
-      <c r="C287" s="2" t="s">
-        <v>2271</v>
-      </c>
-      <c r="D287" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E287" s="13" t="s">
-        <v>2613</v>
-      </c>
-      <c r="F287" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G287" s="13"/>
-      <c r="H287" s="13"/>
-      <c r="I287" s="16"/>
-    </row>
-    <row r="288" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A288" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B288" s="13"/>
-      <c r="C288" s="2" t="s">
-        <v>2272</v>
-      </c>
-      <c r="D288" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E288" s="13" t="s">
-        <v>2614</v>
-      </c>
-      <c r="F288" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G288" s="13"/>
-      <c r="H288" s="13"/>
-      <c r="I288" s="16"/>
-    </row>
-    <row r="289" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A289" s="2" t="s">
-        <v>1931</v>
-      </c>
-      <c r="B289" s="13"/>
-      <c r="C289" s="2" t="s">
-        <v>2273</v>
-      </c>
-      <c r="D289" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E289" s="13" t="s">
-        <v>2615</v>
-      </c>
-      <c r="F289" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G289" s="13"/>
-      <c r="H289" s="13"/>
-      <c r="I289" s="16"/>
-    </row>
-    <row r="290" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A290" s="2" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B290" s="13"/>
-      <c r="C290" s="2" t="s">
-        <v>2274</v>
-      </c>
-      <c r="D290" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E290" s="13" t="s">
-        <v>2616</v>
-      </c>
-      <c r="F290" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G290" s="13"/>
-      <c r="H290" s="13"/>
-      <c r="I290" s="16"/>
-    </row>
-    <row r="291" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A291" s="2" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B291" s="13"/>
-      <c r="C291" s="2" t="s">
-        <v>2275</v>
-      </c>
-      <c r="D291" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E291" s="13" t="s">
-        <v>2617</v>
-      </c>
-      <c r="F291" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G291" s="13"/>
-      <c r="H291" s="13"/>
-      <c r="I291" s="16"/>
-    </row>
-    <row r="292" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A292" s="2" t="s">
-        <v>1934</v>
-      </c>
-      <c r="B292" s="13"/>
-      <c r="C292" s="2" t="s">
-        <v>2276</v>
-      </c>
-      <c r="D292" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E292" s="13" t="s">
-        <v>2618</v>
-      </c>
-      <c r="F292" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G292" s="13"/>
-      <c r="H292" s="13"/>
-      <c r="I292" s="16"/>
-    </row>
-    <row r="293" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A293" s="2" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B293" s="13"/>
-      <c r="C293" s="2" t="s">
-        <v>2277</v>
-      </c>
-      <c r="D293" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E293" s="13" t="s">
-        <v>2619</v>
-      </c>
-      <c r="F293" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G293" s="13"/>
-      <c r="H293" s="13"/>
-      <c r="I293" s="16"/>
-    </row>
-    <row r="294" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A294" s="2" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B294" s="13"/>
-      <c r="C294" s="2" t="s">
-        <v>2278</v>
-      </c>
-      <c r="D294" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E294" s="13" t="s">
-        <v>2620</v>
-      </c>
-      <c r="F294" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G294" s="13"/>
-      <c r="H294" s="13"/>
-      <c r="I294" s="16"/>
-    </row>
-    <row r="295" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A295" s="2" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B295" s="13"/>
-      <c r="C295" s="2" t="s">
-        <v>2279</v>
-      </c>
-      <c r="D295" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E295" s="13" t="s">
-        <v>2621</v>
-      </c>
-      <c r="F295" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G295" s="13"/>
-      <c r="H295" s="13"/>
-      <c r="I295" s="16"/>
-    </row>
-    <row r="296" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A296" s="2" t="s">
-        <v>1938</v>
-      </c>
-      <c r="B296" s="13"/>
-      <c r="C296" s="2" t="s">
-        <v>2280</v>
-      </c>
-      <c r="D296" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E296" s="13" t="s">
-        <v>2622</v>
-      </c>
-      <c r="F296" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G296" s="13"/>
-      <c r="H296" s="13"/>
-      <c r="I296" s="16"/>
-    </row>
-    <row r="297" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A297" s="2" t="s">
-        <v>1939</v>
-      </c>
-      <c r="B297" s="13"/>
-      <c r="C297" s="2" t="s">
-        <v>2281</v>
-      </c>
-      <c r="D297" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E297" s="13" t="s">
-        <v>2623</v>
-      </c>
-      <c r="F297" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G297" s="13"/>
-      <c r="H297" s="13"/>
-      <c r="I297" s="16"/>
-    </row>
-    <row r="298" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A298" s="2" t="s">
-        <v>1940</v>
-      </c>
-      <c r="B298" s="13"/>
-      <c r="C298" s="2" t="s">
-        <v>2282</v>
-      </c>
-      <c r="D298" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E298" s="13" t="s">
-        <v>2624</v>
-      </c>
-      <c r="F298" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G298" s="13"/>
-      <c r="H298" s="13"/>
-      <c r="I298" s="16"/>
-    </row>
-    <row r="299" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A299" s="2" t="s">
-        <v>1941</v>
-      </c>
-      <c r="B299" s="13"/>
-      <c r="C299" s="2" t="s">
-        <v>2283</v>
-      </c>
-      <c r="D299" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E299" s="13" t="s">
-        <v>2625</v>
-      </c>
-      <c r="F299" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G299" s="13"/>
-      <c r="H299" s="13"/>
-      <c r="I299" s="16"/>
-    </row>
-    <row r="300" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A300" s="2" t="s">
-        <v>1942</v>
-      </c>
-      <c r="B300" s="13"/>
-      <c r="C300" s="2" t="s">
-        <v>2284</v>
-      </c>
-      <c r="D300" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E300" s="13" t="s">
-        <v>2626</v>
-      </c>
-      <c r="F300" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G300" s="13"/>
-      <c r="H300" s="13"/>
-      <c r="I300" s="16"/>
-    </row>
-    <row r="301" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A301" s="2" t="s">
-        <v>1943</v>
-      </c>
-      <c r="B301" s="13"/>
-      <c r="C301" s="2" t="s">
-        <v>2285</v>
-      </c>
-      <c r="D301" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E301" s="13" t="s">
-        <v>2627</v>
-      </c>
-      <c r="F301" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G301" s="13"/>
-      <c r="H301" s="13"/>
-      <c r="I301" s="16"/>
-    </row>
-    <row r="302" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A302" s="2" t="s">
-        <v>1944</v>
-      </c>
-      <c r="B302" s="13"/>
-      <c r="C302" s="2" t="s">
-        <v>2286</v>
-      </c>
-      <c r="D302" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E302" s="13" t="s">
-        <v>2628</v>
-      </c>
-      <c r="F302" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G302" s="13"/>
-      <c r="H302" s="13"/>
-      <c r="I302" s="16"/>
-    </row>
-    <row r="303" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A303" s="2" t="s">
-        <v>1945</v>
-      </c>
-      <c r="B303" s="13"/>
-      <c r="C303" s="2" t="s">
-        <v>2287</v>
-      </c>
-      <c r="D303" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E303" s="13" t="s">
-        <v>2629</v>
-      </c>
-      <c r="F303" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G303" s="13"/>
-      <c r="H303" s="13"/>
-      <c r="I303" s="16"/>
-    </row>
-    <row r="304" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A304" s="2" t="s">
-        <v>1946</v>
-      </c>
-      <c r="B304" s="13"/>
-      <c r="C304" s="2" t="s">
-        <v>2288</v>
-      </c>
-      <c r="D304" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E304" s="13" t="s">
-        <v>2630</v>
-      </c>
-      <c r="F304" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G304" s="13"/>
-      <c r="H304" s="13"/>
-      <c r="I304" s="16"/>
-    </row>
-    <row r="305" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A305" s="2" t="s">
-        <v>1947</v>
-      </c>
-      <c r="B305" s="13"/>
-      <c r="C305" s="2" t="s">
-        <v>2289</v>
-      </c>
-      <c r="D305" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E305" s="13" t="s">
-        <v>2631</v>
-      </c>
-      <c r="F305" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G305" s="13"/>
-      <c r="H305" s="13"/>
-      <c r="I305" s="16"/>
-    </row>
-    <row r="306" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A306" s="2" t="s">
-        <v>1948</v>
-      </c>
-      <c r="B306" s="13"/>
-      <c r="C306" s="2" t="s">
-        <v>2290</v>
-      </c>
-      <c r="D306" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E306" s="13" t="s">
-        <v>2632</v>
-      </c>
-      <c r="F306" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G306" s="13"/>
-      <c r="H306" s="13"/>
-      <c r="I306" s="16"/>
-    </row>
-    <row r="307" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A307" s="2" t="s">
-        <v>1949</v>
-      </c>
-      <c r="B307" s="13"/>
-      <c r="C307" s="2" t="s">
-        <v>2291</v>
-      </c>
-      <c r="D307" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E307" s="13" t="s">
-        <v>2633</v>
-      </c>
-      <c r="F307" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G307" s="13"/>
-      <c r="H307" s="13"/>
-      <c r="I307" s="16"/>
-    </row>
-    <row r="308" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A308" s="2" t="s">
-        <v>1950</v>
-      </c>
-      <c r="B308" s="13"/>
-      <c r="C308" s="2" t="s">
-        <v>2292</v>
-      </c>
-      <c r="D308" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E308" s="13" t="s">
-        <v>2634</v>
-      </c>
-      <c r="F308" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G308" s="13"/>
-      <c r="H308" s="13"/>
-      <c r="I308" s="16"/>
-    </row>
-    <row r="309" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A309" s="2" t="s">
-        <v>1951</v>
-      </c>
-      <c r="B309" s="13"/>
-      <c r="C309" s="2" t="s">
-        <v>2293</v>
-      </c>
-      <c r="D309" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E309" s="13" t="s">
-        <v>2635</v>
-      </c>
-      <c r="F309" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G309" s="13"/>
-      <c r="H309" s="13"/>
-      <c r="I309" s="16"/>
-    </row>
-    <row r="310" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A310" s="2" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B310" s="13"/>
-      <c r="C310" s="2" t="s">
-        <v>2294</v>
-      </c>
-      <c r="D310" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E310" s="13" t="s">
-        <v>2636</v>
-      </c>
-      <c r="F310" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G310" s="13"/>
-      <c r="H310" s="13"/>
-      <c r="I310" s="16"/>
-    </row>
-    <row r="311" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A311" s="2" t="s">
-        <v>1953</v>
-      </c>
-      <c r="B311" s="13"/>
-      <c r="C311" s="2" t="s">
-        <v>2295</v>
-      </c>
-      <c r="D311" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E311" s="13" t="s">
-        <v>2637</v>
-      </c>
-      <c r="F311" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G311" s="13"/>
-      <c r="H311" s="13"/>
-      <c r="I311" s="16"/>
-    </row>
-    <row r="312" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A312" s="2" t="s">
-        <v>1954</v>
-      </c>
-      <c r="B312" s="13"/>
-      <c r="C312" s="2" t="s">
-        <v>2296</v>
-      </c>
-      <c r="D312" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E312" s="13" t="s">
-        <v>2638</v>
-      </c>
-      <c r="F312" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G312" s="13"/>
-      <c r="H312" s="13"/>
-      <c r="I312" s="16"/>
-    </row>
-    <row r="313" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A313" s="2" t="s">
-        <v>1955</v>
-      </c>
-      <c r="B313" s="13"/>
-      <c r="C313" s="2" t="s">
-        <v>2297</v>
-      </c>
-      <c r="D313" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E313" s="13" t="s">
-        <v>2639</v>
-      </c>
-      <c r="F313" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G313" s="13"/>
-      <c r="H313" s="13"/>
-      <c r="I313" s="16"/>
-    </row>
-    <row r="314" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A314" s="2" t="s">
-        <v>1956</v>
-      </c>
-      <c r="B314" s="13"/>
-      <c r="C314" s="2" t="s">
-        <v>2298</v>
-      </c>
-      <c r="D314" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E314" s="13" t="s">
-        <v>2640</v>
-      </c>
-      <c r="F314" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G314" s="13"/>
-      <c r="H314" s="13"/>
-      <c r="I314" s="16"/>
-    </row>
-    <row r="315" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A315" s="2" t="s">
-        <v>1957</v>
-      </c>
-      <c r="B315" s="13"/>
-      <c r="C315" s="2" t="s">
-        <v>2299</v>
-      </c>
-      <c r="D315" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E315" s="13" t="s">
-        <v>2641</v>
-      </c>
-      <c r="F315" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G315" s="13"/>
-      <c r="H315" s="13"/>
-      <c r="I315" s="16"/>
-    </row>
-    <row r="316" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A316" s="2" t="s">
-        <v>1958</v>
-      </c>
-      <c r="B316" s="13"/>
-      <c r="C316" s="2" t="s">
-        <v>2300</v>
-      </c>
-      <c r="D316" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E316" s="13" t="s">
-        <v>2642</v>
-      </c>
-      <c r="F316" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G316" s="13"/>
-      <c r="H316" s="13"/>
-      <c r="I316" s="16"/>
-    </row>
-    <row r="317" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A317" s="2" t="s">
-        <v>1959</v>
-      </c>
-      <c r="B317" s="13"/>
-      <c r="C317" s="2" t="s">
-        <v>2301</v>
-      </c>
-      <c r="D317" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E317" s="13" t="s">
-        <v>2643</v>
-      </c>
-      <c r="F317" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G317" s="13"/>
-      <c r="H317" s="13"/>
-      <c r="I317" s="16"/>
-    </row>
-    <row r="318" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A318" s="2" t="s">
-        <v>1960</v>
-      </c>
-      <c r="B318" s="13"/>
-      <c r="C318" s="2" t="s">
-        <v>2302</v>
-      </c>
-      <c r="D318" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E318" s="13" t="s">
-        <v>2644</v>
-      </c>
-      <c r="F318" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G318" s="13"/>
-      <c r="H318" s="13"/>
-      <c r="I318" s="16"/>
-    </row>
-    <row r="319" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A319" s="2" t="s">
-        <v>1961</v>
-      </c>
-      <c r="B319" s="13"/>
-      <c r="C319" s="2" t="s">
-        <v>2303</v>
-      </c>
-      <c r="D319" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E319" s="13" t="s">
-        <v>2645</v>
-      </c>
-      <c r="F319" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G319" s="13"/>
-      <c r="H319" s="13"/>
-      <c r="I319" s="16"/>
-    </row>
-    <row r="320" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A320" s="2" t="s">
-        <v>1962</v>
-      </c>
-      <c r="B320" s="13"/>
-      <c r="C320" s="2" t="s">
-        <v>2304</v>
-      </c>
-      <c r="D320" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E320" s="13" t="s">
-        <v>2646</v>
-      </c>
-      <c r="F320" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G320" s="13"/>
-      <c r="H320" s="13"/>
-      <c r="I320" s="16"/>
-    </row>
-    <row r="321" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A321" s="2" t="s">
-        <v>1963</v>
-      </c>
-      <c r="B321" s="13"/>
-      <c r="C321" s="2" t="s">
-        <v>2305</v>
-      </c>
-      <c r="D321" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E321" s="13" t="s">
-        <v>2647</v>
-      </c>
-      <c r="F321" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G321" s="13"/>
-      <c r="H321" s="13"/>
-      <c r="I321" s="16"/>
-    </row>
-    <row r="322" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A322" s="2" t="s">
-        <v>1964</v>
-      </c>
-      <c r="B322" s="13"/>
-      <c r="C322" s="2" t="s">
-        <v>2306</v>
-      </c>
-      <c r="D322" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E322" s="13" t="s">
-        <v>2648</v>
-      </c>
-      <c r="F322" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G322" s="13"/>
-      <c r="H322" s="13"/>
-      <c r="I322" s="16"/>
-    </row>
-    <row r="323" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A323" s="2" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B323" s="13"/>
-      <c r="C323" s="2" t="s">
-        <v>2307</v>
-      </c>
-      <c r="D323" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E323" s="13" t="s">
-        <v>2649</v>
-      </c>
-      <c r="F323" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G323" s="13"/>
-      <c r="H323" s="13"/>
-      <c r="I323" s="16"/>
-    </row>
-    <row r="324" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A324" s="2" t="s">
-        <v>1966</v>
-      </c>
-      <c r="B324" s="13"/>
-      <c r="C324" s="2" t="s">
-        <v>2308</v>
-      </c>
-      <c r="D324" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E324" s="13" t="s">
-        <v>2650</v>
-      </c>
-      <c r="F324" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G324" s="13"/>
-      <c r="H324" s="13"/>
-      <c r="I324" s="16"/>
-    </row>
-    <row r="325" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A325" s="2" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B325" s="13"/>
-      <c r="C325" s="2" t="s">
-        <v>2309</v>
-      </c>
-      <c r="D325" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E325" s="13" t="s">
-        <v>2651</v>
-      </c>
-      <c r="F325" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G325" s="13"/>
-      <c r="H325" s="13"/>
-      <c r="I325" s="16"/>
-    </row>
-    <row r="326" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A326" s="2" t="s">
-        <v>1968</v>
-      </c>
-      <c r="B326" s="13"/>
-      <c r="C326" s="2" t="s">
-        <v>2310</v>
-      </c>
-      <c r="D326" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E326" s="13" t="s">
-        <v>2652</v>
-      </c>
-      <c r="F326" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G326" s="13"/>
-      <c r="H326" s="13"/>
-      <c r="I326" s="16"/>
-    </row>
-    <row r="327" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A327" s="2" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B327" s="13"/>
-      <c r="C327" s="2" t="s">
-        <v>2311</v>
-      </c>
-      <c r="D327" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E327" s="13" t="s">
-        <v>2653</v>
-      </c>
-      <c r="F327" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G327" s="13"/>
-      <c r="H327" s="13"/>
-      <c r="I327" s="16"/>
-    </row>
-    <row r="328" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A328" s="2" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B328" s="13"/>
-      <c r="C328" s="2" t="s">
-        <v>2312</v>
-      </c>
-      <c r="D328" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E328" s="13" t="s">
-        <v>2654</v>
-      </c>
-      <c r="F328" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G328" s="13"/>
-      <c r="H328" s="13"/>
-      <c r="I328" s="16"/>
-    </row>
-    <row r="329" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A329" s="2" t="s">
-        <v>1971</v>
-      </c>
-      <c r="B329" s="13"/>
-      <c r="C329" s="2" t="s">
-        <v>2313</v>
-      </c>
-      <c r="D329" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E329" s="13" t="s">
-        <v>2655</v>
-      </c>
-      <c r="F329" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G329" s="13"/>
-      <c r="H329" s="13"/>
-      <c r="I329" s="16"/>
-    </row>
-    <row r="330" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A330" s="2" t="s">
-        <v>1972</v>
-      </c>
-      <c r="B330" s="13"/>
-      <c r="C330" s="2" t="s">
-        <v>2314</v>
-      </c>
-      <c r="D330" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E330" s="13" t="s">
-        <v>2656</v>
-      </c>
-      <c r="F330" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G330" s="13"/>
-      <c r="H330" s="13"/>
-      <c r="I330" s="16"/>
-    </row>
-    <row r="331" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A331" s="2" t="s">
-        <v>1973</v>
-      </c>
-      <c r="B331" s="13"/>
-      <c r="C331" s="2" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D331" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E331" s="13" t="s">
-        <v>2657</v>
-      </c>
-      <c r="F331" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G331" s="13"/>
-      <c r="H331" s="13"/>
-      <c r="I331" s="16"/>
-    </row>
-    <row r="332" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A332" s="2" t="s">
-        <v>1974</v>
-      </c>
-      <c r="B332" s="13"/>
-      <c r="C332" s="2" t="s">
-        <v>2316</v>
-      </c>
-      <c r="D332" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E332" s="13" t="s">
-        <v>2658</v>
-      </c>
-      <c r="F332" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G332" s="13"/>
-      <c r="H332" s="13"/>
-      <c r="I332" s="16"/>
-    </row>
-    <row r="333" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A333" s="2" t="s">
-        <v>1975</v>
-      </c>
-      <c r="B333" s="13"/>
-      <c r="C333" s="2" t="s">
-        <v>2317</v>
-      </c>
-      <c r="D333" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E333" s="13" t="s">
-        <v>2659</v>
-      </c>
-      <c r="F333" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G333" s="13"/>
-      <c r="H333" s="13"/>
-      <c r="I333" s="16"/>
-    </row>
-    <row r="334" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A334" s="2" t="s">
-        <v>1976</v>
-      </c>
-      <c r="B334" s="13"/>
-      <c r="C334" s="2" t="s">
-        <v>2318</v>
-      </c>
-      <c r="D334" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E334" s="13" t="s">
-        <v>2660</v>
-      </c>
-      <c r="F334" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G334" s="13"/>
-      <c r="H334" s="13"/>
-      <c r="I334" s="16"/>
-    </row>
-    <row r="335" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A335" s="2" t="s">
-        <v>1977</v>
-      </c>
-      <c r="B335" s="13"/>
-      <c r="C335" s="2" t="s">
-        <v>2319</v>
-      </c>
-      <c r="D335" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E335" s="13" t="s">
-        <v>2661</v>
-      </c>
-      <c r="F335" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G335" s="13"/>
-      <c r="H335" s="13"/>
-      <c r="I335" s="16"/>
-    </row>
-    <row r="336" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A336" s="2" t="s">
-        <v>1978</v>
-      </c>
-      <c r="B336" s="13"/>
-      <c r="C336" s="2" t="s">
-        <v>2320</v>
-      </c>
-      <c r="D336" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E336" s="13" t="s">
-        <v>2662</v>
-      </c>
-      <c r="F336" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G336" s="13"/>
-      <c r="H336" s="13"/>
-      <c r="I336" s="16"/>
-    </row>
-    <row r="337" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A337" s="2" t="s">
-        <v>1979</v>
-      </c>
-      <c r="B337" s="13"/>
-      <c r="C337" s="2" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D337" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E337" s="13" t="s">
-        <v>2663</v>
-      </c>
-      <c r="F337" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G337" s="13"/>
-      <c r="H337" s="13"/>
-      <c r="I337" s="16"/>
-    </row>
-    <row r="338" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A338" s="2" t="s">
-        <v>1980</v>
-      </c>
-      <c r="B338" s="13"/>
-      <c r="C338" s="2" t="s">
-        <v>2322</v>
-      </c>
-      <c r="D338" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E338" s="13" t="s">
-        <v>2664</v>
-      </c>
-      <c r="F338" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G338" s="13"/>
-      <c r="H338" s="13"/>
-      <c r="I338" s="16"/>
-    </row>
-    <row r="339" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A339" s="2" t="s">
-        <v>1981</v>
-      </c>
-      <c r="B339" s="13"/>
-      <c r="C339" s="2" t="s">
-        <v>2323</v>
-      </c>
-      <c r="D339" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E339" s="13" t="s">
-        <v>2665</v>
-      </c>
-      <c r="F339" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G339" s="13"/>
-      <c r="H339" s="13"/>
-      <c r="I339" s="16"/>
-    </row>
-    <row r="340" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A340" s="2" t="s">
-        <v>1982</v>
-      </c>
-      <c r="B340" s="13"/>
-      <c r="C340" s="2" t="s">
-        <v>2324</v>
-      </c>
-      <c r="D340" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E340" s="13" t="s">
-        <v>2666</v>
-      </c>
-      <c r="F340" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G340" s="13"/>
-      <c r="H340" s="13"/>
-      <c r="I340" s="16"/>
-    </row>
-    <row r="341" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A341" s="2" t="s">
-        <v>1983</v>
-      </c>
-      <c r="B341" s="13"/>
-      <c r="C341" s="2" t="s">
-        <v>2325</v>
-      </c>
-      <c r="D341" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E341" s="13" t="s">
-        <v>2667</v>
-      </c>
-      <c r="F341" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G341" s="13"/>
-      <c r="H341" s="13"/>
-      <c r="I341" s="16"/>
-    </row>
-    <row r="342" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A342" s="2" t="s">
-        <v>1984</v>
-      </c>
-      <c r="B342" s="13"/>
-      <c r="C342" s="2" t="s">
-        <v>2326</v>
-      </c>
-      <c r="D342" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E342" s="13" t="s">
-        <v>2668</v>
-      </c>
-      <c r="F342" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G342" s="13"/>
-      <c r="H342" s="13"/>
-      <c r="I342" s="16"/>
-    </row>
-    <row r="343" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A343" s="2" t="s">
-        <v>1985</v>
-      </c>
-      <c r="B343" s="13"/>
-      <c r="C343" s="2" t="s">
-        <v>2327</v>
-      </c>
-      <c r="D343" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E343" s="13" t="s">
-        <v>2669</v>
-      </c>
-      <c r="F343" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G343" s="13"/>
-      <c r="H343" s="13"/>
-      <c r="I343" s="16"/>
-    </row>
-    <row r="344" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A344" s="13" t="s">
-        <v>2672</v>
-      </c>
-      <c r="B344" s="13"/>
-      <c r="C344" s="13" t="s">
-        <v>2690</v>
-      </c>
-      <c r="D344" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E344" s="13" t="s">
-        <v>2673</v>
-      </c>
-      <c r="F344" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G344" s="13"/>
-      <c r="H344" s="13"/>
-      <c r="I344" s="16"/>
-    </row>
-    <row r="345" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A345" s="13" t="s">
-        <v>2674</v>
-      </c>
-      <c r="B345" s="13"/>
-      <c r="C345" s="13" t="s">
-        <v>2691</v>
-      </c>
-      <c r="D345" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E345" s="13" t="s">
-        <v>2675</v>
-      </c>
-      <c r="F345" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G345" s="13"/>
-      <c r="H345" s="13"/>
-      <c r="I345" s="16"/>
-    </row>
-    <row r="346" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A346" s="13" t="s">
-        <v>2676</v>
-      </c>
-      <c r="B346" s="13"/>
-      <c r="C346" s="13" t="s">
-        <v>2692</v>
-      </c>
-      <c r="D346" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E346" s="13" t="s">
-        <v>2677</v>
-      </c>
-      <c r="F346" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G346" s="13"/>
-      <c r="H346" s="13"/>
-      <c r="I346" s="16"/>
-    </row>
-    <row r="347" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A347" s="13" t="s">
-        <v>2678</v>
-      </c>
-      <c r="B347" s="13"/>
-      <c r="C347" s="13" t="s">
-        <v>2693</v>
-      </c>
-      <c r="D347" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E347" s="13" t="s">
-        <v>2679</v>
-      </c>
-      <c r="F347" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G347" s="13"/>
-      <c r="H347" s="13"/>
-      <c r="I347" s="16"/>
-    </row>
-    <row r="348" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A348" s="13" t="s">
-        <v>2680</v>
-      </c>
-      <c r="B348" s="13"/>
-      <c r="C348" s="13" t="s">
-        <v>2694</v>
-      </c>
-      <c r="D348" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E348" s="13" t="s">
-        <v>2681</v>
-      </c>
-      <c r="F348" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G348" s="13"/>
-      <c r="H348" s="13"/>
-      <c r="I348" s="16"/>
-    </row>
-    <row r="349" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A349" s="13" t="s">
-        <v>2682</v>
-      </c>
-      <c r="B349" s="13"/>
-      <c r="C349" s="13" t="s">
-        <v>2695</v>
-      </c>
-      <c r="D349" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E349" s="13" t="s">
-        <v>2683</v>
-      </c>
-      <c r="F349" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G349" s="13"/>
-      <c r="H349" s="13"/>
-      <c r="I349" s="16"/>
-    </row>
-    <row r="350" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A350" s="13" t="s">
-        <v>2684</v>
-      </c>
-      <c r="B350" s="13"/>
-      <c r="C350" s="13" t="s">
-        <v>2696</v>
-      </c>
-      <c r="D350" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E350" s="13" t="s">
-        <v>2685</v>
-      </c>
-      <c r="F350" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G350" s="13"/>
-      <c r="H350" s="13"/>
-      <c r="I350" s="16"/>
-    </row>
-    <row r="351" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A351" s="13" t="s">
-        <v>2686</v>
-      </c>
-      <c r="B351" s="13"/>
-      <c r="C351" s="13" t="s">
-        <v>2697</v>
-      </c>
-      <c r="D351" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E351" s="13" t="s">
-        <v>2687</v>
-      </c>
-      <c r="F351" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G351" s="13"/>
-      <c r="H351" s="13"/>
-      <c r="I351" s="16"/>
-    </row>
-    <row r="352" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A352" s="13" t="s">
-        <v>2688</v>
-      </c>
-      <c r="B352" s="13"/>
-      <c r="C352" s="13" t="s">
-        <v>2698</v>
-      </c>
-      <c r="D352" s="13" t="s">
-        <v>2670</v>
-      </c>
-      <c r="E352" s="13" t="s">
-        <v>2689</v>
-      </c>
-      <c r="F352" s="13" t="s">
-        <v>2671</v>
-      </c>
-      <c r="G352" s="13"/>
-      <c r="H352" s="13"/>
-      <c r="I352" s="16"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2FCAE9-BF71-440F-B5BB-516CA2AC2303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B565C51F-9CF5-40E7-A9EB-92BD02335C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$839</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$833</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="2709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4938" uniqueCount="2708">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8143,9 +8140,6 @@
   </si>
   <si>
     <t>B0GN8RQJRG</t>
-  </si>
-  <si>
-    <t>Electronic Keyboard</t>
   </si>
   <si>
     <t>B0GKNGWLJ2</t>
@@ -8173,7 +8167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8216,13 +8210,6 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -8284,7 +8271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8333,9 +8320,6 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8523,2542 +8507,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Margin Structure"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>SKU</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>ASIN</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>Model</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>FBA75673</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>B0B4DPX2J2</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>AM-C1</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>FBA76864</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>B0BPLZ5CGV</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>AI-04 Red</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>FBA79005</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>B0CKHVHVQ1</v>
-          </cell>
-          <cell r="E4" t="str">
-            <v>AM-W45</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>FBA79380</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>B0D3M1B4Z8</v>
-          </cell>
-          <cell r="E5" t="str">
-            <v>AM-C46</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>FBA75692</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>B0B4G1HPL5</v>
-          </cell>
-          <cell r="E6" t="str">
-            <v>AM-C11</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>FBA75691</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>B0B4G5JG4P</v>
-          </cell>
-          <cell r="E7" t="str">
-            <v>AM-W14</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>FBA79107</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>B0CM9P5CCK</v>
-          </cell>
-          <cell r="E8" t="str">
-            <v>AM-W17</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>FBA75674</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>B0B4G19R58</v>
-          </cell>
-          <cell r="E9" t="str">
-            <v>AM-C2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>FBA79109</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>B0CM9HYVDM</v>
-          </cell>
-          <cell r="E10" t="str">
-            <v>AM-W18</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>FBA75675</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>B0B4G8ZB64</v>
-          </cell>
-          <cell r="E11" t="str">
-            <v>AM-C3</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>FBA79070</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>B0CLH7G5WH</v>
-          </cell>
-          <cell r="E12" t="str">
-            <v>AI-02 2x2| Metallic Red</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>FBA79103</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>B0CM6NTWBP</v>
-          </cell>
-          <cell r="E13" t="str">
-            <v>AI-10</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>FBA75690</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>B0B4K87PR4</v>
-          </cell>
-          <cell r="E14" t="str">
-            <v>AM-C10</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>FBA78975</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>B0CF5TCQKL</v>
-          </cell>
-          <cell r="E15" t="str">
-            <v>AA-21</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>FBA78973</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>B0CF5R3V95</v>
-          </cell>
-          <cell r="E16" t="str">
-            <v>AA-19</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>FBA76414</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>B0BLJVJ2GN</v>
-          </cell>
-          <cell r="E17" t="str">
-            <v>AA-05</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>FBA79379</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>B0D3LZWTHV</v>
-          </cell>
-          <cell r="E18" t="str">
-            <v>AM-C45</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>FBA78925</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>B0CBC7QMNV</v>
-          </cell>
-          <cell r="E19" t="str">
-            <v>AM-C11X</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>FBA75688</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>B0B4G763WS</v>
-          </cell>
-          <cell r="E20" t="str">
-            <v>AM-W12</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>FBA76744</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>B0BLK7VQ2N</v>
-          </cell>
-          <cell r="E21" t="str">
-            <v xml:space="preserve">AM-K3 </v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>FBA78974</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>B0CF5RRTDJ</v>
-          </cell>
-          <cell r="E22" t="str">
-            <v>AA-20</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>FBA79447</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>B0DFMLXD9S</v>
-          </cell>
-          <cell r="E23" t="str">
-            <v>AM-W34</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>FBA75686</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>B0B4G89VQJ</v>
-          </cell>
-          <cell r="E24" t="str">
-            <v>AM-W10</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>FBA79011</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>B0CH4RNWJX</v>
-          </cell>
-          <cell r="E25" t="str">
-            <v>AM-C43</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>FBA79064</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>B0CJR76Y7G</v>
-          </cell>
-          <cell r="E26" t="str">
-            <v>AA-25</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>FBA75679</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>B0B4JRQP22</v>
-          </cell>
-          <cell r="E27" t="str">
-            <v>AA-02</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>FBA79449</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>B0DFMNGFTD</v>
-          </cell>
-          <cell r="E28" t="str">
-            <v>AM-W36</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>FBA79106</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>B0CM9KJZWQ</v>
-          </cell>
-          <cell r="E29" t="str">
-            <v>AM-C44</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>FBA76742</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>B0BLKBJ5HN</v>
-          </cell>
-          <cell r="E30" t="str">
-            <v xml:space="preserve">AM-K1 </v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>FBA79355</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>B0D3M86SH1</v>
-          </cell>
-          <cell r="E31" t="str">
-            <v>AA-19BL</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>FBA76863</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>B0BPM2T7BQ</v>
-          </cell>
-          <cell r="E32" t="str">
-            <v xml:space="preserve">AI-03	</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>FBA75677</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>B0B4KC7VBM</v>
-          </cell>
-          <cell r="E33" t="str">
-            <v>AM-C5</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>FBA77171</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>B0CH4VCD6R</v>
-          </cell>
-          <cell r="E34" t="str">
-            <v>AC-6XL</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>FBA79105</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>B0CM6WH4ZT</v>
-          </cell>
-          <cell r="E35" t="str">
-            <v>AI-12</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>FBA79230</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>B0CX1XK5R6</v>
-          </cell>
-          <cell r="E36" t="str">
-            <v>AM-W46</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>FBA78960</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>B0CBCB82MT</v>
-          </cell>
-          <cell r="E37" t="str">
-            <v>AM-C39</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>FBA75684</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>B0B4G7VWXD</v>
-          </cell>
-          <cell r="E38" t="str">
-            <v>AA-04</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>FBA76723</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>B0BLKF46QG</v>
-          </cell>
-          <cell r="E39" t="str">
-            <v xml:space="preserve">AM-C20 </v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>FBA76721</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>B0BLKB55BM</v>
-          </cell>
-          <cell r="E40" t="str">
-            <v xml:space="preserve">AM-C18 </v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="str">
-            <v>FBA75681</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>B0B4FZS38V</v>
-          </cell>
-          <cell r="E41" t="str">
-            <v>AM-C7</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>FBA75678</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>B0B4G8PH2P</v>
-          </cell>
-          <cell r="E42" t="str">
-            <v>AA-01</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43" t="str">
-            <v>FBA79446</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>B0DFMMTWLY</v>
-          </cell>
-          <cell r="E43" t="str">
-            <v>AM-W33</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44" t="str">
-            <v>FBA76862</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>B0BPLWW72Y</v>
-          </cell>
-          <cell r="E44" t="str">
-            <v>AM-C28</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>FBA79010</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>B0CH4T2BJD</v>
-          </cell>
-          <cell r="E45" t="str">
-            <v>AM-C42</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>FBA79104</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>B0CM6NVLT9</v>
-          </cell>
-          <cell r="E46" t="str">
-            <v>AI-11</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="str">
-            <v>FBA76730</v>
-          </cell>
-          <cell r="C47" t="str">
-            <v>B0BLKB6FRR</v>
-          </cell>
-          <cell r="E47" t="str">
-            <v xml:space="preserve">AM-C27 </v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48" t="str">
-            <v>FBA76597</v>
-          </cell>
-          <cell r="C48" t="str">
-            <v>B0BQ7H7418</v>
-          </cell>
-          <cell r="E48" t="str">
-            <v>AA-06</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49" t="str">
-            <v>FBA79465</v>
-          </cell>
-          <cell r="C49" t="str">
-            <v>B0DFMQCGT1</v>
-          </cell>
-          <cell r="E49" t="str">
-            <v>AM-W21</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50" t="str">
-            <v>FBA79445</v>
-          </cell>
-          <cell r="C50" t="str">
-            <v>B0DFMLS8JG</v>
-          </cell>
-          <cell r="E50" t="str">
-            <v>AM-W32</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51" t="str">
-            <v>FBA75676</v>
-          </cell>
-          <cell r="C51" t="str">
-            <v>B0B4DS678Q</v>
-          </cell>
-          <cell r="E51" t="str">
-            <v>AM-C4</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52" t="str">
-            <v>FBA78986</v>
-          </cell>
-          <cell r="C52" t="str">
-            <v>B0CF5WXWFH</v>
-          </cell>
-          <cell r="E52" t="str">
-            <v>AB-01</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53" t="str">
-            <v>FBA75689</v>
-          </cell>
-          <cell r="C53" t="str">
-            <v>B0B4G59Y8W</v>
-          </cell>
-          <cell r="E53" t="str">
-            <v>AM-W13</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54" t="str">
-            <v>FBA75680</v>
-          </cell>
-          <cell r="C54" t="str">
-            <v>B0B4G1PXWV</v>
-          </cell>
-          <cell r="E54" t="str">
-            <v>AM-C6</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55" t="str">
-            <v>FBA78205</v>
-          </cell>
-          <cell r="C55" t="str">
-            <v>B0C539RBGL</v>
-          </cell>
-          <cell r="E55" t="str">
-            <v>AM-C32</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56" t="str">
-            <v>FBA76729</v>
-          </cell>
-          <cell r="C56" t="str">
-            <v>B0BLNDQ757</v>
-          </cell>
-          <cell r="E56" t="str">
-            <v xml:space="preserve">AM-C26 </v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57" t="str">
-            <v>FBA78976</v>
-          </cell>
-          <cell r="C57" t="str">
-            <v>B0CF5SHL15</v>
-          </cell>
-          <cell r="E57" t="str">
-            <v>AA-22</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58" t="str">
-            <v>FBA76735</v>
-          </cell>
-          <cell r="C58" t="str">
-            <v>B0BLKGPL4X</v>
-          </cell>
-          <cell r="E58" t="str">
-            <v xml:space="preserve">AA-08 </v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59" t="str">
-            <v>FBA79444</v>
-          </cell>
-          <cell r="C59" t="str">
-            <v>B0DFMLQBMC</v>
-          </cell>
-          <cell r="E59" t="str">
-            <v>AM-W20</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60" t="str">
-            <v>FBA76727</v>
-          </cell>
-          <cell r="C60" t="str">
-            <v>B0BLKCDRNB</v>
-          </cell>
-          <cell r="E60" t="str">
-            <v xml:space="preserve">AM-C24 </v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61" t="str">
-            <v>FBA75683</v>
-          </cell>
-          <cell r="C61" t="str">
-            <v>B0B4G94VP3</v>
-          </cell>
-          <cell r="E61" t="str">
-            <v>AA-03</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62" t="str">
-            <v>FBA79016</v>
-          </cell>
-          <cell r="C62" t="str">
-            <v>B0CH4R1V6S</v>
-          </cell>
-          <cell r="E62" t="str">
-            <v>AM-C3a</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="B63" t="str">
-            <v>FBA75687</v>
-          </cell>
-          <cell r="C63" t="str">
-            <v>B0B4G5ZLTB</v>
-          </cell>
-          <cell r="E63" t="str">
-            <v>AM-W11</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="B64" t="str">
-            <v>FBA78203</v>
-          </cell>
-          <cell r="C64" t="str">
-            <v>B0C4YTNJG7</v>
-          </cell>
-          <cell r="E64" t="str">
-            <v>AM-C30</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="B65" t="str">
-            <v>FBA79009</v>
-          </cell>
-          <cell r="C65" t="str">
-            <v>B0CH4PMR8K</v>
-          </cell>
-          <cell r="E65" t="str">
-            <v>AM-C41</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="B66" t="str">
-            <v>FBA79108</v>
-          </cell>
-          <cell r="C66" t="str">
-            <v>B0CM9L1QZG</v>
-          </cell>
-          <cell r="E66" t="str">
-            <v>AM-W16</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="B67" t="str">
-            <v>FBA79008</v>
-          </cell>
-          <cell r="C67" t="str">
-            <v>B0CH4RT4P8</v>
-          </cell>
-          <cell r="E67" t="str">
-            <v>AI-06</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="B68" t="str">
-            <v>FBA79448</v>
-          </cell>
-          <cell r="C68" t="str">
-            <v>B0DFMKY4TT</v>
-          </cell>
-          <cell r="E68" t="str">
-            <v>AM-W35</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="B69" t="str">
-            <v>FBA78961</v>
-          </cell>
-          <cell r="C69" t="str">
-            <v>B0CBCB9S14</v>
-          </cell>
-          <cell r="E69" t="str">
-            <v>AM-C40</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70" t="str">
-            <v>FBA78206</v>
-          </cell>
-          <cell r="C70" t="str">
-            <v>B0C4YSV3XL</v>
-          </cell>
-          <cell r="E70" t="str">
-            <v>AM-W15</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="B71" t="str">
-            <v>FBA79356</v>
-          </cell>
-          <cell r="C71" t="str">
-            <v>B0D3Q2T5XX</v>
-          </cell>
-          <cell r="E71" t="str">
-            <v>AA-19WL</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="B72" t="str">
-            <v>FBA78204</v>
-          </cell>
-          <cell r="C72" t="str">
-            <v>B0C4YT43Z3</v>
-          </cell>
-          <cell r="E72" t="str">
-            <v>AM-C31</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="B73" t="str">
-            <v>FBA76743</v>
-          </cell>
-          <cell r="C73" t="str">
-            <v>B0BLK8PXNY</v>
-          </cell>
-          <cell r="E73" t="str">
-            <v xml:space="preserve">AM-K2 </v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="B74" t="str">
-            <v>FBA76728</v>
-          </cell>
-          <cell r="C74" t="str">
-            <v>B0BLNCP74M</v>
-          </cell>
-          <cell r="E74" t="str">
-            <v xml:space="preserve">AM-C25 </v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="B75" t="str">
-            <v>FBA76716</v>
-          </cell>
-          <cell r="C75" t="str">
-            <v>B0BLK8DNPD</v>
-          </cell>
-          <cell r="E75" t="str">
-            <v xml:space="preserve">AM-C13 </v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="B76" t="str">
-            <v>FBA78423</v>
-          </cell>
-          <cell r="C76" t="str">
-            <v>B0C598Q6PT</v>
-          </cell>
-          <cell r="E76" t="str">
-            <v>AM-C36</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="B77" t="str">
-            <v>FBA78424</v>
-          </cell>
-          <cell r="C77" t="str">
-            <v>B0C55MY66L</v>
-          </cell>
-          <cell r="E77" t="str">
-            <v>AM-C37</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="B78" t="str">
-            <v>FBA78420</v>
-          </cell>
-          <cell r="C78" t="str">
-            <v>B0C5957W3P</v>
-          </cell>
-          <cell r="E78" t="str">
-            <v>AM-C33</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="B79" t="str">
-            <v>FBA77011</v>
-          </cell>
-          <cell r="C79" t="str">
-            <v>B0BPMN89NG</v>
-          </cell>
-          <cell r="E79" t="str">
-            <v>AM-C29</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="B80" t="str">
-            <v>FBA78425</v>
-          </cell>
-          <cell r="C80" t="str">
-            <v>B0C55QXL83</v>
-          </cell>
-          <cell r="E80" t="str">
-            <v>AM-C38</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="B81" t="str">
-            <v>FBA78972</v>
-          </cell>
-          <cell r="C81" t="str">
-            <v>B0CF5T89FT</v>
-          </cell>
-          <cell r="E81" t="str">
-            <v>AA-18</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82" t="str">
-            <v>FBA79014</v>
-          </cell>
-          <cell r="C82" t="str">
-            <v>B0CH4WFQF6</v>
-          </cell>
-          <cell r="E82" t="str">
-            <v>AI-09</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83" t="str">
-            <v>FBA75685</v>
-          </cell>
-          <cell r="C83" t="str">
-            <v>B0B4FXDHXW</v>
-          </cell>
-          <cell r="E83" t="str">
-            <v>AM-C9</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="B84" t="str">
-            <v>FBA76722</v>
-          </cell>
-          <cell r="C84" t="str">
-            <v>B0BLKDC4PP</v>
-          </cell>
-          <cell r="E84" t="str">
-            <v xml:space="preserve">AM-C19 </v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="B85" t="str">
-            <v>FBA76737</v>
-          </cell>
-          <cell r="C85" t="str">
-            <v>B0C59G1C4N</v>
-          </cell>
-          <cell r="E85" t="str">
-            <v>AA-10</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="B86" t="str">
-            <v>FBA76720</v>
-          </cell>
-          <cell r="C86" t="str">
-            <v>B0BLKCWZQD</v>
-          </cell>
-          <cell r="E86" t="str">
-            <v xml:space="preserve">AM-C17 </v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="B87" t="str">
-            <v>FBA78419</v>
-          </cell>
-          <cell r="C87" t="str">
-            <v>B0C55M2GBN</v>
-          </cell>
-          <cell r="E87" t="str">
-            <v>AM-A1</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="B88" t="str">
-            <v>FBA78421</v>
-          </cell>
-          <cell r="C88" t="str">
-            <v>B0C594FZLM</v>
-          </cell>
-          <cell r="E88" t="str">
-            <v>AM-C34</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89" t="str">
-            <v>FBA78971</v>
-          </cell>
-          <cell r="C89" t="str">
-            <v>B0CF5TDLFH</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>AA-17</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="B90" t="str">
-            <v>FBA75682</v>
-          </cell>
-          <cell r="C90" t="str">
-            <v>B0B4FVV78V</v>
-          </cell>
-          <cell r="E90" t="str">
-            <v>AM-C8</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="B91" t="str">
-            <v>FBA76726</v>
-          </cell>
-          <cell r="C91" t="str">
-            <v>B0BLKD4815</v>
-          </cell>
-          <cell r="E91" t="str">
-            <v>AM-C23</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="B92" t="str">
-            <v>FBA76734</v>
-          </cell>
-          <cell r="C92" t="str">
-            <v>B0BLKHVCDX</v>
-          </cell>
-          <cell r="E92" t="str">
-            <v xml:space="preserve">AA-07 </v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="B93" t="str">
-            <v>FBA76739</v>
-          </cell>
-          <cell r="C93" t="str">
-            <v>B0BLRK37TB</v>
-          </cell>
-          <cell r="E93" t="str">
-            <v xml:space="preserve">AA-12 </v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="B94" t="str">
-            <v>FBA76732</v>
-          </cell>
-          <cell r="C94" t="str">
-            <v>B0BLKCB2JY</v>
-          </cell>
-          <cell r="E94" t="str">
-            <v>AI-01 / Q24</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="B95" t="str">
-            <v>FBA76717</v>
-          </cell>
-          <cell r="C95" t="str">
-            <v>B0BLK6P24G</v>
-          </cell>
-          <cell r="E95" t="str">
-            <v xml:space="preserve">AM-C14 </v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="B96" t="str">
-            <v>FBA76718</v>
-          </cell>
-          <cell r="C96" t="str">
-            <v>B0BLKD8FVG</v>
-          </cell>
-          <cell r="E96" t="str">
-            <v xml:space="preserve">AM-C15 </v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="B97" t="str">
-            <v>FBA77010</v>
-          </cell>
-          <cell r="C97" t="str">
-            <v>B0BPMBMN3S</v>
-          </cell>
-          <cell r="E97" t="str">
-            <v>AI-04	Black</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="B98" t="str">
-            <v>FBA76715</v>
-          </cell>
-          <cell r="C98" t="str">
-            <v>B0BLK31PYH</v>
-          </cell>
-          <cell r="E98" t="str">
-            <v xml:space="preserve">AM-C12 </v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="B99" t="str">
-            <v>FBA78422</v>
-          </cell>
-          <cell r="C99" t="str">
-            <v>B0C598MNMC</v>
-          </cell>
-          <cell r="E99" t="str">
-            <v>AM-C35</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="B100" t="str">
-            <v>FBA76725</v>
-          </cell>
-          <cell r="C100" t="str">
-            <v>B0BLKCSJ7Z</v>
-          </cell>
-          <cell r="E100" t="str">
-            <v xml:space="preserve">AM-C22 </v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="B101" t="str">
-            <v>FBA79013</v>
-          </cell>
-          <cell r="C101" t="str">
-            <v>B0CH4TDGPG</v>
-          </cell>
-          <cell r="E101" t="str">
-            <v>AI-08</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="B102" t="str">
-            <v>FBA76738</v>
-          </cell>
-          <cell r="C102" t="str">
-            <v>B0BLRGCNRG</v>
-          </cell>
-          <cell r="E102" t="str">
-            <v xml:space="preserve">AA-11 </v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="B103" t="str">
-            <v>FBAM75673</v>
-          </cell>
-          <cell r="C103" t="str">
-            <v>B0DFTVZPM8</v>
-          </cell>
-          <cell r="E103" t="str">
-            <v>AM-C1</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="B104" t="str">
-            <v>FBA76719</v>
-          </cell>
-          <cell r="C104" t="str">
-            <v>B0BLKCXQRT</v>
-          </cell>
-          <cell r="E104" t="str">
-            <v>AM-C16</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="B105" t="str">
-            <v>FBA76724</v>
-          </cell>
-          <cell r="C105" t="str">
-            <v>B0BLNC5D8L</v>
-          </cell>
-          <cell r="E105" t="str">
-            <v xml:space="preserve">AM-C21 </v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="B106" t="str">
-            <v>FBA76733</v>
-          </cell>
-          <cell r="C106" t="str">
-            <v>B0BLKCJXZR</v>
-          </cell>
-          <cell r="E106" t="str">
-            <v>AI-02 / X2</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="B107" t="str">
-            <v>FBA76736</v>
-          </cell>
-          <cell r="C107" t="str">
-            <v>B0BLS63XCL</v>
-          </cell>
-          <cell r="E107" t="str">
-            <v xml:space="preserve">AA-09 </v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="B108" t="str">
-            <v>FBA76740</v>
-          </cell>
-          <cell r="C108" t="str">
-            <v>B0BLRKFBBP</v>
-          </cell>
-          <cell r="E108" t="str">
-            <v xml:space="preserve">AA-13 </v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="B109" t="str">
-            <v>FBA76741</v>
-          </cell>
-          <cell r="C109" t="str">
-            <v>B0BLS2HJ68</v>
-          </cell>
-          <cell r="E109" t="str">
-            <v xml:space="preserve">AA-14 </v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="B110" t="str">
-            <v>FBA78207</v>
-          </cell>
-          <cell r="C110" t="str">
-            <v>B0C53CQV5Z</v>
-          </cell>
-          <cell r="E110" t="str">
-            <v>AA-15</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="B111" t="str">
-            <v>FBA79482</v>
-          </cell>
-          <cell r="C111" t="str">
-            <v>B0DXFPM4N2</v>
-          </cell>
-          <cell r="E111" t="str">
-            <v>AM-S1</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="B112" t="str">
-            <v>FBA78970</v>
-          </cell>
-          <cell r="C112" t="str">
-            <v>B0CF5T1LFR</v>
-          </cell>
-          <cell r="E112" t="str">
-            <v>AA-16</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="B113" t="str">
-            <v>FBA78977</v>
-          </cell>
-          <cell r="C113" t="str">
-            <v>B0CF5TVDRT</v>
-          </cell>
-          <cell r="E113" t="str">
-            <v>AA-23</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="B114" t="str">
-            <v>FBA78978</v>
-          </cell>
-          <cell r="C114" t="str">
-            <v>B0CF5PCL34</v>
-          </cell>
-          <cell r="E114" t="str">
-            <v>AA-24</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="B115" t="str">
-            <v>FBA79004</v>
-          </cell>
-          <cell r="C115" t="str">
-            <v>B0CF9BY345</v>
-          </cell>
-          <cell r="E115" t="str">
-            <v>AI-05</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="B116" t="str">
-            <v>FBA79012</v>
-          </cell>
-          <cell r="C116" t="str">
-            <v>B0CH4THGGM</v>
-          </cell>
-          <cell r="E116" t="str">
-            <v>AI-07</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="B117" t="str">
-            <v>FBA79389</v>
-          </cell>
-          <cell r="C117" t="str">
-            <v>B0D3M13T6H</v>
-          </cell>
-          <cell r="E117" t="str">
-            <v>AWB-01</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="B118" t="str">
-            <v>FBA77101</v>
-          </cell>
-          <cell r="C118" t="str">
-            <v>B07WLWN2ZT</v>
-          </cell>
-          <cell r="E118" t="str">
-            <v>TC-777</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="B119" t="str">
-            <v>FBA77104</v>
-          </cell>
-          <cell r="C119" t="str">
-            <v>B089SJGQBH</v>
-          </cell>
-          <cell r="E119" t="str">
-            <v>TC20</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="B120" t="str">
-            <v>FBA77111</v>
-          </cell>
-          <cell r="C120" t="str">
-            <v>B08CVP2HXP</v>
-          </cell>
-          <cell r="E120" t="str">
-            <v>TC30</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="B121" t="str">
-            <v>FBA79113</v>
-          </cell>
-          <cell r="C121" t="str">
-            <v>B0BTCXQQ6M</v>
-          </cell>
-          <cell r="E121" t="str">
-            <v>TC310</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="B122" t="str">
-            <v>FBA79114</v>
-          </cell>
-          <cell r="C122" t="str">
-            <v>B0CCV74CL7</v>
-          </cell>
-          <cell r="E122" t="str">
-            <v>TC310+</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="B123" t="str">
-            <v>FBA79116</v>
-          </cell>
-          <cell r="C123" t="str">
-            <v>B0BYHHSLPC</v>
-          </cell>
-          <cell r="E123" t="str">
-            <v>TC-777 PRO</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="B124" t="str">
-            <v>FBA77113</v>
-          </cell>
-          <cell r="C124" t="str">
-            <v>B01ISNU3X4</v>
-          </cell>
-          <cell r="E124" t="str">
-            <v>K1</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="B125" t="str">
-            <v>FBA79111</v>
-          </cell>
-          <cell r="C125" t="str">
-            <v>B0BRKFP94K</v>
-          </cell>
-          <cell r="E125" t="str">
-            <v>TD510</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="B126" t="str">
-            <v>FBA77110</v>
-          </cell>
-          <cell r="C126" t="str">
-            <v>B08NDB5NWP</v>
-          </cell>
-          <cell r="E126" t="str">
-            <v>TM20</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="B127" t="str">
-            <v>FBK77102</v>
-          </cell>
-          <cell r="C127" t="str">
-            <v>B07GVGMW59</v>
-          </cell>
-          <cell r="E127" t="str">
-            <v>G11</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="B128" t="str">
-            <v>FBA77117</v>
-          </cell>
-          <cell r="C128" t="str">
-            <v>B078WNW4YW</v>
-          </cell>
-          <cell r="E128" t="str">
-            <v>S20</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="B129" t="str">
-            <v>FBA79115</v>
-          </cell>
-          <cell r="C129" t="str">
-            <v>B0C8JDHLX9</v>
-          </cell>
-          <cell r="E129" t="str">
-            <v>T10</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="B130" t="str">
-            <v>FBA77106</v>
-          </cell>
-          <cell r="C130" t="str">
-            <v>B082W4B7SX</v>
-          </cell>
-          <cell r="E130" t="str">
-            <v>T20</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="B131" t="str">
-            <v>FBA77105</v>
-          </cell>
-          <cell r="C131" t="str">
-            <v>B089FVQD3Z</v>
-          </cell>
-          <cell r="E131" t="str">
-            <v>T30</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="B132" t="str">
-            <v>FBA79112</v>
-          </cell>
-          <cell r="C132" t="str">
-            <v>B0BRKDLXCD</v>
-          </cell>
-          <cell r="E132" t="str">
-            <v>T90</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="B133" t="str">
-            <v>FBA77103</v>
-          </cell>
-          <cell r="C133" t="str">
-            <v>B09Z5Q194D</v>
-          </cell>
-          <cell r="E133" t="str">
-            <v>ORCA001</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="B134" t="str">
-            <v>FBA77114</v>
-          </cell>
-          <cell r="C134" t="str">
-            <v>B07TSN2H9D</v>
-          </cell>
-          <cell r="E134" t="str">
-            <v>TC-2030</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="B135" t="str">
-            <v>FBA79574</v>
-          </cell>
-          <cell r="C135" t="str">
-            <v>B0B4WTHLX5</v>
-          </cell>
-          <cell r="E135" t="str">
-            <v>TC30S</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="B136" t="str">
-            <v>FBA79575</v>
-          </cell>
-          <cell r="C136" t="str">
-            <v>B0BG8CJXHH</v>
-          </cell>
-          <cell r="E136" t="str">
-            <v>TC30+</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="B137" t="str">
-            <v>FBA79576</v>
-          </cell>
-          <cell r="C137" t="str">
-            <v>B0BRCR2QQ7</v>
-          </cell>
-          <cell r="E137" t="str">
-            <v>TC30S+</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="B138" t="str">
-            <v>FBA79577</v>
-          </cell>
-          <cell r="C138" t="str">
-            <v>B0CSCT63BL</v>
-          </cell>
-          <cell r="E138" t="str">
-            <v>TM310</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="B139" t="str">
-            <v>FBA79578</v>
-          </cell>
-          <cell r="C139" t="str">
-            <v>B0CFKZ72N7</v>
-          </cell>
-          <cell r="E139" t="str">
-            <v>D5</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="B140" t="str">
-            <v>FBA79579</v>
-          </cell>
-          <cell r="C140" t="str">
-            <v>B0CQX4GVSB</v>
-          </cell>
-          <cell r="E140" t="str">
-            <v>D2</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="B141" t="str">
-            <v>FBA79582</v>
-          </cell>
-          <cell r="C141" t="str">
-            <v>B0CCVBQRFX</v>
-          </cell>
-          <cell r="E141" t="str">
-            <v>TD510+</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="B142" t="str">
-            <v>FBA79585</v>
-          </cell>
-          <cell r="C142" t="str">
-            <v>B0CFKHCQ8W</v>
-          </cell>
-          <cell r="E142" t="str">
-            <v>T20LP</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="B143" t="str">
-            <v>FBA79586</v>
-          </cell>
-          <cell r="C143" t="str">
-            <v>B0CH9JR3HL</v>
-          </cell>
-          <cell r="E143" t="str">
-            <v>TRL-20</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="B144" t="str">
-            <v>FBK79010</v>
-          </cell>
-          <cell r="C144" t="str">
-            <v>B0FLYJFC22</v>
-          </cell>
-          <cell r="E144" t="str">
-            <v>AM-C42 Duplicate</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="B145" t="str">
-            <v>FBA79722</v>
-          </cell>
-          <cell r="C145" t="str">
-            <v>B0F2HYY7JF</v>
-          </cell>
-          <cell r="E145" t="str">
-            <v>AM-W21 Duplicate</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="B146" t="str">
-            <v>FBA79909</v>
-          </cell>
-          <cell r="C146" t="str">
-            <v>B0FVM17Q4W</v>
-          </cell>
-          <cell r="E146" t="str">
-            <v>AM-W20 Duplicate</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="B147" t="str">
-            <v>FBK79009</v>
-          </cell>
-          <cell r="C147" t="str">
-            <v>B0FLYHJ6DK</v>
-          </cell>
-          <cell r="E147" t="str">
-            <v>AM-C41 Duplicate</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="B148" t="str">
-            <v>FBA79903</v>
-          </cell>
-          <cell r="C148" t="str">
-            <v>B0FR5DLXH9</v>
-          </cell>
-          <cell r="E148" t="str">
-            <v>AA-25M</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="B149" t="str">
-            <v>FBA79974</v>
-          </cell>
-          <cell r="C149" t="str">
-            <v>B0GD8JSPB1</v>
-          </cell>
-          <cell r="E149" t="str">
-            <v>AM-S1 Bookshelf Speaker</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="B150" t="str">
-            <v>FBA79653</v>
-          </cell>
-          <cell r="C150" t="str">
-            <v>B0DN6LJZBR</v>
-          </cell>
-          <cell r="E150" t="str">
-            <v>AM-C45 Pro</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="B151" t="str">
-            <v>FBA79654</v>
-          </cell>
-          <cell r="C151" t="str">
-            <v>B0DN6MNS1X</v>
-          </cell>
-          <cell r="E151" t="str">
-            <v>AM-C11 Pro</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="B152" t="str">
-            <v>FBA79655</v>
-          </cell>
-          <cell r="C152" t="str">
-            <v>B0DN6PFWNK</v>
-          </cell>
-          <cell r="E152" t="str">
-            <v>AM-C44 Pro</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="B153" t="str">
-            <v>FBA79694</v>
-          </cell>
-          <cell r="C153" t="str">
-            <v>B0DT6T6N6B</v>
-          </cell>
-          <cell r="E153" t="str">
-            <v>AA-26</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="B154" t="str">
-            <v>FBM79708</v>
-          </cell>
-          <cell r="C154" t="str">
-            <v>B0FJS7JZ4V</v>
-          </cell>
-          <cell r="E154" t="str">
-            <v>SB-01</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="B155" t="str">
-            <v>FBM79708</v>
-          </cell>
-          <cell r="C155" t="str">
-            <v>B0FFB6YJM1</v>
-          </cell>
-          <cell r="E155" t="str">
-            <v>SB-01</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="B156" t="str">
-            <v>FBA79783</v>
-          </cell>
-          <cell r="C156" t="str">
-            <v>B0FF9R3GKK</v>
-          </cell>
-          <cell r="E156" t="str">
-            <v>AM-C47</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="B157" t="str">
-            <v>FBA79813</v>
-          </cell>
-          <cell r="C157" t="str">
-            <v>B0FG88HVQ8</v>
-          </cell>
-          <cell r="E157" t="str">
-            <v>AH-50</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="B158" t="str">
-            <v>FBA79814</v>
-          </cell>
-          <cell r="C158" t="str">
-            <v>B0GNM35G8X</v>
-          </cell>
-          <cell r="E158" t="str">
-            <v>AH-50 Ear Cushion</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="B159" t="str">
-            <v>FBA79815</v>
-          </cell>
-          <cell r="C159" t="str">
-            <v>B0FPR7VFCH</v>
-          </cell>
-          <cell r="E159" t="str">
-            <v>AM-W19</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="B160" t="str">
-            <v>FBA79967</v>
-          </cell>
-          <cell r="C160" t="str">
-            <v>B0G2C2RCXN</v>
-          </cell>
-          <cell r="E160" t="str">
-            <v>AM-W19 Duplicate</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="B161" t="str">
-            <v>FBA79816</v>
-          </cell>
-          <cell r="C161" t="str">
-            <v>B0FPR962YS</v>
-          </cell>
-          <cell r="E161" t="str">
-            <v>AM-W22</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="B162" t="str">
-            <v>FBA80016</v>
-          </cell>
-          <cell r="C162" t="str">
-            <v>B0GKPXQ8G3</v>
-          </cell>
-          <cell r="E162" t="str">
-            <v>AM-W22 Duplicate</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="B163" t="str">
-            <v>FBA79820</v>
-          </cell>
-          <cell r="C163" t="str">
-            <v>B0FQJWWDVK</v>
-          </cell>
-          <cell r="E163" t="str">
-            <v>AC-3XL</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="B164" t="str">
-            <v>FBA79838</v>
-          </cell>
-          <cell r="C164" t="str">
-            <v>B0FQBX8J17</v>
-          </cell>
-          <cell r="E164" t="str">
-            <v>AH-40 SL</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="B165" t="str">
-            <v>FBA79839</v>
-          </cell>
-          <cell r="C165" t="str">
-            <v>B0FQBXS6Y2</v>
-          </cell>
-          <cell r="E165" t="str">
-            <v>AH-45 BK</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="B166" t="str">
-            <v>FBA79840</v>
-          </cell>
-          <cell r="C166" t="str">
-            <v>B0FQBWV1ST</v>
-          </cell>
-          <cell r="E166" t="str">
-            <v>AH-60 RD</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="B167" t="str">
-            <v>FBA79841</v>
-          </cell>
-          <cell r="C167" t="str">
-            <v>B0FQBTRM28</v>
-          </cell>
-          <cell r="E167" t="str">
-            <v>AH-60 BL</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="B168" t="str">
-            <v>FBA79842</v>
-          </cell>
-          <cell r="C168" t="str">
-            <v>B0G4DNF8RZ</v>
-          </cell>
-          <cell r="E168" t="str">
-            <v>AM-C48</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="B169" t="str">
-            <v>FBA79821</v>
-          </cell>
-          <cell r="C169" t="str">
-            <v>B0FJ2JJZL3</v>
-          </cell>
-          <cell r="E169" t="str">
-            <v>UB-01</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="B170" t="str">
-            <v>FBA79822</v>
-          </cell>
-          <cell r="C170" t="str">
-            <v>B0FJ2J6MTF</v>
-          </cell>
-          <cell r="E170" t="str">
-            <v>KB-01</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="B171" t="str">
-            <v>FBA79823</v>
-          </cell>
-          <cell r="C171" t="str">
-            <v>B0FJ2HZCVN</v>
-          </cell>
-          <cell r="E171" t="str">
-            <v>PB-01</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="B172" t="str">
-            <v>FBA79824</v>
-          </cell>
-          <cell r="C172" t="str">
-            <v>B0FJ2K95XT</v>
-          </cell>
-          <cell r="E172" t="str">
-            <v>GB-01</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="B173" t="str">
-            <v>FBA79825</v>
-          </cell>
-          <cell r="C173" t="str">
-            <v>B0FJ2DT13L</v>
-          </cell>
-          <cell r="E173" t="str">
-            <v>GB-02</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="B174" t="str">
-            <v>FBA79826</v>
-          </cell>
-          <cell r="C174" t="str">
-            <v>B0FJ2LQT7K</v>
-          </cell>
-          <cell r="E174" t="str">
-            <v>PB-02</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="B175" t="str">
-            <v>FBA79827</v>
-          </cell>
-          <cell r="C175" t="str">
-            <v>B0FJ8S5XJ8</v>
-          </cell>
-          <cell r="E175" t="str">
-            <v>PB-03</v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="B176" t="str">
-            <v>FBA79830</v>
-          </cell>
-          <cell r="C176" t="str">
-            <v>B0FJ8TSQK1</v>
-          </cell>
-          <cell r="E176" t="str">
-            <v>GB-03</v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="B177" t="str">
-            <v>FBA79831</v>
-          </cell>
-          <cell r="C177" t="str">
-            <v>B0FJ8W5Y9Q</v>
-          </cell>
-          <cell r="E177" t="str">
-            <v>GB-04</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="B178" t="str">
-            <v>FBA79832</v>
-          </cell>
-          <cell r="C178" t="str">
-            <v>B0FJ8S53GW</v>
-          </cell>
-          <cell r="E178" t="str">
-            <v>GB-05</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="B179" t="str">
-            <v>FBA79833</v>
-          </cell>
-          <cell r="C179" t="str">
-            <v>B0FJ8PZ9H7</v>
-          </cell>
-          <cell r="E179" t="str">
-            <v>PB-04</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="B180" t="str">
-            <v>FBA79834</v>
-          </cell>
-          <cell r="C180" t="str">
-            <v>B0FJ8T4WXM</v>
-          </cell>
-          <cell r="E180" t="str">
-            <v>PB-05</v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="B181" t="str">
-            <v>FBA79835</v>
-          </cell>
-          <cell r="C181" t="str">
-            <v>B0FJ8TWCQZ</v>
-          </cell>
-          <cell r="E181" t="str">
-            <v>PB-06</v>
-          </cell>
-        </row>
-        <row r="182">
-          <cell r="B182" t="str">
-            <v>FBA79836</v>
-          </cell>
-          <cell r="C182" t="str">
-            <v>B0FJ8Z1W81</v>
-          </cell>
-          <cell r="E182" t="str">
-            <v>PB-07</v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="B183" t="str">
-            <v>FBA79844</v>
-          </cell>
-          <cell r="C183" t="str">
-            <v>B0FN7DYB2M</v>
-          </cell>
-          <cell r="E183" t="str">
-            <v>PB-08</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="B184" t="str">
-            <v>FBA79845</v>
-          </cell>
-          <cell r="C184" t="str">
-            <v>B0FN7B3KWS</v>
-          </cell>
-          <cell r="E184" t="str">
-            <v>UB-02</v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="B185" t="str">
-            <v>FBA79846</v>
-          </cell>
-          <cell r="C185" t="str">
-            <v>B0FN7C25VS</v>
-          </cell>
-          <cell r="E185" t="str">
-            <v>AM-C11X Pro</v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="B186" t="str">
-            <v>FBA79847</v>
-          </cell>
-          <cell r="C186" t="str">
-            <v>B0FN7FYZM3</v>
-          </cell>
-          <cell r="E186" t="str">
-            <v>PB-09</v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="B187" t="str">
-            <v>FBA79848</v>
-          </cell>
-          <cell r="C187" t="str">
-            <v>B0GN97RFPR</v>
-          </cell>
-          <cell r="E187" t="str">
-            <v>AM-S2</v>
-          </cell>
-        </row>
-        <row r="188">
-          <cell r="B188" t="str">
-            <v>FBA79904</v>
-          </cell>
-          <cell r="C188" t="str">
-            <v>B0FTVQQVDC</v>
-          </cell>
-          <cell r="E188" t="str">
-            <v>PB-10</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="B189" t="str">
-            <v>FBA79905</v>
-          </cell>
-          <cell r="C189" t="str">
-            <v>B0FTVSH458</v>
-          </cell>
-          <cell r="E189" t="str">
-            <v>PB-11</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="B190" t="str">
-            <v>FBA79906</v>
-          </cell>
-          <cell r="C190" t="str">
-            <v>B0FTVVLNS9</v>
-          </cell>
-          <cell r="E190" t="str">
-            <v>PB-12</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="B191" t="str">
-            <v>FBA79907</v>
-          </cell>
-          <cell r="C191" t="str">
-            <v>B0FTVS34SD</v>
-          </cell>
-          <cell r="E191" t="str">
-            <v>PB-13</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="B192" t="str">
-            <v>FBA79908</v>
-          </cell>
-          <cell r="C192" t="str">
-            <v>B0FTVV1QJY</v>
-          </cell>
-          <cell r="E192" t="str">
-            <v>PB-14</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="B193" t="str">
-            <v>FBA79969</v>
-          </cell>
-          <cell r="C193" t="str">
-            <v>B0G3B677Z5</v>
-          </cell>
-          <cell r="E193" t="str">
-            <v>UB-03</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="B194" t="str">
-            <v>FBA79957</v>
-          </cell>
-          <cell r="C194" t="str">
-            <v>B0G3Q517Y2</v>
-          </cell>
-          <cell r="E194" t="str">
-            <v>AM-W23</v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="B195" t="str">
-            <v>FBA79958</v>
-          </cell>
-          <cell r="C195" t="str">
-            <v>B0G3Q59X8C</v>
-          </cell>
-          <cell r="E195" t="str">
-            <v>AM-W24</v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="B196" t="str">
-            <v>FBA79961</v>
-          </cell>
-          <cell r="C196" t="str">
-            <v>B0G53H49BS</v>
-          </cell>
-          <cell r="E196" t="str">
-            <v>AI-13</v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="B197" t="str">
-            <v>FBA79962</v>
-          </cell>
-          <cell r="C197" t="str">
-            <v>B0G53LZNY3</v>
-          </cell>
-          <cell r="E197" t="str">
-            <v>AM-Mix4 OTG</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="B198" t="str">
-            <v>FBA79963</v>
-          </cell>
-          <cell r="C198" t="str">
-            <v>B0G53CB72D</v>
-          </cell>
-          <cell r="E198" t="str">
-            <v>AM-Pro8</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="B199" t="str">
-            <v>FBA79964</v>
-          </cell>
-          <cell r="C199" t="str">
-            <v>B0G53KWRWH</v>
-          </cell>
-          <cell r="E199" t="str">
-            <v>AM-Pro12</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="B200" t="str">
-            <v>FBA79965</v>
-          </cell>
-          <cell r="C200" t="str">
-            <v>B0G53PRM34</v>
-          </cell>
-          <cell r="E200" t="str">
-            <v>AM-Mix6</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="B201" t="str">
-            <v>FBA79966</v>
-          </cell>
-          <cell r="C201" t="str">
-            <v>B0G53KWRVW</v>
-          </cell>
-          <cell r="E201" t="str">
-            <v>AM-Mix10</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="B202" t="str">
-            <v>FBA79968</v>
-          </cell>
-          <cell r="C202" t="str">
-            <v>B0G53M9258</v>
-          </cell>
-          <cell r="E202" t="str">
-            <v>AI-14</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="B203" t="str">
-            <v>FBA79972</v>
-          </cell>
-          <cell r="C203" t="str">
-            <v>B0GCP1J2HC</v>
-          </cell>
-          <cell r="E203" t="str">
-            <v>M8</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="B204" t="str">
-            <v>FBA80007</v>
-          </cell>
-          <cell r="C204" t="str">
-            <v>B0GN2LHJY4</v>
-          </cell>
-          <cell r="E204" t="str">
-            <v>MT-12</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="B205" t="str">
-            <v>FBA80084</v>
-          </cell>
-          <cell r="E205" t="str">
-            <v>BE-4</v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="B206" t="str">
-            <v>FBA80085</v>
-          </cell>
-          <cell r="E206" t="str">
-            <v>M6</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="B207" t="str">
-            <v>FBA79956</v>
-          </cell>
-          <cell r="C207" t="str">
-            <v>B0GMPGNXX3</v>
-          </cell>
-          <cell r="E207" t="str">
-            <v>A3-XLR</v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="B208" t="str">
-            <v>FBA80006</v>
-          </cell>
-          <cell r="E208" t="str">
-            <v>A2-XLR</v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="B209" t="str">
-            <v>FBA79959</v>
-          </cell>
-          <cell r="C209" t="str">
-            <v>B0G39ZHDYP</v>
-          </cell>
-          <cell r="E209" t="str">
-            <v>AM-W47 Wired</v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="B210" t="str">
-            <v xml:space="preserve">FBA79960 </v>
-          </cell>
-          <cell r="C210" t="str">
-            <v>B0G3B152FR</v>
-          </cell>
-          <cell r="E210" t="str">
-            <v>AM-W47 Wireless</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="B211" t="str">
-            <v>FBA79975</v>
-          </cell>
-          <cell r="E211" t="str">
-            <v>AE831</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="B212" t="str">
-            <v>FBA79976</v>
-          </cell>
-          <cell r="E212" t="str">
-            <v>JT-1</v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="B213" t="str">
-            <v>FBA79977</v>
-          </cell>
-          <cell r="E213" t="str">
-            <v>BM-320PRO</v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="B214" t="str">
-            <v>FBA79979</v>
-          </cell>
-          <cell r="C214" t="str">
-            <v>B0GN8RQJRG</v>
-          </cell>
-          <cell r="E214" t="str">
-            <v>AK-37-B</v>
-          </cell>
-        </row>
-        <row r="215">
-          <cell r="B215" t="str">
-            <v>FBA79980</v>
-          </cell>
-          <cell r="C215" t="str">
-            <v>B0GN8MMKY1</v>
-          </cell>
-          <cell r="E215" t="str">
-            <v>AK-37-W</v>
-          </cell>
-        </row>
-        <row r="216">
-          <cell r="B216" t="str">
-            <v>FBA79981</v>
-          </cell>
-          <cell r="C216" t="str">
-            <v>B0GN8MFDGZ</v>
-          </cell>
-          <cell r="E216" t="str">
-            <v>AK-61 Neo</v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="B217" t="str">
-            <v>FBA79982</v>
-          </cell>
-          <cell r="C217" t="str">
-            <v>B0GN8MPYPG</v>
-          </cell>
-          <cell r="E217" t="str">
-            <v>AK-61 Pro</v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="B218" t="str">
-            <v>FBA79983</v>
-          </cell>
-          <cell r="C218" t="str">
-            <v>B0GN321RXQ</v>
-          </cell>
-          <cell r="E218" t="str">
-            <v>AM-W48 / AM-S6</v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="B219" t="str">
-            <v>FBA79996</v>
-          </cell>
-          <cell r="E219" t="str">
-            <v>AM-C49</v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="B220" t="str">
-            <v>FBA79995</v>
-          </cell>
-          <cell r="E220" t="str">
-            <v>AM-C50</v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="B221" t="str">
-            <v>FBA79997</v>
-          </cell>
-          <cell r="E221" t="str">
-            <v>W3</v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="B222" t="str">
-            <v>FBA79998</v>
-          </cell>
-          <cell r="E222" t="str">
-            <v>W5</v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="B223" t="str">
-            <v>FBA79999</v>
-          </cell>
-          <cell r="E223" t="str">
-            <v>JTG800</v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="B224" t="str">
-            <v>FBA80000</v>
-          </cell>
-          <cell r="E224" t="str">
-            <v>DP-718H</v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="B225" t="str">
-            <v>FBA80001</v>
-          </cell>
-          <cell r="E225" t="str">
-            <v>USB718</v>
-          </cell>
-        </row>
-        <row r="226">
-          <cell r="B226" t="str">
-            <v>FBA80002</v>
-          </cell>
-          <cell r="E226" t="str">
-            <v>AM-W33 Pro</v>
-          </cell>
-        </row>
-        <row r="227">
-          <cell r="B227" t="str">
-            <v>FBA80003</v>
-          </cell>
-          <cell r="E227" t="str">
-            <v>AM-W32 Pro</v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="B228" t="str">
-            <v>FBA80004</v>
-          </cell>
-          <cell r="E228" t="str">
-            <v>AM-W36 Pro</v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="B229" t="str">
-            <v>FBA80005</v>
-          </cell>
-          <cell r="E229" t="str">
-            <v>T-835</v>
-          </cell>
-        </row>
-        <row r="230">
-          <cell r="B230" t="str">
-            <v>FBA80009</v>
-          </cell>
-          <cell r="E230" t="str">
-            <v>AM-C51</v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="B231" t="str">
-            <v>FBA80010</v>
-          </cell>
-          <cell r="E231" t="str">
-            <v>AM-C52</v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="B232" t="str">
-            <v>FBA80011</v>
-          </cell>
-          <cell r="E232" t="str">
-            <v>AM-Pro16</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="B233" t="str">
-            <v>FBA80012</v>
-          </cell>
-          <cell r="E233" t="str">
-            <v>AM-Pro24</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="B234" t="str">
-            <v>FBA80013</v>
-          </cell>
-          <cell r="E234" t="str">
-            <v>XM-16</v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="B235" t="str">
-            <v>FBA80014</v>
-          </cell>
-          <cell r="E235" t="str">
-            <v>XM-24</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11378,12 +8826,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:I843"/>
+  <dimension ref="A1:I833"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.109375" style="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.88671875" style="13" bestFit="1" customWidth="1"/>
@@ -12990,13 +10438,13 @@
     </row>
     <row r="56" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="C56" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>6</v>
@@ -13715,13 +11163,13 @@
     </row>
     <row r="81" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C81" t="s">
         <v>2704</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>2704</v>
-      </c>
-      <c r="C81" t="s">
-        <v>2705</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>6</v>
@@ -16053,8 +13501,8 @@
         <v>543</v>
       </c>
       <c r="B164" s="2"/>
-      <c r="C164" s="2" t="s">
-        <v>747</v>
+      <c r="C164" t="s">
+        <v>2700</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>523</v>
@@ -16078,8 +13526,8 @@
         <v>544</v>
       </c>
       <c r="B165" s="2"/>
-      <c r="C165" s="2" t="s">
-        <v>747</v>
+      <c r="C165" t="s">
+        <v>2705</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>523</v>
@@ -16103,8 +13551,8 @@
         <v>545</v>
       </c>
       <c r="B166" s="2"/>
-      <c r="C166" s="2" t="s">
-        <v>747</v>
+      <c r="C166" t="s">
+        <v>2706</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>523</v>
@@ -16128,8 +13576,8 @@
         <v>546</v>
       </c>
       <c r="B167" s="2"/>
-      <c r="C167" s="2" t="s">
-        <v>747</v>
+      <c r="C167" t="s">
+        <v>2699</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>523</v>
@@ -18179,7 +15627,7 @@
       </c>
       <c r="B249" s="2"/>
       <c r="C249" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>523</v>
@@ -29990,205 +27438,50 @@
         <v>2671</v>
       </c>
     </row>
-    <row r="834" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A834" s="17" t="s">
-        <v>546</v>
-      </c>
-      <c r="C834" t="s">
-        <v>2699</v>
-      </c>
-      <c r="D834" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E834" s="17" t="s">
-        <v>931</v>
-      </c>
-      <c r="F834" s="17" t="s">
-        <v>2701</v>
-      </c>
-    </row>
-    <row r="835" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A835" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="C835" t="s">
-        <v>2700</v>
-      </c>
-      <c r="D835" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E835" s="17" t="s">
-        <v>928</v>
-      </c>
-      <c r="F835" s="17" t="s">
-        <v>2701</v>
-      </c>
-    </row>
-    <row r="836" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A836" s="17" t="s">
-        <v>576</v>
-      </c>
-      <c r="C836" s="17" t="str">
-        <f>_xlfn.XLOOKUP(A836,[1]Main!$B:$B,[1]Main!$C:$C)</f>
-        <v>B0FJ2JJZL3</v>
-      </c>
-      <c r="D836" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E836" s="17" t="str">
-        <f>_xlfn.XLOOKUP(C836,[1]Main!$C:$C,[1]Main!$E:$E)</f>
-        <v>UB-01</v>
-      </c>
-      <c r="F836" s="17" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="837" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A837" s="13" t="s">
-        <v>692</v>
-      </c>
-      <c r="C837" s="17" t="str">
-        <f>_xlfn.XLOOKUP(A837,[1]Main!$B:$B,[1]Main!$C:$C)</f>
-        <v>B0FN7B3KWS</v>
-      </c>
-      <c r="D837" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E837" s="17" t="str">
-        <f>_xlfn.XLOOKUP(C837,[1]Main!$C:$C,[1]Main!$E:$E)</f>
-        <v>UB-02</v>
-      </c>
-      <c r="F837" s="17" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="838" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A838" s="17" t="s">
-        <v>544</v>
-      </c>
-      <c r="C838" t="s">
-        <v>2706</v>
-      </c>
-      <c r="D838" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E838" s="17" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="839" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A839" s="17" t="s">
-        <v>545</v>
-      </c>
-      <c r="C839" t="s">
-        <v>2707</v>
-      </c>
-      <c r="D839" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E839" s="17" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="840" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A840" s="13" t="s">
-        <v>543</v>
-      </c>
-      <c r="C840" s="13" t="s">
-        <v>2700</v>
-      </c>
-      <c r="D840" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E840" s="13" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="841" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A841" s="13" t="s">
-        <v>544</v>
-      </c>
-      <c r="C841" s="13" t="s">
-        <v>2706</v>
-      </c>
-      <c r="D841" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E841" s="13" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="842" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A842" s="13" t="s">
-        <v>545</v>
-      </c>
-      <c r="C842" s="13" t="s">
-        <v>2707</v>
-      </c>
-      <c r="D842" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E842" s="13" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="843" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A843" s="13" t="s">
-        <v>546</v>
-      </c>
-      <c r="C843" s="13" t="s">
-        <v>2699</v>
-      </c>
-      <c r="D843" s="13" t="s">
-        <v>523</v>
-      </c>
-      <c r="E843" s="13" t="s">
-        <v>931</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="16" priority="67"/>
+  <autoFilter ref="A1:I833" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
+  <conditionalFormatting sqref="A92">
+    <cfRule type="duplicateValues" dxfId="16" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A92">
-    <cfRule type="duplicateValues" dxfId="15" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="59"/>
+  <conditionalFormatting sqref="B56 A93:A104 A106:A122 A31:A91 A21:A29 B81 A2:A19">
+    <cfRule type="duplicateValues" dxfId="14" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A93:A104 A106:A122 A2:A19 A31:A91 A21:A29 B56 B81">
-    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
+  <conditionalFormatting sqref="A123:B123">
+    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A124:B140">
+    <cfRule type="duplicateValues" dxfId="12" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A141:A144">
-    <cfRule type="duplicateValues" dxfId="12" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A123:B123">
-    <cfRule type="duplicateValues" dxfId="11" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A124:B140">
-    <cfRule type="duplicateValues" dxfId="10" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="9" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="7" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="6" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95">
-    <cfRule type="duplicateValues" dxfId="4" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="2" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E124:E140">
-    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E141">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A121" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BE5D17-2B57-487B-A798-CD2069CA5053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C3398A-461E-45E0-9F92-253344F73178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -8410,40 +8410,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -8548,6 +8514,40 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -29211,67 +29211,67 @@
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A92">
-    <cfRule type="duplicateValues" dxfId="32" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A141:A144">
     <cfRule type="duplicateValues" dxfId="30" priority="66"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A836:A839">
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A123:B123">
-    <cfRule type="duplicateValues" dxfId="29" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A124:B140">
-    <cfRule type="duplicateValues" dxfId="28" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B56 A93:A104 A106:A122 A31:A91 A21:A29 B81 A2:A19">
-    <cfRule type="duplicateValues" dxfId="27" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B92">
-    <cfRule type="duplicateValues" dxfId="26" priority="73"/>
     <cfRule type="duplicateValues" dxfId="25" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B122">
-    <cfRule type="duplicateValues" dxfId="24" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="23" priority="71"/>
     <cfRule type="duplicateValues" dxfId="22" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95">
-    <cfRule type="duplicateValues" dxfId="21" priority="68"/>
     <cfRule type="duplicateValues" dxfId="20" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="18" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E124:E140">
-    <cfRule type="duplicateValues" dxfId="19" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E141">
-    <cfRule type="duplicateValues" dxfId="18" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A836:A839">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+  <conditionalFormatting sqref="E400">
+    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E836:E839">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="16" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A121" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C3398A-461E-45E0-9F92-253344F73178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70262608-93A7-4FA8-B3E8-18A04B014BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E36D84-6401-46A3-A6B2-46D2007E0138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FA1A5C-2B51-465A-B1FF-5DF497804438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4973" uniqueCount="2728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4973" uniqueCount="2729">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8221,6 +8221,9 @@
   </si>
   <si>
     <t>FBP79569</t>
+  </si>
+  <si>
+    <t>B0GV154XPQ</t>
   </si>
 </sst>
 </file>
@@ -8412,30 +8415,6 @@
   <dxfs count="34">
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -8560,6 +8539,30 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -18166,7 +18169,7 @@
       </c>
       <c r="B340" s="2"/>
       <c r="C340" s="2" t="s">
-        <v>747</v>
+        <v>2728</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>523</v>
@@ -29265,8 +29268,8 @@
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93">
-    <cfRule type="duplicateValues" dxfId="32" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A142:A145">
     <cfRule type="duplicateValues" dxfId="30" priority="66"/>
@@ -29284,19 +29287,19 @@
     <cfRule type="duplicateValues" dxfId="26" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="25" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
     <cfRule type="duplicateValues" dxfId="23" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="22" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C96">
-    <cfRule type="duplicateValues" dxfId="20" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
     <cfRule type="duplicateValues" dxfId="18" priority="104"/>
@@ -29308,24 +29311,24 @@
     <cfRule type="duplicateValues" dxfId="16" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401">
-    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
     <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A122" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FA1A5C-2B51-465A-B1FF-5DF497804438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194FE2E4-0673-40F3-A71F-CFD349A2C73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -29263,7 +29263,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I841" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194FE2E4-0673-40F3-A71F-CFD349A2C73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BAFB67-2ABB-4D1F-9E82-11318C988AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$841</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$868</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4973" uniqueCount="2729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5121" uniqueCount="2817">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8217,13 +8217,277 @@
     <t>B0D86Y2V7V</t>
   </si>
   <si>
-    <t>B0G1YKMFWT</t>
-  </si>
-  <si>
-    <t>FBP79569</t>
-  </si>
-  <si>
     <t>B0GV154XPQ</t>
+  </si>
+  <si>
+    <t>MK9146</t>
+  </si>
+  <si>
+    <t>AX4611</t>
+  </si>
+  <si>
+    <t>AX2761</t>
+  </si>
+  <si>
+    <t>AX5385</t>
+  </si>
+  <si>
+    <t>AX5616</t>
+  </si>
+  <si>
+    <t>FS6062</t>
+  </si>
+  <si>
+    <t>ES5362</t>
+  </si>
+  <si>
+    <t>AR11673</t>
+  </si>
+  <si>
+    <t>AR11692</t>
+  </si>
+  <si>
+    <t>MK4967</t>
+  </si>
+  <si>
+    <t>DZ2234</t>
+  </si>
+  <si>
+    <t>AR11755</t>
+  </si>
+  <si>
+    <t>ES5455</t>
+  </si>
+  <si>
+    <t>MK7570SET</t>
+  </si>
+  <si>
+    <t>MK7582</t>
+  </si>
+  <si>
+    <t>AX1746</t>
+  </si>
+  <si>
+    <t>FS5665</t>
+  </si>
+  <si>
+    <t>FS5447</t>
+  </si>
+  <si>
+    <t>MK7303</t>
+  </si>
+  <si>
+    <t>ME3154</t>
+  </si>
+  <si>
+    <t>AX1350</t>
+  </si>
+  <si>
+    <t>FS5151</t>
+  </si>
+  <si>
+    <t>DZ4548</t>
+  </si>
+  <si>
+    <t>AR11589</t>
+  </si>
+  <si>
+    <t>AR11606</t>
+  </si>
+  <si>
+    <t>MK4823</t>
+  </si>
+  <si>
+    <t>MK9165</t>
+  </si>
+  <si>
+    <t>AX4614</t>
+  </si>
+  <si>
+    <t>FBA79136</t>
+  </si>
+  <si>
+    <t>B0CFVK4PYT</t>
+  </si>
+  <si>
+    <t>FBA79286</t>
+  </si>
+  <si>
+    <t>B0CR5G3NRL</t>
+  </si>
+  <si>
+    <t>FBA79321</t>
+  </si>
+  <si>
+    <t>B0CR5JQFD5</t>
+  </si>
+  <si>
+    <t>FBA79407</t>
+  </si>
+  <si>
+    <t>B0CWR5S3R7</t>
+  </si>
+  <si>
+    <t>FBA79408</t>
+  </si>
+  <si>
+    <t>B0CYN8F826</t>
+  </si>
+  <si>
+    <t>FBA79419</t>
+  </si>
+  <si>
+    <t>B0CZSF6LVY</t>
+  </si>
+  <si>
+    <t>FBA79528</t>
+  </si>
+  <si>
+    <t>B0D93652ZY</t>
+  </si>
+  <si>
+    <t>FBA79726</t>
+  </si>
+  <si>
+    <t>B0DT2S2Y7F</t>
+  </si>
+  <si>
+    <t>FBA79858</t>
+  </si>
+  <si>
+    <t>B0FFJ4N8BK</t>
+  </si>
+  <si>
+    <t>FBA79947</t>
+  </si>
+  <si>
+    <t>B0FS6N1YT5</t>
+  </si>
+  <si>
+    <t>FBA80035</t>
+  </si>
+  <si>
+    <t>B07SV6Q9QX</t>
+  </si>
+  <si>
+    <t>FBA80038</t>
+  </si>
+  <si>
+    <t>B0GDJJ86QY</t>
+  </si>
+  <si>
+    <t>FBA80041</t>
+  </si>
+  <si>
+    <t>B0GF72VQSX</t>
+  </si>
+  <si>
+    <t>FBA80051</t>
+  </si>
+  <si>
+    <t>B0GF7BSTKP</t>
+  </si>
+  <si>
+    <t>FBA80053</t>
+  </si>
+  <si>
+    <t>B0GF73VZZ2</t>
+  </si>
+  <si>
+    <t>FBA80095</t>
+  </si>
+  <si>
+    <t>B0CHXGWVZJ</t>
+  </si>
+  <si>
+    <t>FBA80096</t>
+  </si>
+  <si>
+    <t>B07WQ9WRJ9</t>
+  </si>
+  <si>
+    <t>FBO67237</t>
+  </si>
+  <si>
+    <t>B079D8QRRL</t>
+  </si>
+  <si>
+    <t>FBO76805</t>
+  </si>
+  <si>
+    <t>B0BG17DJQS</t>
+  </si>
+  <si>
+    <t>FBO76876</t>
+  </si>
+  <si>
+    <t>B0769YW2KN</t>
+  </si>
+  <si>
+    <t>FBO77014</t>
+  </si>
+  <si>
+    <t>B00CJ06DYG</t>
+  </si>
+  <si>
+    <t>FBS66987</t>
+  </si>
+  <si>
+    <t>B017SN1OI8</t>
+  </si>
+  <si>
+    <t>FBS74343</t>
+  </si>
+  <si>
+    <t>B08SW1LBDF</t>
+  </si>
+  <si>
+    <t>FBS79303</t>
+  </si>
+  <si>
+    <t>B0CR5RZRMH</t>
+  </si>
+  <si>
+    <t>FBS79417</t>
+  </si>
+  <si>
+    <t>B0CYNH9X11</t>
+  </si>
+  <si>
+    <t>FBS79424</t>
+  </si>
+  <si>
+    <t>B0CZ9BTN24</t>
+  </si>
+  <si>
+    <t>FBS79428</t>
+  </si>
+  <si>
+    <t>B0CZ93BN92</t>
+  </si>
+  <si>
+    <t>FBS79516</t>
+  </si>
+  <si>
+    <t>B0D85F9QCK</t>
+  </si>
+  <si>
+    <t>Headphone</t>
+  </si>
+  <si>
+    <t>Audio Mixer</t>
+  </si>
+  <si>
+    <t>16 Channel Mixer</t>
+  </si>
+  <si>
+    <t>24 Channel Mixer</t>
+  </si>
+  <si>
+    <t>16 Channel Mixer With Carry Case</t>
+  </si>
+  <si>
+    <t>24 Channel Mixer With Carry Case</t>
   </si>
 </sst>
 </file>
@@ -8415,6 +8679,30 @@
   <dxfs count="34">
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -8539,30 +8827,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -9091,7 +9355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:I841"/>
+  <dimension ref="A1:I868"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
@@ -18169,7 +18433,7 @@
       </c>
       <c r="B340" s="2"/>
       <c r="C340" s="2" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>523</v>
@@ -29148,8 +29412,12 @@
       <c r="E835" s="22" t="s">
         <v>2698</v>
       </c>
-      <c r="F835" s="2"/>
-      <c r="G835" s="2"/>
+      <c r="F835" s="2" t="s">
+        <v>2811</v>
+      </c>
+      <c r="G835" s="2" t="s">
+        <v>2811</v>
+      </c>
       <c r="H835" s="2"/>
       <c r="I835" s="11"/>
     </row>
@@ -29167,8 +29435,12 @@
       <c r="E836" s="22" t="s">
         <v>2699</v>
       </c>
-      <c r="F836" s="2"/>
-      <c r="G836" s="2"/>
+      <c r="F836" s="2" t="s">
+        <v>2811</v>
+      </c>
+      <c r="G836" s="2" t="s">
+        <v>2811</v>
+      </c>
       <c r="H836" s="2"/>
       <c r="I836" s="11"/>
     </row>
@@ -29186,8 +29458,12 @@
       <c r="E837" s="19" t="s">
         <v>2709</v>
       </c>
-      <c r="F837" s="2"/>
-      <c r="G837" s="2"/>
+      <c r="F837" s="2" t="s">
+        <v>2812</v>
+      </c>
+      <c r="G837" s="2" t="s">
+        <v>2813</v>
+      </c>
       <c r="H837" s="2"/>
       <c r="I837" s="11"/>
     </row>
@@ -29205,8 +29481,12 @@
       <c r="E838" s="19" t="s">
         <v>2710</v>
       </c>
-      <c r="F838" s="2"/>
-      <c r="G838" s="2"/>
+      <c r="F838" s="2" t="s">
+        <v>2812</v>
+      </c>
+      <c r="G838" s="2" t="s">
+        <v>2814</v>
+      </c>
       <c r="H838" s="2"/>
       <c r="I838" s="11"/>
     </row>
@@ -29224,8 +29504,12 @@
       <c r="E839" s="19" t="s">
         <v>2711</v>
       </c>
-      <c r="F839" s="2"/>
-      <c r="G839" s="2"/>
+      <c r="F839" s="2" t="s">
+        <v>2812</v>
+      </c>
+      <c r="G839" s="2" t="s">
+        <v>2815</v>
+      </c>
       <c r="H839" s="2"/>
       <c r="I839" s="11"/>
     </row>
@@ -29243,32 +29527,499 @@
       <c r="E840" s="19" t="s">
         <v>2712</v>
       </c>
-      <c r="F840" s="2"/>
-      <c r="G840" s="2"/>
+      <c r="F840" s="2" t="s">
+        <v>2812</v>
+      </c>
+      <c r="G840" s="2" t="s">
+        <v>2816</v>
+      </c>
       <c r="H840" s="2"/>
       <c r="I840" s="11"/>
     </row>
     <row r="841" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A841" s="13" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C841" s="13" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D841" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E841" s="13" t="s">
         <v>2727</v>
       </c>
-      <c r="C841" s="13" t="s">
-        <v>2726</v>
-      </c>
-      <c r="D841" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E841" s="13" t="s">
-        <v>331</v>
+      <c r="F841" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="842" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A842" s="13" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C842" s="13" t="s">
+        <v>2758</v>
+      </c>
+      <c r="D842" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E842" s="13" t="s">
+        <v>2728</v>
+      </c>
+      <c r="F842" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="843" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A843" s="13" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C843" s="13" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D843" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E843" s="13" t="s">
+        <v>2729</v>
+      </c>
+      <c r="F843" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="844" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A844" s="13" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C844" s="13" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D844" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E844" s="13" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F844" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="845" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A845" s="13" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C845" s="13" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D845" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E845" s="13" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F845" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="846" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A846" s="13" t="s">
+        <v>2765</v>
+      </c>
+      <c r="C846" s="13" t="s">
+        <v>2766</v>
+      </c>
+      <c r="D846" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E846" s="13" t="s">
+        <v>2732</v>
+      </c>
+      <c r="F846" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="847" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A847" s="13" t="s">
+        <v>2767</v>
+      </c>
+      <c r="C847" s="13" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D847" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E847" s="13" t="s">
+        <v>2733</v>
+      </c>
+      <c r="F847" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="848" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A848" s="13" t="s">
+        <v>2769</v>
+      </c>
+      <c r="C848" s="13" t="s">
+        <v>2770</v>
+      </c>
+      <c r="D848" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E848" s="13" t="s">
+        <v>2734</v>
+      </c>
+      <c r="F848" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A849" s="13" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C849" s="13" t="s">
+        <v>2772</v>
+      </c>
+      <c r="D849" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E849" s="13" t="s">
+        <v>2735</v>
+      </c>
+      <c r="F849" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A850" s="13" t="s">
+        <v>2773</v>
+      </c>
+      <c r="C850" s="13" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D850" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E850" s="13" t="s">
+        <v>2736</v>
+      </c>
+      <c r="F850" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A851" s="13" t="s">
+        <v>2775</v>
+      </c>
+      <c r="C851" s="13" t="s">
+        <v>2776</v>
+      </c>
+      <c r="D851" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E851" s="13" t="s">
+        <v>2737</v>
+      </c>
+      <c r="F851" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A852" s="13" t="s">
+        <v>2777</v>
+      </c>
+      <c r="C852" s="13" t="s">
+        <v>2778</v>
+      </c>
+      <c r="D852" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E852" s="13" t="s">
+        <v>2738</v>
+      </c>
+      <c r="F852" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A853" s="13" t="s">
+        <v>2779</v>
+      </c>
+      <c r="C853" s="13" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D853" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E853" s="13" t="s">
+        <v>2739</v>
+      </c>
+      <c r="F853" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A854" s="13" t="s">
+        <v>2781</v>
+      </c>
+      <c r="C854" s="13" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D854" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E854" s="13" t="s">
+        <v>2740</v>
+      </c>
+      <c r="F854" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A855" s="13" t="s">
+        <v>2783</v>
+      </c>
+      <c r="C855" s="13" t="s">
+        <v>2784</v>
+      </c>
+      <c r="D855" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E855" s="13" t="s">
+        <v>2741</v>
+      </c>
+      <c r="F855" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A856" s="13" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C856" s="13" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D856" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E856" s="13" t="s">
+        <v>2742</v>
+      </c>
+      <c r="F856" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A857" s="13" t="s">
+        <v>2787</v>
+      </c>
+      <c r="C857" s="13" t="s">
+        <v>2788</v>
+      </c>
+      <c r="D857" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E857" s="13" t="s">
+        <v>2743</v>
+      </c>
+      <c r="F857" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A858" s="13" t="s">
+        <v>2789</v>
+      </c>
+      <c r="C858" s="13" t="s">
+        <v>2790</v>
+      </c>
+      <c r="D858" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E858" s="13" t="s">
+        <v>2744</v>
+      </c>
+      <c r="F858" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A859" s="13" t="s">
+        <v>2791</v>
+      </c>
+      <c r="C859" s="13" t="s">
+        <v>2792</v>
+      </c>
+      <c r="D859" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E859" s="13" t="s">
+        <v>2745</v>
+      </c>
+      <c r="F859" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A860" s="13" t="s">
+        <v>2793</v>
+      </c>
+      <c r="C860" s="13" t="s">
+        <v>2794</v>
+      </c>
+      <c r="D860" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E860" s="13" t="s">
+        <v>2746</v>
+      </c>
+      <c r="F860" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A861" s="13" t="s">
+        <v>2795</v>
+      </c>
+      <c r="C861" s="13" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D861" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E861" s="13" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F861" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A862" s="13" t="s">
+        <v>2797</v>
+      </c>
+      <c r="C862" s="13" t="s">
+        <v>2798</v>
+      </c>
+      <c r="D862" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E862" s="13" t="s">
+        <v>2748</v>
+      </c>
+      <c r="F862" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A863" s="13" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C863" s="13" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D863" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E863" s="13" t="s">
+        <v>2749</v>
+      </c>
+      <c r="F863" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A864" s="13" t="s">
+        <v>2801</v>
+      </c>
+      <c r="C864" s="13" t="s">
+        <v>2802</v>
+      </c>
+      <c r="D864" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E864" s="13" t="s">
+        <v>2750</v>
+      </c>
+      <c r="F864" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A865" s="13" t="s">
+        <v>2803</v>
+      </c>
+      <c r="C865" s="13" t="s">
+        <v>2804</v>
+      </c>
+      <c r="D865" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E865" s="13" t="s">
+        <v>2751</v>
+      </c>
+      <c r="F865" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A866" s="13" t="s">
+        <v>2805</v>
+      </c>
+      <c r="C866" s="13" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D866" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E866" s="13" t="s">
+        <v>2752</v>
+      </c>
+      <c r="F866" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A867" s="13" t="s">
+        <v>2807</v>
+      </c>
+      <c r="C867" s="13" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D867" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E867" s="13" t="s">
+        <v>2753</v>
+      </c>
+      <c r="F867" s="13" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A868" s="13" t="s">
+        <v>2809</v>
+      </c>
+      <c r="C868" s="13" t="s">
+        <v>2810</v>
+      </c>
+      <c r="D868" s="13" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E868" s="13" t="s">
+        <v>2754</v>
+      </c>
+      <c r="F868" s="13" t="s">
+        <v>2661</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I868" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93">
-    <cfRule type="duplicateValues" dxfId="32" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A142:A145">
     <cfRule type="duplicateValues" dxfId="30" priority="66"/>
@@ -29286,19 +30037,19 @@
     <cfRule type="duplicateValues" dxfId="26" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
     <cfRule type="duplicateValues" dxfId="23" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="22" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C96">
-    <cfRule type="duplicateValues" dxfId="20" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
     <cfRule type="duplicateValues" dxfId="18" priority="104"/>
@@ -29310,24 +30061,24 @@
     <cfRule type="duplicateValues" dxfId="16" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401">
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="8" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
     <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A122" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BAFB67-2ABB-4D1F-9E82-11318C988AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690AF3F8-13A2-4772-A982-B5FF5A7DE602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5121" uniqueCount="2817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="2869">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8488,6 +8488,162 @@
   </si>
   <si>
     <t>24 Channel Mixer With Carry Case</t>
+  </si>
+  <si>
+    <t>AA-26 Pro</t>
+  </si>
+  <si>
+    <t>FBA80124</t>
+  </si>
+  <si>
+    <t>AA-28</t>
+  </si>
+  <si>
+    <t>FBA80125</t>
+  </si>
+  <si>
+    <t>AA-29</t>
+  </si>
+  <si>
+    <t>FBA80126</t>
+  </si>
+  <si>
+    <t>AM-C49</t>
+  </si>
+  <si>
+    <t>B0GW8Z556N</t>
+  </si>
+  <si>
+    <t>FBA80009</t>
+  </si>
+  <si>
+    <t>FBA80010</t>
+  </si>
+  <si>
+    <t>FBA80119</t>
+  </si>
+  <si>
+    <t>FBA80120</t>
+  </si>
+  <si>
+    <t>AM-C50</t>
+  </si>
+  <si>
+    <t>AM-C51</t>
+  </si>
+  <si>
+    <t>AM-C52</t>
+  </si>
+  <si>
+    <t>AM-C53</t>
+  </si>
+  <si>
+    <t>AM-C54</t>
+  </si>
+  <si>
+    <t>SP-01</t>
+  </si>
+  <si>
+    <t>FBA79971</t>
+  </si>
+  <si>
+    <t>B0GGHZWMVW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexlev </t>
+  </si>
+  <si>
+    <t>FBA79988</t>
+  </si>
+  <si>
+    <t>B0GN8N96R5</t>
+  </si>
+  <si>
+    <t>AP-04</t>
+  </si>
+  <si>
+    <t>FBA79989</t>
+  </si>
+  <si>
+    <t>B0GN86G345</t>
+  </si>
+  <si>
+    <t>CAP-05</t>
+  </si>
+  <si>
+    <t>FBA79992</t>
+  </si>
+  <si>
+    <t>B0GN94YDY2</t>
+  </si>
+  <si>
+    <t>ST-02</t>
+  </si>
+  <si>
+    <t>FBA79993</t>
+  </si>
+  <si>
+    <t>B0GN8WW6BC</t>
+  </si>
+  <si>
+    <t>ST-03</t>
+  </si>
+  <si>
+    <t>FBA80085</t>
+  </si>
+  <si>
+    <t>B0GXPBHDRF</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>FBA80084</t>
+  </si>
+  <si>
+    <t>B0GXP97CZG</t>
+  </si>
+  <si>
+    <t>BE-4</t>
+  </si>
+  <si>
+    <t>FBA79984</t>
+  </si>
+  <si>
+    <t>B0GM1CZC7Y</t>
+  </si>
+  <si>
+    <t>MR-03</t>
+  </si>
+  <si>
+    <t>FBA80109</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>FBA80110</t>
+  </si>
+  <si>
+    <t>X5</t>
+  </si>
+  <si>
+    <t>FBA80121</t>
+  </si>
+  <si>
+    <t>AM-C55</t>
+  </si>
+  <si>
+    <t>FBA80122</t>
+  </si>
+  <si>
+    <t>AM-C56</t>
+  </si>
+  <si>
+    <t>FBA80123</t>
+  </si>
+  <si>
+    <t>AM-W25</t>
   </si>
 </sst>
 </file>
@@ -9355,13 +9511,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:I868"/>
+  <dimension ref="A1:I893"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.77734375" style="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.109375" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.88671875" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="50.88671875" style="13" bestFit="1" customWidth="1"/>
@@ -30010,6 +30166,332 @@
       </c>
       <c r="F868" s="13" t="s">
         <v>2661</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A869" s="13" t="s">
+        <v>2818</v>
+      </c>
+      <c r="D869" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E869" s="13" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A870" s="13" t="s">
+        <v>2820</v>
+      </c>
+      <c r="D870" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E870" s="13" t="s">
+        <v>2819</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A871" s="13" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D871" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E871" s="13" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A872" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="C872" s="13" t="s">
+        <v>2824</v>
+      </c>
+      <c r="D872" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E872" s="13" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A873" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="D873" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E873" s="13" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A874" s="13" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D874" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E874" s="13" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A875" s="13" t="s">
+        <v>2826</v>
+      </c>
+      <c r="D875" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E875" s="13" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A876" s="13" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D876" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E876" s="13" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A877" s="13" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D877" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E877" s="13" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A878" s="13" t="s">
+        <v>2835</v>
+      </c>
+      <c r="C878" s="13" t="s">
+        <v>2836</v>
+      </c>
+      <c r="D878" s="13" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E878" s="13" t="s">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A879" s="13" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C879" s="13" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D879" s="13" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E879" s="13" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A880" s="13" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C880" s="13" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D880" s="13" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E880" s="13" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="881" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A881" s="13" t="s">
+        <v>2844</v>
+      </c>
+      <c r="C881" s="13" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D881" s="13" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E881" s="13" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="882" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A882" s="13" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C882" s="13" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D882" s="13" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E882" s="13" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A883" s="13" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C883" s="13" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D883" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E883" s="13" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="884" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A884" s="13" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C884" s="13" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D884" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E884" s="13" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="885" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A885" s="13" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C885" s="13" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D885" s="13" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E885" s="13" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="886" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A886" s="13" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C886" s="13" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D886" s="13" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E886" s="13" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="887" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A887" s="13" t="s">
+        <v>2850</v>
+      </c>
+      <c r="C887" s="13" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D887" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E887" s="13" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="888" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A888" s="13" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C888" s="13" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D888" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E888" s="13" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="889" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A889" s="13" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C889" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D889" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E889" s="13" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="890" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A890" s="13" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C890" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D890" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E890" s="13" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="891" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A891" s="13" t="s">
+        <v>2863</v>
+      </c>
+      <c r="C891" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D891" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E891" s="13" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="892" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A892" s="13" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C892" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D892" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E892" s="13" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="893" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A893" s="13" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C893" s="13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D893" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E893" s="13" t="s">
+        <v>2868</v>
       </c>
     </row>
   </sheetData>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFA4518-4A73-4CE9-949F-D2C828ED58E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09DB798-8221-4884-9756-E2898909A798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5347" uniqueCount="2960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5348" uniqueCount="2961">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8917,6 +8917,9 @@
   </si>
   <si>
     <t>B0GW96CQMG</t>
+  </si>
+  <si>
+    <t>B0H1H3K6B2</t>
   </si>
 </sst>
 </file>
@@ -9118,40 +9121,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -9256,6 +9225,40 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -31360,8 +31363,8 @@
         <v>2888</v>
       </c>
       <c r="B903" s="2"/>
-      <c r="C903" s="2" t="e">
-        <v>#N/A</v>
+      <c r="C903" s="2" t="s">
+        <v>2960</v>
       </c>
       <c r="D903" s="2" t="s">
         <v>523</v>
@@ -31636,8 +31639,8 @@
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A93">
-    <cfRule type="duplicateValues" dxfId="32" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A142:A145">
     <cfRule type="duplicateValues" dxfId="30" priority="66"/>
@@ -31655,48 +31658,48 @@
     <cfRule type="duplicateValues" dxfId="26" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="25" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B123">
     <cfRule type="duplicateValues" dxfId="23" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="22" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C96">
-    <cfRule type="duplicateValues" dxfId="20" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="18" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E125:E141">
-    <cfRule type="duplicateValues" dxfId="18" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142">
-    <cfRule type="duplicateValues" dxfId="17" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
     <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
     <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="16" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A122" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09DB798-8221-4884-9756-E2898909A798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1ACE144-34E3-4440-87B4-2B4EB3AE0438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BE5AA2-7268-4684-9FD3-4490AB572BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE3D72C-F15A-4927-991E-7B6E3D90A7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6273" uniqueCount="3028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6273" uniqueCount="3027">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8509,9 +8509,6 @@
   </si>
   <si>
     <t>B0GGHZWMVW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nexlev </t>
   </si>
   <si>
     <t>FBA79988</t>
@@ -10027,16 +10024,16 @@
         <v>521</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>2957</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>2958</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>2959</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>518</v>
@@ -10104,10 +10101,10 @@
         <v>2399</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>2960</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>2961</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>176</v>
@@ -10145,13 +10142,13 @@
         <v>3999</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>2961</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>2962</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>357</v>
@@ -10186,13 +10183,13 @@
         <v>699</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>357</v>
@@ -10227,10 +10224,10 @@
         <v>699</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>747</v>
@@ -10268,10 +10265,10 @@
         <v>699</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>747</v>
@@ -10474,10 +10471,10 @@
         <v>2199</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>747</v>
@@ -10614,13 +10611,13 @@
         <v>2399</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>357</v>
@@ -10655,10 +10652,10 @@
         <v>2999</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>2960</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>2961</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>5</v>
@@ -10696,10 +10693,10 @@
         <v>999</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>747</v>
@@ -10737,10 +10734,10 @@
         <v>1999</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>747</v>
@@ -10778,10 +10775,10 @@
         <v>1059</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>747</v>
@@ -10819,10 +10816,10 @@
         <v>1999</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>22</v>
@@ -10860,13 +10857,13 @@
         <v>1399</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>358</v>
@@ -10901,10 +10898,10 @@
         <v>799</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>747</v>
@@ -10942,10 +10939,10 @@
         <v>799</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>747</v>
@@ -10983,10 +10980,10 @@
         <v>3799</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>747</v>
@@ -11024,10 +11021,10 @@
         <v>7199</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>747</v>
@@ -11065,10 +11062,10 @@
         <v>1499</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>143</v>
@@ -11106,10 +11103,10 @@
         <v>899</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>747</v>
@@ -11147,13 +11144,13 @@
         <v>999</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>358</v>
@@ -11188,13 +11185,13 @@
         <v>1499</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>358</v>
@@ -11229,10 +11226,10 @@
         <v>799</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>104</v>
@@ -11270,10 +11267,10 @@
         <v>799</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>747</v>
@@ -11375,10 +11372,10 @@
         <v>999</v>
       </c>
       <c r="G36" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>747</v>
@@ -11416,10 +11413,10 @@
         <v>1099</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>747</v>
@@ -11490,13 +11487,13 @@
         <v>1199</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="I39" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>357</v>
@@ -11531,13 +11528,13 @@
         <v>299</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>358</v>
@@ -11572,13 +11569,13 @@
         <v>299</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>358</v>
@@ -11646,10 +11643,10 @@
         <v>1249</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>747</v>
@@ -11687,10 +11684,10 @@
         <v>1699</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>747</v>
@@ -11728,10 +11725,10 @@
         <v>1949</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>747</v>
@@ -11769,10 +11766,10 @@
         <v>2699</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>747</v>
@@ -11810,10 +11807,10 @@
         <v>3399</v>
       </c>
       <c r="G47" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>2960</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>2961</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>8</v>
@@ -11851,10 +11848,10 @@
         <v>1999</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>747</v>
@@ -11892,10 +11889,10 @@
         <v>1699</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>747</v>
@@ -11966,10 +11963,10 @@
         <v>209</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>747</v>
@@ -12007,10 +12004,10 @@
         <v>2499</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>84</v>
@@ -12048,10 +12045,10 @@
         <v>1499</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>50</v>
@@ -12089,13 +12086,13 @@
         <v>999</v>
       </c>
       <c r="G54" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="I54" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>357</v>
@@ -12130,10 +12127,10 @@
         <v>1199</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>162</v>
@@ -12204,10 +12201,10 @@
         <v>3899</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>747</v>
@@ -12245,10 +12242,10 @@
         <v>1529</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>747</v>
@@ -12286,10 +12283,10 @@
         <v>1399</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>40</v>
@@ -12327,10 +12324,10 @@
         <v>1699</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>180</v>
@@ -12368,10 +12365,10 @@
         <v>1949</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>178</v>
@@ -12409,10 +12406,10 @@
         <v>1999</v>
       </c>
       <c r="G62" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>747</v>
@@ -12450,13 +12447,13 @@
         <v>1999</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>357</v>
@@ -12491,10 +12488,10 @@
         <v>1999</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>747</v>
@@ -12532,13 +12529,13 @@
         <v>1999</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H65" s="2" t="s">
+        <v>2963</v>
+      </c>
+      <c r="I65" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>358</v>
@@ -12573,13 +12570,13 @@
         <v>1399</v>
       </c>
       <c r="G66" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="I66" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>357</v>
@@ -12647,10 +12644,10 @@
         <v>1999</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>20</v>
@@ -12688,10 +12685,10 @@
         <v>2099</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>32</v>
@@ -12729,13 +12726,13 @@
         <v>2299</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>358</v>
@@ -12770,13 +12767,13 @@
         <v>2049</v>
       </c>
       <c r="G71" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H71" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H71" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I71" s="2" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>358</v>
@@ -12811,13 +12808,13 @@
         <v>2499</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H72" s="2" t="s">
+        <v>2963</v>
+      </c>
+      <c r="I72" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>357</v>
@@ -12852,10 +12849,10 @@
         <v>2299</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>52</v>
@@ -12893,13 +12890,13 @@
         <v>5999</v>
       </c>
       <c r="G74" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H74" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I74" s="2" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>357</v>
@@ -12967,10 +12964,10 @@
         <v>1799</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>747</v>
@@ -13074,10 +13071,10 @@
         <v>2499</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>747</v>
@@ -13181,10 +13178,10 @@
         <v>1699</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>747</v>
@@ -13222,10 +13219,10 @@
         <v>2999</v>
       </c>
       <c r="G83" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H83" s="2" t="s">
         <v>2960</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>2961</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>243</v>
@@ -13263,13 +13260,13 @@
         <v>1499</v>
       </c>
       <c r="G84" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="I84" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>358</v>
@@ -13286,7 +13283,7 @@
     </row>
     <row r="85" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>67</v>
@@ -13469,10 +13466,10 @@
         <v>1799</v>
       </c>
       <c r="G90" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>747</v>
@@ -13576,13 +13573,13 @@
         <v>1499</v>
       </c>
       <c r="G93" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H93" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="I93" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>357</v>
@@ -13617,13 +13614,13 @@
         <v>3149</v>
       </c>
       <c r="G94" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H94" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H94" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I94" s="2" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>357</v>
@@ -13658,13 +13655,13 @@
         <v>799</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H95" s="2" t="s">
+        <v>2963</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>358</v>
@@ -13798,10 +13795,10 @@
         <v>999</v>
       </c>
       <c r="G99" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>747</v>
@@ -13839,13 +13836,13 @@
         <v>999</v>
       </c>
       <c r="G100" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="I100" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>357</v>
@@ -13880,13 +13877,13 @@
         <v>5999</v>
       </c>
       <c r="G101" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H101" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I101" s="2" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>357</v>
@@ -13921,10 +13918,10 @@
         <v>1999</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>54</v>
@@ -13962,10 +13959,10 @@
         <v>1799</v>
       </c>
       <c r="G103" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>2960</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>2961</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>42</v>
@@ -14003,13 +14000,13 @@
         <v>16990</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>357</v>
@@ -14110,13 +14107,13 @@
         <v>899</v>
       </c>
       <c r="G107" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="I107" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J107" s="3" t="s">
         <v>358</v>
@@ -14151,13 +14148,13 @@
         <v>2119</v>
       </c>
       <c r="G108" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>2963</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="I108" s="2" t="s">
         <v>2964</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>2965</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>358</v>
@@ -14225,10 +14222,10 @@
         <v>5999</v>
       </c>
       <c r="G110" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>747</v>
@@ -14299,10 +14296,10 @@
         <v>4199</v>
       </c>
       <c r="G112" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>2960</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>2961</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>208</v>
@@ -14340,10 +14337,10 @@
         <v>3499</v>
       </c>
       <c r="G113" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>747</v>
@@ -14447,10 +14444,10 @@
         <v>799</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>156</v>
@@ -14488,10 +14485,10 @@
         <v>749</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>747</v>
@@ -14529,10 +14526,10 @@
         <v>599</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>747</v>
@@ -14570,10 +14567,10 @@
         <v>599</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>747</v>
@@ -14611,10 +14608,10 @@
         <v>2399</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>747</v>
@@ -14652,10 +14649,10 @@
         <v>399</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>1616</v>
@@ -14693,10 +14690,10 @@
         <v>4999</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>58</v>
@@ -14734,13 +14731,13 @@
         <v>1499</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="J123" s="3" t="s">
         <v>358</v>
@@ -14775,10 +14772,10 @@
         <v>1499</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>241</v>
@@ -15509,10 +15506,10 @@
         <v>5999</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>747</v>
@@ -15546,13 +15543,13 @@
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H147" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H147" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I147" s="2" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>1101</v>
@@ -15581,13 +15578,13 @@
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H148" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H148" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I148" s="2" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>1102</v>
@@ -15616,13 +15613,13 @@
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H149" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H149" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I149" s="2" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>1104</v>
@@ -15651,13 +15648,13 @@
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H150" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H150" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I150" s="2" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>1102</v>
@@ -15686,13 +15683,13 @@
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H151" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H151" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I151" s="2" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>1107</v>
@@ -15721,10 +15718,10 @@
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>747</v>
@@ -15756,10 +15753,10 @@
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H153" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I153" s="2" t="s">
         <v>747</v>
@@ -15791,13 +15788,13 @@
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>1110</v>
@@ -15826,13 +15823,13 @@
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>1112</v>
@@ -15861,13 +15858,13 @@
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H156" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H156" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I156" s="2" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>1101</v>
@@ -15896,10 +15893,10 @@
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>747</v>
@@ -15931,13 +15928,13 @@
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H158" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H158" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I158" s="2" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>1102</v>
@@ -15966,13 +15963,13 @@
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H159" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H159" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I159" s="2" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>1102</v>
@@ -16001,19 +15998,19 @@
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H160" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H160" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I160" s="2" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="11">
@@ -16036,13 +16033,13 @@
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H161" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H161" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I161" s="2" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>1112</v>
@@ -16071,13 +16068,13 @@
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>1101</v>
@@ -16106,13 +16103,13 @@
       </c>
       <c r="F163" s="2"/>
       <c r="G163" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>1107</v>
@@ -16141,10 +16138,10 @@
       </c>
       <c r="F164" s="2"/>
       <c r="G164" s="2" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I164" s="2" t="s">
         <v>747</v>
@@ -16176,13 +16173,13 @@
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2" t="s">
+        <v>2995</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>2960</v>
+      </c>
+      <c r="I165" s="2" t="s">
         <v>2996</v>
-      </c>
-      <c r="H165" s="2" t="s">
-        <v>2961</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>2997</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>1121</v>
@@ -16211,13 +16208,13 @@
       </c>
       <c r="F166" s="2"/>
       <c r="G166" s="2" t="s">
+        <v>2995</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>2960</v>
+      </c>
+      <c r="I166" s="2" t="s">
         <v>2996</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>2961</v>
-      </c>
-      <c r="I166" s="2" t="s">
-        <v>2997</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>1121</v>
@@ -16246,10 +16243,10 @@
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I167" s="2" t="s">
         <v>747</v>
@@ -16281,10 +16278,10 @@
       </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I168" s="2" t="s">
         <v>747</v>
@@ -16312,14 +16309,14 @@
         <v>523</v>
       </c>
       <c r="E169" s="24" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I169" s="2" t="s">
         <v>747</v>
@@ -16351,10 +16348,10 @@
       </c>
       <c r="F170" s="2"/>
       <c r="G170" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I170" s="2" t="s">
         <v>747</v>
@@ -16386,13 +16383,13 @@
       </c>
       <c r="F171" s="2"/>
       <c r="G171" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H171" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H171" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I171" s="2" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>1117</v>
@@ -16421,10 +16418,10 @@
       </c>
       <c r="F172" s="2"/>
       <c r="G172" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>747</v>
@@ -16456,13 +16453,13 @@
       </c>
       <c r="F173" s="2"/>
       <c r="G173" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>1130</v>
@@ -16491,10 +16488,10 @@
       </c>
       <c r="F174" s="2"/>
       <c r="G174" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I174" s="2" t="s">
         <v>752</v>
@@ -16526,13 +16523,13 @@
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>1107</v>
@@ -16561,13 +16558,13 @@
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>1107</v>
@@ -16596,13 +16593,13 @@
       </c>
       <c r="F177" s="2"/>
       <c r="G177" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>1130</v>
@@ -16631,10 +16628,10 @@
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I178" s="2" t="s">
         <v>747</v>
@@ -16666,10 +16663,10 @@
       </c>
       <c r="F179" s="2"/>
       <c r="G179" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I179" s="2" t="s">
         <v>747</v>
@@ -16701,13 +16698,13 @@
       </c>
       <c r="F180" s="2"/>
       <c r="G180" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>1102</v>
@@ -16736,13 +16733,13 @@
       </c>
       <c r="F181" s="2"/>
       <c r="G181" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>1112</v>
@@ -16771,13 +16768,13 @@
       </c>
       <c r="F182" s="2"/>
       <c r="G182" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>1117</v>
@@ -16806,13 +16803,13 @@
       </c>
       <c r="F183" s="2"/>
       <c r="G183" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H183" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H183" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I183" s="2" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>1117</v>
@@ -16841,10 +16838,10 @@
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H184" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H184" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I184" s="2" t="s">
         <v>747</v>
@@ -16876,13 +16873,13 @@
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>1112</v>
@@ -16911,13 +16908,13 @@
       </c>
       <c r="F186" s="2"/>
       <c r="G186" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H186" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H186" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I186" s="2" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>1130</v>
@@ -16946,10 +16943,10 @@
       </c>
       <c r="F187" s="2"/>
       <c r="G187" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H187" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H187" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I187" s="2" t="s">
         <v>747</v>
@@ -16981,13 +16978,13 @@
       </c>
       <c r="F188" s="2"/>
       <c r="G188" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>1130</v>
@@ -17016,10 +17013,10 @@
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I189" s="2" t="s">
         <v>747</v>
@@ -17051,13 +17048,13 @@
       </c>
       <c r="F190" s="2"/>
       <c r="G190" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>1102</v>
@@ -17086,13 +17083,13 @@
       </c>
       <c r="F191" s="2"/>
       <c r="G191" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I191" s="2" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>1101</v>
@@ -17121,13 +17118,13 @@
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>1117</v>
@@ -17156,13 +17153,13 @@
       </c>
       <c r="F193" s="2"/>
       <c r="G193" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I193" s="2" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>1117</v>
@@ -17191,10 +17188,10 @@
       </c>
       <c r="F194" s="2"/>
       <c r="G194" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I194" s="2" t="s">
         <v>747</v>
@@ -17226,19 +17223,19 @@
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="11">
@@ -17261,13 +17258,13 @@
       </c>
       <c r="F196" s="2"/>
       <c r="G196" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H196" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H196" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I196" s="2" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>1112</v>
@@ -17296,13 +17293,13 @@
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I197" s="2" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>1128</v>
@@ -17331,10 +17328,10 @@
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I198" s="2" t="s">
         <v>747</v>
@@ -17366,13 +17363,13 @@
       </c>
       <c r="F199" s="2"/>
       <c r="G199" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H199" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H199" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I199" s="2" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>1130</v>
@@ -17401,13 +17398,13 @@
       </c>
       <c r="F200" s="2"/>
       <c r="G200" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>1112</v>
@@ -17436,10 +17433,10 @@
       </c>
       <c r="F201" s="2"/>
       <c r="G201" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H201" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H201" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I201" s="2" t="s">
         <v>747</v>
@@ -17471,13 +17468,13 @@
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>1130</v>
@@ -17506,10 +17503,10 @@
       </c>
       <c r="F203" s="2"/>
       <c r="G203" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H203" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I203" s="2" t="s">
         <v>747</v>
@@ -17541,13 +17538,13 @@
       </c>
       <c r="F204" s="2"/>
       <c r="G204" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>1130</v>
@@ -17576,13 +17573,13 @@
       </c>
       <c r="F205" s="2"/>
       <c r="G205" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>1102</v>
@@ -17611,13 +17608,13 @@
       </c>
       <c r="F206" s="2"/>
       <c r="G206" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>1110</v>
@@ -17646,10 +17643,10 @@
       </c>
       <c r="F207" s="2"/>
       <c r="G207" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H207" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I207" s="2" t="s">
         <v>747</v>
@@ -17681,13 +17678,13 @@
       </c>
       <c r="F208" s="2"/>
       <c r="G208" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>1110</v>
@@ -17716,13 +17713,13 @@
       </c>
       <c r="F209" s="2"/>
       <c r="G209" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>1128</v>
@@ -17751,13 +17748,13 @@
       </c>
       <c r="F210" s="2"/>
       <c r="G210" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>1102</v>
@@ -17786,10 +17783,10 @@
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I211" s="2" t="s">
         <v>747</v>
@@ -17821,10 +17818,10 @@
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H212" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I212" s="2" t="s">
         <v>747</v>
@@ -17856,13 +17853,13 @@
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I213" s="2" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>1130</v>
@@ -17891,13 +17888,13 @@
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>1110</v>
@@ -17926,13 +17923,13 @@
       </c>
       <c r="F215" s="2"/>
       <c r="G215" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I215" s="2" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>1102</v>
@@ -17961,13 +17958,13 @@
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I216" s="2" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>1102</v>
@@ -17996,13 +17993,13 @@
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I217" s="2" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>1110</v>
@@ -18031,13 +18028,13 @@
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I218" s="2" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>1117</v>
@@ -18066,13 +18063,13 @@
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I219" s="2" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>1130</v>
@@ -18101,10 +18098,10 @@
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I220" s="2" t="s">
         <v>747</v>
@@ -18136,13 +18133,13 @@
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I221" s="2" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>1102</v>
@@ -18171,13 +18168,13 @@
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I222" s="2" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>1117</v>
@@ -18206,13 +18203,13 @@
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I223" s="2" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>1101</v>
@@ -18241,13 +18238,13 @@
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I224" s="2" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>1128</v>
@@ -18276,13 +18273,13 @@
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I225" s="2" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>1102</v>
@@ -18311,13 +18308,13 @@
       </c>
       <c r="F226" s="2"/>
       <c r="G226" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I226" s="2" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>1117</v>
@@ -18346,13 +18343,13 @@
       </c>
       <c r="F227" s="2"/>
       <c r="G227" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I227" s="2" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>1102</v>
@@ -18381,13 +18378,13 @@
       </c>
       <c r="F228" s="2"/>
       <c r="G228" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I228" s="2" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>1128</v>
@@ -18416,13 +18413,13 @@
       </c>
       <c r="F229" s="2"/>
       <c r="G229" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I229" s="2" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>1128</v>
@@ -18451,13 +18448,13 @@
       </c>
       <c r="F230" s="2"/>
       <c r="G230" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I230" s="2" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>1102</v>
@@ -18486,13 +18483,13 @@
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I231" s="2" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>1117</v>
@@ -18521,10 +18518,10 @@
       </c>
       <c r="F232" s="2"/>
       <c r="G232" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I232" s="2" t="s">
         <v>747</v>
@@ -18556,10 +18553,10 @@
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I233" s="2" t="s">
         <v>747</v>
@@ -18591,13 +18588,13 @@
       </c>
       <c r="F234" s="2"/>
       <c r="G234" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I234" s="2" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>1102</v>
@@ -18626,13 +18623,13 @@
       </c>
       <c r="F235" s="2"/>
       <c r="G235" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H235" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H235" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I235" s="2" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>1112</v>
@@ -18661,13 +18658,13 @@
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I236" s="2" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>1128</v>
@@ -18696,13 +18693,13 @@
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I237" s="2" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>1130</v>
@@ -18731,10 +18728,10 @@
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H238" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I238" s="2" t="s">
         <v>747</v>
@@ -18766,10 +18763,10 @@
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H239" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I239" s="2" t="s">
         <v>747</v>
@@ -18801,10 +18798,10 @@
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H240" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I240" s="2" t="s">
         <v>747</v>
@@ -18836,10 +18833,10 @@
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H241" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I241" s="2" t="s">
         <v>747</v>
@@ -18871,13 +18868,13 @@
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I242" s="2" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>1128</v>
@@ -18906,13 +18903,13 @@
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I243" s="2" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>1112</v>
@@ -18941,13 +18938,13 @@
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I244" s="2" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>1147</v>
@@ -18976,13 +18973,13 @@
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>1128</v>
@@ -19011,13 +19008,13 @@
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I246" s="2" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>1150</v>
@@ -19046,13 +19043,13 @@
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I247" s="2" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>1152</v>
@@ -19081,10 +19078,10 @@
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I248" s="2" t="s">
         <v>747</v>
@@ -19116,10 +19113,10 @@
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H249" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H249" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I249" s="2" t="s">
         <v>747</v>
@@ -19151,13 +19148,13 @@
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I250" s="2" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>1102</v>
@@ -19186,13 +19183,13 @@
       </c>
       <c r="F251" s="2"/>
       <c r="G251" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I251" s="2" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>1102</v>
@@ -19221,10 +19218,10 @@
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I252" s="2" t="s">
         <v>752</v>
@@ -19256,13 +19253,13 @@
       </c>
       <c r="F253" s="2"/>
       <c r="G253" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I253" s="2" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>1102</v>
@@ -19291,13 +19288,13 @@
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I254" s="2" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>1102</v>
@@ -19326,13 +19323,13 @@
       </c>
       <c r="F255" s="2"/>
       <c r="G255" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I255" s="2" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>1147</v>
@@ -19361,13 +19358,13 @@
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I256" s="2" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>1102</v>
@@ -19396,13 +19393,13 @@
       </c>
       <c r="F257" s="2"/>
       <c r="G257" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I257" s="2" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>1147</v>
@@ -19431,10 +19428,10 @@
       </c>
       <c r="F258" s="2"/>
       <c r="G258" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H258" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I258" s="2" t="s">
         <v>747</v>
@@ -19466,13 +19463,13 @@
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I259" s="2" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>1152</v>
@@ -19491,7 +19488,7 @@
       </c>
       <c r="B260" s="2"/>
       <c r="C260" s="2" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>523</v>
@@ -19501,10 +19498,10 @@
       </c>
       <c r="F260" s="2"/>
       <c r="G260" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I260" s="2" t="s">
         <v>747</v>
@@ -19536,10 +19533,10 @@
       </c>
       <c r="F261" s="2"/>
       <c r="G261" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H261" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H261" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I261" s="2" t="s">
         <v>747</v>
@@ -19571,10 +19568,10 @@
       </c>
       <c r="F262" s="2"/>
       <c r="G262" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H262" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H262" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I262" s="2" t="s">
         <v>747</v>
@@ -19606,13 +19603,13 @@
       </c>
       <c r="F263" s="2"/>
       <c r="G263" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I263" s="2" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>1150</v>
@@ -19641,13 +19638,13 @@
       </c>
       <c r="F264" s="2"/>
       <c r="G264" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I264" s="2" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>1102</v>
@@ -19676,10 +19673,10 @@
       </c>
       <c r="F265" s="2"/>
       <c r="G265" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H265" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H265" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I265" s="2" t="s">
         <v>747</v>
@@ -19711,10 +19708,10 @@
       </c>
       <c r="F266" s="2"/>
       <c r="G266" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H266" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H266" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I266" s="2" t="s">
         <v>747</v>
@@ -19746,10 +19743,10 @@
       </c>
       <c r="F267" s="2"/>
       <c r="G267" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H267" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H267" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I267" s="2" t="s">
         <v>747</v>
@@ -19781,13 +19778,13 @@
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I268" s="2" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>1117</v>
@@ -19816,10 +19813,10 @@
       </c>
       <c r="F269" s="2"/>
       <c r="G269" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H269" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H269" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I269" s="2" t="s">
         <v>747</v>
@@ -19851,10 +19848,10 @@
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H270" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H270" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I270" s="2" t="s">
         <v>747</v>
@@ -19886,13 +19883,13 @@
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I271" s="2" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>1152</v>
@@ -19921,13 +19918,13 @@
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I272" s="2" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>1152</v>
@@ -19956,10 +19953,10 @@
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H273" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H273" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I273" s="2" t="s">
         <v>747</v>
@@ -19991,13 +19988,13 @@
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I274" s="2" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>1117</v>
@@ -20026,10 +20023,10 @@
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H275" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H275" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I275" s="2" t="s">
         <v>747</v>
@@ -20061,10 +20058,10 @@
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H276" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H276" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I276" s="2" t="s">
         <v>747</v>
@@ -20096,10 +20093,10 @@
       </c>
       <c r="F277" s="2"/>
       <c r="G277" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H277" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H277" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I277" s="2" t="s">
         <v>747</v>
@@ -20131,10 +20128,10 @@
       </c>
       <c r="F278" s="2"/>
       <c r="G278" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H278" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H278" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I278" s="2" t="s">
         <v>747</v>
@@ -20166,10 +20163,10 @@
       </c>
       <c r="F279" s="2"/>
       <c r="G279" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H279" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H279" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I279" s="2" t="s">
         <v>747</v>
@@ -20201,10 +20198,10 @@
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H280" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H280" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I280" s="2" t="s">
         <v>747</v>
@@ -20236,13 +20233,13 @@
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I281" s="2" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>1152</v>
@@ -20271,13 +20268,13 @@
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I282" s="2" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>1102</v>
@@ -20306,10 +20303,10 @@
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H283" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H283" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I283" s="2" t="s">
         <v>747</v>
@@ -20341,13 +20338,13 @@
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I284" s="2" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>1150</v>
@@ -20376,10 +20373,10 @@
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H285" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H285" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I285" s="2" t="s">
         <v>747</v>
@@ -20411,10 +20408,10 @@
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H286" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H286" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I286" s="2" t="s">
         <v>747</v>
@@ -20446,13 +20443,13 @@
       </c>
       <c r="F287" s="2"/>
       <c r="G287" s="2" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>1101</v>
@@ -20481,10 +20478,10 @@
       </c>
       <c r="F288" s="2"/>
       <c r="G288" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H288" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H288" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I288" s="2" t="s">
         <v>747</v>
@@ -20516,10 +20513,10 @@
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H289" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H289" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I289" s="2" t="s">
         <v>747</v>
@@ -20551,10 +20548,10 @@
       </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H290" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H290" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I290" s="2" t="s">
         <v>747</v>
@@ -20586,10 +20583,10 @@
       </c>
       <c r="F291" s="2"/>
       <c r="G291" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H291" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H291" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I291" s="2" t="s">
         <v>747</v>
@@ -20621,10 +20618,10 @@
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H292" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H292" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I292" s="2" t="s">
         <v>747</v>
@@ -20656,10 +20653,10 @@
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H293" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H293" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I293" s="2" t="s">
         <v>747</v>
@@ -20691,10 +20688,10 @@
       </c>
       <c r="F294" s="2"/>
       <c r="G294" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H294" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H294" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I294" s="2" t="s">
         <v>747</v>
@@ -20726,10 +20723,10 @@
       </c>
       <c r="F295" s="2"/>
       <c r="G295" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H295" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H295" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I295" s="2" t="s">
         <v>747</v>
@@ -20761,10 +20758,10 @@
       </c>
       <c r="F296" s="2"/>
       <c r="G296" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H296" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H296" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I296" s="2" t="s">
         <v>747</v>
@@ -20796,10 +20793,10 @@
       </c>
       <c r="F297" s="2"/>
       <c r="G297" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H297" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H297" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I297" s="2" t="s">
         <v>747</v>
@@ -20831,10 +20828,10 @@
       </c>
       <c r="F298" s="2"/>
       <c r="G298" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H298" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I298" s="2" t="s">
         <v>747</v>
@@ -20866,10 +20863,10 @@
       </c>
       <c r="F299" s="2"/>
       <c r="G299" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H299" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H299" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I299" s="2" t="s">
         <v>747</v>
@@ -20901,10 +20898,10 @@
       </c>
       <c r="F300" s="2"/>
       <c r="G300" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H300" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H300" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I300" s="2" t="s">
         <v>747</v>
@@ -20936,10 +20933,10 @@
       </c>
       <c r="F301" s="2"/>
       <c r="G301" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H301" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H301" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I301" s="2" t="s">
         <v>747</v>
@@ -20971,10 +20968,10 @@
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H302" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I302" s="2" t="s">
         <v>747</v>
@@ -21006,10 +21003,10 @@
       </c>
       <c r="F303" s="2"/>
       <c r="G303" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H303" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H303" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I303" s="2" t="s">
         <v>747</v>
@@ -21041,13 +21038,13 @@
       </c>
       <c r="F304" s="2"/>
       <c r="G304" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I304" s="2" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>1130</v>
@@ -21076,13 +21073,13 @@
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I305" s="2" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>1128</v>
@@ -21111,13 +21108,13 @@
       </c>
       <c r="F306" s="2"/>
       <c r="G306" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I306" s="2" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>1128</v>
@@ -21146,13 +21143,13 @@
       </c>
       <c r="F307" s="2"/>
       <c r="G307" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I307" s="2" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>1128</v>
@@ -21181,10 +21178,10 @@
       </c>
       <c r="F308" s="2"/>
       <c r="G308" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I308" s="2" t="s">
         <v>747</v>
@@ -21216,13 +21213,13 @@
       </c>
       <c r="F309" s="2"/>
       <c r="G309" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I309" s="2" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>1128</v>
@@ -21251,13 +21248,13 @@
       </c>
       <c r="F310" s="2"/>
       <c r="G310" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I310" s="2" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>1128</v>
@@ -21286,10 +21283,10 @@
       </c>
       <c r="F311" s="2"/>
       <c r="G311" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H311" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H311" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I311" s="2" t="s">
         <v>747</v>
@@ -21321,13 +21318,13 @@
       </c>
       <c r="F312" s="2"/>
       <c r="G312" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I312" s="2" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>1128</v>
@@ -21356,13 +21353,13 @@
       </c>
       <c r="F313" s="2"/>
       <c r="G313" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>1128</v>
@@ -21391,13 +21388,13 @@
       </c>
       <c r="F314" s="2"/>
       <c r="G314" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>1128</v>
@@ -21426,10 +21423,10 @@
       </c>
       <c r="F315" s="2"/>
       <c r="G315" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I315" s="2" t="s">
         <v>747</v>
@@ -21461,10 +21458,10 @@
       </c>
       <c r="F316" s="2"/>
       <c r="G316" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I316" s="2" t="s">
         <v>747</v>
@@ -21496,10 +21493,10 @@
       </c>
       <c r="F317" s="2"/>
       <c r="G317" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I317" s="2" t="s">
         <v>747</v>
@@ -21531,10 +21528,10 @@
       </c>
       <c r="F318" s="2"/>
       <c r="G318" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I318" s="2" t="s">
         <v>747</v>
@@ -21566,10 +21563,10 @@
       </c>
       <c r="F319" s="2"/>
       <c r="G319" s="2" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H319" s="2" t="s">
         <v>2963</v>
-      </c>
-      <c r="H319" s="2" t="s">
-        <v>2964</v>
       </c>
       <c r="I319" s="2" t="s">
         <v>747</v>
@@ -21601,10 +21598,10 @@
       </c>
       <c r="F320" s="2"/>
       <c r="G320" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I320" s="2" t="s">
         <v>747</v>
@@ -21636,13 +21633,13 @@
       </c>
       <c r="F321" s="2"/>
       <c r="G321" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H321" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H321" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I321" s="2" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>1110</v>
@@ -21671,13 +21668,13 @@
       </c>
       <c r="F322" s="2"/>
       <c r="G322" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I322" s="2" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>1110</v>
@@ -21706,13 +21703,13 @@
       </c>
       <c r="F323" s="2"/>
       <c r="G323" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H323" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H323" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I323" s="2" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>1174</v>
@@ -21741,13 +21738,13 @@
       </c>
       <c r="F324" s="2"/>
       <c r="G324" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>1174</v>
@@ -21776,13 +21773,13 @@
       </c>
       <c r="F325" s="2"/>
       <c r="G325" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H325" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H325" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I325" s="2" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>2799</v>
@@ -21811,10 +21808,10 @@
       </c>
       <c r="F326" s="2"/>
       <c r="G326" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I326" s="2" t="s">
         <v>747</v>
@@ -21842,14 +21839,14 @@
         <v>523</v>
       </c>
       <c r="E327" s="24" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F327" s="2"/>
       <c r="G327" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I327" s="2" t="s">
         <v>747</v>
@@ -21881,10 +21878,10 @@
       </c>
       <c r="F328" s="2"/>
       <c r="G328" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I328" s="2" t="s">
         <v>747</v>
@@ -21916,13 +21913,13 @@
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="J329" s="2" t="s">
         <v>2799</v>
@@ -21951,13 +21948,13 @@
       </c>
       <c r="F330" s="2"/>
       <c r="G330" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="J330" s="2" t="s">
         <v>2799</v>
@@ -21986,13 +21983,13 @@
       </c>
       <c r="F331" s="2"/>
       <c r="G331" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="J331" s="2" t="s">
         <v>2799</v>
@@ -22021,13 +22018,13 @@
       </c>
       <c r="F332" s="2"/>
       <c r="G332" s="2" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H332" s="2" t="s">
         <v>2960</v>
       </c>
-      <c r="H332" s="2" t="s">
-        <v>2961</v>
-      </c>
       <c r="I332" s="2" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="J332" s="2" t="s">
         <v>1110</v>
@@ -22052,14 +22049,14 @@
         <v>523</v>
       </c>
       <c r="E333" s="24" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="F333" s="2"/>
       <c r="G333" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I333" s="2" t="s">
         <v>747</v>
@@ -22091,10 +22088,10 @@
       </c>
       <c r="F334" s="2"/>
       <c r="G334" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I334" s="2" t="s">
         <v>747</v>
@@ -22126,10 +22123,10 @@
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I335" s="2" t="s">
         <v>747</v>
@@ -22151,7 +22148,7 @@
       </c>
       <c r="B336" s="2"/>
       <c r="C336" s="2" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>523</v>
@@ -22161,10 +22158,10 @@
       </c>
       <c r="F336" s="2"/>
       <c r="G336" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I336" s="2" t="s">
         <v>747</v>
@@ -22186,7 +22183,7 @@
       </c>
       <c r="B337" s="2"/>
       <c r="C337" s="2" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>523</v>
@@ -22196,10 +22193,10 @@
       </c>
       <c r="F337" s="2"/>
       <c r="G337" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I337" s="2" t="s">
         <v>747</v>
@@ -22231,10 +22228,10 @@
       </c>
       <c r="F338" s="2"/>
       <c r="G338" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I338" s="2" t="s">
         <v>747</v>
@@ -22256,7 +22253,7 @@
       </c>
       <c r="B339" s="2"/>
       <c r="C339" s="2" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>523</v>
@@ -22266,10 +22263,10 @@
       </c>
       <c r="F339" s="2"/>
       <c r="G339" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I339" s="2" t="s">
         <v>747</v>
@@ -22291,7 +22288,7 @@
       </c>
       <c r="B340" s="2"/>
       <c r="C340" s="2" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>523</v>
@@ -22301,10 +22298,10 @@
       </c>
       <c r="F340" s="2"/>
       <c r="G340" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I340" s="2" t="s">
         <v>747</v>
@@ -22326,7 +22323,7 @@
       </c>
       <c r="B341" s="2"/>
       <c r="C341" s="2" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>523</v>
@@ -22336,10 +22333,10 @@
       </c>
       <c r="F341" s="2"/>
       <c r="G341" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I341" s="2" t="s">
         <v>747</v>
@@ -22361,7 +22358,7 @@
       </c>
       <c r="B342" s="2"/>
       <c r="C342" s="2" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>523</v>
@@ -22371,10 +22368,10 @@
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I342" s="2" t="s">
         <v>747</v>
@@ -22396,7 +22393,7 @@
       </c>
       <c r="B343" s="2"/>
       <c r="C343" s="2" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>523</v>
@@ -22406,10 +22403,10 @@
       </c>
       <c r="F343" s="2"/>
       <c r="G343" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I343" s="2" t="s">
         <v>747</v>
@@ -22431,7 +22428,7 @@
       </c>
       <c r="B344" s="2"/>
       <c r="C344" s="2" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>523</v>
@@ -22441,10 +22438,10 @@
       </c>
       <c r="F344" s="2"/>
       <c r="G344" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I344" s="2" t="s">
         <v>747</v>
@@ -22466,7 +22463,7 @@
       </c>
       <c r="B345" s="2"/>
       <c r="C345" s="2" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>523</v>
@@ -22476,10 +22473,10 @@
       </c>
       <c r="F345" s="2"/>
       <c r="G345" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I345" s="2" t="s">
         <v>747</v>
@@ -22501,7 +22498,7 @@
       </c>
       <c r="B346" s="2"/>
       <c r="C346" s="2" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>523</v>
@@ -22511,10 +22508,10 @@
       </c>
       <c r="F346" s="2"/>
       <c r="G346" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I346" s="2" t="s">
         <v>747</v>
@@ -22536,7 +22533,7 @@
       </c>
       <c r="B347" s="2"/>
       <c r="C347" s="2" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>523</v>
@@ -22546,10 +22543,10 @@
       </c>
       <c r="F347" s="2"/>
       <c r="G347" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I347" s="2" t="s">
         <v>747</v>
@@ -35155,13 +35152,13 @@
       </c>
       <c r="F830" s="2"/>
       <c r="G830" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H830" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I830" s="2" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="J830" s="2" t="s">
         <v>2798</v>
@@ -35190,13 +35187,13 @@
       </c>
       <c r="F831" s="2"/>
       <c r="G831" s="2" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="H831" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I831" s="2" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="J831" s="2" t="s">
         <v>2798</v>
@@ -35225,10 +35222,10 @@
       </c>
       <c r="F832" s="2"/>
       <c r="G832" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H832" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I832" s="2" t="s">
         <v>747</v>
@@ -35260,10 +35257,10 @@
       </c>
       <c r="F833" s="2"/>
       <c r="G833" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H833" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I833" s="2" t="s">
         <v>747</v>
@@ -35295,10 +35292,10 @@
       </c>
       <c r="F834" s="2"/>
       <c r="G834" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H834" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I834" s="2" t="s">
         <v>747</v>
@@ -35330,10 +35327,10 @@
       </c>
       <c r="F835" s="2"/>
       <c r="G835" s="2" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="H835" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I835" s="2" t="s">
         <v>747</v>
@@ -36063,10 +36060,10 @@
       </c>
       <c r="F864" s="2"/>
       <c r="G864" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H864" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I864" s="2" t="s">
         <v>747</v>
@@ -36075,7 +36072,7 @@
         <v>1117</v>
       </c>
       <c r="K864" s="2" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="L864" s="2"/>
       <c r="M864" s="11">
@@ -36097,7 +36094,7 @@
       <c r="F865" s="2"/>
       <c r="G865" s="2"/>
       <c r="H865" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I865" s="2" t="s">
         <v>747</v>
@@ -36106,7 +36103,7 @@
         <v>1117</v>
       </c>
       <c r="K865" s="2" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="L865" s="2"/>
       <c r="M865" s="11">
@@ -36128,7 +36125,7 @@
       <c r="F866" s="2"/>
       <c r="G866" s="2"/>
       <c r="H866" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I866" s="2" t="s">
         <v>747</v>
@@ -36160,10 +36157,10 @@
       </c>
       <c r="F867" s="2"/>
       <c r="G867" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H867" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I867" s="2" t="s">
         <v>747</v>
@@ -36185,7 +36182,7 @@
       </c>
       <c r="B868" s="2"/>
       <c r="C868" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="D868" s="2" t="s">
         <v>523</v>
@@ -36195,10 +36192,10 @@
       </c>
       <c r="F868" s="2"/>
       <c r="G868" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H868" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I868" s="2" t="s">
         <v>747</v>
@@ -36220,7 +36217,7 @@
       </c>
       <c r="B869" s="2"/>
       <c r="C869" s="2" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="D869" s="2" t="s">
         <v>523</v>
@@ -36230,10 +36227,10 @@
       </c>
       <c r="F869" s="2"/>
       <c r="G869" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H869" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I869" s="2" t="s">
         <v>747</v>
@@ -36255,7 +36252,7 @@
       </c>
       <c r="B870" s="2"/>
       <c r="C870" s="2" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="D870" s="2" t="s">
         <v>523</v>
@@ -36265,10 +36262,10 @@
       </c>
       <c r="F870" s="2"/>
       <c r="G870" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H870" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I870" s="2" t="s">
         <v>747</v>
@@ -36298,10 +36295,10 @@
       </c>
       <c r="F871" s="2"/>
       <c r="G871" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H871" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I871" s="2" t="s">
         <v>747</v>
@@ -36310,7 +36307,7 @@
         <v>1102</v>
       </c>
       <c r="K871" s="2" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="L871" s="2"/>
       <c r="M871" s="11">
@@ -36331,10 +36328,10 @@
       </c>
       <c r="F872" s="2"/>
       <c r="G872" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H872" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I872" s="2" t="s">
         <v>747</v>
@@ -36343,7 +36340,7 @@
         <v>1102</v>
       </c>
       <c r="K872" s="2" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="L872" s="2"/>
       <c r="M872" s="11">
@@ -36359,7 +36356,7 @@
         <v>2823</v>
       </c>
       <c r="D873" s="2" t="s">
-        <v>2824</v>
+        <v>6</v>
       </c>
       <c r="E873" s="2" t="s">
         <v>2821</v>
@@ -36375,29 +36372,29 @@
     </row>
     <row r="874" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A874" s="2" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="B874" s="2"/>
       <c r="C874" s="2" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D874" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E874" s="2" t="s">
         <v>2826</v>
-      </c>
-      <c r="D874" s="2" t="s">
-        <v>2824</v>
-      </c>
-      <c r="E874" s="2" t="s">
-        <v>2827</v>
       </c>
       <c r="F874" s="2">
         <v>6199</v>
       </c>
       <c r="G874" s="2" t="s">
+        <v>2979</v>
+      </c>
+      <c r="H874" s="2" t="s">
+        <v>2960</v>
+      </c>
+      <c r="I874" s="2" t="s">
         <v>2980</v>
-      </c>
-      <c r="H874" s="2" t="s">
-        <v>2961</v>
-      </c>
-      <c r="I874" s="2" t="s">
-        <v>2981</v>
       </c>
       <c r="J874" s="2"/>
       <c r="K874" s="2"/>
@@ -36406,29 +36403,29 @@
     </row>
     <row r="875" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A875" s="2" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="B875" s="2"/>
       <c r="C875" s="2" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D875" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E875" s="2" t="s">
         <v>2832</v>
-      </c>
-      <c r="D875" s="2" t="s">
-        <v>2824</v>
-      </c>
-      <c r="E875" s="2" t="s">
-        <v>2833</v>
       </c>
       <c r="F875" s="2">
         <v>10199</v>
       </c>
       <c r="G875" s="2" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="H875" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I875" s="2" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J875" s="2"/>
       <c r="K875" s="2"/>
@@ -36437,29 +36434,29 @@
     </row>
     <row r="876" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A876" s="2" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="B876" s="2"/>
       <c r="C876" s="2" t="s">
+        <v>2834</v>
+      </c>
+      <c r="D876" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E876" s="2" t="s">
         <v>2835</v>
-      </c>
-      <c r="D876" s="2" t="s">
-        <v>2824</v>
-      </c>
-      <c r="E876" s="2" t="s">
-        <v>2836</v>
       </c>
       <c r="F876" s="2">
         <v>12499</v>
       </c>
       <c r="G876" s="2" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="H876" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I876" s="2" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="J876" s="2"/>
       <c r="K876" s="2"/>
@@ -36468,17 +36465,17 @@
     </row>
     <row r="877" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A877" s="2" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="B877" s="2"/>
       <c r="C877" s="2" t="s">
+        <v>2843</v>
+      </c>
+      <c r="D877" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E877" s="2" t="s">
         <v>2844</v>
-      </c>
-      <c r="D877" s="2" t="s">
-        <v>2824</v>
-      </c>
-      <c r="E877" s="2" t="s">
-        <v>2845</v>
       </c>
       <c r="F877" s="2"/>
       <c r="G877" s="2"/>
@@ -36491,29 +36488,29 @@
     </row>
     <row r="878" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A878" s="2" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="B878" s="2"/>
       <c r="C878" s="2" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D878" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E878" s="2" t="s">
         <v>2829</v>
-      </c>
-      <c r="D878" s="2" t="s">
-        <v>2824</v>
-      </c>
-      <c r="E878" s="2" t="s">
-        <v>2830</v>
       </c>
       <c r="F878" s="2">
         <v>2299</v>
       </c>
       <c r="G878" s="2" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="H878" s="2" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="I878" s="2" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="J878" s="2"/>
       <c r="K878" s="2"/>
@@ -36522,24 +36519,24 @@
     </row>
     <row r="879" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A879" s="2" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="B879" s="2"/>
       <c r="C879" s="2" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="D879" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E879" s="2" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="F879" s="2"/>
       <c r="G879" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H879" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I879" s="2" t="s">
         <v>747</v>
@@ -36548,7 +36545,7 @@
         <v>2799</v>
       </c>
       <c r="K879" s="2" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="L879" s="2"/>
       <c r="M879" s="11">
@@ -36557,24 +36554,24 @@
     </row>
     <row r="880" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A880" s="2" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="B880" s="2"/>
       <c r="C880" s="2" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="D880" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E880" s="2" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="F880" s="2"/>
       <c r="G880" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H880" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I880" s="2" t="s">
         <v>747</v>
@@ -36583,7 +36580,7 @@
         <v>2799</v>
       </c>
       <c r="K880" s="2" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="L880" s="2"/>
       <c r="M880" s="11">
@@ -36592,7 +36589,7 @@
     </row>
     <row r="881" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A881" s="2" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="B881" s="2"/>
       <c r="C881" s="2" t="e">
@@ -36602,7 +36599,7 @@
         <v>523</v>
       </c>
       <c r="E881" s="2" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="F881" s="2"/>
       <c r="G881" s="2"/>
@@ -36612,7 +36609,7 @@
         <v>1104</v>
       </c>
       <c r="K881" s="2" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="L881" s="2"/>
       <c r="M881" s="11">
@@ -36621,7 +36618,7 @@
     </row>
     <row r="882" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A882" s="2" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="B882" s="2"/>
       <c r="C882" s="2" t="e">
@@ -36631,7 +36628,7 @@
         <v>523</v>
       </c>
       <c r="E882" s="2" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="F882" s="2"/>
       <c r="G882" s="2"/>
@@ -36641,7 +36638,7 @@
         <v>1104</v>
       </c>
       <c r="K882" s="2" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="L882" s="2"/>
       <c r="M882" s="11">
@@ -36650,7 +36647,7 @@
     </row>
     <row r="883" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A883" s="2" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="B883" s="2"/>
       <c r="C883" s="2" t="e">
@@ -36660,7 +36657,7 @@
         <v>523</v>
       </c>
       <c r="E883" s="2" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="F883" s="2"/>
       <c r="G883" s="2"/>
@@ -36670,7 +36667,7 @@
         <v>1102</v>
       </c>
       <c r="K883" s="2" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="L883" s="2"/>
       <c r="M883" s="11">
@@ -36679,7 +36676,7 @@
     </row>
     <row r="884" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A884" s="2" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="B884" s="2"/>
       <c r="C884" s="2" t="e">
@@ -36689,7 +36686,7 @@
         <v>523</v>
       </c>
       <c r="E884" s="2" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="F884" s="2"/>
       <c r="G884" s="2"/>
@@ -36699,7 +36696,7 @@
         <v>1130</v>
       </c>
       <c r="K884" s="2" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="L884" s="2"/>
       <c r="M884" s="11">
@@ -36708,7 +36705,7 @@
     </row>
     <row r="885" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A885" s="2" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="B885" s="2"/>
       <c r="C885" s="2" t="e">
@@ -36718,7 +36715,7 @@
         <v>523</v>
       </c>
       <c r="E885" s="2" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="F885" s="2"/>
       <c r="G885" s="2"/>
@@ -36728,7 +36725,7 @@
         <v>1113</v>
       </c>
       <c r="K885" s="2" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="L885" s="2"/>
       <c r="M885" s="11">
@@ -36737,11 +36734,11 @@
     </row>
     <row r="886" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A886" s="2" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="B886" s="2"/>
       <c r="C886" s="2" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="D886" s="2" t="s">
         <v>523</v>
@@ -36751,10 +36748,10 @@
       </c>
       <c r="F886" s="2"/>
       <c r="G886" s="2" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="H886" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I886" s="2" t="s">
         <v>747</v>
@@ -36772,24 +36769,24 @@
     </row>
     <row r="887" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A887" s="2" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="B887" s="2"/>
       <c r="C887" s="2" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="D887" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E887" s="2" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="F887" s="2"/>
       <c r="G887" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H887" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I887" s="2" t="s">
         <v>747</v>
@@ -36798,7 +36795,7 @@
         <v>1128</v>
       </c>
       <c r="K887" s="2" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="L887" s="2"/>
       <c r="M887" s="11">
@@ -36807,24 +36804,24 @@
     </row>
     <row r="888" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A888" s="2" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="B888" s="2"/>
       <c r="C888" s="2" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="D888" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E888" s="2" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="F888" s="2"/>
       <c r="G888" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H888" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I888" s="2" t="s">
         <v>747</v>
@@ -36833,7 +36830,7 @@
         <v>1128</v>
       </c>
       <c r="K888" s="2" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="L888" s="2"/>
       <c r="M888" s="11">
@@ -36842,24 +36839,24 @@
     </row>
     <row r="889" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A889" s="2" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="B889" s="2"/>
       <c r="C889" s="2" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="D889" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E889" s="2" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="F889" s="2"/>
       <c r="G889" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H889" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I889" s="2" t="s">
         <v>747</v>
@@ -36868,7 +36865,7 @@
         <v>1128</v>
       </c>
       <c r="K889" s="2" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="L889" s="2"/>
       <c r="M889" s="11">
@@ -36877,24 +36874,24 @@
     </row>
     <row r="890" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A890" s="2" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="B890" s="2"/>
       <c r="C890" s="2" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="D890" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E890" s="2" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="F890" s="2"/>
       <c r="G890" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H890" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I890" s="2" t="s">
         <v>747</v>
@@ -36903,7 +36900,7 @@
         <v>1128</v>
       </c>
       <c r="K890" s="2" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="L890" s="2"/>
       <c r="M890" s="11">
@@ -36912,24 +36909,24 @@
     </row>
     <row r="891" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A891" s="2" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="B891" s="2"/>
       <c r="C891" s="2" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="D891" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E891" s="2" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="F891" s="2"/>
       <c r="G891" s="2" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="H891" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I891" s="2" t="s">
         <v>747</v>
@@ -36938,7 +36935,7 @@
         <v>1128</v>
       </c>
       <c r="K891" s="2" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="L891" s="2"/>
       <c r="M891" s="11">
@@ -36947,7 +36944,7 @@
     </row>
     <row r="892" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A892" s="2" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="B892" s="2"/>
       <c r="C892" s="2" t="e">
@@ -36957,7 +36954,7 @@
         <v>523</v>
       </c>
       <c r="E892" s="2" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="F892" s="2"/>
       <c r="G892" s="2"/>
@@ -36967,7 +36964,7 @@
         <v>1128</v>
       </c>
       <c r="K892" s="2" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="L892" s="2"/>
       <c r="M892" s="11">
@@ -36976,7 +36973,7 @@
     </row>
     <row r="893" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A893" s="2" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="B893" s="2"/>
       <c r="C893" s="2" t="e">
@@ -36986,7 +36983,7 @@
         <v>523</v>
       </c>
       <c r="E893" s="2" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="F893" s="2"/>
       <c r="G893" s="2"/>
@@ -36996,7 +36993,7 @@
         <v>1128</v>
       </c>
       <c r="K893" s="2" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="L893" s="2"/>
       <c r="M893" s="11">
@@ -37005,7 +37002,7 @@
     </row>
     <row r="894" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A894" s="2" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="B894" s="2"/>
       <c r="C894" s="2" t="e">
@@ -37015,7 +37012,7 @@
         <v>523</v>
       </c>
       <c r="E894" s="2" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="F894" s="2"/>
       <c r="G894" s="2"/>
@@ -37025,7 +37022,7 @@
         <v>2798</v>
       </c>
       <c r="K894" s="2" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="L894" s="2"/>
       <c r="M894" s="11">
@@ -37034,7 +37031,7 @@
     </row>
     <row r="895" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A895" s="2" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="B895" s="2"/>
       <c r="C895" s="2" t="e">
@@ -37044,7 +37041,7 @@
         <v>523</v>
       </c>
       <c r="E895" s="2" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="F895" s="2"/>
       <c r="G895" s="2"/>
@@ -37054,7 +37051,7 @@
         <v>2798</v>
       </c>
       <c r="K895" s="2" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="L895" s="2"/>
       <c r="M895" s="11">
@@ -37063,7 +37060,7 @@
     </row>
     <row r="896" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A896" s="2" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="B896" s="2"/>
       <c r="C896" s="2" t="e">
@@ -37073,7 +37070,7 @@
         <v>523</v>
       </c>
       <c r="E896" s="2" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="F896" s="2"/>
       <c r="G896" s="2"/>
@@ -37083,7 +37080,7 @@
         <v>2798</v>
       </c>
       <c r="K896" s="2" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="L896" s="2"/>
       <c r="M896" s="11">
@@ -37092,7 +37089,7 @@
     </row>
     <row r="897" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A897" s="2" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="B897" s="2"/>
       <c r="C897" s="2" t="e">
@@ -37102,7 +37099,7 @@
         <v>523</v>
       </c>
       <c r="E897" s="2" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="F897" s="2"/>
       <c r="G897" s="2"/>
@@ -37112,7 +37109,7 @@
         <v>2798</v>
       </c>
       <c r="K897" s="2" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="L897" s="2"/>
       <c r="M897" s="11">
@@ -37121,24 +37118,24 @@
     </row>
     <row r="898" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A898" s="2" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="B898" s="2"/>
       <c r="C898" s="2" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="D898" s="2" t="s">
         <v>523</v>
       </c>
       <c r="E898" s="2" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="F898" s="2"/>
       <c r="G898" s="2" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H898" s="2" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="I898" s="2" t="s">
         <v>747</v>
@@ -37147,7 +37144,7 @@
         <v>2799</v>
       </c>
       <c r="K898" s="2" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="L898" s="2"/>
       <c r="M898" s="11">
@@ -37156,7 +37153,7 @@
     </row>
     <row r="899" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A899" s="2" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="B899" s="2"/>
       <c r="C899" s="2" t="e">
@@ -37166,7 +37163,7 @@
         <v>523</v>
       </c>
       <c r="E899" s="2" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="F899" s="2"/>
       <c r="G899" s="2"/>
@@ -37176,7 +37173,7 @@
         <v>1156</v>
       </c>
       <c r="K899" s="2" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="L899" s="2"/>
       <c r="M899" s="11">
@@ -37185,7 +37182,7 @@
     </row>
     <row r="900" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A900" s="2" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="B900" s="2"/>
       <c r="C900" s="2" t="e">
@@ -37195,7 +37192,7 @@
         <v>523</v>
       </c>
       <c r="E900" s="2" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="F900" s="2"/>
       <c r="G900" s="2"/>
@@ -37205,7 +37202,7 @@
         <v>1156</v>
       </c>
       <c r="K900" s="2" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="L900" s="2"/>
       <c r="M900" s="11">
@@ -37214,7 +37211,7 @@
     </row>
     <row r="901" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A901" s="2" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="B901" s="2"/>
       <c r="C901" s="2" t="e">
@@ -37224,7 +37221,7 @@
         <v>523</v>
       </c>
       <c r="E901" s="2" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="F901" s="2"/>
       <c r="G901" s="2"/>
@@ -37234,7 +37231,7 @@
         <v>1156</v>
       </c>
       <c r="K901" s="2" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="L901" s="2"/>
       <c r="M901" s="11">
@@ -37243,7 +37240,7 @@
     </row>
     <row r="902" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A902" s="2" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="B902" s="2"/>
       <c r="C902" s="2" t="e">
@@ -37253,7 +37250,7 @@
         <v>523</v>
       </c>
       <c r="E902" s="2" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="F902" s="2"/>
       <c r="G902" s="2"/>
@@ -37263,7 +37260,7 @@
         <v>1156</v>
       </c>
       <c r="K902" s="2" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="L902" s="2"/>
       <c r="M902" s="11">
@@ -37272,7 +37269,7 @@
     </row>
     <row r="903" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A903" s="2" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="B903" s="2"/>
       <c r="C903" s="2" t="e">
@@ -37282,7 +37279,7 @@
         <v>523</v>
       </c>
       <c r="E903" s="2" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="F903" s="2"/>
       <c r="G903" s="2"/>
@@ -37292,7 +37289,7 @@
         <v>1156</v>
       </c>
       <c r="K903" s="2" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="L903" s="2"/>
       <c r="M903" s="11">
@@ -37301,7 +37298,7 @@
     </row>
     <row r="904" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A904" s="2" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="B904" s="2"/>
       <c r="C904" s="2" t="e">
@@ -37311,7 +37308,7 @@
         <v>523</v>
       </c>
       <c r="E904" s="2" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="F904" s="2"/>
       <c r="G904" s="2"/>
@@ -37321,7 +37318,7 @@
         <v>1156</v>
       </c>
       <c r="K904" s="2" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="L904" s="2"/>
       <c r="M904" s="11">
@@ -37330,7 +37327,7 @@
     </row>
     <row r="905" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A905" s="2" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="B905" s="2"/>
       <c r="C905" s="2" t="e">
@@ -37340,7 +37337,7 @@
         <v>523</v>
       </c>
       <c r="E905" s="2" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="F905" s="2"/>
       <c r="G905" s="2"/>
@@ -37350,7 +37347,7 @@
         <v>1156</v>
       </c>
       <c r="K905" s="2" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="L905" s="2"/>
       <c r="M905" s="11">
@@ -37359,7 +37356,7 @@
     </row>
     <row r="906" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A906" s="2" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="B906" s="2"/>
       <c r="C906" s="2" t="e">
@@ -37369,7 +37366,7 @@
         <v>523</v>
       </c>
       <c r="E906" s="2" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="F906" s="2"/>
       <c r="G906" s="2"/>
@@ -37379,7 +37376,7 @@
         <v>1156</v>
       </c>
       <c r="K906" s="2" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="L906" s="2"/>
       <c r="M906" s="11">
@@ -37388,7 +37385,7 @@
     </row>
     <row r="907" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A907" s="2" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B907" s="2"/>
       <c r="C907" s="2" t="e">
@@ -37398,7 +37395,7 @@
         <v>523</v>
       </c>
       <c r="E907" s="2" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="F907" s="2"/>
       <c r="G907" s="2"/>
@@ -37408,7 +37405,7 @@
         <v>1156</v>
       </c>
       <c r="K907" s="2" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="L907" s="2"/>
       <c r="M907" s="11">
@@ -37417,7 +37414,7 @@
     </row>
     <row r="908" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A908" s="2" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="B908" s="2"/>
       <c r="C908" s="2" t="e">
@@ -37427,17 +37424,17 @@
         <v>523</v>
       </c>
       <c r="E908" s="2" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="F908" s="2"/>
       <c r="G908" s="2"/>
       <c r="H908" s="2"/>
       <c r="I908" s="2"/>
       <c r="J908" s="2" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="K908" s="2" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="L908" s="2"/>
       <c r="M908" s="11">
@@ -37445,7 +37442,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M908" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F353C13-2289-4B64-8AD8-16978C39C26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69F1D9C-1412-4B05-A00B-CF50E69AD3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$914</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$915</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6316" uniqueCount="3033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6319" uniqueCount="3034">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -9136,13 +9136,16 @@
   </si>
   <si>
     <t>BE-4T</t>
+  </si>
+  <si>
+    <t>FBA79260</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9191,6 +9194,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -9252,7 +9263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9320,11 +9331,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10009,7 +10026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M914"/>
+  <dimension ref="A1:M915"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
@@ -15850,38 +15867,38 @@
         <v>1201.7320127999999</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
+    <row r="156" spans="1:13" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="25" t="s">
         <v>530</v>
       </c>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2" t="s">
+      <c r="B156" s="25"/>
+      <c r="C156" s="25" t="s">
         <v>734</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="D156" s="25" t="s">
         <v>521</v>
       </c>
-      <c r="E156" s="2" t="s">
+      <c r="E156" s="25" t="s">
         <v>915</v>
       </c>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2" t="s">
+      <c r="F156" s="25"/>
+      <c r="G156" s="25" t="s">
         <v>2957</v>
       </c>
-      <c r="H156" s="2" t="s">
+      <c r="H156" s="25" t="s">
         <v>2958</v>
       </c>
-      <c r="I156" s="2" t="s">
+      <c r="I156" s="25" t="s">
         <v>745</v>
       </c>
-      <c r="J156" s="2" t="s">
+      <c r="J156" s="25" t="s">
         <v>1107</v>
       </c>
-      <c r="K156" s="2" t="s">
+      <c r="K156" s="25" t="s">
         <v>1108</v>
       </c>
-      <c r="L156" s="2"/>
-      <c r="M156" s="11">
+      <c r="L156" s="25"/>
+      <c r="M156" s="26">
         <v>1679.60406096</v>
       </c>
     </row>
@@ -16421,7 +16438,7 @@
       <c r="D172" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="E172" s="24" t="s">
+      <c r="E172" s="23" t="s">
         <v>2950</v>
       </c>
       <c r="F172" s="2"/>
@@ -21986,7 +22003,7 @@
       <c r="D331" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="E331" s="24" t="s">
+      <c r="E331" s="23" t="s">
         <v>2949</v>
       </c>
       <c r="F331" s="2"/>
@@ -22739,32 +22756,32 @@
         <v>848</v>
       </c>
     </row>
-    <row r="353" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="23" t="s">
+    <row r="353" spans="1:13" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A353" s="24" t="s">
         <v>1210</v>
       </c>
-      <c r="B353" s="2"/>
-      <c r="C353" s="2" t="s">
+      <c r="B353" s="25"/>
+      <c r="C353" s="25" t="s">
         <v>1227</v>
       </c>
-      <c r="D353" s="2" t="s">
+      <c r="D353" s="25" t="s">
         <v>523</v>
       </c>
-      <c r="E353" s="2" t="s">
+      <c r="E353" s="25" t="s">
         <v>1260</v>
       </c>
-      <c r="F353" s="2"/>
-      <c r="G353" s="2"/>
-      <c r="H353" s="2"/>
-      <c r="I353" s="2"/>
-      <c r="J353" s="2" t="s">
+      <c r="F353" s="25"/>
+      <c r="G353" s="25"/>
+      <c r="H353" s="25"/>
+      <c r="I353" s="25"/>
+      <c r="J353" s="25" t="s">
         <v>1116</v>
       </c>
-      <c r="K353" s="2" t="s">
+      <c r="K353" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="L353" s="2"/>
-      <c r="M353" s="11">
+      <c r="L353" s="25"/>
+      <c r="M353" s="26">
         <v>1108</v>
       </c>
     </row>
@@ -37593,8 +37610,18 @@
         <v>3031</v>
       </c>
     </row>
+    <row r="915" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A915" t="s">
+        <v>3033</v>
+      </c>
+      <c r="D915" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E915" t="s">
+        <v>1260</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M914" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69F1D9C-1412-4B05-A00B-CF50E69AD3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3B6C08-C9DC-40A8-8400-607C7CE8B30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6319" uniqueCount="3034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6329" uniqueCount="3040">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -9139,6 +9139,24 @@
   </si>
   <si>
     <t>FBA79260</t>
+  </si>
+  <si>
+    <t>B0G1YKMFWT</t>
+  </si>
+  <si>
+    <t>FBP79569</t>
+  </si>
+  <si>
+    <t>SC-01_Mop_Cloth</t>
+  </si>
+  <si>
+    <t>FBA80113</t>
+  </si>
+  <si>
+    <t>B0GYS6CJD9</t>
+  </si>
+  <si>
+    <t>B0DS2HLR6S</t>
   </si>
 </sst>
 </file>
@@ -10026,7 +10044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M915"/>
+  <dimension ref="A1:M918"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
@@ -37619,6 +37637,42 @@
       </c>
       <c r="E915" t="s">
         <v>1260</v>
+      </c>
+    </row>
+    <row r="916" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A916" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C916" s="13" t="s">
+        <v>3034</v>
+      </c>
+      <c r="D916" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E916" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="917" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A917" s="13" t="s">
+        <v>3037</v>
+      </c>
+      <c r="C917" t="s">
+        <v>3038</v>
+      </c>
+      <c r="D917" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E917" s="13" t="s">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="918" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C918" s="13" t="s">
+        <v>3039</v>
+      </c>
+      <c r="D918" s="13" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3B6C08-C9DC-40A8-8400-607C7CE8B30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C5368B-F9E1-4116-A570-1DAE53FF9CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C5368B-F9E1-4116-A570-1DAE53FF9CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D66D190-EDCA-4956-8C2B-BD07590D461F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6329" uniqueCount="3040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6327" uniqueCount="3039">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -9154,9 +9154,6 @@
   </si>
   <si>
     <t>B0GYS6CJD9</t>
-  </si>
-  <si>
-    <t>B0DS2HLR6S</t>
   </si>
 </sst>
 </file>
@@ -9378,6 +9375,20 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -9428,20 +9439,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -10044,7 +10041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M918"/>
+  <dimension ref="A1:M917"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
@@ -37665,14 +37662,6 @@
       </c>
       <c r="E917" s="13" t="s">
         <v>3036</v>
-      </c>
-    </row>
-    <row r="918" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C918" s="13" t="s">
-        <v>3039</v>
-      </c>
-      <c r="D918" s="13" t="s">
-        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -37710,8 +37699,8 @@
     <cfRule type="duplicateValues" dxfId="21" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="20" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E127:E143">
     <cfRule type="duplicateValues" dxfId="18" priority="63"/>
@@ -37731,13 +37720,13 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="E836:E839">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
     <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">
     <cfRule type="duplicateValues" dxfId="0" priority="107"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D66D190-EDCA-4956-8C2B-BD07590D461F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DEC919-39B7-4281-8051-60C91AC70208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6327" uniqueCount="3039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6332" uniqueCount="3041">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -9154,6 +9154,12 @@
   </si>
   <si>
     <t>B0GYS6CJD9</t>
+  </si>
+  <si>
+    <t>B0DTYHXMRQ</t>
+  </si>
+  <si>
+    <t>B0BVHZ5MKZ</t>
   </si>
 </sst>
 </file>
@@ -9375,20 +9381,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -9439,6 +9431,20 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -10041,7 +10047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M917"/>
+  <dimension ref="A1:M918"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
@@ -37629,6 +37635,9 @@
       <c r="A915" t="s">
         <v>3033</v>
       </c>
+      <c r="C915" s="13" t="s">
+        <v>3039</v>
+      </c>
       <c r="D915" s="13" t="s">
         <v>523</v>
       </c>
@@ -37662,6 +37671,20 @@
       </c>
       <c r="E917" s="13" t="s">
         <v>3036</v>
+      </c>
+    </row>
+    <row r="918" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A918" s="13" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C918" s="13" t="s">
+        <v>3040</v>
+      </c>
+      <c r="D918" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="E918" s="13" t="s">
+        <v>1260</v>
       </c>
     </row>
   </sheetData>
@@ -37699,8 +37722,8 @@
     <cfRule type="duplicateValues" dxfId="21" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="20" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E127:E143">
     <cfRule type="duplicateValues" dxfId="18" priority="63"/>
@@ -37720,13 +37743,13 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="E836:E839">
     <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
     <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="16" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">
     <cfRule type="duplicateValues" dxfId="0" priority="107"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6830BC-D0D3-4AA3-84B9-EE5C05804355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85C6266-F9AE-4AD6-AC76-677040D8152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6332" uniqueCount="3041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6333" uniqueCount="3042">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -9160,6 +9160,9 @@
   </si>
   <si>
     <t>B0BVHZ5MKZ</t>
+  </si>
+  <si>
+    <t>B0H2FCK54H</t>
   </si>
 </sst>
 </file>
@@ -9270,7 +9273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9326,6 +9329,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -37147,7 +37151,9 @@
         <v>2869</v>
       </c>
       <c r="B898" s="5"/>
-      <c r="C898" s="5"/>
+      <c r="C898" s="19" t="s">
+        <v>3041</v>
+      </c>
       <c r="D898" s="5" t="s">
         <v>521</v>
       </c>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAA88DE-273D-457E-A148-7192D821578A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78574D12-5D4A-40AE-9E54-B7328B11C4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -91972,7 +91972,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M3007" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="33" priority="103"/>
   </conditionalFormatting>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78574D12-5D4A-40AE-9E54-B7328B11C4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EEFFE6-1D31-4ED3-98A8-D814A544D0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3007</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3009</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16769" uniqueCount="9295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16781" uniqueCount="9298">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -27922,6 +27922,15 @@
   </si>
   <si>
     <t>B0FTKJC5JW</t>
+  </si>
+  <si>
+    <t>FBA80181</t>
+  </si>
+  <si>
+    <t>AI-04 Pro</t>
+  </si>
+  <si>
+    <t>B0H2FNV2RC</t>
   </si>
 </sst>
 </file>
@@ -28783,7 +28792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3007"/>
+  <dimension ref="A1:M3009"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -91716,7 +91725,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2993" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2993" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2993" s="2" t="s">
         <v>7203</v>
       </c>
@@ -91733,7 +91742,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2994" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2994" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2994" s="2" t="s">
         <v>7204</v>
       </c>
@@ -91750,7 +91759,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2995" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2995" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2995" s="2" t="s">
         <v>7205</v>
       </c>
@@ -91767,7 +91776,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2996" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2996" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2996" s="2" t="s">
         <v>7206</v>
       </c>
@@ -91784,7 +91793,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2997" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2997" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2997" s="2" t="s">
         <v>7207</v>
       </c>
@@ -91801,7 +91810,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2998" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2998" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2998" s="2">
         <v>0</v>
       </c>
@@ -91818,7 +91827,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="2999" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2999" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2999" s="2">
         <v>0</v>
       </c>
@@ -91835,7 +91844,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3000" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3000" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3000" s="2" t="s">
         <v>7208</v>
       </c>
@@ -91852,7 +91861,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3001" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3001" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3001" s="2" t="s">
         <v>7209</v>
       </c>
@@ -91869,7 +91878,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3002" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3002" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3002" s="2" t="s">
         <v>7210</v>
       </c>
@@ -91886,7 +91895,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3003" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3003" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3003" s="2" t="s">
         <v>7211</v>
       </c>
@@ -91903,7 +91912,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3004" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3004" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3004" s="2" t="s">
         <v>7212</v>
       </c>
@@ -91920,7 +91929,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3005" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3005" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3005" s="2" t="s">
         <v>7213</v>
       </c>
@@ -91937,7 +91946,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3006" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3006" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3006" s="2" t="s">
         <v>7214</v>
       </c>
@@ -91954,7 +91963,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="3007" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3007" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3007" s="2" t="s">
         <v>7215</v>
       </c>
@@ -91969,6 +91978,46 @@
       </c>
       <c r="J3007" s="5" t="s">
         <v>2645</v>
+      </c>
+    </row>
+    <row r="3008" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3008" s="2" t="s">
+        <v>9295</v>
+      </c>
+      <c r="D3008" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E3008" s="2" t="s">
+        <v>9296</v>
+      </c>
+      <c r="G3008" s="2" t="s">
+        <v>2954</v>
+      </c>
+      <c r="J3008" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K3008" s="2" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="3009" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3009" s="2" t="s">
+        <v>2868</v>
+      </c>
+      <c r="C3009" s="2" t="s">
+        <v>9297</v>
+      </c>
+      <c r="D3009" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E3009" s="2" t="s">
+        <v>2896</v>
+      </c>
+      <c r="J3009" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K3009" s="2" t="s">
+        <v>2917</v>
       </c>
     </row>
   </sheetData>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EEFFE6-1D31-4ED3-98A8-D814A544D0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51803002-810A-4C69-AF65-5A946AAF9B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3009</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3040</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16781" uniqueCount="9298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16934" uniqueCount="9390">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -27931,13 +27931,289 @@
   </si>
   <si>
     <t>B0H2FNV2RC</t>
+  </si>
+  <si>
+    <t>FBA80215</t>
+  </si>
+  <si>
+    <t>SP-02</t>
+  </si>
+  <si>
+    <t>FBA80220</t>
+  </si>
+  <si>
+    <t>B0GDKG6QRV</t>
+  </si>
+  <si>
+    <t>AR11742</t>
+  </si>
+  <si>
+    <t>FBA80221</t>
+  </si>
+  <si>
+    <t>B0GDX6M95H</t>
+  </si>
+  <si>
+    <t>AR11743</t>
+  </si>
+  <si>
+    <t>FBA80222</t>
+  </si>
+  <si>
+    <t>B0GHJMFM23</t>
+  </si>
+  <si>
+    <t>AR11763</t>
+  </si>
+  <si>
+    <t>FBA80223</t>
+  </si>
+  <si>
+    <t>B0GHD9GN9C</t>
+  </si>
+  <si>
+    <t>AR11769</t>
+  </si>
+  <si>
+    <t>FBA80224</t>
+  </si>
+  <si>
+    <t>B0GTC9238R</t>
+  </si>
+  <si>
+    <t>AX4300</t>
+  </si>
+  <si>
+    <t>FBA80225</t>
+  </si>
+  <si>
+    <t>B0GTC9PS5Z</t>
+  </si>
+  <si>
+    <t>AX7178SET</t>
+  </si>
+  <si>
+    <t>FBA80226</t>
+  </si>
+  <si>
+    <t>B07SV6HR8T</t>
+  </si>
+  <si>
+    <t>DZ2237</t>
+  </si>
+  <si>
+    <t>FBA80227</t>
+  </si>
+  <si>
+    <t>B07SW9C6ZH</t>
+  </si>
+  <si>
+    <t>DZ2239</t>
+  </si>
+  <si>
+    <t>FBA80228</t>
+  </si>
+  <si>
+    <t>B07SYFYGR6</t>
+  </si>
+  <si>
+    <t>DZ4711</t>
+  </si>
+  <si>
+    <t>FBA80229</t>
+  </si>
+  <si>
+    <t>B07SYSQJDN</t>
+  </si>
+  <si>
+    <t>DZ4712</t>
+  </si>
+  <si>
+    <t>FBA80230</t>
+  </si>
+  <si>
+    <t>B0GTC2MW2C</t>
+  </si>
+  <si>
+    <t>ES5473</t>
+  </si>
+  <si>
+    <t>FBA80231</t>
+  </si>
+  <si>
+    <t>B0GTC3BMTN</t>
+  </si>
+  <si>
+    <t>ES5477</t>
+  </si>
+  <si>
+    <t>FBA80232</t>
+  </si>
+  <si>
+    <t>B0GTC7QS9P</t>
+  </si>
+  <si>
+    <t>ES5478</t>
+  </si>
+  <si>
+    <t>FBA80233</t>
+  </si>
+  <si>
+    <t>B0GTBY76NG</t>
+  </si>
+  <si>
+    <t>FS6166</t>
+  </si>
+  <si>
+    <t>FBA80234</t>
+  </si>
+  <si>
+    <t>B0GTCF15F4</t>
+  </si>
+  <si>
+    <t>FS6169</t>
+  </si>
+  <si>
+    <t>FBA80235</t>
+  </si>
+  <si>
+    <t>B0GF71S5WW</t>
+  </si>
+  <si>
+    <t>MK4992SET</t>
+  </si>
+  <si>
+    <t>FBA80236</t>
+  </si>
+  <si>
+    <t>B0GF7N3S44</t>
+  </si>
+  <si>
+    <t>MK4994SET</t>
+  </si>
+  <si>
+    <t>FBA80243</t>
+  </si>
+  <si>
+    <t>B0GTC998R6</t>
+  </si>
+  <si>
+    <t>MK7615</t>
+  </si>
+  <si>
+    <t>FBA80244</t>
+  </si>
+  <si>
+    <t>B0GTC4D5NP</t>
+  </si>
+  <si>
+    <t>MK7616</t>
+  </si>
+  <si>
+    <t>FBA80245</t>
+  </si>
+  <si>
+    <t>B0CLH9H16G</t>
+  </si>
+  <si>
+    <t>MK9107</t>
+  </si>
+  <si>
+    <t>FBA80246</t>
+  </si>
+  <si>
+    <t>B0CJJXL9TJ</t>
+  </si>
+  <si>
+    <t>MK9108</t>
+  </si>
+  <si>
+    <t>FBA80247</t>
+  </si>
+  <si>
+    <t>B0GTC5JGY7</t>
+  </si>
+  <si>
+    <t>MK9263</t>
+  </si>
+  <si>
+    <t>FBA80248</t>
+  </si>
+  <si>
+    <t>B0GTC9239V</t>
+  </si>
+  <si>
+    <t>MK9270SET</t>
+  </si>
+  <si>
+    <t>FBA80249</t>
+  </si>
+  <si>
+    <t>B0GTBY2FK6</t>
+  </si>
+  <si>
+    <t>MK9272SET</t>
+  </si>
+  <si>
+    <t>FBA80237</t>
+  </si>
+  <si>
+    <t>B0GF7CZNZC</t>
+  </si>
+  <si>
+    <t>MK7569</t>
+  </si>
+  <si>
+    <t>FBA80238</t>
+  </si>
+  <si>
+    <t>B0GF7BHFS4</t>
+  </si>
+  <si>
+    <t>MK7586</t>
+  </si>
+  <si>
+    <t>FBA80239</t>
+  </si>
+  <si>
+    <t>B0GTC5GQY4</t>
+  </si>
+  <si>
+    <t>MK7606</t>
+  </si>
+  <si>
+    <t>FBA80240</t>
+  </si>
+  <si>
+    <t>B0GTC2G6FF</t>
+  </si>
+  <si>
+    <t>MK7607</t>
+  </si>
+  <si>
+    <t>FBA80241</t>
+  </si>
+  <si>
+    <t>B0GTC6M3QM</t>
+  </si>
+  <si>
+    <t>MK7613</t>
+  </si>
+  <si>
+    <t>FBA80242</t>
+  </si>
+  <si>
+    <t>B0GTCB716R</t>
+  </si>
+  <si>
+    <t>MK7614</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -27983,6 +28259,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Bookman Old Style"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
@@ -28047,7 +28329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -28109,13 +28391,28 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="42">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28188,8 +28485,80 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28792,7 +29161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3009"/>
+  <dimension ref="A1:M3040"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -92020,72 +92389,603 @@
         <v>2917</v>
       </c>
     </row>
+    <row r="3010" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3010" s="2" t="s">
+        <v>9298</v>
+      </c>
+      <c r="D3010" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3010" s="21" t="s">
+        <v>9299</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3011" s="2" t="s">
+        <v>9300</v>
+      </c>
+      <c r="C3011" s="2" t="s">
+        <v>9301</v>
+      </c>
+      <c r="D3011" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3011" s="2" t="s">
+        <v>9302</v>
+      </c>
+      <c r="J3011" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3012" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3012" s="2" t="s">
+        <v>9303</v>
+      </c>
+      <c r="C3012" s="2" t="s">
+        <v>9304</v>
+      </c>
+      <c r="D3012" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3012" s="2" t="s">
+        <v>9305</v>
+      </c>
+      <c r="J3012" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3013" s="2" t="s">
+        <v>9306</v>
+      </c>
+      <c r="C3013" s="2" t="s">
+        <v>9307</v>
+      </c>
+      <c r="D3013" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3013" s="2" t="s">
+        <v>9308</v>
+      </c>
+      <c r="J3013" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3014" s="2" t="s">
+        <v>9309</v>
+      </c>
+      <c r="C3014" s="2" t="s">
+        <v>9310</v>
+      </c>
+      <c r="D3014" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3014" s="2" t="s">
+        <v>9311</v>
+      </c>
+      <c r="J3014" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3015" s="2" t="s">
+        <v>9312</v>
+      </c>
+      <c r="C3015" s="2" t="s">
+        <v>9313</v>
+      </c>
+      <c r="D3015" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3015" s="2" t="s">
+        <v>9314</v>
+      </c>
+      <c r="J3015" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3016" s="2" t="s">
+        <v>9315</v>
+      </c>
+      <c r="C3016" s="2" t="s">
+        <v>9316</v>
+      </c>
+      <c r="D3016" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3016" s="2" t="s">
+        <v>9317</v>
+      </c>
+      <c r="J3016" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3017" s="2" t="s">
+        <v>9318</v>
+      </c>
+      <c r="C3017" s="2" t="s">
+        <v>9319</v>
+      </c>
+      <c r="D3017" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3017" s="2" t="s">
+        <v>9320</v>
+      </c>
+      <c r="J3017" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3018" s="2" t="s">
+        <v>9321</v>
+      </c>
+      <c r="C3018" s="2" t="s">
+        <v>9322</v>
+      </c>
+      <c r="D3018" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3018" s="2" t="s">
+        <v>9323</v>
+      </c>
+      <c r="J3018" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3019" s="2" t="s">
+        <v>9324</v>
+      </c>
+      <c r="C3019" s="2" t="s">
+        <v>9325</v>
+      </c>
+      <c r="D3019" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3019" s="2" t="s">
+        <v>9326</v>
+      </c>
+      <c r="J3019" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3020" s="2" t="s">
+        <v>9327</v>
+      </c>
+      <c r="C3020" s="2" t="s">
+        <v>9328</v>
+      </c>
+      <c r="D3020" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3020" s="2" t="s">
+        <v>9329</v>
+      </c>
+      <c r="J3020" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3021" s="2" t="s">
+        <v>9330</v>
+      </c>
+      <c r="C3021" s="2" t="s">
+        <v>9331</v>
+      </c>
+      <c r="D3021" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3021" s="2" t="s">
+        <v>9332</v>
+      </c>
+      <c r="J3021" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3022" s="2" t="s">
+        <v>9333</v>
+      </c>
+      <c r="C3022" s="2" t="s">
+        <v>9334</v>
+      </c>
+      <c r="D3022" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3022" s="2" t="s">
+        <v>9335</v>
+      </c>
+      <c r="J3022" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3023" s="2" t="s">
+        <v>9336</v>
+      </c>
+      <c r="C3023" s="2" t="s">
+        <v>9337</v>
+      </c>
+      <c r="D3023" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3023" s="2" t="s">
+        <v>9338</v>
+      </c>
+      <c r="J3023" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3024" s="2" t="s">
+        <v>9339</v>
+      </c>
+      <c r="C3024" s="2" t="s">
+        <v>9340</v>
+      </c>
+      <c r="D3024" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3024" s="2" t="s">
+        <v>9341</v>
+      </c>
+      <c r="J3024" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3025" s="2" t="s">
+        <v>9342</v>
+      </c>
+      <c r="C3025" s="2" t="s">
+        <v>9343</v>
+      </c>
+      <c r="D3025" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3025" s="2" t="s">
+        <v>9344</v>
+      </c>
+      <c r="J3025" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3026" s="2" t="s">
+        <v>9345</v>
+      </c>
+      <c r="C3026" s="2" t="s">
+        <v>9346</v>
+      </c>
+      <c r="D3026" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3026" s="2" t="s">
+        <v>9347</v>
+      </c>
+      <c r="J3026" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3027" s="2" t="s">
+        <v>9348</v>
+      </c>
+      <c r="C3027" s="2" t="s">
+        <v>9349</v>
+      </c>
+      <c r="D3027" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3027" s="2" t="s">
+        <v>9350</v>
+      </c>
+      <c r="J3027" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3028" s="2" t="s">
+        <v>9351</v>
+      </c>
+      <c r="C3028" s="2" t="s">
+        <v>9352</v>
+      </c>
+      <c r="D3028" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3028" s="2" t="s">
+        <v>9353</v>
+      </c>
+      <c r="J3028" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3029" s="2" t="s">
+        <v>9354</v>
+      </c>
+      <c r="C3029" s="2" t="s">
+        <v>9355</v>
+      </c>
+      <c r="D3029" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3029" s="2" t="s">
+        <v>9356</v>
+      </c>
+      <c r="J3029" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3030" s="2" t="s">
+        <v>9357</v>
+      </c>
+      <c r="C3030" s="2" t="s">
+        <v>9358</v>
+      </c>
+      <c r="D3030" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3030" s="2" t="s">
+        <v>9359</v>
+      </c>
+      <c r="J3030" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3031" s="2" t="s">
+        <v>9360</v>
+      </c>
+      <c r="C3031" s="2" t="s">
+        <v>9361</v>
+      </c>
+      <c r="D3031" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3031" s="2" t="s">
+        <v>9362</v>
+      </c>
+      <c r="J3031" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3032" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3032" s="2" t="s">
+        <v>9363</v>
+      </c>
+      <c r="C3032" s="2" t="s">
+        <v>9364</v>
+      </c>
+      <c r="D3032" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3032" s="2" t="s">
+        <v>9365</v>
+      </c>
+      <c r="J3032" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3033" s="2" t="s">
+        <v>9366</v>
+      </c>
+      <c r="C3033" s="2" t="s">
+        <v>9367</v>
+      </c>
+      <c r="D3033" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3033" s="2" t="s">
+        <v>9368</v>
+      </c>
+      <c r="J3033" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3034" s="2" t="s">
+        <v>9369</v>
+      </c>
+      <c r="C3034" s="2" t="s">
+        <v>9370</v>
+      </c>
+      <c r="D3034" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3034" s="2" t="s">
+        <v>9371</v>
+      </c>
+      <c r="J3034" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3035" s="2" t="s">
+        <v>9372</v>
+      </c>
+      <c r="C3035" s="2" t="s">
+        <v>9373</v>
+      </c>
+      <c r="D3035" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3035" s="2" t="s">
+        <v>9374</v>
+      </c>
+      <c r="J3035" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3036" s="2" t="s">
+        <v>9375</v>
+      </c>
+      <c r="C3036" s="2" t="s">
+        <v>9376</v>
+      </c>
+      <c r="D3036" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3036" s="2" t="s">
+        <v>9377</v>
+      </c>
+      <c r="J3036" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3037" s="2" t="s">
+        <v>9378</v>
+      </c>
+      <c r="C3037" s="2" t="s">
+        <v>9379</v>
+      </c>
+      <c r="D3037" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3037" s="2" t="s">
+        <v>9380</v>
+      </c>
+      <c r="J3037" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3038" s="2" t="s">
+        <v>9381</v>
+      </c>
+      <c r="C3038" s="2" t="s">
+        <v>9382</v>
+      </c>
+      <c r="D3038" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3038" s="2" t="s">
+        <v>9383</v>
+      </c>
+      <c r="J3038" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3039" s="2" t="s">
+        <v>9384</v>
+      </c>
+      <c r="C3039" s="2" t="s">
+        <v>9385</v>
+      </c>
+      <c r="D3039" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3039" s="2" t="s">
+        <v>9386</v>
+      </c>
+      <c r="J3039" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3040" s="2" t="s">
+        <v>9387</v>
+      </c>
+      <c r="C3040" s="2" t="s">
+        <v>9388</v>
+      </c>
+      <c r="D3040" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E3040" s="2" t="s">
+        <v>9389</v>
+      </c>
+      <c r="J3040" s="5" t="s">
+        <v>2645</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="33" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A95">
-    <cfRule type="duplicateValues" dxfId="32" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A144:A147">
-    <cfRule type="duplicateValues" dxfId="30" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A837:A840">
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A126:B126">
-    <cfRule type="duplicateValues" dxfId="28" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A127:B143">
-    <cfRule type="duplicateValues" dxfId="27" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59 A96:A107 A109:A125 A21:A29 B84 A3:A19 B35 A31:A94">
-    <cfRule type="duplicateValues" dxfId="26" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="25" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
-    <cfRule type="duplicateValues" dxfId="23" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95">
-    <cfRule type="duplicateValues" dxfId="22" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="duplicateValues" dxfId="20" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E127:E143">
-    <cfRule type="duplicateValues" dxfId="18" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E144">
-    <cfRule type="duplicateValues" dxfId="17" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="15" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="16" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="15" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3010">
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A124" r:id="rId1" display="https://sellercentral.amazon.in/skucentral?mSku=FBA79849&amp;condition=New&amp;ref_=myp_skuc" xr:uid="{F5F7F880-2E3B-44E2-BABD-2E8055A5AAE6}"/>

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51803002-810A-4C69-AF65-5A946AAF9B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EC6881-2420-427E-9F67-07AAC048814E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16934" uniqueCount="9390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16938" uniqueCount="9393">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -28207,6 +28207,15 @@
   </si>
   <si>
     <t>MK7614</t>
+  </si>
+  <si>
+    <t>B0GYSS16FJ</t>
+  </si>
+  <si>
+    <t>FBA80111</t>
+  </si>
+  <si>
+    <t>MR-01_Part</t>
   </si>
 </sst>
 </file>
@@ -28423,6 +28432,28 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28485,26 +28516,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -28517,8 +28528,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -29161,7 +29170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3040"/>
+  <dimension ref="A1:M3041"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -92908,6 +92917,20 @@
       </c>
       <c r="J3040" s="5" t="s">
         <v>2645</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3041" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="C3041" s="2" t="s">
+        <v>9390</v>
+      </c>
+      <c r="D3041" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3041" s="2" t="s">
+        <v>9392</v>
       </c>
     </row>
   </sheetData>
@@ -92934,8 +92957,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -92955,9 +92978,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -92965,23 +92988,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EC6881-2420-427E-9F67-07AAC048814E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4BFCDE-E1E9-45B4-A126-9F05DC20DC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -16,9 +16,10 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3040</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3041</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16938" uniqueCount="9393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16952" uniqueCount="9393">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -28432,28 +28433,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28516,6 +28495,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -28528,6 +28527,8 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -55765,9 +55766,15 @@
       <c r="I880" s="5" t="s">
         <v>2976</v>
       </c>
-      <c r="J880" s="5"/>
-      <c r="K880" s="5"/>
-      <c r="L880" s="5"/>
+      <c r="J880" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K880" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="L880" s="5" t="s">
+        <v>393</v>
+      </c>
       <c r="M880" s="15"/>
     </row>
     <row r="881" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -55796,9 +55803,15 @@
       <c r="I881" s="5" t="s">
         <v>2977</v>
       </c>
-      <c r="J881" s="5"/>
-      <c r="K881" s="5"/>
-      <c r="L881" s="5"/>
+      <c r="J881" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K881" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="L881" s="5" t="s">
+        <v>393</v>
+      </c>
       <c r="M881" s="15"/>
     </row>
     <row r="882" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -55819,9 +55832,15 @@
       <c r="G882" s="5"/>
       <c r="H882" s="5"/>
       <c r="I882" s="5"/>
-      <c r="J882" s="5"/>
-      <c r="K882" s="5"/>
-      <c r="L882" s="5"/>
+      <c r="J882" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K882" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="L882" s="5" t="s">
+        <v>369</v>
+      </c>
       <c r="M882" s="15"/>
     </row>
     <row r="883" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -55851,7 +55870,9 @@
         <v>2978</v>
       </c>
       <c r="J883" s="5"/>
-      <c r="K883" s="5"/>
+      <c r="K883" s="5" t="s">
+        <v>367</v>
+      </c>
       <c r="L883" s="5"/>
       <c r="M883" s="15"/>
     </row>
@@ -56818,8 +56839,12 @@
       <c r="G916" s="5"/>
       <c r="H916" s="5"/>
       <c r="I916" s="5"/>
-      <c r="J916" s="5"/>
-      <c r="K916" s="5"/>
+      <c r="J916" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K916" s="16" t="s">
+        <v>1293</v>
+      </c>
       <c r="L916" s="5"/>
       <c r="M916" s="15"/>
     </row>
@@ -56887,8 +56912,12 @@
       <c r="G919" s="5"/>
       <c r="H919" s="5"/>
       <c r="I919" s="5"/>
-      <c r="J919" s="5"/>
-      <c r="K919" s="5"/>
+      <c r="J919" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K919" s="16" t="s">
+        <v>1293</v>
+      </c>
       <c r="L919" s="5"/>
       <c r="M919" s="15"/>
     </row>
@@ -92957,8 +92986,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -92978,9 +93007,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -92988,23 +93017,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976D9C33-F683-4FF6-A434-5C4FEDC16DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66BC89-0C0A-45A7-9C57-06BC79507239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$3041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3041</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16960" uniqueCount="9392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17439" uniqueCount="9404">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -28213,6 +28216,42 @@
   </si>
   <si>
     <t>MR-01_Part</t>
+  </si>
+  <si>
+    <t>IXD Non-Hazmat</t>
+  </si>
+  <si>
+    <t>IXD Hazmat</t>
+  </si>
+  <si>
+    <t>Non-IXD Non Hazmat</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Spot Cleaner</t>
+  </si>
+  <si>
+    <t>Car Air Purifier</t>
+  </si>
+  <si>
+    <t>Spares</t>
+  </si>
+  <si>
+    <t>Hazmat Type 1p</t>
+  </si>
+  <si>
+    <t>Hazmat Type 3p</t>
+  </si>
+  <si>
+    <t>DP - Charges</t>
+  </si>
+  <si>
+    <t>1p Unit Cost - (Months Name)</t>
+  </si>
+  <si>
+    <t>T-Code (EAN)</t>
   </si>
 </sst>
 </file>
@@ -28335,7 +28374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -28400,6 +28439,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28407,6 +28452,18 @@
   <dxfs count="42">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28479,28 +28536,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28525,6 +28560,16 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28850,6 +28895,378 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="AA"/>
+      <sheetName val="WM"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>ASIN</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>Master Carton</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>B0CPFS24ML</v>
+          </cell>
+          <cell r="O2">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>B0BFWD6SNF</v>
+          </cell>
+          <cell r="O3">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>B0BFVMDJ2K</v>
+          </cell>
+          <cell r="O4">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>B0BFW59TRG</v>
+          </cell>
+          <cell r="O5">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>B0BFVNS8HS</v>
+          </cell>
+          <cell r="O6">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>B0CPT3Q25C</v>
+          </cell>
+          <cell r="O7">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>B0CPT34B2L</v>
+          </cell>
+          <cell r="O8">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>B0CPT2NY5M</v>
+          </cell>
+          <cell r="O9">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>B0BF4VRJJ1</v>
+          </cell>
+          <cell r="O10">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>B0BF4TKQKN</v>
+          </cell>
+          <cell r="O11">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>B0DC3JRBW1</v>
+          </cell>
+          <cell r="O12">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>B0DQ4ZK2WQ</v>
+          </cell>
+          <cell r="O13">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>B0DQ51R95T</v>
+          </cell>
+          <cell r="O14">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>B0DQ4YWSMC</v>
+          </cell>
+          <cell r="O15">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>B0BF4S7V8C</v>
+          </cell>
+          <cell r="O16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>B0CPT25SD8</v>
+          </cell>
+          <cell r="O17">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>B0BMV1WPHL</v>
+          </cell>
+          <cell r="O18">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>B0BF4T7SWK</v>
+          </cell>
+          <cell r="O19">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>B0DQ1PKNSP</v>
+          </cell>
+          <cell r="O20">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>B0DQ1NV8D2</v>
+          </cell>
+          <cell r="O21">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>B0CPFPT6DZ</v>
+          </cell>
+          <cell r="O22">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>B0CPFN27Z2</v>
+          </cell>
+          <cell r="O23">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>B0DB5VG39T</v>
+          </cell>
+          <cell r="O24">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>B0DB5VVPSB</v>
+          </cell>
+          <cell r="O25">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>B0DB5W4TCP</v>
+          </cell>
+          <cell r="O26">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>B0DB5YTQZV</v>
+          </cell>
+          <cell r="O27">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>B0DP2WC5VW</v>
+          </cell>
+          <cell r="O28">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>B0DP2VVRND</v>
+          </cell>
+          <cell r="O29">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>B0DP313R77</v>
+          </cell>
+          <cell r="O30">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>B0DP2Z5DQ9</v>
+          </cell>
+          <cell r="O31">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>B0DP3194QN</v>
+          </cell>
+          <cell r="O32">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>B0DP32F346</v>
+          </cell>
+          <cell r="O33">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>B0FN4FHH5Y</v>
+          </cell>
+          <cell r="O34">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>B0FN4HDBN5</v>
+          </cell>
+          <cell r="O35">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>B0FN4FPJ83</v>
+          </cell>
+          <cell r="O36">
+            <v>15</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>B0FN4GQ9HT</v>
+          </cell>
+          <cell r="O37">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>B0FN4D3C89</v>
+          </cell>
+          <cell r="O38">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>B0FN4DSQ6P</v>
+          </cell>
+          <cell r="O39">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>B0FHVWHQHR</v>
+          </cell>
+          <cell r="O40">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>B0FN4HDM6Z</v>
+          </cell>
+          <cell r="O41">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>B0FN4JG97R</v>
+          </cell>
+          <cell r="O42">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>B0FN81FD8M</v>
+          </cell>
+          <cell r="O43">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>B0CPT2YJX2</v>
+          </cell>
+          <cell r="O44">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -29167,7 +29584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:M3041"/>
+  <dimension ref="A1:S3041"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -29180,10 +29597,16 @@
     <col min="11" max="11" width="50.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="30.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.109375" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="2"/>
+    <col min="14" max="14" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="2"/>
+    <col min="17" max="17" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -29223,8 +29646,26 @@
       <c r="M1" s="9" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="1" t="s">
+        <v>9399</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>9400</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>9395</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>9401</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>9402</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>9403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>111</v>
       </c>
@@ -29256,8 +29697,17 @@
       <c r="M2" s="10">
         <v>1260</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N2" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P2" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>21</v>
       </c>
@@ -29297,8 +29747,17 @@
       <c r="M3" s="10">
         <v>1260</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P3" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -29338,8 +29797,17 @@
       <c r="M4" s="10">
         <v>1786</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P4" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>61</v>
       </c>
@@ -29379,8 +29847,17 @@
       <c r="M5" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N5" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P5" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>59</v>
       </c>
@@ -29420,8 +29897,17 @@
       <c r="M6" s="10">
         <v>418</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N6" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P6" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>71</v>
       </c>
@@ -29461,8 +29947,17 @@
       <c r="M7" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P7" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>199</v>
       </c>
@@ -29494,8 +29989,17 @@
       <c r="M8" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N8" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P8" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>191</v>
       </c>
@@ -29527,8 +30031,17 @@
       <c r="M9" s="10">
         <v>558</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N9" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P9" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>125</v>
       </c>
@@ -29560,8 +30073,17 @@
       <c r="M10" s="10">
         <v>633</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P10" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>99</v>
       </c>
@@ -29593,8 +30115,17 @@
       <c r="M11" s="10">
         <v>1073</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N11" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P11" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>195</v>
       </c>
@@ -29626,8 +30157,17 @@
       <c r="M12" s="10">
         <v>527</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P12" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>169</v>
       </c>
@@ -29667,8 +30207,17 @@
       <c r="M13" s="10">
         <v>1512</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P13" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>149</v>
       </c>
@@ -29700,8 +30249,17 @@
       <c r="M14" s="10">
         <v>282</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N14" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P14" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>157</v>
       </c>
@@ -29733,8 +30291,17 @@
       <c r="M15" s="10">
         <v>282</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N15" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P15" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>97</v>
       </c>
@@ -29766,8 +30333,17 @@
       <c r="M16" s="10">
         <v>193</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N16" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P16" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>13</v>
       </c>
@@ -29807,8 +30383,17 @@
       <c r="M17" s="10">
         <v>1377</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N17" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P17" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -29848,8 +30433,17 @@
       <c r="M18" s="10">
         <v>1162</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N18" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P18" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>129</v>
       </c>
@@ -29889,8 +30483,17 @@
       <c r="M19" s="10">
         <v>533</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N19" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P19" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>77</v>
       </c>
@@ -29930,8 +30533,17 @@
       <c r="M20" s="10">
         <v>516</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P20" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>105</v>
       </c>
@@ -29971,8 +30583,17 @@
       <c r="M21" s="10">
         <v>606</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N21" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P21" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>173</v>
       </c>
@@ -30012,8 +30633,17 @@
       <c r="M22" s="10">
         <v>987</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N22" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P22" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>81</v>
       </c>
@@ -30053,8 +30683,17 @@
       <c r="M23" s="10">
         <v>728</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N23" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P23" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>151</v>
       </c>
@@ -30094,8 +30733,17 @@
       <c r="M24" s="10">
         <v>378</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N24" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P24" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>119</v>
       </c>
@@ -30135,8 +30783,17 @@
       <c r="M25" s="10">
         <v>389</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N25" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P25" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>43</v>
       </c>
@@ -30176,8 +30833,17 @@
       <c r="M26" s="10">
         <v>2357</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N26" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>73</v>
       </c>
@@ -30217,8 +30883,17 @@
       <c r="M27" s="10">
         <v>4052</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N27" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>147</v>
       </c>
@@ -30258,8 +30933,17 @@
       <c r="M28" s="10">
         <v>769</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N28" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P28" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>167</v>
       </c>
@@ -30299,8 +30983,17 @@
       <c r="M29" s="10">
         <v>444</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P29" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>137</v>
       </c>
@@ -30340,8 +31033,17 @@
       <c r="M30" s="10">
         <v>490</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P30" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>109</v>
       </c>
@@ -30381,8 +31083,17 @@
       <c r="M31" s="10">
         <v>714</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N31" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P31" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>153</v>
       </c>
@@ -30422,8 +31133,17 @@
       <c r="M32" s="10">
         <v>412</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N32" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P32" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>143</v>
       </c>
@@ -30463,8 +31183,17 @@
       <c r="M33" s="10">
         <v>413</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N33" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P33" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>141</v>
       </c>
@@ -30496,8 +31225,17 @@
       <c r="M34" s="10">
         <v>448</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N34" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P34" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>2707</v>
       </c>
@@ -30527,8 +31265,17 @@
       <c r="M35" s="10">
         <v>448</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N35" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P35" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
@@ -30568,8 +31315,17 @@
       <c r="M36" s="10">
         <v>409</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N36" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P36" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>3022</v>
       </c>
@@ -30599,8 +31355,17 @@
       <c r="M37" s="10">
         <v>409</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N37" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P37" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>3021</v>
       </c>
@@ -30640,8 +31405,17 @@
       <c r="M38" s="10">
         <v>710</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N38" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P38" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>513</v>
       </c>
@@ -30673,8 +31447,17 @@
       <c r="M39" s="10">
         <v>356</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N39" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P39" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>161</v>
       </c>
@@ -30704,8 +31487,17 @@
       <c r="M40" s="10">
         <v>356</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N40" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P40" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>65</v>
       </c>
@@ -30745,8 +31537,17 @@
       <c r="M41" s="10">
         <v>562</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N41" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P41" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>89</v>
       </c>
@@ -30786,8 +31587,17 @@
       <c r="M42" s="10">
         <v>295</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N42" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P42" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>87</v>
       </c>
@@ -30827,8 +31637,17 @@
       <c r="M43" s="10">
         <v>295</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N43" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P43" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>179</v>
       </c>
@@ -30860,8 +31679,17 @@
       <c r="M44" s="10">
         <v>193</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N44" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P44" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>95</v>
       </c>
@@ -30901,8 +31729,17 @@
       <c r="M45" s="10">
         <v>672</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N45" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P45" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>29</v>
       </c>
@@ -30942,8 +31779,17 @@
       <c r="M46" s="10">
         <v>896</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N46" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P46" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>133</v>
       </c>
@@ -30983,8 +31829,17 @@
       <c r="M47" s="10">
         <v>868</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N47" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P47" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>107</v>
       </c>
@@ -31024,8 +31879,17 @@
       <c r="M48" s="10">
         <v>961</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N48" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P48" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>4</v>
       </c>
@@ -31065,8 +31929,17 @@
       <c r="M49" s="10">
         <v>1381</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N49" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P49" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>27</v>
       </c>
@@ -31106,8 +31979,17 @@
       <c r="M50" s="10">
         <v>810</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N50" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P50" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>165</v>
       </c>
@@ -31147,8 +32029,17 @@
       <c r="M51" s="10">
         <v>1089</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N51" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P51" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>171</v>
       </c>
@@ -31180,8 +32071,17 @@
       <c r="M52" s="10">
         <v>1532</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N52" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P52" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>33</v>
       </c>
@@ -31221,8 +32121,17 @@
       <c r="M53" s="10">
         <v>1088</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N53" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P53" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>51</v>
       </c>
@@ -31262,8 +32171,17 @@
       <c r="M54" s="10">
         <v>1291</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N54" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P54" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>39</v>
       </c>
@@ -31303,8 +32221,17 @@
       <c r="M55" s="10">
         <v>560</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N55" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P55" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>177</v>
       </c>
@@ -31344,8 +32271,17 @@
       <c r="M56" s="10">
         <v>1250</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N56" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P56" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>139</v>
       </c>
@@ -31385,8 +32321,17 @@
       <c r="M57" s="10">
         <v>483</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N57" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P57" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>201</v>
       </c>
@@ -31418,8 +32363,17 @@
       <c r="M58" s="10">
         <v>2775</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N58" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P58" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>2675</v>
       </c>
@@ -31459,8 +32413,17 @@
       <c r="M59" s="10">
         <v>2775</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N59" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P59" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>131</v>
       </c>
@@ -31500,8 +32463,17 @@
       <c r="M60" s="10">
         <v>594</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N60" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P60" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>49</v>
       </c>
@@ -31541,8 +32513,17 @@
       <c r="M61" s="10">
         <v>560</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N61" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P61" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>101</v>
       </c>
@@ -31582,8 +32563,17 @@
       <c r="M62" s="10">
         <v>865</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N62" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P62" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>85</v>
       </c>
@@ -31623,8 +32613,17 @@
       <c r="M63" s="10">
         <v>814</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N63" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P63" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>175</v>
       </c>
@@ -31664,8 +32663,17 @@
       <c r="M64" s="10">
         <v>1392</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N64" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P64" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>117</v>
       </c>
@@ -31705,8 +32713,17 @@
       <c r="M65" s="10">
         <v>803</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N65" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P65" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>145</v>
       </c>
@@ -31746,8 +32763,17 @@
       <c r="M66" s="10">
         <v>1302</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N66" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P66" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>155</v>
       </c>
@@ -31787,8 +32813,17 @@
       <c r="M67" s="10">
         <v>594</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N67" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P67" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>113</v>
       </c>
@@ -31828,8 +32863,17 @@
       <c r="M68" s="10">
         <v>716</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N68" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P68" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>159</v>
       </c>
@@ -31861,8 +32905,17 @@
       <c r="M69" s="10">
         <v>460</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N69" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P69" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>31</v>
       </c>
@@ -31902,8 +32955,17 @@
       <c r="M70" s="10">
         <v>984</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N70" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P70" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>19</v>
       </c>
@@ -31943,8 +33005,17 @@
       <c r="M71" s="10">
         <v>980</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N71" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P71" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>135</v>
       </c>
@@ -31984,8 +33055,17 @@
       <c r="M72" s="10">
         <v>1095</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N72" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P72" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>79</v>
       </c>
@@ -32025,8 +33105,17 @@
       <c r="M73" s="10">
         <v>852</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N73" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P73" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>115</v>
       </c>
@@ -32066,8 +33155,17 @@
       <c r="M74" s="10">
         <v>1112</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N74" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P74" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>83</v>
       </c>
@@ -32107,8 +33205,17 @@
       <c r="M75" s="10">
         <v>1063</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N75" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P75" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>11</v>
       </c>
@@ -32148,8 +33255,17 @@
       <c r="M76" s="10">
         <v>2695</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N76" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P76" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>189</v>
       </c>
@@ -32181,8 +33297,17 @@
       <c r="M77" s="10">
         <v>721</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N77" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P77" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>25</v>
       </c>
@@ -32222,8 +33347,17 @@
       <c r="M78" s="10">
         <v>536</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N78" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P78" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>163</v>
       </c>
@@ -32255,8 +33389,17 @@
       <c r="M79" s="10">
         <v>1307</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N79" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P79" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>197</v>
       </c>
@@ -32288,8 +33431,17 @@
       <c r="M80" s="10">
         <v>709</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N80" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P80" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
@@ -32329,8 +33481,17 @@
       <c r="M81" s="10">
         <v>1345</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N81" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P81" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>183</v>
       </c>
@@ -32362,8 +33523,17 @@
       <c r="M82" s="10">
         <v>710</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N82" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P82" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>55</v>
       </c>
@@ -32395,8 +33565,17 @@
       <c r="M83" s="10">
         <v>1306</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N83" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P83" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>2676</v>
       </c>
@@ -32436,8 +33615,17 @@
       <c r="M84" s="10">
         <v>1306</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N84" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P84" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>57</v>
       </c>
@@ -32477,8 +33665,17 @@
       <c r="M85" s="10">
         <v>1014</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N85" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P85" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>67</v>
       </c>
@@ -32518,8 +33715,17 @@
       <c r="M86" s="10">
         <v>1039</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N86" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P86" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>2944</v>
       </c>
@@ -32551,8 +33757,17 @@
       <c r="M87" s="10">
         <v>1039</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N87" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P87" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>185</v>
       </c>
@@ -32584,8 +33799,17 @@
       <c r="M88" s="10">
         <v>1837</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N88" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P88" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>187</v>
       </c>
@@ -32617,8 +33841,17 @@
       <c r="M89" s="10">
         <v>890</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N89" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P89" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>193</v>
       </c>
@@ -32650,8 +33883,17 @@
       <c r="M90" s="10">
         <v>714</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N90" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P90" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>69</v>
       </c>
@@ -32683,8 +33925,17 @@
       <c r="M91" s="10">
         <v>1422</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N91" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P91" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>121</v>
       </c>
@@ -32724,8 +33975,17 @@
       <c r="M92" s="10">
         <v>926</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N92" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P92" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>181</v>
       </c>
@@ -32757,8 +34017,17 @@
       <c r="M93" s="10">
         <v>765</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N93" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P93" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>3024</v>
       </c>
@@ -32790,8 +34059,17 @@
       <c r="M94" s="10">
         <v>970</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N94" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P94" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>203</v>
       </c>
@@ -32831,8 +34109,17 @@
       <c r="M95" s="10">
         <v>954</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N95" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P95" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>35</v>
       </c>
@@ -32872,8 +34159,17 @@
       <c r="M96" s="10">
         <v>1443</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N96" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P96" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>228</v>
       </c>
@@ -32913,8 +34209,17 @@
       <c r="M97" s="10">
         <v>371</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N97" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P97" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>209</v>
       </c>
@@ -32946,8 +34251,17 @@
       <c r="M98" s="10">
         <v>975</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N98" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P98" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>211</v>
       </c>
@@ -32979,8 +34293,17 @@
       <c r="M99" s="10">
         <v>969</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N99" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P99" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>215</v>
       </c>
@@ -33012,8 +34335,17 @@
       <c r="M100" s="10">
         <v>1175</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N100" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P100" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>91</v>
       </c>
@@ -33053,8 +34385,17 @@
       <c r="M101" s="10">
         <v>501</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N101" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P101" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>207</v>
       </c>
@@ -33094,8 +34435,17 @@
       <c r="M102" s="10">
         <v>501</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N102" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P102" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>75</v>
       </c>
@@ -33135,8 +34485,17 @@
       <c r="M103" s="10">
         <v>3423</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N103" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P103" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>41</v>
       </c>
@@ -33176,8 +34535,17 @@
       <c r="M104" s="10">
         <v>829</v>
       </c>
-    </row>
-    <row r="105" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N104" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P104" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>53</v>
       </c>
@@ -33217,8 +34585,17 @@
       <c r="M105" s="10">
         <v>818</v>
       </c>
-    </row>
-    <row r="106" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N105" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P105" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>205</v>
       </c>
@@ -33258,8 +34635,17 @@
       <c r="M106" s="10">
         <v>10158</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N106" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O106" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P106" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>230</v>
       </c>
@@ -33291,8 +34677,17 @@
       <c r="M107" s="10">
         <v>6416</v>
       </c>
-    </row>
-    <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N107" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="O107" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P107" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>514</v>
       </c>
@@ -33324,8 +34719,17 @@
       <c r="M108" s="10">
         <v>781</v>
       </c>
-    </row>
-    <row r="109" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N108" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P108" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>219</v>
       </c>
@@ -33365,8 +34769,17 @@
       <c r="M109" s="10">
         <v>436</v>
       </c>
-    </row>
-    <row r="110" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N109" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P109" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>221</v>
       </c>
@@ -33406,8 +34819,17 @@
       <c r="M110" s="10">
         <v>980</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N110" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O110" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P110" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>223</v>
       </c>
@@ -33439,8 +34861,17 @@
       <c r="M111" s="10">
         <v>6146</v>
       </c>
-    </row>
-    <row r="112" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N111" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P111" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>225</v>
       </c>
@@ -33480,8 +34911,17 @@
       <c r="M112" s="10">
         <v>3229</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N112" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P112" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>213</v>
       </c>
@@ -33513,8 +34953,17 @@
       <c r="M113" s="10">
         <v>963</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N113" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P113" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>37</v>
       </c>
@@ -33554,8 +35003,17 @@
       <c r="M114" s="10">
         <v>2005</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N114" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P114" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>127</v>
       </c>
@@ -33595,8 +35053,17 @@
       <c r="M115" s="10">
         <v>1177</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N115" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P115" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>63</v>
       </c>
@@ -33628,8 +35095,17 @@
       <c r="M116" s="10">
         <v>1227</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N116" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P116" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>47</v>
       </c>
@@ -33661,8 +35137,17 @@
       <c r="M117" s="10">
         <v>2827</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N117" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O117" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P117" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>103</v>
       </c>
@@ -33702,8 +35187,17 @@
       <c r="M118" s="10">
         <v>373</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N118" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O118" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P118" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
         <v>93</v>
       </c>
@@ -33743,8 +35237,17 @@
       <c r="M119" s="10">
         <v>324</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N119" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O119" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P119" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>236</v>
       </c>
@@ -33784,8 +35287,17 @@
       <c r="M120" s="10">
         <v>261</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N120" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O120" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P120" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>234</v>
       </c>
@@ -33825,8 +35337,17 @@
       <c r="M121" s="10">
         <v>297</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N121" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P121" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>232</v>
       </c>
@@ -33866,8 +35387,17 @@
       <c r="M122" s="10">
         <v>1307</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N122" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P122" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>238</v>
       </c>
@@ -33907,8 +35437,17 @@
       <c r="M123" s="10">
         <v>145</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N123" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P123" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>240</v>
       </c>
@@ -33948,8 +35487,17 @@
       <c r="M124" s="10">
         <v>2004</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N124" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P124" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>15</v>
       </c>
@@ -33989,8 +35537,17 @@
       <c r="M125" s="10">
         <v>663</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N125" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P125" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>438</v>
       </c>
@@ -34030,8 +35587,17 @@
       <c r="M126" s="10">
         <v>899</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N126" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P126" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>439</v>
       </c>
@@ -34063,8 +35629,17 @@
       <c r="M127" s="10">
         <v>82</v>
       </c>
-    </row>
-    <row r="128" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N127" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P127" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>440</v>
       </c>
@@ -34096,8 +35671,17 @@
       <c r="M128" s="10">
         <v>40</v>
       </c>
-    </row>
-    <row r="129" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N128" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P128" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>441</v>
       </c>
@@ -34129,8 +35713,17 @@
       <c r="M129" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N129" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O129" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P129" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>442</v>
       </c>
@@ -34162,8 +35755,17 @@
       <c r="M130" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N130" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O130" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P130" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>443</v>
       </c>
@@ -34195,8 +35797,17 @@
       <c r="M131" s="10">
         <v>108</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N131" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O131" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P131" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>444</v>
       </c>
@@ -34228,8 +35839,17 @@
       <c r="M132" s="10">
         <v>145</v>
       </c>
-    </row>
-    <row r="133" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N132" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P132" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>445</v>
       </c>
@@ -34261,8 +35881,17 @@
       <c r="M133" s="10">
         <v>35</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N133" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P133" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>446</v>
       </c>
@@ -34294,8 +35923,17 @@
       <c r="M134" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="135" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N134" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O134" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P134" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>447</v>
       </c>
@@ -34327,8 +35965,17 @@
       <c r="M135" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N135" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P135" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>448</v>
       </c>
@@ -34360,8 +36007,17 @@
       <c r="M136" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N136" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P136" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>449</v>
       </c>
@@ -34393,8 +36049,17 @@
       <c r="M137" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N137" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O137" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P137" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>450</v>
       </c>
@@ -34426,8 +36091,17 @@
       <c r="M138" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N138" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O138" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P138" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>451</v>
       </c>
@@ -34459,8 +36133,17 @@
       <c r="M139" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N139" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O139" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P139" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>452</v>
       </c>
@@ -34492,8 +36175,17 @@
       <c r="M140" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N140" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O140" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P140" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>453</v>
       </c>
@@ -34525,8 +36217,17 @@
       <c r="M141" s="10">
         <v>45</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N141" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O141" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P141" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>454</v>
       </c>
@@ -34558,8 +36259,17 @@
       <c r="M142" s="10">
         <v>2350</v>
       </c>
-    </row>
-    <row r="143" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N142" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O142" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P142" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>455</v>
       </c>
@@ -34591,8 +36301,17 @@
       <c r="M143" s="10">
         <v>500</v>
       </c>
-    </row>
-    <row r="144" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N143" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O143" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P143" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="13" t="s">
         <v>456</v>
       </c>
@@ -34624,8 +36343,17 @@
       <c r="M144" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N144" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O144" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P144" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
         <v>457</v>
       </c>
@@ -34657,8 +36385,17 @@
       <c r="M145" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="146" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N145" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O145" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P145" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="13" t="s">
         <v>458</v>
       </c>
@@ -34690,8 +36427,17 @@
       <c r="M146" s="10">
         <v>2000</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N146" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O146" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P146" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="13" t="s">
         <v>459</v>
       </c>
@@ -34723,8 +36469,17 @@
       <c r="M147" s="10">
         <v>550</v>
       </c>
-    </row>
-    <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N147" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="O147" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P147" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
         <v>1606</v>
       </c>
@@ -34764,8 +36519,17 @@
       <c r="M148" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N148" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O148" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P148" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
         <v>3025</v>
       </c>
@@ -34797,8 +36561,17 @@
       <c r="M149" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N149" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="O149" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P149" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>523</v>
       </c>
@@ -34833,7 +36606,7 @@
         <v>2165.5744819986176</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
         <v>524</v>
       </c>
@@ -34868,7 +36641,7 @@
         <v>1475.9646878294116</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
         <v>525</v>
       </c>
@@ -34903,7 +36676,7 @@
         <v>4486.0109796000006</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
         <v>526</v>
       </c>
@@ -34938,7 +36711,7 @@
         <v>2021.2626509999998</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>527</v>
       </c>
@@ -34973,7 +36746,7 @@
         <v>2738.4848820000002</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
         <v>528</v>
       </c>
@@ -35008,7 +36781,7 @@
         <v>1201.7320127999999</v>
       </c>
     </row>
-    <row r="156" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="16" t="s">
         <v>529</v>
       </c>
@@ -35042,8 +36815,10 @@
       <c r="M156" s="17">
         <v>1679.60406096</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+    </row>
+    <row r="157" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>1610</v>
       </c>
@@ -35078,7 +36853,7 @@
         <v>1679.6</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>530</v>
       </c>
@@ -35113,7 +36888,7 @@
         <v>4042.5253019999996</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>531</v>
       </c>
@@ -35148,7 +36923,7 @@
         <v>1499.646483</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>532</v>
       </c>
@@ -41897,7 +43672,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="353" spans="1:13" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="16" t="s">
         <v>1209</v>
       </c>
@@ -41925,8 +43700,10 @@
       <c r="M353" s="17">
         <v>1108</v>
       </c>
-    </row>
-    <row r="354" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N353" s="2"/>
+      <c r="O353" s="2"/>
+    </row>
+    <row r="354" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="5" t="s">
         <v>1192</v>
       </c>
@@ -41955,7 +43732,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="355" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="5" t="s">
         <v>1193</v>
       </c>
@@ -41984,7 +43761,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="356" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="5" t="s">
         <v>1194</v>
       </c>
@@ -42013,7 +43790,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="357" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="5" t="s">
         <v>1195</v>
       </c>
@@ -42042,7 +43819,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="358" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="5" t="s">
         <v>1196</v>
       </c>
@@ -42071,7 +43848,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="359" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="5" t="s">
         <v>1197</v>
       </c>
@@ -42100,7 +43877,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="360" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="5" t="s">
         <v>1198</v>
       </c>
@@ -42129,7 +43906,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="361" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="5" t="s">
         <v>1199</v>
       </c>
@@ -42158,7 +43935,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="362" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="5" t="s">
         <v>1200</v>
       </c>
@@ -42187,7 +43964,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="363" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="5" t="s">
         <v>1201</v>
       </c>
@@ -42216,7 +43993,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="364" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="5" t="s">
         <v>1202</v>
       </c>
@@ -42245,7 +44022,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="365" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="5" t="s">
         <v>1203</v>
       </c>
@@ -42274,7 +44051,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="366" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="5" t="s">
         <v>1204</v>
       </c>
@@ -42303,7 +44080,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="367" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="5" t="s">
         <v>1205</v>
       </c>
@@ -42332,7 +44109,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="368" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="5" t="s">
         <v>1206</v>
       </c>
@@ -42825,7 +44602,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="385" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="5" t="s">
         <v>1224</v>
       </c>
@@ -42854,7 +44631,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="386" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="5" t="s">
         <v>1312</v>
       </c>
@@ -42882,8 +44659,15 @@
       <c r="M386" s="15">
         <v>3269</v>
       </c>
-    </row>
-    <row r="387" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N386" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P386" s="2">
+        <f>_xlfn.XLOOKUP(C386,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="5" t="s">
         <v>1313</v>
       </c>
@@ -42911,8 +44695,15 @@
       <c r="M387" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="388" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N387" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P387" s="2">
+        <f>_xlfn.XLOOKUP(C387,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="5" t="s">
         <v>1314</v>
       </c>
@@ -42940,8 +44731,15 @@
       <c r="M388" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="389" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N388" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P388" s="2">
+        <f>_xlfn.XLOOKUP(C388,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="5" t="s">
         <v>1315</v>
       </c>
@@ -42969,8 +44767,15 @@
       <c r="M389" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="390" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N389" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P389" s="2">
+        <f>_xlfn.XLOOKUP(C389,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="5" t="s">
         <v>1316</v>
       </c>
@@ -42998,8 +44803,15 @@
       <c r="M390" s="15">
         <v>3943</v>
       </c>
-    </row>
-    <row r="391" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N390" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P390" s="2">
+        <f>_xlfn.XLOOKUP(C390,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="5" t="s">
         <v>1317</v>
       </c>
@@ -43027,8 +44839,14 @@
       <c r="M391" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="392" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N391" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P391" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="392" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="5" t="s">
         <v>1318</v>
       </c>
@@ -43056,8 +44874,14 @@
       <c r="M392" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="393" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N392" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P392" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="393" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>1319</v>
       </c>
@@ -43085,8 +44909,14 @@
       <c r="M393" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="394" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N393" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P393" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="394" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="5" t="s">
         <v>1320</v>
       </c>
@@ -43114,8 +44944,14 @@
       <c r="M394" s="15">
         <v>3607</v>
       </c>
-    </row>
-    <row r="395" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N394" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P394" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="395" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="5" t="s">
         <v>1321</v>
       </c>
@@ -43143,8 +44979,14 @@
       <c r="M395" s="15">
         <v>3272</v>
       </c>
-    </row>
-    <row r="396" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N395" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P395" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="396" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="5" t="s">
         <v>1322</v>
       </c>
@@ -43172,8 +45014,14 @@
       <c r="M396" s="15">
         <v>3272</v>
       </c>
-    </row>
-    <row r="397" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N396" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P396" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="397" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="5" t="s">
         <v>1323</v>
       </c>
@@ -43201,8 +45049,14 @@
       <c r="M397" s="15">
         <v>3262</v>
       </c>
-    </row>
-    <row r="398" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N397" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P397" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="398" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="5" t="s">
         <v>1324</v>
       </c>
@@ -43230,8 +45084,14 @@
       <c r="M398" s="15">
         <v>3262</v>
       </c>
-    </row>
-    <row r="399" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N398" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P398" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="399" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="5" t="s">
         <v>1325</v>
       </c>
@@ -43259,8 +45119,15 @@
       <c r="M399" s="15">
         <v>7852</v>
       </c>
-    </row>
-    <row r="400" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N399" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P399" s="2">
+        <f>_xlfn.XLOOKUP(C399,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="5" t="s">
         <v>1326</v>
       </c>
@@ -43288,8 +45155,15 @@
       <c r="M400" s="15">
         <v>6978</v>
       </c>
-    </row>
-    <row r="401" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N400" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P400" s="2">
+        <f>_xlfn.XLOOKUP(C400,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="5" t="s">
         <v>1327</v>
       </c>
@@ -43317,8 +45191,15 @@
       <c r="M401" s="15">
         <v>7852</v>
       </c>
-    </row>
-    <row r="402" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N401" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P401" s="2">
+        <f>_xlfn.XLOOKUP(C401,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="5" t="s">
         <v>1328</v>
       </c>
@@ -43346,8 +45227,15 @@
       <c r="M402" s="15">
         <v>7852</v>
       </c>
-    </row>
-    <row r="403" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N402" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P402" s="2">
+        <f>_xlfn.XLOOKUP(C402,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="5" t="s">
         <v>1329</v>
       </c>
@@ -43375,8 +45263,15 @@
       <c r="M403" s="15">
         <v>6978</v>
       </c>
-    </row>
-    <row r="404" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N403" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P403" s="2">
+        <f>_xlfn.XLOOKUP(C403,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="5" t="s">
         <v>1330</v>
       </c>
@@ -43404,8 +45299,15 @@
       <c r="M404" s="15">
         <v>10654</v>
       </c>
-    </row>
-    <row r="405" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N404" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P404" s="2">
+        <f>_xlfn.XLOOKUP(C404,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="5" t="s">
         <v>1331</v>
       </c>
@@ -43433,8 +45335,15 @@
       <c r="M405" s="15">
         <v>10654</v>
       </c>
-    </row>
-    <row r="406" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N405" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P405" s="2">
+        <f>_xlfn.XLOOKUP(C405,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="5" t="s">
         <v>1332</v>
       </c>
@@ -43462,8 +45371,15 @@
       <c r="M406" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="407" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N406" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P406" s="2">
+        <f>_xlfn.XLOOKUP(C406,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="5" t="s">
         <v>1333</v>
       </c>
@@ -43491,8 +45407,15 @@
       <c r="M407" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="408" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N407" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P407" s="2">
+        <f>_xlfn.XLOOKUP(C407,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="5" t="s">
         <v>1334</v>
       </c>
@@ -43520,8 +45443,15 @@
       <c r="M408" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="409" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N408" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P408" s="2">
+        <f>_xlfn.XLOOKUP(C408,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="5" t="s">
         <v>1335</v>
       </c>
@@ -43549,8 +45479,15 @@
       <c r="M409" s="15">
         <v>7018</v>
       </c>
-    </row>
-    <row r="410" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N409" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P409" s="2">
+        <f>_xlfn.XLOOKUP(C409,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="5" t="s">
         <v>1336</v>
       </c>
@@ -43578,8 +45515,15 @@
       <c r="M410" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="411" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N410" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P410" s="2">
+        <f>_xlfn.XLOOKUP(C410,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="5" t="s">
         <v>1337</v>
       </c>
@@ -43607,8 +45551,15 @@
       <c r="M411" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="412" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N411" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P411" s="2">
+        <f>_xlfn.XLOOKUP(C411,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="5" t="s">
         <v>1338</v>
       </c>
@@ -43636,8 +45587,14 @@
       <c r="M412" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="413" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N412" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P412" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="413" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="5" t="s">
         <v>1339</v>
       </c>
@@ -43665,8 +45622,14 @@
       <c r="M413" s="15">
         <v>11345</v>
       </c>
-    </row>
-    <row r="414" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N413" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P413" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="414" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="5" t="s">
         <v>1340</v>
       </c>
@@ -43694,8 +45657,14 @@
       <c r="M414" s="15">
         <v>12094</v>
       </c>
-    </row>
-    <row r="415" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N414" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P414" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="415" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="5" t="s">
         <v>1341</v>
       </c>
@@ -43723,8 +45692,15 @@
       <c r="M415" s="15">
         <v>6432</v>
       </c>
-    </row>
-    <row r="416" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N415" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P415" s="2">
+        <f>_xlfn.XLOOKUP(C415,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="5" t="s">
         <v>1342</v>
       </c>
@@ -43752,8 +45728,15 @@
       <c r="M416" s="15">
         <v>6432</v>
       </c>
-    </row>
-    <row r="417" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N416" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P416" s="2">
+        <f>_xlfn.XLOOKUP(C416,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="5" t="s">
         <v>1343</v>
       </c>
@@ -43781,8 +45764,15 @@
       <c r="M417" s="15">
         <v>7641</v>
       </c>
-    </row>
-    <row r="418" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N417" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P417" s="2">
+        <f>_xlfn.XLOOKUP(C417,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="5" t="s">
         <v>1344</v>
       </c>
@@ -43810,8 +45800,15 @@
       <c r="M418" s="15">
         <v>7641</v>
       </c>
-    </row>
-    <row r="419" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N418" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P418" s="2">
+        <f>_xlfn.XLOOKUP(C418,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="5" t="s">
         <v>1345</v>
       </c>
@@ -43839,8 +45836,15 @@
       <c r="M419" s="15">
         <v>7641</v>
       </c>
-    </row>
-    <row r="420" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N419" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P419" s="2">
+        <f>_xlfn.XLOOKUP(C419,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="5" t="s">
         <v>1346</v>
       </c>
@@ -43868,8 +45872,14 @@
       <c r="M420" s="15">
         <v>623</v>
       </c>
-    </row>
-    <row r="421" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N420" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P420" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="421" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>1347</v>
       </c>
@@ -43897,8 +45907,14 @@
       <c r="M421" s="15">
         <v>832</v>
       </c>
-    </row>
-    <row r="422" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N421" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P421" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="422" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="5" t="s">
         <v>1348</v>
       </c>
@@ -43926,8 +45942,14 @@
       <c r="M422" s="15">
         <v>1032</v>
       </c>
-    </row>
-    <row r="423" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N422" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P422" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="423" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="5" t="s">
         <v>1349</v>
       </c>
@@ -43955,8 +45977,14 @@
       <c r="M423" s="15">
         <v>1822</v>
       </c>
-    </row>
-    <row r="424" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N423" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P423" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="424" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="5" t="s">
         <v>1350</v>
       </c>
@@ -43984,8 +46012,15 @@
       <c r="M424" s="15">
         <v>1074</v>
       </c>
-    </row>
-    <row r="425" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N424" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P424" s="2">
+        <f>_xlfn.XLOOKUP(C424,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="5" t="s">
         <v>1351</v>
       </c>
@@ -44013,8 +46048,15 @@
       <c r="M425" s="15">
         <v>720</v>
       </c>
-    </row>
-    <row r="426" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N425" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P425" s="2">
+        <f>_xlfn.XLOOKUP(C425,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="5" t="s">
         <v>1352</v>
       </c>
@@ -44042,8 +46084,15 @@
       <c r="M426" s="15">
         <v>1015</v>
       </c>
-    </row>
-    <row r="427" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N426" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P426" s="2">
+        <f>_xlfn.XLOOKUP(C426,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="5" t="s">
         <v>1353</v>
       </c>
@@ -44071,8 +46120,15 @@
       <c r="M427" s="15">
         <v>1130</v>
       </c>
-    </row>
-    <row r="428" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N427" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P427" s="2">
+        <f>_xlfn.XLOOKUP(C427,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="5" t="s">
         <v>1354</v>
       </c>
@@ -44100,8 +46156,15 @@
       <c r="M428" s="15">
         <v>1566</v>
       </c>
-    </row>
-    <row r="429" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N428" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P428" s="2">
+        <f>_xlfn.XLOOKUP(C428,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="5" t="s">
         <v>1355</v>
       </c>
@@ -44129,8 +46192,15 @@
       <c r="M429" s="15">
         <v>1254</v>
       </c>
-    </row>
-    <row r="430" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N429" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P429" s="2">
+        <f>_xlfn.XLOOKUP(C429,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="5" t="s">
         <v>1356</v>
       </c>
@@ -44158,8 +46228,15 @@
       <c r="M430" s="15">
         <v>1341</v>
       </c>
-    </row>
-    <row r="431" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N430" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P430" s="2">
+        <f>_xlfn.XLOOKUP(C430,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
         <v>1357</v>
       </c>
@@ -44187,8 +46264,15 @@
       <c r="M431" s="15">
         <v>2236</v>
       </c>
-    </row>
-    <row r="432" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N431" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P431" s="2">
+        <f>_xlfn.XLOOKUP(C431,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="5" t="s">
         <v>1358</v>
       </c>
@@ -44216,8 +46300,15 @@
       <c r="M432" s="15">
         <v>866</v>
       </c>
-    </row>
-    <row r="433" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N432" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P432" s="2">
+        <f>_xlfn.XLOOKUP(C432,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="5" t="s">
         <v>1359</v>
       </c>
@@ -44245,8 +46336,15 @@
       <c r="M433" s="15">
         <v>1380</v>
       </c>
-    </row>
-    <row r="434" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N433" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P433" s="2">
+        <f>_xlfn.XLOOKUP(C433,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="5" t="s">
         <v>2697</v>
       </c>
@@ -44274,8 +46372,15 @@
       <c r="M434" s="15">
         <v>3200</v>
       </c>
-    </row>
-    <row r="435" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N434" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P434" s="2">
+        <f>_xlfn.XLOOKUP(C434,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="5" t="s">
         <v>2698</v>
       </c>
@@ -44303,8 +46408,15 @@
       <c r="M435" s="15">
         <v>2043</v>
       </c>
-    </row>
-    <row r="436" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N435" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P435" s="2">
+        <f>_xlfn.XLOOKUP(C435,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="5" t="s">
         <v>2699</v>
       </c>
@@ -44332,8 +46444,15 @@
       <c r="M436" s="15">
         <v>2016</v>
       </c>
-    </row>
-    <row r="437" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N436" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P436" s="2">
+        <f>_xlfn.XLOOKUP(C436,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="5" t="s">
         <v>2700</v>
       </c>
@@ -44361,8 +46480,15 @@
       <c r="M437" s="15">
         <v>2722</v>
       </c>
-    </row>
-    <row r="438" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N437" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P437" s="2">
+        <f>_xlfn.XLOOKUP(C437,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="18" t="s">
         <v>2696</v>
       </c>
@@ -44390,8 +46516,15 @@
       <c r="M438" s="15">
         <v>589</v>
       </c>
-    </row>
-    <row r="439" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N438" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P438" s="2">
+        <f>_xlfn.XLOOKUP(C438,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="439" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="5" t="s">
         <v>2701</v>
       </c>
@@ -44419,8 +46552,15 @@
       <c r="M439" s="15">
         <v>724</v>
       </c>
-    </row>
-    <row r="440" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N439" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P439" s="2">
+        <f>_xlfn.XLOOKUP(C439,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="440" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="5" t="s">
         <v>2702</v>
       </c>
@@ -44448,8 +46588,15 @@
       <c r="M440" s="15">
         <v>175</v>
       </c>
-    </row>
-    <row r="441" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N440" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P440" s="2">
+        <f>_xlfn.XLOOKUP(C440,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="441" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="5" t="s">
         <v>2703</v>
       </c>
@@ -44477,8 +46624,15 @@
       <c r="M441" s="15">
         <v>113</v>
       </c>
-    </row>
-    <row r="442" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N441" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P441" s="2">
+        <f>_xlfn.XLOOKUP(C441,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="442" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="5" t="s">
         <v>2704</v>
       </c>
@@ -44506,8 +46660,15 @@
       <c r="M442" s="15">
         <v>179</v>
       </c>
-    </row>
-    <row r="443" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N442" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P442" s="2">
+        <f>_xlfn.XLOOKUP(C442,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="443" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="5" t="s">
         <v>1360</v>
       </c>
@@ -44535,8 +46696,15 @@
       <c r="M443" s="15">
         <v>230</v>
       </c>
-    </row>
-    <row r="444" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N443" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P443" s="2">
+        <f>_xlfn.XLOOKUP(C443,[1]WM!$B:$B,[1]WM!$O:$O)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="444" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
         <v>3045</v>
       </c>
@@ -44564,8 +46732,14 @@
       <c r="M444" s="15">
         <v>230</v>
       </c>
-    </row>
-    <row r="445" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N444" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P444" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="445" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="5" t="s">
         <v>1361</v>
       </c>
@@ -44593,8 +46767,14 @@
       <c r="M445" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="446" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N445" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P445" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="446" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="5" t="s">
         <v>1362</v>
       </c>
@@ -44622,8 +46802,14 @@
       <c r="M446" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="447" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N446" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P446" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="447" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="5" t="s">
         <v>1363</v>
       </c>
@@ -44651,8 +46837,14 @@
       <c r="M447" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="448" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N447" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P447" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="448" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="5" t="s">
         <v>1364</v>
       </c>
@@ -44680,8 +46872,14 @@
       <c r="M448" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="449" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N448" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P448" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="449" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
         <v>1365</v>
       </c>
@@ -44709,8 +46907,14 @@
       <c r="M449" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="450" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N449" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P449" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="450" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="5" t="s">
         <v>1366</v>
       </c>
@@ -44738,8 +46942,14 @@
       <c r="M450" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="451" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N450" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P450" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="451" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="5" t="s">
         <v>1367</v>
       </c>
@@ -44767,8 +46977,14 @@
       <c r="M451" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="452" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N451" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P451" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="452" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="5" t="s">
         <v>1368</v>
       </c>
@@ -44796,8 +47012,14 @@
       <c r="M452" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="453" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N452" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P452" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="453" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="5" t="s">
         <v>1369</v>
       </c>
@@ -44825,8 +47047,14 @@
       <c r="M453" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="454" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N453" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P453" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="454" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="5" t="s">
         <v>1370</v>
       </c>
@@ -44854,8 +47082,14 @@
       <c r="M454" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="455" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N454" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P454" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="455" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="5" t="s">
         <v>1371</v>
       </c>
@@ -44883,8 +47117,14 @@
       <c r="M455" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="456" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N455" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P455" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="456" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="5" t="s">
         <v>1372</v>
       </c>
@@ -44912,8 +47152,14 @@
       <c r="M456" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="457" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N456" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P456" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="457" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="5" t="s">
         <v>1373</v>
       </c>
@@ -44941,8 +47187,14 @@
       <c r="M457" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="458" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N457" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P457" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="458" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="5" t="s">
         <v>1374</v>
       </c>
@@ -44970,8 +47222,14 @@
       <c r="M458" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="459" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N458" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P458" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="459" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="5" t="s">
         <v>1375</v>
       </c>
@@ -44999,8 +47257,14 @@
       <c r="M459" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="460" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N459" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P459" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="460" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="5" t="s">
         <v>1376</v>
       </c>
@@ -45028,8 +47292,14 @@
       <c r="M460" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="461" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N460" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P460" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="461" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="5" t="s">
         <v>1377</v>
       </c>
@@ -45057,8 +47327,14 @@
       <c r="M461" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="462" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N461" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P461" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="462" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
         <v>1378</v>
       </c>
@@ -45086,8 +47362,14 @@
       <c r="M462" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="463" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N462" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P462" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="463" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="5" t="s">
         <v>1379</v>
       </c>
@@ -45115,8 +47397,14 @@
       <c r="M463" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="464" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N463" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P463" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="464" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="5" t="s">
         <v>1380</v>
       </c>
@@ -45144,8 +47432,14 @@
       <c r="M464" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="465" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N464" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P464" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="465" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="5" t="s">
         <v>1381</v>
       </c>
@@ -45173,8 +47467,14 @@
       <c r="M465" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="466" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N465" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P465" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="466" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="5" t="s">
         <v>1382</v>
       </c>
@@ -45202,8 +47502,14 @@
       <c r="M466" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="467" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N466" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P466" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="467" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="5" t="s">
         <v>1383</v>
       </c>
@@ -45231,8 +47537,14 @@
       <c r="M467" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="468" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N467" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P467" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="468" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="5" t="s">
         <v>1384</v>
       </c>
@@ -45260,8 +47572,14 @@
       <c r="M468" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="469" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N468" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P468" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="469" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="5" t="s">
         <v>1385</v>
       </c>
@@ -45289,8 +47607,14 @@
       <c r="M469" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="470" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N469" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P469" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="470" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="5" t="s">
         <v>1386</v>
       </c>
@@ -45318,8 +47642,14 @@
       <c r="M470" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="471" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N470" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P470" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="471" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="5" t="s">
         <v>1387</v>
       </c>
@@ -45347,8 +47677,14 @@
       <c r="M471" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="472" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N471" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P471" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="472" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="5" t="s">
         <v>1388</v>
       </c>
@@ -45376,8 +47712,14 @@
       <c r="M472" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="473" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N472" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P472" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="473" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="5" t="s">
         <v>1389</v>
       </c>
@@ -45405,8 +47747,14 @@
       <c r="M473" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="474" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N473" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P473" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="474" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="5" t="s">
         <v>1390</v>
       </c>
@@ -45434,8 +47782,14 @@
       <c r="M474" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="475" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N474" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P474" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="475" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="5" t="s">
         <v>1391</v>
       </c>
@@ -45463,8 +47817,14 @@
       <c r="M475" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="476" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N475" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P475" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="476" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="5" t="s">
         <v>1392</v>
       </c>
@@ -45492,8 +47852,14 @@
       <c r="M476" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="477" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N476" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P476" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="477" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="5" t="s">
         <v>1393</v>
       </c>
@@ -45521,8 +47887,14 @@
       <c r="M477" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="478" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N477" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P477" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="478" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="5" t="s">
         <v>1394</v>
       </c>
@@ -45550,8 +47922,14 @@
       <c r="M478" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="479" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N478" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P478" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="479" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>1395</v>
       </c>
@@ -45579,8 +47957,14 @@
       <c r="M479" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="480" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N479" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P479" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="480" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="5" t="s">
         <v>1396</v>
       </c>
@@ -45608,8 +47992,14 @@
       <c r="M480" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="481" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N480" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P480" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="481" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="5" t="s">
         <v>1397</v>
       </c>
@@ -45637,8 +48027,14 @@
       <c r="M481" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="482" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N481" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P481" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="482" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="5" t="s">
         <v>1398</v>
       </c>
@@ -45666,8 +48062,14 @@
       <c r="M482" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="483" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N482" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P482" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="483" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="5" t="s">
         <v>1399</v>
       </c>
@@ -45695,8 +48097,14 @@
       <c r="M483" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="484" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N483" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P483" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="484" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="5" t="s">
         <v>1617</v>
       </c>
@@ -45721,7 +48129,7 @@
       <c r="L484" s="5"/>
       <c r="M484" s="15"/>
     </row>
-    <row r="485" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="5" t="s">
         <v>1618</v>
       </c>
@@ -45746,7 +48154,7 @@
       <c r="L485" s="5"/>
       <c r="M485" s="15"/>
     </row>
-    <row r="486" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="5" t="s">
         <v>1619</v>
       </c>
@@ -45771,7 +48179,7 @@
       <c r="L486" s="5"/>
       <c r="M486" s="15"/>
     </row>
-    <row r="487" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="5" t="s">
         <v>1620</v>
       </c>
@@ -45796,7 +48204,7 @@
       <c r="L487" s="5"/>
       <c r="M487" s="15"/>
     </row>
-    <row r="488" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="5" t="s">
         <v>1621</v>
       </c>
@@ -45821,7 +48229,7 @@
       <c r="L488" s="5"/>
       <c r="M488" s="15"/>
     </row>
-    <row r="489" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="5" t="s">
         <v>1622</v>
       </c>
@@ -45846,7 +48254,7 @@
       <c r="L489" s="5"/>
       <c r="M489" s="15"/>
     </row>
-    <row r="490" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="5" t="s">
         <v>1623</v>
       </c>
@@ -45871,7 +48279,7 @@
       <c r="L490" s="5"/>
       <c r="M490" s="15"/>
     </row>
-    <row r="491" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="5" t="s">
         <v>1624</v>
       </c>
@@ -45896,7 +48304,7 @@
       <c r="L491" s="5"/>
       <c r="M491" s="15"/>
     </row>
-    <row r="492" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="5" t="s">
         <v>1625</v>
       </c>
@@ -45921,7 +48329,7 @@
       <c r="L492" s="5"/>
       <c r="M492" s="15"/>
     </row>
-    <row r="493" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="5" t="s">
         <v>1626</v>
       </c>
@@ -45946,7 +48354,7 @@
       <c r="L493" s="5"/>
       <c r="M493" s="15"/>
     </row>
-    <row r="494" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="5" t="s">
         <v>1627</v>
       </c>
@@ -45971,7 +48379,7 @@
       <c r="L494" s="5"/>
       <c r="M494" s="15"/>
     </row>
-    <row r="495" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="5" t="s">
         <v>1628</v>
       </c>
@@ -45996,7 +48404,7 @@
       <c r="L495" s="5"/>
       <c r="M495" s="15"/>
     </row>
-    <row r="496" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="5" t="s">
         <v>1629</v>
       </c>
@@ -55281,7 +57689,7 @@
       <c r="L864" s="5"/>
       <c r="M864" s="15"/>
     </row>
-    <row r="865" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A865" s="5" t="s">
         <v>2786</v>
       </c>
@@ -55306,7 +57714,7 @@
       <c r="L865" s="5"/>
       <c r="M865" s="15"/>
     </row>
-    <row r="866" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A866" s="5" t="s">
         <v>2788</v>
       </c>
@@ -55331,7 +57739,7 @@
       <c r="L866" s="5"/>
       <c r="M866" s="15"/>
     </row>
-    <row r="867" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A867" s="5" t="s">
         <v>2790</v>
       </c>
@@ -55356,7 +57764,7 @@
       <c r="L867" s="5"/>
       <c r="M867" s="15"/>
     </row>
-    <row r="868" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A868" s="5" t="s">
         <v>2792</v>
       </c>
@@ -55381,7 +57789,7 @@
       <c r="L868" s="5"/>
       <c r="M868" s="15"/>
     </row>
-    <row r="869" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A869" s="5" t="s">
         <v>2801</v>
       </c>
@@ -55414,7 +57822,7 @@
         <v>443.37374279999995</v>
       </c>
     </row>
-    <row r="870" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A870" s="5" t="s">
         <v>2803</v>
       </c>
@@ -55445,7 +57853,7 @@
         <v>997.59092129999999</v>
       </c>
     </row>
-    <row r="871" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A871" s="5" t="s">
         <v>2805</v>
       </c>
@@ -55476,7 +57884,7 @@
         <v>1382.2828451999997</v>
       </c>
     </row>
-    <row r="872" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A872" s="5" t="s">
         <v>717</v>
       </c>
@@ -55511,7 +57919,7 @@
         <v>534.65657219999991</v>
       </c>
     </row>
-    <row r="873" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A873" s="5" t="s">
         <v>716</v>
       </c>
@@ -55546,7 +57954,7 @@
         <v>534.65657219999991</v>
       </c>
     </row>
-    <row r="874" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A874" s="5" t="s">
         <v>2808</v>
       </c>
@@ -55581,7 +57989,7 @@
         <v>912.8282939999998</v>
       </c>
     </row>
-    <row r="875" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A875" s="5" t="s">
         <v>2809</v>
       </c>
@@ -55616,7 +58024,7 @@
         <v>912.8282939999998</v>
       </c>
     </row>
-    <row r="876" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A876" s="5" t="s">
         <v>2810</v>
       </c>
@@ -55649,7 +58057,7 @@
         <v>1093.3791264000001</v>
       </c>
     </row>
-    <row r="877" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A877" s="5" t="s">
         <v>2811</v>
       </c>
@@ -55682,7 +58090,7 @@
         <v>1118.228652</v>
       </c>
     </row>
-    <row r="878" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A878" s="5" t="s">
         <v>2818</v>
       </c>
@@ -55706,10 +58114,18 @@
       <c r="K878" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="L878" s="5"/>
+      <c r="L878" s="22" t="s">
+        <v>9396</v>
+      </c>
       <c r="M878" s="15"/>
-    </row>
-    <row r="879" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N878" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P878" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A879" s="5" t="s">
         <v>2820</v>
       </c>
@@ -55745,8 +58161,14 @@
         <v>362</v>
       </c>
       <c r="M879" s="15"/>
-    </row>
-    <row r="880" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N879" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P879" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="880" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A880" s="5" t="s">
         <v>2826</v>
       </c>
@@ -55782,8 +58204,14 @@
         <v>392</v>
       </c>
       <c r="M880" s="15"/>
-    </row>
-    <row r="881" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N880" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P880" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="881" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A881" s="5" t="s">
         <v>2829</v>
       </c>
@@ -55819,8 +58247,14 @@
         <v>392</v>
       </c>
       <c r="M881" s="15"/>
-    </row>
-    <row r="882" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N881" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P881" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="882" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A882" s="5" t="s">
         <v>2838</v>
       </c>
@@ -55848,8 +58282,14 @@
         <v>369</v>
       </c>
       <c r="M882" s="15"/>
-    </row>
-    <row r="883" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N882" s="2" t="s">
+        <v>9394</v>
+      </c>
+      <c r="P882" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="883" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A883" s="5" t="s">
         <v>2823</v>
       </c>
@@ -55878,13 +58318,21 @@
       <c r="J883" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="K883" s="5" t="s">
+      <c r="K883" s="22" t="s">
         <v>367</v>
       </c>
-      <c r="L883" s="5"/>
+      <c r="L883" s="22" t="s">
+        <v>9397</v>
+      </c>
       <c r="M883" s="15"/>
-    </row>
-    <row r="884" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N883" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P883" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="884" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A884" s="5" t="s">
         <v>2832</v>
       </c>
@@ -55919,7 +58367,7 @@
         <v>3998.5908929999996</v>
       </c>
     </row>
-    <row r="885" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A885" s="5" t="s">
         <v>2835</v>
       </c>
@@ -55954,7 +58402,7 @@
         <v>1948.4042896799995</v>
       </c>
     </row>
-    <row r="886" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A886" s="5" t="s">
         <v>2841</v>
       </c>
@@ -55983,7 +58431,7 @@
         <v>11675.918987999998</v>
       </c>
     </row>
-    <row r="887" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A887" s="5" t="s">
         <v>2843</v>
       </c>
@@ -56012,7 +58460,7 @@
         <v>11675.918987999998</v>
       </c>
     </row>
-    <row r="888" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A888" s="5" t="s">
         <v>2845</v>
       </c>
@@ -56039,7 +58487,7 @@
         <v>1428.8477220000002</v>
       </c>
     </row>
-    <row r="889" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A889" s="5" t="s">
         <v>2847</v>
       </c>
@@ -56066,7 +58514,7 @@
         <v>1528.2458244000002</v>
       </c>
     </row>
-    <row r="890" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A890" s="5" t="s">
         <v>2849</v>
       </c>
@@ -56093,7 +58541,7 @@
         <v>1900.9887084</v>
       </c>
     </row>
-    <row r="891" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A891" s="5" t="s">
         <v>2861</v>
       </c>
@@ -56128,7 +58576,7 @@
         <v>1693.3</v>
       </c>
     </row>
-    <row r="892" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A892" s="5" t="s">
         <v>3026</v>
       </c>
@@ -56163,7 +58611,7 @@
         <v>1693.3</v>
       </c>
     </row>
-    <row r="893" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="893" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A893" s="5" t="s">
         <v>2862</v>
       </c>
@@ -56198,7 +58646,7 @@
         <v>5083.8175999999994</v>
       </c>
     </row>
-    <row r="894" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A894" s="5" t="s">
         <v>2863</v>
       </c>
@@ -56233,7 +58681,7 @@
         <v>4617.7883999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A895" s="5" t="s">
         <v>2864</v>
       </c>
@@ -56268,7 +58716,7 @@
         <v>3186.0472</v>
       </c>
     </row>
-    <row r="896" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A896" s="5" t="s">
         <v>2865</v>
       </c>
@@ -56753,7 +59201,7 @@
         <v>2412.4747769999999</v>
       </c>
     </row>
-    <row r="913" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A913" s="5" t="s">
         <v>2882</v>
       </c>
@@ -56780,7 +59228,7 @@
         <v>1551.8080997999998</v>
       </c>
     </row>
-    <row r="914" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A914" s="5" t="s">
         <v>2883</v>
       </c>
@@ -56807,7 +59255,7 @@
         <v>2034.3030551999998</v>
       </c>
     </row>
-    <row r="915" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A915" s="5" t="s">
         <v>3029</v>
       </c>
@@ -56829,7 +59277,7 @@
       <c r="L915" s="5"/>
       <c r="M915" s="15"/>
     </row>
-    <row r="916" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A916" s="5" t="s">
         <v>3032</v>
       </c>
@@ -56856,7 +59304,7 @@
       <c r="L916" s="5"/>
       <c r="M916" s="15"/>
     </row>
-    <row r="917" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A917" s="5" t="s">
         <v>3034</v>
       </c>
@@ -56874,12 +59322,24 @@
       <c r="G917" s="5"/>
       <c r="H917" s="5"/>
       <c r="I917" s="5"/>
-      <c r="J917" s="5"/>
-      <c r="K917" s="5"/>
-      <c r="L917" s="5"/>
+      <c r="J917" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="K917" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="L917" s="22" t="s">
+        <v>361</v>
+      </c>
       <c r="M917" s="15"/>
-    </row>
-    <row r="918" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N917" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P917" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="918" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A918" s="5" t="s">
         <v>3036</v>
       </c>
@@ -56897,12 +59357,24 @@
       <c r="G918" s="5"/>
       <c r="H918" s="5"/>
       <c r="I918" s="5"/>
-      <c r="J918" s="5"/>
-      <c r="K918" s="5"/>
-      <c r="L918" s="5"/>
+      <c r="J918" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="K918" s="22" t="s">
+        <v>9398</v>
+      </c>
+      <c r="L918" s="22" t="s">
+        <v>9398</v>
+      </c>
       <c r="M918" s="15"/>
-    </row>
-    <row r="919" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N918" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P918" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="919" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A919" s="5" t="s">
         <v>1209</v>
       </c>
@@ -56929,7 +59401,7 @@
       <c r="L919" s="5"/>
       <c r="M919" s="15"/>
     </row>
-    <row r="920" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A920" s="2" t="s">
         <v>3047</v>
       </c>
@@ -56939,8 +59411,14 @@
       <c r="D920" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="921" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N920" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P920" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="921" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A921" s="2" t="s">
         <v>3049</v>
       </c>
@@ -56950,8 +59428,14 @@
       <c r="D921" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="922" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N921" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P921" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="922" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A922" s="2" t="s">
         <v>3050</v>
       </c>
@@ -56961,8 +59445,14 @@
       <c r="D922" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="923" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N922" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P922" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="923" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A923" s="2" t="s">
         <v>3052</v>
       </c>
@@ -56972,8 +59462,14 @@
       <c r="D923" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="924" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N923" s="2" t="s">
+        <v>9393</v>
+      </c>
+      <c r="P923" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="924" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A924" s="2" t="s">
         <v>3055</v>
       </c>
@@ -56983,8 +59479,14 @@
       <c r="D924" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="925" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N924" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P924" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="925" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A925" s="2" t="s">
         <v>5135</v>
       </c>
@@ -57001,7 +59503,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="926" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A926" s="2" t="s">
         <v>5136</v>
       </c>
@@ -57018,7 +59520,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="927" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A927" s="2" t="s">
         <v>5137</v>
       </c>
@@ -57035,7 +59537,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="928" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A928" s="2" t="s">
         <v>5138</v>
       </c>
@@ -92415,7 +94917,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="3009" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3009" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3009" s="2" t="s">
         <v>2867</v>
       </c>
@@ -92435,7 +94937,7 @@
         <v>2916</v>
       </c>
     </row>
-    <row r="3010" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3010" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3010" s="2" t="s">
         <v>9297</v>
       </c>
@@ -92451,8 +94953,17 @@
       <c r="K3010" s="5" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="3011" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3010" s="2" t="s">
+        <v>9396</v>
+      </c>
+      <c r="N3010" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P3010" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3011" s="2" t="s">
         <v>9299</v>
       </c>
@@ -92469,7 +94980,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3012" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3012" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3012" s="2" t="s">
         <v>9302</v>
       </c>
@@ -92486,7 +94997,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3013" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3013" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3013" s="2" t="s">
         <v>9305</v>
       </c>
@@ -92503,7 +95014,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3014" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3014" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3014" s="2" t="s">
         <v>9308</v>
       </c>
@@ -92520,7 +95031,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3015" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3015" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3015" s="2" t="s">
         <v>9311</v>
       </c>
@@ -92537,7 +95048,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3016" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3016" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3016" s="2" t="s">
         <v>9314</v>
       </c>
@@ -92554,7 +95065,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3017" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3017" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3017" s="2" t="s">
         <v>9317</v>
       </c>
@@ -92571,7 +95082,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3018" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3018" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3018" s="2" t="s">
         <v>9320</v>
       </c>
@@ -92588,7 +95099,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3019" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3019" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3019" s="2" t="s">
         <v>9323</v>
       </c>
@@ -92605,7 +95116,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3020" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3020" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3020" s="2" t="s">
         <v>9326</v>
       </c>
@@ -92622,7 +95133,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3021" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3021" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3021" s="2" t="s">
         <v>9329</v>
       </c>
@@ -92639,7 +95150,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3022" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3022" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3022" s="2" t="s">
         <v>9332</v>
       </c>
@@ -92656,7 +95167,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3023" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3023" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3023" s="2" t="s">
         <v>9335</v>
       </c>
@@ -92673,7 +95184,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3024" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3024" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3024" s="2" t="s">
         <v>9338</v>
       </c>
@@ -92962,7 +95473,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3041" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3041" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3041" s="2" t="s">
         <v>9390</v>
       </c>
@@ -92975,8 +95486,15 @@
       <c r="E3041" s="2" t="s">
         <v>9391</v>
       </c>
+      <c r="N3041" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P3041" s="2" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>
@@ -93000,8 +95518,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -93021,9 +95539,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -93031,23 +95549,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66BC89-0C0A-45A7-9C57-06BC79507239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93541365-ACED-4337-978C-5E9A4F9468AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17439" uniqueCount="9404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17604" uniqueCount="9503">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -28252,6 +28252,303 @@
   </si>
   <si>
     <t>T-Code (EAN)</t>
+  </si>
+  <si>
+    <t>B07WGWGMBM</t>
+  </si>
+  <si>
+    <t>B0H1K1XJBK</t>
+  </si>
+  <si>
+    <t>B0H1JTMVMW</t>
+  </si>
+  <si>
+    <t>B0H1K4MHH4</t>
+  </si>
+  <si>
+    <t>B0H1JZFQRZ</t>
+  </si>
+  <si>
+    <t>B0H1K1W6GJ</t>
+  </si>
+  <si>
+    <t>B0H44QP75W</t>
+  </si>
+  <si>
+    <t>B0H44XPFRC</t>
+  </si>
+  <si>
+    <t>B0H8XG2F43</t>
+  </si>
+  <si>
+    <t>B0H8XXYKBC</t>
+  </si>
+  <si>
+    <t>B0H8Y4Z1KK</t>
+  </si>
+  <si>
+    <t>B0H1K56S6V</t>
+  </si>
+  <si>
+    <t>B0H1K216VW</t>
+  </si>
+  <si>
+    <t>B0H1JTL93N</t>
+  </si>
+  <si>
+    <t>B0H8Y38KKY</t>
+  </si>
+  <si>
+    <t>B0H1K2HBC9</t>
+  </si>
+  <si>
+    <t>B0H1KB3F39</t>
+  </si>
+  <si>
+    <t>B0H1K5RK6V</t>
+  </si>
+  <si>
+    <t>B0H8XZ9N1P</t>
+  </si>
+  <si>
+    <t>B0H1K4MHGJ</t>
+  </si>
+  <si>
+    <t>B0H1JY5HK3</t>
+  </si>
+  <si>
+    <t>B0H1JN7L2Z</t>
+  </si>
+  <si>
+    <t>B0H2ZX1W6F</t>
+  </si>
+  <si>
+    <t>B0H2ZVD5RS</t>
+  </si>
+  <si>
+    <t>B0H312FS95</t>
+  </si>
+  <si>
+    <t>B0H2ZX6LSV</t>
+  </si>
+  <si>
+    <t>B0H2ZMP3LX</t>
+  </si>
+  <si>
+    <t>B0H2ZZQDC9</t>
+  </si>
+  <si>
+    <t>B0H2ZPG58N</t>
+  </si>
+  <si>
+    <t>B0H1JXJ5LV</t>
+  </si>
+  <si>
+    <t>B0H1K1N4X4</t>
+  </si>
+  <si>
+    <t>B0H2ZT21NJ</t>
+  </si>
+  <si>
+    <t>B0H2ZR4K77</t>
+  </si>
+  <si>
+    <t>FBA80118</t>
+  </si>
+  <si>
+    <t>FBA80257</t>
+  </si>
+  <si>
+    <t>FBA80258</t>
+  </si>
+  <si>
+    <t>FBA80259</t>
+  </si>
+  <si>
+    <t>FBA80262</t>
+  </si>
+  <si>
+    <t>FBA80263</t>
+  </si>
+  <si>
+    <t>FBA80265</t>
+  </si>
+  <si>
+    <t>FBA80266</t>
+  </si>
+  <si>
+    <t>FBA80268</t>
+  </si>
+  <si>
+    <t>FBA80269</t>
+  </si>
+  <si>
+    <t>FBA80270</t>
+  </si>
+  <si>
+    <t>FBA80271</t>
+  </si>
+  <si>
+    <t>FBA80272</t>
+  </si>
+  <si>
+    <t>FBA80273</t>
+  </si>
+  <si>
+    <t>FBA80274</t>
+  </si>
+  <si>
+    <t>FBA80275</t>
+  </si>
+  <si>
+    <t>FBA80276</t>
+  </si>
+  <si>
+    <t>FBA80277</t>
+  </si>
+  <si>
+    <t>FBA80278</t>
+  </si>
+  <si>
+    <t>FBA80279</t>
+  </si>
+  <si>
+    <t>FBA80280</t>
+  </si>
+  <si>
+    <t>FBA80281</t>
+  </si>
+  <si>
+    <t>FBA80282</t>
+  </si>
+  <si>
+    <t>FBA80283</t>
+  </si>
+  <si>
+    <t>FBA80284</t>
+  </si>
+  <si>
+    <t>FBA80285</t>
+  </si>
+  <si>
+    <t>FBA80288</t>
+  </si>
+  <si>
+    <t>FBA80290</t>
+  </si>
+  <si>
+    <t>FBA80292</t>
+  </si>
+  <si>
+    <t>FBA80260</t>
+  </si>
+  <si>
+    <t>FBA80261</t>
+  </si>
+  <si>
+    <t>FBA80286</t>
+  </si>
+  <si>
+    <t>FBA80289</t>
+  </si>
+  <si>
+    <t>FS5661</t>
+  </si>
+  <si>
+    <t>AX2467</t>
+  </si>
+  <si>
+    <t>AX2468</t>
+  </si>
+  <si>
+    <t>AX2652</t>
+  </si>
+  <si>
+    <t>AX4409</t>
+  </si>
+  <si>
+    <t>AX4410</t>
+  </si>
+  <si>
+    <t>DZ4715</t>
+  </si>
+  <si>
+    <t>DZ4724</t>
+  </si>
+  <si>
+    <t>CE1135</t>
+  </si>
+  <si>
+    <t>CE1136</t>
+  </si>
+  <si>
+    <t>CE1137</t>
+  </si>
+  <si>
+    <t>ES5503</t>
+  </si>
+  <si>
+    <t>ES5504</t>
+  </si>
+  <si>
+    <t>ES5505</t>
+  </si>
+  <si>
+    <t>ES5512</t>
+  </si>
+  <si>
+    <t>FS6180</t>
+  </si>
+  <si>
+    <t>FS6181</t>
+  </si>
+  <si>
+    <t>FS6182</t>
+  </si>
+  <si>
+    <t>FS6189</t>
+  </si>
+  <si>
+    <t>FS6194</t>
+  </si>
+  <si>
+    <t>FS6198SET</t>
+  </si>
+  <si>
+    <t>FS6199SET</t>
+  </si>
+  <si>
+    <t>MK7618</t>
+  </si>
+  <si>
+    <t>MK7619</t>
+  </si>
+  <si>
+    <t>MK7620</t>
+  </si>
+  <si>
+    <t>MK7621</t>
+  </si>
+  <si>
+    <t>MK7641</t>
+  </si>
+  <si>
+    <t>MK9273</t>
+  </si>
+  <si>
+    <t>MK9277</t>
+  </si>
+  <si>
+    <t>AX4174</t>
+  </si>
+  <si>
+    <t>AX4175</t>
+  </si>
+  <si>
+    <t>MK7626</t>
+  </si>
+  <si>
+    <t>MK7642</t>
   </si>
 </sst>
 </file>
@@ -28474,28 +28771,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28558,6 +28833,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -28570,6 +28865,8 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -29584,7 +29881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:S3041"/>
+  <dimension ref="A1:S3074"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -95491,6 +95788,567 @@
       </c>
       <c r="P3041" s="2" t="e">
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3042" s="2" t="s">
+        <v>9437</v>
+      </c>
+      <c r="C3042" s="2" t="s">
+        <v>9404</v>
+      </c>
+      <c r="D3042" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3042" s="2" t="s">
+        <v>9470</v>
+      </c>
+      <c r="J3042" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3043" s="2" t="s">
+        <v>9438</v>
+      </c>
+      <c r="C3043" s="2" t="s">
+        <v>9405</v>
+      </c>
+      <c r="D3043" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3043" s="2" t="s">
+        <v>9471</v>
+      </c>
+      <c r="J3043" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3044" s="2" t="s">
+        <v>9439</v>
+      </c>
+      <c r="C3044" s="2" t="s">
+        <v>9406</v>
+      </c>
+      <c r="D3044" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3044" s="2" t="s">
+        <v>9472</v>
+      </c>
+      <c r="J3044" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3045" s="2" t="s">
+        <v>9440</v>
+      </c>
+      <c r="C3045" s="2" t="s">
+        <v>9407</v>
+      </c>
+      <c r="D3045" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3045" s="2" t="s">
+        <v>9473</v>
+      </c>
+      <c r="J3045" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3046" s="2" t="s">
+        <v>9441</v>
+      </c>
+      <c r="C3046" s="2" t="s">
+        <v>9408</v>
+      </c>
+      <c r="D3046" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3046" s="2" t="s">
+        <v>9474</v>
+      </c>
+      <c r="J3046" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3047" s="2" t="s">
+        <v>9442</v>
+      </c>
+      <c r="C3047" s="2" t="s">
+        <v>9409</v>
+      </c>
+      <c r="D3047" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3047" s="2" t="s">
+        <v>9475</v>
+      </c>
+      <c r="J3047" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3048" s="2" t="s">
+        <v>9443</v>
+      </c>
+      <c r="C3048" s="2" t="s">
+        <v>9410</v>
+      </c>
+      <c r="D3048" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3048" s="2" t="s">
+        <v>9476</v>
+      </c>
+      <c r="J3048" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3049" s="2" t="s">
+        <v>9444</v>
+      </c>
+      <c r="C3049" s="2" t="s">
+        <v>9411</v>
+      </c>
+      <c r="D3049" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3049" s="2" t="s">
+        <v>9477</v>
+      </c>
+      <c r="J3049" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3050" s="2" t="s">
+        <v>9445</v>
+      </c>
+      <c r="C3050" s="2" t="s">
+        <v>9412</v>
+      </c>
+      <c r="D3050" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3050" s="2" t="s">
+        <v>9478</v>
+      </c>
+      <c r="J3050" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3051" s="2" t="s">
+        <v>9446</v>
+      </c>
+      <c r="C3051" s="2" t="s">
+        <v>9413</v>
+      </c>
+      <c r="D3051" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3051" s="2" t="s">
+        <v>9479</v>
+      </c>
+      <c r="J3051" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3052" s="2" t="s">
+        <v>9447</v>
+      </c>
+      <c r="C3052" s="2" t="s">
+        <v>9414</v>
+      </c>
+      <c r="D3052" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3052" s="2" t="s">
+        <v>9480</v>
+      </c>
+      <c r="J3052" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3053" s="2" t="s">
+        <v>9448</v>
+      </c>
+      <c r="C3053" s="2" t="s">
+        <v>9415</v>
+      </c>
+      <c r="D3053" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3053" s="2" t="s">
+        <v>9481</v>
+      </c>
+      <c r="J3053" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3054" s="2" t="s">
+        <v>9449</v>
+      </c>
+      <c r="C3054" s="2" t="s">
+        <v>9416</v>
+      </c>
+      <c r="D3054" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3054" s="2" t="s">
+        <v>9482</v>
+      </c>
+      <c r="J3054" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3055" s="2" t="s">
+        <v>9450</v>
+      </c>
+      <c r="C3055" s="2" t="s">
+        <v>9417</v>
+      </c>
+      <c r="D3055" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3055" s="2" t="s">
+        <v>9483</v>
+      </c>
+      <c r="J3055" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3056" s="2" t="s">
+        <v>9451</v>
+      </c>
+      <c r="C3056" s="2" t="s">
+        <v>9418</v>
+      </c>
+      <c r="D3056" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3056" s="2" t="s">
+        <v>9484</v>
+      </c>
+      <c r="J3056" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3057" s="2" t="s">
+        <v>9452</v>
+      </c>
+      <c r="C3057" s="2" t="s">
+        <v>9419</v>
+      </c>
+      <c r="D3057" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3057" s="2" t="s">
+        <v>9485</v>
+      </c>
+      <c r="J3057" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3058" s="2" t="s">
+        <v>9453</v>
+      </c>
+      <c r="C3058" s="2" t="s">
+        <v>9420</v>
+      </c>
+      <c r="D3058" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3058" s="2" t="s">
+        <v>9486</v>
+      </c>
+      <c r="J3058" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3059" s="2" t="s">
+        <v>9454</v>
+      </c>
+      <c r="C3059" s="2" t="s">
+        <v>9421</v>
+      </c>
+      <c r="D3059" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3059" s="2" t="s">
+        <v>9487</v>
+      </c>
+      <c r="J3059" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3060" s="2" t="s">
+        <v>9455</v>
+      </c>
+      <c r="C3060" s="2" t="s">
+        <v>9422</v>
+      </c>
+      <c r="D3060" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3060" s="2" t="s">
+        <v>9488</v>
+      </c>
+      <c r="J3060" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3061" s="2" t="s">
+        <v>9456</v>
+      </c>
+      <c r="C3061" s="2" t="s">
+        <v>9423</v>
+      </c>
+      <c r="D3061" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3061" s="2" t="s">
+        <v>9489</v>
+      </c>
+      <c r="J3061" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3062" s="2" t="s">
+        <v>9457</v>
+      </c>
+      <c r="C3062" s="2" t="s">
+        <v>9424</v>
+      </c>
+      <c r="D3062" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3062" s="2" t="s">
+        <v>9490</v>
+      </c>
+      <c r="J3062" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3063" s="2" t="s">
+        <v>9458</v>
+      </c>
+      <c r="C3063" s="2" t="s">
+        <v>9425</v>
+      </c>
+      <c r="D3063" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3063" s="2" t="s">
+        <v>9491</v>
+      </c>
+      <c r="J3063" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3064" s="2" t="s">
+        <v>9459</v>
+      </c>
+      <c r="C3064" s="2" t="s">
+        <v>9426</v>
+      </c>
+      <c r="D3064" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3064" s="2" t="s">
+        <v>9492</v>
+      </c>
+      <c r="J3064" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3065" s="2" t="s">
+        <v>9460</v>
+      </c>
+      <c r="C3065" s="2" t="s">
+        <v>9427</v>
+      </c>
+      <c r="D3065" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3065" s="2" t="s">
+        <v>9493</v>
+      </c>
+      <c r="J3065" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3066" s="2" t="s">
+        <v>9461</v>
+      </c>
+      <c r="C3066" s="2" t="s">
+        <v>9428</v>
+      </c>
+      <c r="D3066" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3066" s="2" t="s">
+        <v>9494</v>
+      </c>
+      <c r="J3066" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3067" s="2" t="s">
+        <v>9462</v>
+      </c>
+      <c r="C3067" s="2" t="s">
+        <v>9429</v>
+      </c>
+      <c r="D3067" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3067" s="2" t="s">
+        <v>9495</v>
+      </c>
+      <c r="J3067" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3068" s="2" t="s">
+        <v>9463</v>
+      </c>
+      <c r="C3068" s="2" t="s">
+        <v>9430</v>
+      </c>
+      <c r="D3068" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3068" s="2" t="s">
+        <v>9496</v>
+      </c>
+      <c r="J3068" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3069" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3069" s="2" t="s">
+        <v>9464</v>
+      </c>
+      <c r="C3069" s="2" t="s">
+        <v>9431</v>
+      </c>
+      <c r="D3069" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3069" s="2" t="s">
+        <v>9497</v>
+      </c>
+      <c r="J3069" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3070" s="2" t="s">
+        <v>9465</v>
+      </c>
+      <c r="C3070" s="2" t="s">
+        <v>9432</v>
+      </c>
+      <c r="D3070" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3070" s="2" t="s">
+        <v>9498</v>
+      </c>
+      <c r="J3070" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3071" s="2" t="s">
+        <v>9466</v>
+      </c>
+      <c r="C3071" s="2" t="s">
+        <v>9433</v>
+      </c>
+      <c r="D3071" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3071" s="2" t="s">
+        <v>9499</v>
+      </c>
+      <c r="J3071" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3072" s="2" t="s">
+        <v>9467</v>
+      </c>
+      <c r="C3072" s="2" t="s">
+        <v>9434</v>
+      </c>
+      <c r="D3072" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3072" s="2" t="s">
+        <v>9500</v>
+      </c>
+      <c r="J3072" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3073" s="2" t="s">
+        <v>9468</v>
+      </c>
+      <c r="C3073" s="2" t="s">
+        <v>9435</v>
+      </c>
+      <c r="D3073" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3073" s="2" t="s">
+        <v>9501</v>
+      </c>
+      <c r="J3073" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3074" s="2" t="s">
+        <v>9469</v>
+      </c>
+      <c r="C3074" s="2" t="s">
+        <v>9436</v>
+      </c>
+      <c r="D3074" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3074" s="2" t="s">
+        <v>9502</v>
+      </c>
+      <c r="J3074" s="2" t="s">
+        <v>2644</v>
       </c>
     </row>
   </sheetData>
@@ -95518,8 +96376,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -95539,9 +96397,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -95549,23 +96407,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">

--- a/data/master/sku_master.xlsx
+++ b/data/master/sku_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93541365-ACED-4337-978C-5E9A4F9468AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375909CC-C73F-450E-82FD-1A8FC1FF50F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{117C6BDF-C413-4A9B-8C98-0B7CEC880D6C}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$3073</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17604" uniqueCount="9503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17595" uniqueCount="9502">
   <si>
     <t>FBA SKU</t>
   </si>
@@ -8623,9 +8623,6 @@
   </si>
   <si>
     <t>Monitor Speaker Stand Pair</t>
-  </si>
-  <si>
-    <t>FBM79783</t>
   </si>
   <si>
     <t>FBA80074</t>
@@ -28771,6 +28768,28 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -28833,26 +28852,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -28865,8 +28864,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -29881,7 +29878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}">
-  <dimension ref="A1:S3074"/>
+  <dimension ref="A1:S3073"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -29920,16 +29917,16 @@
         <v>518</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>2949</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>2950</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>2951</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>2952</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>515</v>
@@ -29944,22 +29941,22 @@
         <v>437</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>9398</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>9399</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>9394</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>9400</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>9395</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9401</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>9402</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>9403</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -29995,10 +29992,10 @@
         <v>1260</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P2" s="2">
         <v>8</v>
@@ -30024,10 +30021,10 @@
         <v>2399</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>174</v>
@@ -30045,10 +30042,10 @@
         <v>1260</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P3" s="2">
         <v>8</v>
@@ -30074,13 +30071,13 @@
         <v>3999</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>2954</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>2955</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>355</v>
@@ -30095,10 +30092,10 @@
         <v>1786</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P4" s="2">
         <v>6</v>
@@ -30124,13 +30121,13 @@
         <v>699</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>355</v>
@@ -30145,10 +30142,10 @@
         <v>413</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P5" s="2">
         <v>36</v>
@@ -30174,10 +30171,10 @@
         <v>699</v>
       </c>
       <c r="G6" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>744</v>
@@ -30195,10 +30192,10 @@
         <v>418</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P6" s="2">
         <v>36</v>
@@ -30224,10 +30221,10 @@
         <v>699</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>744</v>
@@ -30245,10 +30242,10 @@
         <v>413</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P7" s="2">
         <v>36</v>
@@ -30287,10 +30284,10 @@
         <v>413</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P8" s="2">
         <v>36</v>
@@ -30329,10 +30326,10 @@
         <v>558</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P9" s="2">
         <v>36</v>
@@ -30371,10 +30368,10 @@
         <v>633</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P10" s="2">
         <v>40</v>
@@ -30413,10 +30410,10 @@
         <v>1073</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P11" s="2">
         <v>36</v>
@@ -30455,10 +30452,10 @@
         <v>527</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P12" s="2" t="e">
         <v>#N/A</v>
@@ -30484,10 +30481,10 @@
         <v>2199</v>
       </c>
       <c r="G13" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>744</v>
@@ -30505,10 +30502,10 @@
         <v>1512</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P13" s="2">
         <v>8</v>
@@ -30547,10 +30544,10 @@
         <v>282</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P14" s="2" t="e">
         <v>#N/A</v>
@@ -30589,10 +30586,10 @@
         <v>282</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P15" s="2" t="e">
         <v>#N/A</v>
@@ -30631,10 +30628,10 @@
         <v>193</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P16" s="2" t="e">
         <v>#N/A</v>
@@ -30660,13 +30657,13 @@
         <v>2399</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>355</v>
@@ -30681,10 +30678,10 @@
         <v>1377</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P17" s="2">
         <v>6</v>
@@ -30710,10 +30707,10 @@
         <v>2999</v>
       </c>
       <c r="G18" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>5</v>
@@ -30731,10 +30728,10 @@
         <v>1162</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P18" s="2">
         <v>6</v>
@@ -30760,10 +30757,10 @@
         <v>999</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>744</v>
@@ -30781,10 +30778,10 @@
         <v>533</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P19" s="2">
         <v>40</v>
@@ -30810,10 +30807,10 @@
         <v>1999</v>
       </c>
       <c r="G20" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>744</v>
@@ -30831,10 +30828,10 @@
         <v>516</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P20" s="2">
         <v>60</v>
@@ -30860,10 +30857,10 @@
         <v>1059</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>744</v>
@@ -30881,10 +30878,10 @@
         <v>606</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P21" s="2">
         <v>60</v>
@@ -30910,10 +30907,10 @@
         <v>1999</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>22</v>
@@ -30931,10 +30928,10 @@
         <v>987</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P22" s="2">
         <v>8</v>
@@ -30960,13 +30957,13 @@
         <v>1399</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>356</v>
@@ -30981,10 +30978,10 @@
         <v>728</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P23" s="2">
         <v>12</v>
@@ -31010,10 +31007,10 @@
         <v>799</v>
       </c>
       <c r="G24" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>744</v>
@@ -31031,10 +31028,10 @@
         <v>378</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P24" s="2">
         <v>12</v>
@@ -31060,10 +31057,10 @@
         <v>799</v>
       </c>
       <c r="G25" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>744</v>
@@ -31081,10 +31078,10 @@
         <v>389</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P25" s="2">
         <v>12</v>
@@ -31110,10 +31107,10 @@
         <v>3799</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>744</v>
@@ -31131,10 +31128,10 @@
         <v>2357</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P26" s="2">
         <v>2</v>
@@ -31160,10 +31157,10 @@
         <v>7199</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>744</v>
@@ -31181,10 +31178,10 @@
         <v>4052</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P27" s="2">
         <v>2</v>
@@ -31210,10 +31207,10 @@
         <v>1499</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>142</v>
@@ -31231,10 +31228,10 @@
         <v>769</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P28" s="2">
         <v>20</v>
@@ -31260,10 +31257,10 @@
         <v>899</v>
       </c>
       <c r="G29" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>744</v>
@@ -31281,10 +31278,10 @@
         <v>444</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P29" s="2">
         <v>60</v>
@@ -31310,13 +31307,13 @@
         <v>999</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>356</v>
@@ -31331,10 +31328,10 @@
         <v>490</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P30" s="2">
         <v>60</v>
@@ -31360,13 +31357,13 @@
         <v>1499</v>
       </c>
       <c r="G31" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>356</v>
@@ -31381,10 +31378,10 @@
         <v>714</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P31" s="2">
         <v>60</v>
@@ -31410,10 +31407,10 @@
         <v>799</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>104</v>
@@ -31431,10 +31428,10 @@
         <v>412</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P32" s="2">
         <v>50</v>
@@ -31460,10 +31457,10 @@
         <v>799</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>744</v>
@@ -31481,10 +31478,10 @@
         <v>413</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P33" s="2">
         <v>50</v>
@@ -31523,10 +31520,10 @@
         <v>448</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P34" s="2">
         <v>20</v>
@@ -31563,10 +31560,10 @@
         <v>448</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P35" s="2" t="e">
         <v>#N/A</v>
@@ -31592,10 +31589,10 @@
         <v>999</v>
       </c>
       <c r="G36" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>744</v>
@@ -31613,10 +31610,10 @@
         <v>409</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P36" s="2">
         <v>40</v>
@@ -31624,11 +31621,11 @@
     </row>
     <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>6</v>
@@ -31653,10 +31650,10 @@
         <v>409</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P37" s="2">
         <v>40</v>
@@ -31664,7 +31661,7 @@
     </row>
     <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>23</v>
@@ -31682,10 +31679,10 @@
         <v>1099</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>744</v>
@@ -31703,10 +31700,10 @@
         <v>710</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P38" s="2">
         <v>60</v>
@@ -31745,10 +31742,10 @@
         <v>356</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P39" s="2">
         <v>50</v>
@@ -31785,10 +31782,10 @@
         <v>356</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P40" s="2">
         <v>50</v>
@@ -31814,13 +31811,13 @@
         <v>1199</v>
       </c>
       <c r="G41" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>355</v>
@@ -31835,10 +31832,10 @@
         <v>562</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P41" s="2">
         <v>18</v>
@@ -31864,13 +31861,13 @@
         <v>299</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>356</v>
@@ -31885,10 +31882,10 @@
         <v>295</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P42" s="2">
         <v>100</v>
@@ -31914,13 +31911,13 @@
         <v>299</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>356</v>
@@ -31935,10 +31932,10 @@
         <v>295</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P43" s="2">
         <v>100</v>
@@ -31977,10 +31974,10 @@
         <v>193</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P44" s="2">
         <v>200</v>
@@ -32006,10 +32003,10 @@
         <v>1249</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>744</v>
@@ -32027,10 +32024,10 @@
         <v>672</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P45" s="2">
         <v>20</v>
@@ -32056,10 +32053,10 @@
         <v>1699</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>744</v>
@@ -32077,10 +32074,10 @@
         <v>896</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P46" s="2">
         <v>20</v>
@@ -32106,10 +32103,10 @@
         <v>1949</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>744</v>
@@ -32127,10 +32124,10 @@
         <v>868</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P47" s="2">
         <v>12</v>
@@ -32156,10 +32153,10 @@
         <v>2699</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>744</v>
@@ -32177,10 +32174,10 @@
         <v>961</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P48" s="2">
         <v>60</v>
@@ -32206,10 +32203,10 @@
         <v>3399</v>
       </c>
       <c r="G49" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H49" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>8</v>
@@ -32227,10 +32224,10 @@
         <v>1381</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P49" s="2">
         <v>8</v>
@@ -32256,10 +32253,10 @@
         <v>1999</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I50" s="5" t="s">
         <v>744</v>
@@ -32277,10 +32274,10 @@
         <v>810</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P50" s="2">
         <v>50</v>
@@ -32306,10 +32303,10 @@
         <v>1699</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>744</v>
@@ -32327,10 +32324,10 @@
         <v>1089</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P51" s="2">
         <v>50</v>
@@ -32369,10 +32366,10 @@
         <v>1532</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P52" s="2" t="e">
         <v>#N/A</v>
@@ -32398,10 +32395,10 @@
         <v>209</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>744</v>
@@ -32419,10 +32416,10 @@
         <v>1088</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P53" s="2">
         <v>6</v>
@@ -32448,10 +32445,10 @@
         <v>2499</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>84</v>
@@ -32469,10 +32466,10 @@
         <v>1291</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P54" s="2">
         <v>20</v>
@@ -32498,10 +32495,10 @@
         <v>1499</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>50</v>
@@ -32519,10 +32516,10 @@
         <v>560</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P55" s="2">
         <v>40</v>
@@ -32548,13 +32545,13 @@
         <v>999</v>
       </c>
       <c r="G56" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H56" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="I56" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>355</v>
@@ -32569,10 +32566,10 @@
         <v>1250</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P56" s="2">
         <v>18</v>
@@ -32598,10 +32595,10 @@
         <v>1199</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>160</v>
@@ -32619,10 +32616,10 @@
         <v>483</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P57" s="2">
         <v>20</v>
@@ -32661,10 +32658,10 @@
         <v>2775</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P58" s="2" t="e">
         <v>#N/A</v>
@@ -32690,10 +32687,10 @@
         <v>3899</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>744</v>
@@ -32711,10 +32708,10 @@
         <v>2775</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P59" s="2">
         <v>6</v>
@@ -32740,10 +32737,10 @@
         <v>1529</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>744</v>
@@ -32761,10 +32758,10 @@
         <v>594</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P60" s="2">
         <v>40</v>
@@ -32790,10 +32787,10 @@
         <v>1399</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>40</v>
@@ -32811,10 +32808,10 @@
         <v>560</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P61" s="2">
         <v>40</v>
@@ -32840,10 +32837,10 @@
         <v>1699</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I62" s="5" t="s">
         <v>178</v>
@@ -32861,10 +32858,10 @@
         <v>865</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P62" s="2">
         <v>24</v>
@@ -32890,10 +32887,10 @@
         <v>1949</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>176</v>
@@ -32911,10 +32908,10 @@
         <v>814</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P63" s="2">
         <v>24</v>
@@ -32940,10 +32937,10 @@
         <v>1999</v>
       </c>
       <c r="G64" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H64" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>744</v>
@@ -32961,10 +32958,10 @@
         <v>1392</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P64" s="2">
         <v>20</v>
@@ -32990,13 +32987,13 @@
         <v>1999</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="J65" s="6" t="s">
         <v>355</v>
@@ -33011,10 +33008,10 @@
         <v>803</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P65" s="2">
         <v>20</v>
@@ -33040,10 +33037,10 @@
         <v>1999</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>744</v>
@@ -33061,10 +33058,10 @@
         <v>1302</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P66" s="2">
         <v>32</v>
@@ -33090,13 +33087,13 @@
         <v>1999</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H67" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J67" s="6" t="s">
         <v>356</v>
@@ -33111,10 +33108,10 @@
         <v>594</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P67" s="2">
         <v>20</v>
@@ -33140,13 +33137,13 @@
         <v>1399</v>
       </c>
       <c r="G68" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H68" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="I68" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>355</v>
@@ -33161,10 +33158,10 @@
         <v>716</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P68" s="2">
         <v>6</v>
@@ -33203,10 +33200,10 @@
         <v>460</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P69" s="2">
         <v>50</v>
@@ -33232,10 +33229,10 @@
         <v>1999</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>20</v>
@@ -33253,10 +33250,10 @@
         <v>984</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P70" s="2">
         <v>12</v>
@@ -33282,10 +33279,10 @@
         <v>2099</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>32</v>
@@ -33303,10 +33300,10 @@
         <v>980</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P71" s="2">
         <v>12</v>
@@ -33332,13 +33329,13 @@
         <v>2299</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="J72" s="6" t="s">
         <v>356</v>
@@ -33353,10 +33350,10 @@
         <v>1095</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P72" s="2">
         <v>12</v>
@@ -33382,13 +33379,13 @@
         <v>2049</v>
       </c>
       <c r="G73" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H73" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H73" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I73" s="5" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>356</v>
@@ -33403,10 +33400,10 @@
         <v>852</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P73" s="2">
         <v>12</v>
@@ -33432,13 +33429,13 @@
         <v>2499</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H74" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I74" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I74" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>355</v>
@@ -33453,10 +33450,10 @@
         <v>1112</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P74" s="2">
         <v>24</v>
@@ -33482,10 +33479,10 @@
         <v>2299</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>52</v>
@@ -33503,10 +33500,10 @@
         <v>1063</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P75" s="2">
         <v>16</v>
@@ -33532,13 +33529,13 @@
         <v>5999</v>
       </c>
       <c r="G76" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H76" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H76" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I76" s="5" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>355</v>
@@ -33553,10 +33550,10 @@
         <v>2695</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P76" s="2">
         <v>4</v>
@@ -33595,10 +33592,10 @@
         <v>721</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P77" s="2" t="e">
         <v>#N/A</v>
@@ -33624,10 +33621,10 @@
         <v>1799</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>744</v>
@@ -33645,10 +33642,10 @@
         <v>536</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P78" s="2">
         <v>50</v>
@@ -33687,10 +33684,10 @@
         <v>1307</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P79" s="2">
         <v>4</v>
@@ -33729,10 +33726,10 @@
         <v>709</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P80" s="2">
         <v>20</v>
@@ -33758,10 +33755,10 @@
         <v>2499</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>744</v>
@@ -33779,10 +33776,10 @@
         <v>1345</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P81" s="2">
         <v>30</v>
@@ -33821,10 +33818,10 @@
         <v>710</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P82" s="2" t="e">
         <v>#N/A</v>
@@ -33863,10 +33860,10 @@
         <v>1306</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P83" s="2" t="e">
         <v>#N/A</v>
@@ -33892,10 +33889,10 @@
         <v>1699</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>744</v>
@@ -33913,10 +33910,10 @@
         <v>1306</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P84" s="2">
         <v>10</v>
@@ -33942,10 +33939,10 @@
         <v>2999</v>
       </c>
       <c r="G85" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H85" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>241</v>
@@ -33963,10 +33960,10 @@
         <v>1014</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P85" s="2">
         <v>20</v>
@@ -33992,13 +33989,13 @@
         <v>1499</v>
       </c>
       <c r="G86" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H86" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H86" s="5" t="s">
+      <c r="I86" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J86" s="6" t="s">
         <v>356</v>
@@ -34013,10 +34010,10 @@
         <v>1039</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P86" s="2" t="e">
         <v>#N/A</v>
@@ -34024,7 +34021,7 @@
     </row>
     <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>67</v>
@@ -34055,10 +34052,10 @@
         <v>1039</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P87" s="2">
         <v>20</v>
@@ -34097,10 +34094,10 @@
         <v>1837</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P88" s="2">
         <v>6</v>
@@ -34139,10 +34136,10 @@
         <v>890</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P89" s="2">
         <v>8</v>
@@ -34181,10 +34178,10 @@
         <v>714</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P90" s="2">
         <v>30</v>
@@ -34223,10 +34220,10 @@
         <v>1422</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P91" s="2">
         <v>30</v>
@@ -34252,10 +34249,10 @@
         <v>1799</v>
       </c>
       <c r="G92" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H92" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>744</v>
@@ -34273,10 +34270,10 @@
         <v>926</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P92" s="2">
         <v>20</v>
@@ -34315,10 +34312,10 @@
         <v>765</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P93" s="2">
         <v>10</v>
@@ -34326,7 +34323,7 @@
     </row>
     <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>123</v>
@@ -34357,10 +34354,10 @@
         <v>970</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P94" s="2">
         <v>6</v>
@@ -34386,13 +34383,13 @@
         <v>1499</v>
       </c>
       <c r="G95" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H95" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H95" s="5" t="s">
+      <c r="I95" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I95" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J95" s="6" t="s">
         <v>355</v>
@@ -34407,10 +34404,10 @@
         <v>954</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P95" s="2">
         <v>9</v>
@@ -34436,13 +34433,13 @@
         <v>3149</v>
       </c>
       <c r="G96" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H96" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H96" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I96" s="5" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="J96" s="6" t="s">
         <v>355</v>
@@ -34457,10 +34454,10 @@
         <v>1443</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P96" s="2">
         <v>6</v>
@@ -34486,13 +34483,13 @@
         <v>799</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H97" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I97" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I97" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J97" s="6" t="s">
         <v>356</v>
@@ -34507,10 +34504,10 @@
         <v>371</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P97" s="2">
         <v>50</v>
@@ -34549,10 +34546,10 @@
         <v>975</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P98" s="2">
         <v>12</v>
@@ -34591,10 +34588,10 @@
         <v>969</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P99" s="2">
         <v>14</v>
@@ -34633,10 +34630,10 @@
         <v>1175</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P100" s="2">
         <v>4</v>
@@ -34662,10 +34659,10 @@
         <v>999</v>
       </c>
       <c r="G101" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H101" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H101" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I101" s="5" t="s">
         <v>744</v>
@@ -34683,10 +34680,10 @@
         <v>501</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P101" s="2">
         <v>36</v>
@@ -34712,13 +34709,13 @@
         <v>999</v>
       </c>
       <c r="G102" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H102" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H102" s="5" t="s">
+      <c r="I102" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J102" s="6" t="s">
         <v>355</v>
@@ -34733,10 +34730,10 @@
         <v>501</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P102" s="2">
         <v>36</v>
@@ -34762,13 +34759,13 @@
         <v>5999</v>
       </c>
       <c r="G103" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H103" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H103" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I103" s="5" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="J103" s="6" t="s">
         <v>355</v>
@@ -34783,10 +34780,10 @@
         <v>3423</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P103" s="2">
         <v>1</v>
@@ -34812,10 +34809,10 @@
         <v>1999</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I104" s="5" t="s">
         <v>54</v>
@@ -34833,10 +34830,10 @@
         <v>829</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P104" s="2">
         <v>6</v>
@@ -34862,10 +34859,10 @@
         <v>1799</v>
       </c>
       <c r="G105" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H105" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I105" s="5" t="s">
         <v>42</v>
@@ -34883,10 +34880,10 @@
         <v>818</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P105" s="2">
         <v>12</v>
@@ -34912,13 +34909,13 @@
         <v>16990</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>355</v>
@@ -34933,10 +34930,10 @@
         <v>10158</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P106" s="2">
         <v>1</v>
@@ -34975,10 +34972,10 @@
         <v>6416</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P107" s="2">
         <v>1</v>
@@ -35017,10 +35014,10 @@
         <v>781</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P108" s="2" t="e">
         <v>#N/A</v>
@@ -35046,13 +35043,13 @@
         <v>899</v>
       </c>
       <c r="G109" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H109" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H109" s="5" t="s">
+      <c r="I109" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I109" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J109" s="6" t="s">
         <v>356</v>
@@ -35067,10 +35064,10 @@
         <v>436</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P109" s="2">
         <v>20</v>
@@ -35096,13 +35093,13 @@
         <v>2119</v>
       </c>
       <c r="G110" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H110" s="5" t="s">
         <v>2956</v>
       </c>
-      <c r="H110" s="5" t="s">
+      <c r="I110" s="5" t="s">
         <v>2957</v>
-      </c>
-      <c r="I110" s="5" t="s">
-        <v>2958</v>
       </c>
       <c r="J110" s="6" t="s">
         <v>356</v>
@@ -35117,10 +35114,10 @@
         <v>980</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P110" s="2">
         <v>12</v>
@@ -35159,10 +35156,10 @@
         <v>6146</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P111" s="2">
         <v>1</v>
@@ -35188,10 +35185,10 @@
         <v>5999</v>
       </c>
       <c r="G112" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H112" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>744</v>
@@ -35209,10 +35206,10 @@
         <v>3229</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P112" s="2">
         <v>6</v>
@@ -35251,10 +35248,10 @@
         <v>963</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P113" s="2">
         <v>16</v>
@@ -35280,10 +35277,10 @@
         <v>4199</v>
       </c>
       <c r="G114" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H114" s="5" t="s">
         <v>2953</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>2954</v>
       </c>
       <c r="I114" s="5" t="s">
         <v>206</v>
@@ -35301,10 +35298,10 @@
         <v>2005</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P114" s="2">
         <v>4</v>
@@ -35330,10 +35327,10 @@
         <v>3499</v>
       </c>
       <c r="G115" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H115" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I115" s="5" t="s">
         <v>744</v>
@@ -35351,10 +35348,10 @@
         <v>1177</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P115" s="2">
         <v>20</v>
@@ -35393,10 +35390,10 @@
         <v>1227</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P116" s="2">
         <v>10</v>
@@ -35435,10 +35432,10 @@
         <v>2827</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P117" s="2" t="e">
         <v>#N/A</v>
@@ -35464,10 +35461,10 @@
         <v>799</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I118" s="5" t="s">
         <v>154</v>
@@ -35485,10 +35482,10 @@
         <v>373</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P118" s="2">
         <v>50</v>
@@ -35514,10 +35511,10 @@
         <v>749</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I119" s="5" t="s">
         <v>744</v>
@@ -35535,10 +35532,10 @@
         <v>324</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P119" s="2">
         <v>12</v>
@@ -35564,10 +35561,10 @@
         <v>599</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I120" s="5" t="s">
         <v>744</v>
@@ -35585,10 +35582,10 @@
         <v>261</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P120" s="2">
         <v>60</v>
@@ -35614,10 +35611,10 @@
         <v>599</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>744</v>
@@ -35635,10 +35632,10 @@
         <v>297</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P121" s="2">
         <v>50</v>
@@ -35664,10 +35661,10 @@
         <v>2399</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>744</v>
@@ -35685,10 +35682,10 @@
         <v>1307</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P122" s="2">
         <v>8</v>
@@ -35714,10 +35711,10 @@
         <v>399</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>1612</v>
@@ -35735,10 +35732,10 @@
         <v>145</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P123" s="2">
         <v>100</v>
@@ -35764,10 +35761,10 @@
         <v>4999</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>58</v>
@@ -35785,10 +35782,10 @@
         <v>2004</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P124" s="2">
         <v>20</v>
@@ -35814,13 +35811,13 @@
         <v>1499</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="J125" s="6" t="s">
         <v>356</v>
@@ -35835,10 +35832,10 @@
         <v>663</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P125" s="2">
         <v>12</v>
@@ -35864,10 +35861,10 @@
         <v>1499</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>239</v>
@@ -35885,10 +35882,10 @@
         <v>899</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P126" s="2">
         <v>40</v>
@@ -35927,10 +35924,10 @@
         <v>82</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P127" s="2" t="e">
         <v>#N/A</v>
@@ -35969,10 +35966,10 @@
         <v>40</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P128" s="2" t="e">
         <v>#N/A</v>
@@ -36011,10 +36008,10 @@
         <v>300</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P129" s="2" t="e">
         <v>#N/A</v>
@@ -36053,10 +36050,10 @@
         <v>250</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P130" s="2" t="e">
         <v>#N/A</v>
@@ -36095,10 +36092,10 @@
         <v>108</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P131" s="2" t="e">
         <v>#N/A</v>
@@ -36137,10 +36134,10 @@
         <v>145</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P132" s="2" t="e">
         <v>#N/A</v>
@@ -36179,10 +36176,10 @@
         <v>35</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P133" s="2" t="e">
         <v>#N/A</v>
@@ -36221,10 +36218,10 @@
         <v>45</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P134" s="2" t="e">
         <v>#N/A</v>
@@ -36263,10 +36260,10 @@
         <v>350</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P135" s="2" t="e">
         <v>#N/A</v>
@@ -36305,10 +36302,10 @@
         <v>350</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O136" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P136" s="2" t="e">
         <v>#N/A</v>
@@ -36347,10 +36344,10 @@
         <v>350</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P137" s="2" t="e">
         <v>#N/A</v>
@@ -36389,10 +36386,10 @@
         <v>45</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P138" s="2" t="e">
         <v>#N/A</v>
@@ -36431,10 +36428,10 @@
         <v>45</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P139" s="2" t="e">
         <v>#N/A</v>
@@ -36473,10 +36470,10 @@
         <v>45</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P140" s="2" t="e">
         <v>#N/A</v>
@@ -36515,10 +36512,10 @@
         <v>45</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P141" s="2" t="e">
         <v>#N/A</v>
@@ -36557,10 +36554,10 @@
         <v>2350</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O142" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P142" s="2" t="e">
         <v>#N/A</v>
@@ -36599,10 +36596,10 @@
         <v>500</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P143" s="2" t="e">
         <v>#N/A</v>
@@ -36641,10 +36638,10 @@
         <v>350</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P144" s="2" t="e">
         <v>#N/A</v>
@@ -36683,10 +36680,10 @@
         <v>350</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P145" s="2" t="e">
         <v>#N/A</v>
@@ -36725,10 +36722,10 @@
         <v>2000</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O146" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P146" s="2" t="e">
         <v>#N/A</v>
@@ -36767,10 +36764,10 @@
         <v>550</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P147" s="2" t="e">
         <v>#N/A</v>
@@ -36796,10 +36793,10 @@
         <v>5999</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>744</v>
@@ -36817,10 +36814,10 @@
         <v>0</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P148" s="2">
         <v>9</v>
@@ -36828,7 +36825,7 @@
     </row>
     <row r="149" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B149" s="14"/>
       <c r="C149" s="5" t="s">
@@ -36842,7 +36839,7 @@
       </c>
       <c r="F149" s="5"/>
       <c r="G149" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
@@ -36859,10 +36856,10 @@
         <v>0</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P149" s="2">
         <v>9</v>
@@ -36884,13 +36881,13 @@
       </c>
       <c r="F150" s="5"/>
       <c r="G150" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H150" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H150" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I150" s="5" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>1097</v>
@@ -36919,13 +36916,13 @@
       </c>
       <c r="F151" s="5"/>
       <c r="G151" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H151" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H151" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I151" s="5" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="J151" s="5" t="s">
         <v>1098</v>
@@ -36954,13 +36951,13 @@
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H152" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H152" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I152" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J152" s="5" t="s">
         <v>1100</v>
@@ -36989,13 +36986,13 @@
       </c>
       <c r="F153" s="5"/>
       <c r="G153" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H153" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H153" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I153" s="5" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="J153" s="5" t="s">
         <v>1098</v>
@@ -37024,13 +37021,13 @@
       </c>
       <c r="F154" s="5"/>
       <c r="G154" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H154" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H154" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I154" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J154" s="5" t="s">
         <v>1103</v>
@@ -37059,10 +37056,10 @@
       </c>
       <c r="F155" s="5"/>
       <c r="G155" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I155" s="5" t="s">
         <v>744</v>
@@ -37094,10 +37091,10 @@
       </c>
       <c r="F156" s="16"/>
       <c r="G156" s="16" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H156" s="16" t="s">
         <v>2956</v>
-      </c>
-      <c r="H156" s="16" t="s">
-        <v>2957</v>
       </c>
       <c r="I156" s="16" t="s">
         <v>744</v>
@@ -37131,13 +37128,13 @@
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I157" s="5" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="J157" s="5" t="s">
         <v>1106</v>
@@ -37166,13 +37163,13 @@
       </c>
       <c r="F158" s="5"/>
       <c r="G158" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="J158" s="5" t="s">
         <v>1108</v>
@@ -37201,13 +37198,13 @@
       </c>
       <c r="F159" s="5"/>
       <c r="G159" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H159" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H159" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I159" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J159" s="5" t="s">
         <v>1097</v>
@@ -37236,10 +37233,10 @@
       </c>
       <c r="F160" s="5"/>
       <c r="G160" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I160" s="5" t="s">
         <v>744</v>
@@ -37271,13 +37268,13 @@
       </c>
       <c r="F161" s="5"/>
       <c r="G161" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H161" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H161" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I161" s="5" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J161" s="5" t="s">
         <v>1098</v>
@@ -37306,13 +37303,13 @@
       </c>
       <c r="F162" s="5"/>
       <c r="G162" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H162" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H162" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I162" s="5" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J162" s="5" t="s">
         <v>1098</v>
@@ -37341,13 +37338,13 @@
       </c>
       <c r="F163" s="5"/>
       <c r="G163" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H163" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H163" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I163" s="5" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="J163" s="5" t="s">
         <v>2851</v>
@@ -37376,13 +37373,13 @@
       </c>
       <c r="F164" s="5"/>
       <c r="G164" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H164" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H164" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I164" s="5" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J164" s="5" t="s">
         <v>1108</v>
@@ -37411,13 +37408,13 @@
       </c>
       <c r="F165" s="5"/>
       <c r="G165" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I165" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J165" s="5" t="s">
         <v>1097</v>
@@ -37446,13 +37443,13 @@
       </c>
       <c r="F166" s="5"/>
       <c r="G166" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I166" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>1103</v>
@@ -37481,10 +37478,10 @@
       </c>
       <c r="F167" s="5"/>
       <c r="G167" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I167" s="5" t="s">
         <v>744</v>
@@ -37516,13 +37513,13 @@
       </c>
       <c r="F168" s="5"/>
       <c r="G168" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I168" s="5" t="s">
         <v>2989</v>
-      </c>
-      <c r="H168" s="5" t="s">
-        <v>2954</v>
-      </c>
-      <c r="I168" s="5" t="s">
-        <v>2990</v>
       </c>
       <c r="J168" s="5" t="s">
         <v>1117</v>
@@ -37551,13 +37548,13 @@
       </c>
       <c r="F169" s="5"/>
       <c r="G169" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I169" s="5" t="s">
         <v>2989</v>
-      </c>
-      <c r="H169" s="5" t="s">
-        <v>2954</v>
-      </c>
-      <c r="I169" s="5" t="s">
-        <v>2990</v>
       </c>
       <c r="J169" s="5" t="s">
         <v>1117</v>
@@ -37586,10 +37583,10 @@
       </c>
       <c r="F170" s="5"/>
       <c r="G170" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I170" s="5" t="s">
         <v>744</v>
@@ -37621,10 +37618,10 @@
       </c>
       <c r="F171" s="5"/>
       <c r="G171" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I171" s="5" t="s">
         <v>744</v>
@@ -37652,14 +37649,14 @@
         <v>520</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="F172" s="5"/>
       <c r="G172" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I172" s="5" t="s">
         <v>744</v>
@@ -37691,10 +37688,10 @@
       </c>
       <c r="F173" s="5"/>
       <c r="G173" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I173" s="5" t="s">
         <v>744</v>
@@ -37726,13 +37723,13 @@
       </c>
       <c r="F174" s="5"/>
       <c r="G174" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H174" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H174" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I174" s="5" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>1113</v>
@@ -37761,10 +37758,10 @@
       </c>
       <c r="F175" s="5"/>
       <c r="G175" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I175" s="5" t="s">
         <v>744</v>
@@ -37796,13 +37793,13 @@
       </c>
       <c r="F176" s="5"/>
       <c r="G176" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J176" s="5" t="s">
         <v>1126</v>
@@ -37831,10 +37828,10 @@
       </c>
       <c r="F177" s="5"/>
       <c r="G177" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I177" s="5" t="s">
         <v>749</v>
@@ -37866,13 +37863,13 @@
       </c>
       <c r="F178" s="5"/>
       <c r="G178" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J178" s="5" t="s">
         <v>1103</v>
@@ -37901,13 +37898,13 @@
       </c>
       <c r="F179" s="5"/>
       <c r="G179" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="J179" s="5" t="s">
         <v>1103</v>
@@ -37936,13 +37933,13 @@
       </c>
       <c r="F180" s="5"/>
       <c r="G180" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J180" s="5" t="s">
         <v>1126</v>
@@ -37971,10 +37968,10 @@
       </c>
       <c r="F181" s="5"/>
       <c r="G181" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I181" s="5" t="s">
         <v>744</v>
@@ -38006,10 +38003,10 @@
       </c>
       <c r="F182" s="5"/>
       <c r="G182" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I182" s="5" t="s">
         <v>744</v>
@@ -38041,13 +38038,13 @@
       </c>
       <c r="F183" s="5"/>
       <c r="G183" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I183" s="5" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J183" s="5" t="s">
         <v>1098</v>
@@ -38076,13 +38073,13 @@
       </c>
       <c r="F184" s="5"/>
       <c r="G184" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I184" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J184" s="5" t="s">
         <v>1108</v>
@@ -38111,13 +38108,13 @@
       </c>
       <c r="F185" s="5"/>
       <c r="G185" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J185" s="5" t="s">
         <v>1113</v>
@@ -38146,13 +38143,13 @@
       </c>
       <c r="F186" s="5"/>
       <c r="G186" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H186" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H186" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I186" s="5" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="J186" s="5" t="s">
         <v>1113</v>
@@ -38181,10 +38178,10 @@
       </c>
       <c r="F187" s="5"/>
       <c r="G187" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H187" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H187" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I187" s="5" t="s">
         <v>744</v>
@@ -38216,13 +38213,13 @@
       </c>
       <c r="F188" s="5"/>
       <c r="G188" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I188" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J188" s="5" t="s">
         <v>1108</v>
@@ -38251,13 +38248,13 @@
       </c>
       <c r="F189" s="5"/>
       <c r="G189" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H189" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H189" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I189" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J189" s="5" t="s">
         <v>1126</v>
@@ -38286,10 +38283,10 @@
       </c>
       <c r="F190" s="5"/>
       <c r="G190" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="H190" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H190" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I190" s="5" t="s">
         <v>744</v>
@@ -38321,13 +38318,13 @@
       </c>
       <c r="F191" s="5"/>
       <c r="G191" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I191" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>1126</v>
@@ -38356,10 +38353,10 @@
       </c>
       <c r="F192" s="5"/>
       <c r="G192" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I192" s="5" t="s">
         <v>744</v>
@@ -38391,13 +38388,13 @@
       </c>
       <c r="F193" s="5"/>
       <c r="G193" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I193" s="5" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="J193" s="5" t="s">
         <v>1098</v>
@@ -38426,13 +38423,13 @@
       </c>
       <c r="F194" s="5"/>
       <c r="G194" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I194" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>1097</v>
@@ -38461,13 +38458,13 @@
       </c>
       <c r="F195" s="5"/>
       <c r="G195" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I195" s="5" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>1113</v>
@@ -38496,13 +38493,13 @@
       </c>
       <c r="F196" s="5"/>
       <c r="G196" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I196" s="5" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="J196" s="5" t="s">
         <v>1113</v>
@@ -38531,10 +38528,10 @@
       </c>
       <c r="F197" s="5"/>
       <c r="G197" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I197" s="5" t="s">
         <v>744</v>
@@ -38566,13 +38563,13 @@
       </c>
       <c r="F198" s="5"/>
       <c r="G198" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I198" s="5" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="J198" s="5" t="s">
         <v>2851</v>
@@ -38601,13 +38598,13 @@
       </c>
       <c r="F199" s="5"/>
       <c r="G199" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H199" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H199" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I199" s="5" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J199" s="5" t="s">
         <v>1108</v>
@@ -38636,13 +38633,13 @@
       </c>
       <c r="F200" s="5"/>
       <c r="G200" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I200" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J200" s="5" t="s">
         <v>1124</v>
@@ -38671,10 +38668,10 @@
       </c>
       <c r="F201" s="5"/>
       <c r="G201" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I201" s="5" t="s">
         <v>744</v>
@@ -38706,13 +38703,13 @@
       </c>
       <c r="F202" s="5"/>
       <c r="G202" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H202" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H202" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I202" s="5" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="J202" s="5" t="s">
         <v>1126</v>
@@ -38741,13 +38738,13 @@
       </c>
       <c r="F203" s="5"/>
       <c r="G203" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H203" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I203" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J203" s="5" t="s">
         <v>1108</v>
@@ -38776,10 +38773,10 @@
       </c>
       <c r="F204" s="5"/>
       <c r="G204" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H204" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H204" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I204" s="5" t="s">
         <v>744</v>
@@ -38811,13 +38808,13 @@
       </c>
       <c r="F205" s="5"/>
       <c r="G205" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I205" s="5" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J205" s="5" t="s">
         <v>1126</v>
@@ -38846,10 +38843,10 @@
       </c>
       <c r="F206" s="5"/>
       <c r="G206" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H206" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H206" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I206" s="5" t="s">
         <v>744</v>
@@ -38881,13 +38878,13 @@
       </c>
       <c r="F207" s="5"/>
       <c r="G207" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I207" s="5" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J207" s="5" t="s">
         <v>1126</v>
@@ -38916,13 +38913,13 @@
       </c>
       <c r="F208" s="5"/>
       <c r="G208" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I208" s="5" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="J208" s="5" t="s">
         <v>1098</v>
@@ -38951,13 +38948,13 @@
       </c>
       <c r="F209" s="5"/>
       <c r="G209" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I209" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J209" s="5" t="s">
         <v>1106</v>
@@ -38986,10 +38983,10 @@
       </c>
       <c r="F210" s="5"/>
       <c r="G210" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H210" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H210" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I210" s="5" t="s">
         <v>744</v>
@@ -39021,13 +39018,13 @@
       </c>
       <c r="F211" s="5"/>
       <c r="G211" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I211" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J211" s="5" t="s">
         <v>1106</v>
@@ -39056,13 +39053,13 @@
       </c>
       <c r="F212" s="5"/>
       <c r="G212" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I212" s="5" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J212" s="5" t="s">
         <v>1124</v>
@@ -39091,13 +39088,13 @@
       </c>
       <c r="F213" s="5"/>
       <c r="G213" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I213" s="5" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="J213" s="5" t="s">
         <v>1098</v>
@@ -39126,10 +39123,10 @@
       </c>
       <c r="F214" s="5"/>
       <c r="G214" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I214" s="5" t="s">
         <v>744</v>
@@ -39161,10 +39158,10 @@
       </c>
       <c r="F215" s="5"/>
       <c r="G215" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H215" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H215" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>744</v>
@@ -39196,13 +39193,13 @@
       </c>
       <c r="F216" s="5"/>
       <c r="G216" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I216" s="5" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="J216" s="5" t="s">
         <v>1126</v>
@@ -39231,13 +39228,13 @@
       </c>
       <c r="F217" s="5"/>
       <c r="G217" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I217" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J217" s="5" t="s">
         <v>1106</v>
@@ -39266,13 +39263,13 @@
       </c>
       <c r="F218" s="5"/>
       <c r="G218" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I218" s="5" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J218" s="5" t="s">
         <v>1098</v>
@@ -39301,13 +39298,13 @@
       </c>
       <c r="F219" s="5"/>
       <c r="G219" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I219" s="5" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="J219" s="5" t="s">
         <v>1098</v>
@@ -39336,13 +39333,13 @@
       </c>
       <c r="F220" s="5"/>
       <c r="G220" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I220" s="5" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="J220" s="5" t="s">
         <v>1106</v>
@@ -39371,13 +39368,13 @@
       </c>
       <c r="F221" s="5"/>
       <c r="G221" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I221" s="5" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J221" s="5" t="s">
         <v>1113</v>
@@ -39406,13 +39403,13 @@
       </c>
       <c r="F222" s="5"/>
       <c r="G222" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I222" s="5" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J222" s="5" t="s">
         <v>1126</v>
@@ -39441,10 +39438,10 @@
       </c>
       <c r="F223" s="5"/>
       <c r="G223" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I223" s="5" t="s">
         <v>744</v>
@@ -39476,13 +39473,13 @@
       </c>
       <c r="F224" s="5"/>
       <c r="G224" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I224" s="5" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J224" s="5" t="s">
         <v>1098</v>
@@ -39511,13 +39508,13 @@
       </c>
       <c r="F225" s="5"/>
       <c r="G225" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I225" s="5" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="J225" s="5" t="s">
         <v>1113</v>
@@ -39546,13 +39543,13 @@
       </c>
       <c r="F226" s="5"/>
       <c r="G226" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I226" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J226" s="5" t="s">
         <v>1097</v>
@@ -39581,13 +39578,13 @@
       </c>
       <c r="F227" s="5"/>
       <c r="G227" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I227" s="5" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="J227" s="5" t="s">
         <v>1124</v>
@@ -39616,13 +39613,13 @@
       </c>
       <c r="F228" s="5"/>
       <c r="G228" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I228" s="5" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J228" s="5" t="s">
         <v>1098</v>
@@ -39651,13 +39648,13 @@
       </c>
       <c r="F229" s="5"/>
       <c r="G229" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I229" s="5" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="J229" s="5" t="s">
         <v>1113</v>
@@ -39686,13 +39683,13 @@
       </c>
       <c r="F230" s="5"/>
       <c r="G230" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I230" s="5" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J230" s="5" t="s">
         <v>1098</v>
@@ -39721,13 +39718,13 @@
       </c>
       <c r="F231" s="5"/>
       <c r="G231" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I231" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J231" s="5" t="s">
         <v>1124</v>
@@ -39756,13 +39753,13 @@
       </c>
       <c r="F232" s="5"/>
       <c r="G232" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I232" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J232" s="5" t="s">
         <v>1124</v>
@@ -39791,13 +39788,13 @@
       </c>
       <c r="F233" s="5"/>
       <c r="G233" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I233" s="5" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="J233" s="5" t="s">
         <v>1098</v>
@@ -39826,13 +39823,13 @@
       </c>
       <c r="F234" s="5"/>
       <c r="G234" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I234" s="5" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J234" s="5" t="s">
         <v>1113</v>
@@ -39861,10 +39858,10 @@
       </c>
       <c r="F235" s="5"/>
       <c r="G235" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I235" s="5" t="s">
         <v>744</v>
@@ -39896,10 +39893,10 @@
       </c>
       <c r="F236" s="5"/>
       <c r="G236" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I236" s="5" t="s">
         <v>744</v>
@@ -39931,13 +39928,13 @@
       </c>
       <c r="F237" s="5"/>
       <c r="G237" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I237" s="5" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="J237" s="5" t="s">
         <v>1098</v>
@@ -39966,13 +39963,13 @@
       </c>
       <c r="F238" s="5"/>
       <c r="G238" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H238" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H238" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I238" s="5" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="J238" s="5" t="s">
         <v>1108</v>
@@ -40001,13 +39998,13 @@
       </c>
       <c r="F239" s="5"/>
       <c r="G239" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I239" s="5" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J239" s="5" t="s">
         <v>1124</v>
@@ -40036,13 +40033,13 @@
       </c>
       <c r="F240" s="5"/>
       <c r="G240" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H240" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I240" s="5" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J240" s="5" t="s">
         <v>1126</v>
@@ -40071,10 +40068,10 @@
       </c>
       <c r="F241" s="5"/>
       <c r="G241" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H241" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H241" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I241" s="5" t="s">
         <v>744</v>
@@ -40106,10 +40103,10 @@
       </c>
       <c r="F242" s="5"/>
       <c r="G242" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H242" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H242" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I242" s="5" t="s">
         <v>744</v>
@@ -40141,10 +40138,10 @@
       </c>
       <c r="F243" s="5"/>
       <c r="G243" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H243" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H243" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I243" s="5" t="s">
         <v>744</v>
@@ -40176,10 +40173,10 @@
       </c>
       <c r="F244" s="5"/>
       <c r="G244" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H244" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H244" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I244" s="5" t="s">
         <v>744</v>
@@ -40211,13 +40208,13 @@
       </c>
       <c r="F245" s="5"/>
       <c r="G245" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I245" s="5" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J245" s="5" t="s">
         <v>1124</v>
@@ -40246,13 +40243,13 @@
       </c>
       <c r="F246" s="5"/>
       <c r="G246" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I246" s="5" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="J246" s="5" t="s">
         <v>1108</v>
@@ -40281,13 +40278,13 @@
       </c>
       <c r="F247" s="5"/>
       <c r="G247" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I247" s="5" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J247" s="5" t="s">
         <v>1143</v>
@@ -40316,13 +40313,13 @@
       </c>
       <c r="F248" s="5"/>
       <c r="G248" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H248" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I248" s="5" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="J248" s="5" t="s">
         <v>1124</v>
@@ -40351,13 +40348,13 @@
       </c>
       <c r="F249" s="5"/>
       <c r="G249" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I249" s="5" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J249" s="5" t="s">
         <v>1146</v>
@@ -40386,13 +40383,13 @@
       </c>
       <c r="F250" s="5"/>
       <c r="G250" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I250" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J250" s="5" t="s">
         <v>1148</v>
@@ -40421,10 +40418,10 @@
       </c>
       <c r="F251" s="5"/>
       <c r="G251" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H251" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I251" s="5" t="s">
         <v>744</v>
@@ -40442,11 +40439,11 @@
     </row>
     <row r="252" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="5" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B252" s="5"/>
       <c r="C252" s="5" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="D252" s="5" t="s">
         <v>520</v>
@@ -40456,10 +40453,10 @@
       </c>
       <c r="F252" s="5"/>
       <c r="G252" s="5" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I252" s="5" t="s">
         <v>744</v>
@@ -40491,10 +40488,10 @@
       </c>
       <c r="F253" s="5"/>
       <c r="G253" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H253" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I253" s="5" t="s">
         <v>744</v>
@@ -40526,13 +40523,13 @@
       </c>
       <c r="F254" s="5"/>
       <c r="G254" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I254" s="5" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="J254" s="5" t="s">
         <v>1098</v>
@@ -40561,13 +40558,13 @@
       </c>
       <c r="F255" s="5"/>
       <c r="G255" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I255" s="5" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J255" s="5" t="s">
         <v>1098</v>
@@ -40596,10 +40593,10 @@
       </c>
       <c r="F256" s="5"/>
       <c r="G256" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I256" s="5" t="s">
         <v>749</v>
@@ -40631,13 +40628,13 @@
       </c>
       <c r="F257" s="5"/>
       <c r="G257" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I257" s="5" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J257" s="5" t="s">
         <v>1098</v>
@@ -40666,13 +40663,13 @@
       </c>
       <c r="F258" s="5"/>
       <c r="G258" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H258" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I258" s="5" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="J258" s="5" t="s">
         <v>1098</v>
@@ -40701,13 +40698,13 @@
       </c>
       <c r="F259" s="5"/>
       <c r="G259" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I259" s="5" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J259" s="5" t="s">
         <v>1143</v>
@@ -40736,13 +40733,13 @@
       </c>
       <c r="F260" s="5"/>
       <c r="G260" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I260" s="5" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J260" s="5" t="s">
         <v>1098</v>
@@ -40771,13 +40768,13 @@
       </c>
       <c r="F261" s="5"/>
       <c r="G261" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I261" s="5" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="J261" s="5" t="s">
         <v>1143</v>
@@ -40806,10 +40803,10 @@
       </c>
       <c r="F262" s="5"/>
       <c r="G262" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H262" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H262" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I262" s="5" t="s">
         <v>744</v>
@@ -40841,13 +40838,13 @@
       </c>
       <c r="F263" s="5"/>
       <c r="G263" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I263" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J263" s="5" t="s">
         <v>1148</v>
@@ -40866,7 +40863,7 @@
       </c>
       <c r="B264" s="5"/>
       <c r="C264" s="5" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="D264" s="5" t="s">
         <v>520</v>
@@ -40876,10 +40873,10 @@
       </c>
       <c r="F264" s="5"/>
       <c r="G264" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I264" s="5" t="s">
         <v>744</v>
@@ -40911,10 +40908,10 @@
       </c>
       <c r="F265" s="5"/>
       <c r="G265" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H265" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H265" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I265" s="5" t="s">
         <v>744</v>
@@ -40946,10 +40943,10 @@
       </c>
       <c r="F266" s="5"/>
       <c r="G266" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H266" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H266" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I266" s="5" t="s">
         <v>744</v>
@@ -40981,13 +40978,13 @@
       </c>
       <c r="F267" s="5"/>
       <c r="G267" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I267" s="5" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J267" s="5" t="s">
         <v>1146</v>
@@ -41016,13 +41013,13 @@
       </c>
       <c r="F268" s="5"/>
       <c r="G268" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H268" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I268" s="5" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J268" s="5" t="s">
         <v>1098</v>
@@ -41051,10 +41048,10 @@
       </c>
       <c r="F269" s="5"/>
       <c r="G269" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H269" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H269" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I269" s="5" t="s">
         <v>744</v>
@@ -41086,10 +41083,10 @@
       </c>
       <c r="F270" s="5"/>
       <c r="G270" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H270" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H270" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I270" s="5" t="s">
         <v>744</v>
@@ -41121,10 +41118,10 @@
       </c>
       <c r="F271" s="5"/>
       <c r="G271" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H271" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H271" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I271" s="5" t="s">
         <v>744</v>
@@ -41156,13 +41153,13 @@
       </c>
       <c r="F272" s="5"/>
       <c r="G272" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H272" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I272" s="5" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="J272" s="5" t="s">
         <v>1113</v>
@@ -41191,10 +41188,10 @@
       </c>
       <c r="F273" s="5"/>
       <c r="G273" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H273" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H273" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I273" s="5" t="s">
         <v>744</v>
@@ -41226,10 +41223,10 @@
       </c>
       <c r="F274" s="5"/>
       <c r="G274" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H274" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H274" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I274" s="5" t="s">
         <v>744</v>
@@ -41261,13 +41258,13 @@
       </c>
       <c r="F275" s="5"/>
       <c r="G275" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H275" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I275" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J275" s="5" t="s">
         <v>1148</v>
@@ -41296,13 +41293,13 @@
       </c>
       <c r="F276" s="5"/>
       <c r="G276" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H276" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I276" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J276" s="5" t="s">
         <v>1148</v>
@@ -41331,10 +41328,10 @@
       </c>
       <c r="F277" s="5"/>
       <c r="G277" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H277" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H277" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I277" s="5" t="s">
         <v>744</v>
@@ -41366,13 +41363,13 @@
       </c>
       <c r="F278" s="5"/>
       <c r="G278" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="J278" s="5" t="s">
         <v>1113</v>
@@ -41401,10 +41398,10 @@
       </c>
       <c r="F279" s="5"/>
       <c r="G279" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H279" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H279" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I279" s="5" t="s">
         <v>744</v>
@@ -41436,10 +41433,10 @@
       </c>
       <c r="F280" s="5"/>
       <c r="G280" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H280" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H280" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I280" s="5" t="s">
         <v>744</v>
@@ -41471,10 +41468,10 @@
       </c>
       <c r="F281" s="5"/>
       <c r="G281" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H281" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H281" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I281" s="5" t="s">
         <v>744</v>
@@ -41506,10 +41503,10 @@
       </c>
       <c r="F282" s="5"/>
       <c r="G282" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H282" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H282" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I282" s="5" t="s">
         <v>744</v>
@@ -41541,10 +41538,10 @@
       </c>
       <c r="F283" s="5"/>
       <c r="G283" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H283" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H283" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I283" s="5" t="s">
         <v>744</v>
@@ -41576,10 +41573,10 @@
       </c>
       <c r="F284" s="5"/>
       <c r="G284" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H284" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H284" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I284" s="5" t="s">
         <v>744</v>
@@ -41611,13 +41608,13 @@
       </c>
       <c r="F285" s="5"/>
       <c r="G285" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="J285" s="5" t="s">
         <v>1148</v>
@@ -41646,13 +41643,13 @@
       </c>
       <c r="F286" s="5"/>
       <c r="G286" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H286" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I286" s="5" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="J286" s="5" t="s">
         <v>1098</v>
@@ -41681,10 +41678,10 @@
       </c>
       <c r="F287" s="5"/>
       <c r="G287" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H287" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H287" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I287" s="5" t="s">
         <v>744</v>
@@ -41716,13 +41713,13 @@
       </c>
       <c r="F288" s="5"/>
       <c r="G288" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H288" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I288" s="5" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J288" s="5" t="s">
         <v>1146</v>
@@ -41751,10 +41748,10 @@
       </c>
       <c r="F289" s="5"/>
       <c r="G289" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H289" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H289" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I289" s="5" t="s">
         <v>744</v>
@@ -41786,10 +41783,10 @@
       </c>
       <c r="F290" s="5"/>
       <c r="G290" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H290" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H290" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I290" s="5" t="s">
         <v>744</v>
@@ -41821,13 +41818,13 @@
       </c>
       <c r="F291" s="5"/>
       <c r="G291" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="H291" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I291" s="5" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="J291" s="5" t="s">
         <v>1097</v>
@@ -41856,10 +41853,10 @@
       </c>
       <c r="F292" s="5"/>
       <c r="G292" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H292" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H292" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I292" s="5" t="s">
         <v>744</v>
@@ -41891,10 +41888,10 @@
       </c>
       <c r="F293" s="5"/>
       <c r="G293" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H293" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H293" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I293" s="5" t="s">
         <v>744</v>
@@ -41926,10 +41923,10 @@
       </c>
       <c r="F294" s="5"/>
       <c r="G294" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H294" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H294" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I294" s="5" t="s">
         <v>744</v>
@@ -41961,10 +41958,10 @@
       </c>
       <c r="F295" s="5"/>
       <c r="G295" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H295" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H295" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I295" s="5" t="s">
         <v>744</v>
@@ -41996,10 +41993,10 @@
       </c>
       <c r="F296" s="5"/>
       <c r="G296" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H296" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H296" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I296" s="5" t="s">
         <v>744</v>
@@ -42031,10 +42028,10 @@
       </c>
       <c r="F297" s="5"/>
       <c r="G297" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H297" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H297" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I297" s="5" t="s">
         <v>744</v>
@@ -42066,10 +42063,10 @@
       </c>
       <c r="F298" s="5"/>
       <c r="G298" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H298" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H298" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I298" s="5" t="s">
         <v>744</v>
@@ -42101,10 +42098,10 @@
       </c>
       <c r="F299" s="5"/>
       <c r="G299" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H299" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H299" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I299" s="5" t="s">
         <v>744</v>
@@ -42136,10 +42133,10 @@
       </c>
       <c r="F300" s="5"/>
       <c r="G300" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H300" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H300" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I300" s="5" t="s">
         <v>744</v>
@@ -42171,10 +42168,10 @@
       </c>
       <c r="F301" s="5"/>
       <c r="G301" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H301" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H301" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I301" s="5" t="s">
         <v>744</v>
@@ -42206,10 +42203,10 @@
       </c>
       <c r="F302" s="5"/>
       <c r="G302" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H302" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H302" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I302" s="5" t="s">
         <v>744</v>
@@ -42241,10 +42238,10 @@
       </c>
       <c r="F303" s="5"/>
       <c r="G303" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H303" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H303" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I303" s="5" t="s">
         <v>744</v>
@@ -42276,10 +42273,10 @@
       </c>
       <c r="F304" s="5"/>
       <c r="G304" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H304" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H304" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I304" s="5" t="s">
         <v>744</v>
@@ -42311,10 +42308,10 @@
       </c>
       <c r="F305" s="5"/>
       <c r="G305" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H305" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H305" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I305" s="5" t="s">
         <v>744</v>
@@ -42346,10 +42343,10 @@
       </c>
       <c r="F306" s="5"/>
       <c r="G306" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H306" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H306" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I306" s="5" t="s">
         <v>744</v>
@@ -42381,10 +42378,10 @@
       </c>
       <c r="F307" s="5"/>
       <c r="G307" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H307" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H307" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I307" s="5" t="s">
         <v>744</v>
@@ -42416,13 +42413,13 @@
       </c>
       <c r="F308" s="5"/>
       <c r="G308" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H308" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I308" s="5" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J308" s="5" t="s">
         <v>1126</v>
@@ -42451,13 +42448,13 @@
       </c>
       <c r="F309" s="5"/>
       <c r="G309" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H309" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I309" s="5" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="J309" s="5" t="s">
         <v>1124</v>
@@ -42486,13 +42483,13 @@
       </c>
       <c r="F310" s="5"/>
       <c r="G310" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H310" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I310" s="5" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="J310" s="5" t="s">
         <v>1124</v>
@@ -42521,13 +42518,13 @@
       </c>
       <c r="F311" s="5"/>
       <c r="G311" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H311" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I311" s="5" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J311" s="5" t="s">
         <v>1124</v>
@@ -42556,10 +42553,10 @@
       </c>
       <c r="F312" s="5"/>
       <c r="G312" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H312" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I312" s="5" t="s">
         <v>744</v>
@@ -42591,13 +42588,13 @@
       </c>
       <c r="F313" s="5"/>
       <c r="G313" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H313" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I313" s="5" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J313" s="5" t="s">
         <v>1124</v>
@@ -42626,13 +42623,13 @@
       </c>
       <c r="F314" s="5"/>
       <c r="G314" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H314" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I314" s="5" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="J314" s="5" t="s">
         <v>1124</v>
@@ -42661,10 +42658,10 @@
       </c>
       <c r="F315" s="5"/>
       <c r="G315" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H315" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H315" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I315" s="5" t="s">
         <v>744</v>
@@ -42696,13 +42693,13 @@
       </c>
       <c r="F316" s="5"/>
       <c r="G316" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H316" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I316" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J316" s="5" t="s">
         <v>1124</v>
@@ -42731,13 +42728,13 @@
       </c>
       <c r="F317" s="5"/>
       <c r="G317" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H317" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I317" s="5" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="J317" s="5" t="s">
         <v>1124</v>
@@ -42766,13 +42763,13 @@
       </c>
       <c r="F318" s="5"/>
       <c r="G318" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H318" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I318" s="5" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="J318" s="5" t="s">
         <v>1124</v>
@@ -42801,10 +42798,10 @@
       </c>
       <c r="F319" s="5"/>
       <c r="G319" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H319" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I319" s="5" t="s">
         <v>744</v>
@@ -42836,10 +42833,10 @@
       </c>
       <c r="F320" s="5"/>
       <c r="G320" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H320" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I320" s="5" t="s">
         <v>744</v>
@@ -42871,10 +42868,10 @@
       </c>
       <c r="F321" s="5"/>
       <c r="G321" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H321" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I321" s="5" t="s">
         <v>744</v>
@@ -42906,10 +42903,10 @@
       </c>
       <c r="F322" s="5"/>
       <c r="G322" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H322" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I322" s="5" t="s">
         <v>744</v>
@@ -42941,10 +42938,10 @@
       </c>
       <c r="F323" s="5"/>
       <c r="G323" s="5" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H323" s="5" t="s">
         <v>2956</v>
-      </c>
-      <c r="H323" s="5" t="s">
-        <v>2957</v>
       </c>
       <c r="I323" s="5" t="s">
         <v>744</v>
@@ -42976,10 +42973,10 @@
       </c>
       <c r="F324" s="5"/>
       <c r="G324" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H324" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I324" s="5" t="s">
         <v>744</v>
@@ -43011,13 +43008,13 @@
       </c>
       <c r="F325" s="5"/>
       <c r="G325" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H325" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H325" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I325" s="5" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="J325" s="5" t="s">
         <v>1106</v>
@@ -43046,13 +43043,13 @@
       </c>
       <c r="F326" s="5"/>
       <c r="G326" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H326" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I326" s="5" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J326" s="5" t="s">
         <v>1106</v>
@@ -43081,13 +43078,13 @@
       </c>
       <c r="F327" s="5"/>
       <c r="G327" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H327" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H327" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I327" s="5" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J327" s="5" t="s">
         <v>1170</v>
@@ -43116,13 +43113,13 @@
       </c>
       <c r="F328" s="5"/>
       <c r="G328" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H328" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I328" s="5" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="J328" s="5" t="s">
         <v>1170</v>
@@ -43151,13 +43148,13 @@
       </c>
       <c r="F329" s="5"/>
       <c r="G329" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H329" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H329" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I329" s="5" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J329" s="5" t="s">
         <v>2795</v>
@@ -43182,14 +43179,14 @@
         <v>520</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="F330" s="5"/>
       <c r="G330" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H330" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I330" s="5" t="s">
         <v>744</v>
@@ -43217,14 +43214,14 @@
         <v>520</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="F331" s="5"/>
       <c r="G331" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H331" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I331" s="5" t="s">
         <v>744</v>
@@ -43256,10 +43253,10 @@
       </c>
       <c r="F332" s="5"/>
       <c r="G332" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H332" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I332" s="5" t="s">
         <v>744</v>
@@ -43291,13 +43288,13 @@
       </c>
       <c r="F333" s="5"/>
       <c r="G333" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H333" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I333" s="5" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J333" s="5" t="s">
         <v>2795</v>
@@ -43326,13 +43323,13 @@
       </c>
       <c r="F334" s="5"/>
       <c r="G334" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H334" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I334" s="5" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J334" s="5" t="s">
         <v>2795</v>
@@ -43361,13 +43358,13 @@
       </c>
       <c r="F335" s="5"/>
       <c r="G335" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H335" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I335" s="5" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="J335" s="5" t="s">
         <v>2795</v>
@@ -43396,13 +43393,13 @@
       </c>
       <c r="F336" s="5"/>
       <c r="G336" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H336" s="5" t="s">
         <v>2953</v>
       </c>
-      <c r="H336" s="5" t="s">
-        <v>2954</v>
-      </c>
       <c r="I336" s="5" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J336" s="5" t="s">
         <v>1106</v>
@@ -43431,10 +43428,10 @@
       </c>
       <c r="F337" s="5"/>
       <c r="G337" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H337" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I337" s="5" t="s">
         <v>744</v>
@@ -43466,10 +43463,10 @@
       </c>
       <c r="F338" s="5"/>
       <c r="G338" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H338" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I338" s="5" t="s">
         <v>744</v>
@@ -43501,10 +43498,10 @@
       </c>
       <c r="F339" s="5"/>
       <c r="G339" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H339" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I339" s="5" t="s">
         <v>744</v>
@@ -43526,7 +43523,7 @@
       </c>
       <c r="B340" s="5"/>
       <c r="C340" s="5" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="D340" s="5" t="s">
         <v>520</v>
@@ -43536,10 +43533,10 @@
       </c>
       <c r="F340" s="5"/>
       <c r="G340" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H340" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I340" s="5" t="s">
         <v>744</v>
@@ -43561,7 +43558,7 @@
       </c>
       <c r="B341" s="5"/>
       <c r="C341" s="5" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="D341" s="5" t="s">
         <v>520</v>
@@ -43571,10 +43568,10 @@
       </c>
       <c r="F341" s="5"/>
       <c r="G341" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H341" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I341" s="5" t="s">
         <v>744</v>
@@ -43606,10 +43603,10 @@
       </c>
       <c r="F342" s="5"/>
       <c r="G342" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H342" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I342" s="5" t="s">
         <v>744</v>
@@ -43631,7 +43628,7 @@
       </c>
       <c r="B343" s="5"/>
       <c r="C343" s="5" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="D343" s="5" t="s">
         <v>520</v>
@@ -43641,10 +43638,10 @@
       </c>
       <c r="F343" s="5"/>
       <c r="G343" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H343" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I343" s="5" t="s">
         <v>744</v>
@@ -43666,7 +43663,7 @@
       </c>
       <c r="B344" s="5"/>
       <c r="C344" s="5" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="D344" s="5" t="s">
         <v>520</v>
@@ -43676,10 +43673,10 @@
       </c>
       <c r="F344" s="5"/>
       <c r="G344" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H344" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I344" s="5" t="s">
         <v>744</v>
@@ -43701,7 +43698,7 @@
       </c>
       <c r="B345" s="5"/>
       <c r="C345" s="5" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="D345" s="5" t="s">
         <v>520</v>
@@ -43711,10 +43708,10 @@
       </c>
       <c r="F345" s="5"/>
       <c r="G345" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H345" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I345" s="5" t="s">
         <v>744</v>
@@ -43736,7 +43733,7 @@
       </c>
       <c r="B346" s="5"/>
       <c r="C346" s="5" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="D346" s="5" t="s">
         <v>520</v>
@@ -43746,10 +43743,10 @@
       </c>
       <c r="F346" s="5"/>
       <c r="G346" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H346" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I346" s="5" t="s">
         <v>744</v>
@@ -43771,7 +43768,7 @@
       </c>
       <c r="B347" s="5"/>
       <c r="C347" s="5" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="D347" s="5" t="s">
         <v>520</v>
@@ -43781,10 +43778,10 @@
       </c>
       <c r="F347" s="5"/>
       <c r="G347" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H347" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I347" s="5" t="s">
         <v>744</v>
@@ -43806,7 +43803,7 @@
       </c>
       <c r="B348" s="5"/>
       <c r="C348" s="5" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="D348" s="5" t="s">
         <v>520</v>
@@ -43816,10 +43813,10 @@
       </c>
       <c r="F348" s="5"/>
       <c r="G348" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H348" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I348" s="5" t="s">
         <v>744</v>
@@ -43841,7 +43838,7 @@
       </c>
       <c r="B349" s="5"/>
       <c r="C349" s="5" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="D349" s="5" t="s">
         <v>520</v>
@@ -43851,10 +43848,10 @@
       </c>
       <c r="F349" s="5"/>
       <c r="G349" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H349" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I349" s="5" t="s">
         <v>744</v>
@@ -43876,7 +43873,7 @@
       </c>
       <c r="B350" s="5"/>
       <c r="C350" s="5" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="D350" s="5" t="s">
         <v>520</v>
@@ -43886,10 +43883,10 @@
       </c>
       <c r="F350" s="5"/>
       <c r="G350" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H350" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I350" s="5" t="s">
         <v>744</v>
@@ -43911,7 +43908,7 @@
       </c>
       <c r="B351" s="5"/>
       <c r="C351" s="5" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="D351" s="5" t="s">
         <v>520</v>
@@ -43921,10 +43918,10 @@
       </c>
       <c r="F351" s="5"/>
       <c r="G351" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H351" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I351" s="5" t="s">
         <v>744</v>
@@ -44957,7 +44954,7 @@
         <v>3269</v>
       </c>
       <c r="N386" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P386" s="2">
         <f>_xlfn.XLOOKUP(C386,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -44993,7 +44990,7 @@
         <v>3943</v>
       </c>
       <c r="N387" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P387" s="2">
         <f>_xlfn.XLOOKUP(C387,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45029,7 +45026,7 @@
         <v>3943</v>
       </c>
       <c r="N388" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P388" s="2">
         <f>_xlfn.XLOOKUP(C388,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45065,7 +45062,7 @@
         <v>3943</v>
       </c>
       <c r="N389" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P389" s="2">
         <f>_xlfn.XLOOKUP(C389,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45101,7 +45098,7 @@
         <v>3943</v>
       </c>
       <c r="N390" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P390" s="2">
         <f>_xlfn.XLOOKUP(C390,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45137,7 +45134,7 @@
         <v>3607</v>
       </c>
       <c r="N391" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P391" s="2" t="s">
         <v>744</v>
@@ -45172,7 +45169,7 @@
         <v>3607</v>
       </c>
       <c r="N392" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P392" s="2" t="s">
         <v>744</v>
@@ -45207,7 +45204,7 @@
         <v>3607</v>
       </c>
       <c r="N393" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P393" s="2" t="s">
         <v>744</v>
@@ -45242,7 +45239,7 @@
         <v>3607</v>
       </c>
       <c r="N394" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P394" s="2" t="s">
         <v>744</v>
@@ -45277,7 +45274,7 @@
         <v>3272</v>
       </c>
       <c r="N395" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P395" s="2" t="s">
         <v>744</v>
@@ -45312,7 +45309,7 @@
         <v>3272</v>
       </c>
       <c r="N396" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P396" s="2" t="s">
         <v>744</v>
@@ -45347,7 +45344,7 @@
         <v>3262</v>
       </c>
       <c r="N397" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P397" s="2" t="s">
         <v>744</v>
@@ -45382,7 +45379,7 @@
         <v>3262</v>
       </c>
       <c r="N398" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P398" s="2" t="s">
         <v>744</v>
@@ -45417,7 +45414,7 @@
         <v>7852</v>
       </c>
       <c r="N399" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P399" s="2">
         <f>_xlfn.XLOOKUP(C399,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45453,7 +45450,7 @@
         <v>6978</v>
       </c>
       <c r="N400" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P400" s="2">
         <f>_xlfn.XLOOKUP(C400,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45489,7 +45486,7 @@
         <v>7852</v>
       </c>
       <c r="N401" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P401" s="2">
         <f>_xlfn.XLOOKUP(C401,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45525,7 +45522,7 @@
         <v>7852</v>
       </c>
       <c r="N402" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P402" s="2">
         <f>_xlfn.XLOOKUP(C402,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45561,7 +45558,7 @@
         <v>6978</v>
       </c>
       <c r="N403" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P403" s="2">
         <f>_xlfn.XLOOKUP(C403,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45597,7 +45594,7 @@
         <v>10654</v>
       </c>
       <c r="N404" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P404" s="2">
         <f>_xlfn.XLOOKUP(C404,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45633,7 +45630,7 @@
         <v>10654</v>
       </c>
       <c r="N405" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P405" s="2">
         <f>_xlfn.XLOOKUP(C405,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45669,7 +45666,7 @@
         <v>7018</v>
       </c>
       <c r="N406" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P406" s="2">
         <f>_xlfn.XLOOKUP(C406,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45705,7 +45702,7 @@
         <v>7018</v>
       </c>
       <c r="N407" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P407" s="2">
         <f>_xlfn.XLOOKUP(C407,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45741,7 +45738,7 @@
         <v>7018</v>
       </c>
       <c r="N408" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P408" s="2">
         <f>_xlfn.XLOOKUP(C408,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45777,7 +45774,7 @@
         <v>7018</v>
       </c>
       <c r="N409" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P409" s="2">
         <f>_xlfn.XLOOKUP(C409,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45813,7 +45810,7 @@
         <v>11345</v>
       </c>
       <c r="N410" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P410" s="2">
         <f>_xlfn.XLOOKUP(C410,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45849,7 +45846,7 @@
         <v>11345</v>
       </c>
       <c r="N411" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P411" s="2">
         <f>_xlfn.XLOOKUP(C411,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -45885,7 +45882,7 @@
         <v>11345</v>
       </c>
       <c r="N412" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P412" s="2" t="s">
         <v>744</v>
@@ -45920,7 +45917,7 @@
         <v>11345</v>
       </c>
       <c r="N413" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P413" s="2" t="s">
         <v>744</v>
@@ -45955,7 +45952,7 @@
         <v>12094</v>
       </c>
       <c r="N414" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P414" s="2" t="s">
         <v>744</v>
@@ -45990,7 +45987,7 @@
         <v>6432</v>
       </c>
       <c r="N415" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P415" s="2">
         <f>_xlfn.XLOOKUP(C415,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46026,7 +46023,7 @@
         <v>6432</v>
       </c>
       <c r="N416" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P416" s="2">
         <f>_xlfn.XLOOKUP(C416,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46062,7 +46059,7 @@
         <v>7641</v>
       </c>
       <c r="N417" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P417" s="2">
         <f>_xlfn.XLOOKUP(C417,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46098,7 +46095,7 @@
         <v>7641</v>
       </c>
       <c r="N418" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P418" s="2">
         <f>_xlfn.XLOOKUP(C418,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46134,7 +46131,7 @@
         <v>7641</v>
       </c>
       <c r="N419" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P419" s="2">
         <f>_xlfn.XLOOKUP(C419,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46170,7 +46167,7 @@
         <v>623</v>
       </c>
       <c r="N420" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P420" s="2" t="s">
         <v>744</v>
@@ -46205,7 +46202,7 @@
         <v>832</v>
       </c>
       <c r="N421" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P421" s="2" t="s">
         <v>744</v>
@@ -46240,7 +46237,7 @@
         <v>1032</v>
       </c>
       <c r="N422" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P422" s="2" t="s">
         <v>744</v>
@@ -46275,7 +46272,7 @@
         <v>1822</v>
       </c>
       <c r="N423" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P423" s="2" t="s">
         <v>744</v>
@@ -46310,7 +46307,7 @@
         <v>1074</v>
       </c>
       <c r="N424" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P424" s="2">
         <f>_xlfn.XLOOKUP(C424,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46346,7 +46343,7 @@
         <v>720</v>
       </c>
       <c r="N425" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P425" s="2">
         <f>_xlfn.XLOOKUP(C425,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46382,7 +46379,7 @@
         <v>1015</v>
       </c>
       <c r="N426" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P426" s="2">
         <f>_xlfn.XLOOKUP(C426,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46418,7 +46415,7 @@
         <v>1130</v>
       </c>
       <c r="N427" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P427" s="2">
         <f>_xlfn.XLOOKUP(C427,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46454,7 +46451,7 @@
         <v>1566</v>
       </c>
       <c r="N428" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P428" s="2">
         <f>_xlfn.XLOOKUP(C428,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46490,7 +46487,7 @@
         <v>1254</v>
       </c>
       <c r="N429" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P429" s="2">
         <f>_xlfn.XLOOKUP(C429,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46526,7 +46523,7 @@
         <v>1341</v>
       </c>
       <c r="N430" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P430" s="2">
         <f>_xlfn.XLOOKUP(C430,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46562,7 +46559,7 @@
         <v>2236</v>
       </c>
       <c r="N431" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P431" s="2">
         <f>_xlfn.XLOOKUP(C431,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46598,7 +46595,7 @@
         <v>866</v>
       </c>
       <c r="N432" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P432" s="2">
         <f>_xlfn.XLOOKUP(C432,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46634,7 +46631,7 @@
         <v>1380</v>
       </c>
       <c r="N433" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P433" s="2">
         <f>_xlfn.XLOOKUP(C433,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46670,7 +46667,7 @@
         <v>3200</v>
       </c>
       <c r="N434" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P434" s="2">
         <f>_xlfn.XLOOKUP(C434,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46706,7 +46703,7 @@
         <v>2043</v>
       </c>
       <c r="N435" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P435" s="2">
         <f>_xlfn.XLOOKUP(C435,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46742,7 +46739,7 @@
         <v>2016</v>
       </c>
       <c r="N436" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P436" s="2">
         <f>_xlfn.XLOOKUP(C436,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46778,7 +46775,7 @@
         <v>2722</v>
       </c>
       <c r="N437" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P437" s="2">
         <f>_xlfn.XLOOKUP(C437,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46814,7 +46811,7 @@
         <v>589</v>
       </c>
       <c r="N438" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P438" s="2">
         <f>_xlfn.XLOOKUP(C438,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46850,7 +46847,7 @@
         <v>724</v>
       </c>
       <c r="N439" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P439" s="2">
         <f>_xlfn.XLOOKUP(C439,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46886,7 +46883,7 @@
         <v>175</v>
       </c>
       <c r="N440" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P440" s="2">
         <f>_xlfn.XLOOKUP(C440,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46922,7 +46919,7 @@
         <v>113</v>
       </c>
       <c r="N441" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P441" s="2">
         <f>_xlfn.XLOOKUP(C441,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46958,7 +46955,7 @@
         <v>179</v>
       </c>
       <c r="N442" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P442" s="2">
         <f>_xlfn.XLOOKUP(C442,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -46994,7 +46991,7 @@
         <v>230</v>
       </c>
       <c r="N443" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P443" s="2">
         <f>_xlfn.XLOOKUP(C443,[1]WM!$B:$B,[1]WM!$O:$O)</f>
@@ -47003,11 +47000,11 @@
     </row>
     <row r="444" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="B444" s="5"/>
       <c r="C444" s="20" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="D444" s="5" t="s">
         <v>521</v>
@@ -47030,7 +47027,7 @@
         <v>230</v>
       </c>
       <c r="N444" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P444" s="2" t="s">
         <v>744</v>
@@ -47065,7 +47062,7 @@
         <v>0</v>
       </c>
       <c r="N445" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P445" s="2" t="s">
         <v>744</v>
@@ -47100,7 +47097,7 @@
         <v>0</v>
       </c>
       <c r="N446" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P446" s="2" t="s">
         <v>744</v>
@@ -47135,7 +47132,7 @@
         <v>0</v>
       </c>
       <c r="N447" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P447" s="2" t="s">
         <v>744</v>
@@ -47170,7 +47167,7 @@
         <v>0</v>
       </c>
       <c r="N448" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P448" s="2" t="s">
         <v>744</v>
@@ -47205,7 +47202,7 @@
         <v>0</v>
       </c>
       <c r="N449" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P449" s="2" t="s">
         <v>744</v>
@@ -47240,7 +47237,7 @@
         <v>0</v>
       </c>
       <c r="N450" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P450" s="2" t="s">
         <v>744</v>
@@ -47275,7 +47272,7 @@
         <v>0</v>
       </c>
       <c r="N451" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P451" s="2" t="s">
         <v>744</v>
@@ -47310,7 +47307,7 @@
         <v>0</v>
       </c>
       <c r="N452" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P452" s="2" t="s">
         <v>744</v>
@@ -47345,7 +47342,7 @@
         <v>0</v>
       </c>
       <c r="N453" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P453" s="2" t="s">
         <v>744</v>
@@ -47380,7 +47377,7 @@
         <v>0</v>
       </c>
       <c r="N454" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P454" s="2" t="s">
         <v>744</v>
@@ -47415,7 +47412,7 @@
         <v>0</v>
       </c>
       <c r="N455" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P455" s="2" t="s">
         <v>744</v>
@@ -47450,7 +47447,7 @@
         <v>0</v>
       </c>
       <c r="N456" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P456" s="2" t="s">
         <v>744</v>
@@ -47485,7 +47482,7 @@
         <v>0</v>
       </c>
       <c r="N457" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P457" s="2" t="s">
         <v>744</v>
@@ -47520,7 +47517,7 @@
         <v>0</v>
       </c>
       <c r="N458" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P458" s="2" t="s">
         <v>744</v>
@@ -47555,7 +47552,7 @@
         <v>0</v>
       </c>
       <c r="N459" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P459" s="2" t="s">
         <v>744</v>
@@ -47590,7 +47587,7 @@
         <v>0</v>
       </c>
       <c r="N460" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P460" s="2" t="s">
         <v>744</v>
@@ -47625,7 +47622,7 @@
         <v>0</v>
       </c>
       <c r="N461" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P461" s="2" t="s">
         <v>744</v>
@@ -47660,7 +47657,7 @@
         <v>0</v>
       </c>
       <c r="N462" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P462" s="2" t="s">
         <v>744</v>
@@ -47695,7 +47692,7 @@
         <v>0</v>
       </c>
       <c r="N463" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P463" s="2" t="s">
         <v>744</v>
@@ -47730,7 +47727,7 @@
         <v>0</v>
       </c>
       <c r="N464" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P464" s="2" t="s">
         <v>744</v>
@@ -47765,7 +47762,7 @@
         <v>0</v>
       </c>
       <c r="N465" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P465" s="2" t="s">
         <v>744</v>
@@ -47800,7 +47797,7 @@
         <v>0</v>
       </c>
       <c r="N466" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P466" s="2" t="s">
         <v>744</v>
@@ -47835,7 +47832,7 @@
         <v>0</v>
       </c>
       <c r="N467" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P467" s="2" t="s">
         <v>744</v>
@@ -47870,7 +47867,7 @@
         <v>0</v>
       </c>
       <c r="N468" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P468" s="2" t="s">
         <v>744</v>
@@ -47905,7 +47902,7 @@
         <v>0</v>
       </c>
       <c r="N469" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P469" s="2" t="s">
         <v>744</v>
@@ -47940,7 +47937,7 @@
         <v>0</v>
       </c>
       <c r="N470" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P470" s="2" t="s">
         <v>744</v>
@@ -47975,7 +47972,7 @@
         <v>0</v>
       </c>
       <c r="N471" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P471" s="2" t="s">
         <v>744</v>
@@ -48010,7 +48007,7 @@
         <v>0</v>
       </c>
       <c r="N472" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P472" s="2" t="s">
         <v>744</v>
@@ -48045,7 +48042,7 @@
         <v>0</v>
       </c>
       <c r="N473" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P473" s="2" t="s">
         <v>744</v>
@@ -48080,7 +48077,7 @@
         <v>0</v>
       </c>
       <c r="N474" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P474" s="2" t="s">
         <v>744</v>
@@ -48115,7 +48112,7 @@
         <v>0</v>
       </c>
       <c r="N475" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P475" s="2" t="s">
         <v>744</v>
@@ -48150,7 +48147,7 @@
         <v>0</v>
       </c>
       <c r="N476" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P476" s="2" t="s">
         <v>744</v>
@@ -48185,7 +48182,7 @@
         <v>0</v>
       </c>
       <c r="N477" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P477" s="2" t="s">
         <v>744</v>
@@ -48220,7 +48217,7 @@
         <v>0</v>
       </c>
       <c r="N478" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P478" s="2" t="s">
         <v>744</v>
@@ -48255,7 +48252,7 @@
         <v>0</v>
       </c>
       <c r="N479" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P479" s="2" t="s">
         <v>744</v>
@@ -48290,7 +48287,7 @@
         <v>0</v>
       </c>
       <c r="N480" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P480" s="2" t="s">
         <v>744</v>
@@ -48325,7 +48322,7 @@
         <v>0</v>
       </c>
       <c r="N481" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P481" s="2" t="s">
         <v>744</v>
@@ -48360,7 +48357,7 @@
         <v>0</v>
       </c>
       <c r="N482" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P482" s="2" t="s">
         <v>744</v>
@@ -48395,7 +48392,7 @@
         <v>0</v>
       </c>
       <c r="N483" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P483" s="2" t="s">
         <v>744</v>
@@ -57192,13 +57189,13 @@
       </c>
       <c r="F835" s="5"/>
       <c r="G835" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H835" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I835" s="5" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="J835" s="5" t="s">
         <v>2794</v>
@@ -57227,13 +57224,13 @@
       </c>
       <c r="F836" s="5"/>
       <c r="G836" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="H836" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I836" s="5" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="J836" s="5" t="s">
         <v>2794</v>
@@ -57262,10 +57259,10 @@
       </c>
       <c r="F837" s="5"/>
       <c r="G837" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H837" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I837" s="5" t="s">
         <v>744</v>
@@ -57297,10 +57294,10 @@
       </c>
       <c r="F838" s="5"/>
       <c r="G838" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H838" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I838" s="5" t="s">
         <v>744</v>
@@ -57332,10 +57329,10 @@
       </c>
       <c r="F839" s="5"/>
       <c r="G839" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H839" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I839" s="5" t="s">
         <v>744</v>
@@ -57367,10 +57364,10 @@
       </c>
       <c r="F840" s="5"/>
       <c r="G840" s="5" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="H840" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I840" s="5" t="s">
         <v>744</v>
@@ -58100,10 +58097,10 @@
       </c>
       <c r="F869" s="5"/>
       <c r="G869" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H869" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I869" s="5" t="s">
         <v>744</v>
@@ -58134,7 +58131,7 @@
       <c r="F870" s="5"/>
       <c r="G870" s="5"/>
       <c r="H870" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I870" s="5" t="s">
         <v>744</v>
@@ -58165,7 +58162,7 @@
       <c r="F871" s="5"/>
       <c r="G871" s="5"/>
       <c r="H871" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I871" s="5" t="s">
         <v>744</v>
@@ -58197,10 +58194,10 @@
       </c>
       <c r="F872" s="5"/>
       <c r="G872" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H872" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I872" s="5" t="s">
         <v>744</v>
@@ -58222,7 +58219,7 @@
       </c>
       <c r="B873" s="5"/>
       <c r="C873" s="5" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="D873" s="5" t="s">
         <v>520</v>
@@ -58232,10 +58229,10 @@
       </c>
       <c r="F873" s="5"/>
       <c r="G873" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H873" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I873" s="5" t="s">
         <v>744</v>
@@ -58257,7 +58254,7 @@
       </c>
       <c r="B874" s="5"/>
       <c r="C874" s="5" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="D874" s="5" t="s">
         <v>520</v>
@@ -58267,10 +58264,10 @@
       </c>
       <c r="F874" s="5"/>
       <c r="G874" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H874" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I874" s="5" t="s">
         <v>744</v>
@@ -58292,7 +58289,7 @@
       </c>
       <c r="B875" s="5"/>
       <c r="C875" s="5" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="D875" s="5" t="s">
         <v>520</v>
@@ -58302,10 +58299,10 @@
       </c>
       <c r="F875" s="5"/>
       <c r="G875" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H875" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I875" s="5" t="s">
         <v>744</v>
@@ -58335,10 +58332,10 @@
       </c>
       <c r="F876" s="5"/>
       <c r="G876" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H876" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I876" s="5" t="s">
         <v>744</v>
@@ -58368,10 +58365,10 @@
       </c>
       <c r="F877" s="5"/>
       <c r="G877" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H877" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I877" s="5" t="s">
         <v>744</v>
@@ -58412,11 +58409,11 @@
         <v>357</v>
       </c>
       <c r="L878" s="22" t="s">
-        <v>9396</v>
+        <v>9395</v>
       </c>
       <c r="M878" s="15"/>
       <c r="N878" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P878" s="2">
         <v>1</v>
@@ -58440,13 +58437,13 @@
         <v>6199</v>
       </c>
       <c r="G879" s="5" t="s">
+        <v>2972</v>
+      </c>
+      <c r="H879" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I879" s="5" t="s">
         <v>2973</v>
-      </c>
-      <c r="H879" s="5" t="s">
-        <v>2954</v>
-      </c>
-      <c r="I879" s="5" t="s">
-        <v>2974</v>
       </c>
       <c r="J879" s="6" t="s">
         <v>355</v>
@@ -58459,7 +58456,7 @@
       </c>
       <c r="M879" s="15"/>
       <c r="N879" s="2" t="s">
-        <v>9392</v>
+        <v>9391</v>
       </c>
       <c r="P879" s="2" t="e">
         <v>#N/A</v>
@@ -58483,13 +58480,13 @@
         <v>10199</v>
       </c>
       <c r="G880" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H880" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I880" s="5" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="J880" s="6" t="s">
         <v>355</v>
@@ -58502,7 +58499,7 @@
       </c>
       <c r="M880" s="15"/>
       <c r="N880" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P880" s="2">
         <v>1</v>
@@ -58526,13 +58523,13 @@
         <v>12499</v>
       </c>
       <c r="G881" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H881" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I881" s="5" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="J881" s="6" t="s">
         <v>355</v>
@@ -58545,7 +58542,7 @@
       </c>
       <c r="M881" s="15"/>
       <c r="N881" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P881" s="2">
         <v>1</v>
@@ -58580,7 +58577,7 @@
       </c>
       <c r="M882" s="15"/>
       <c r="N882" s="2" t="s">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="P882" s="2">
         <v>4</v>
@@ -58604,13 +58601,13 @@
         <v>2299</v>
       </c>
       <c r="G883" s="5" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="H883" s="5" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="I883" s="5" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="J883" s="5" t="s">
         <v>356</v>
@@ -58619,11 +58616,11 @@
         <v>367</v>
       </c>
       <c r="L883" s="22" t="s">
-        <v>9397</v>
+        <v>9396</v>
       </c>
       <c r="M883" s="15"/>
       <c r="N883" s="2" t="s">
-        <v>9393</v>
+        <v>9392</v>
       </c>
       <c r="P883" s="2">
         <v>50</v>
@@ -58645,10 +58642,10 @@
       </c>
       <c r="F884" s="5"/>
       <c r="G884" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H884" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I884" s="5" t="s">
         <v>744</v>
@@ -58680,10 +58677,10 @@
       </c>
       <c r="F885" s="5"/>
       <c r="G885" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H885" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I885" s="5" t="s">
         <v>744</v>
@@ -58705,7 +58702,7 @@
       </c>
       <c r="B886" s="5"/>
       <c r="C886" s="19" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="D886" s="5" t="s">
         <v>520</v>
@@ -58734,7 +58731,7 @@
       </c>
       <c r="B887" s="5"/>
       <c r="C887" s="19" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="D887" s="5" t="s">
         <v>520</v>
@@ -58840,11 +58837,11 @@
     </row>
     <row r="891" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A891" s="5" t="s">
-        <v>2861</v>
+        <v>3025</v>
       </c>
       <c r="B891" s="5"/>
       <c r="C891" s="5" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="D891" s="5" t="s">
         <v>520</v>
@@ -58854,10 +58851,10 @@
       </c>
       <c r="F891" s="5"/>
       <c r="G891" s="5" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="H891" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I891" s="5" t="s">
         <v>744</v>
@@ -58875,7 +58872,7 @@
     </row>
     <row r="892" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A892" s="5" t="s">
-        <v>3026</v>
+        <v>2861</v>
       </c>
       <c r="B892" s="5"/>
       <c r="C892" s="5" t="s">
@@ -58885,27 +58882,27 @@
         <v>520</v>
       </c>
       <c r="E892" s="5" t="s">
-        <v>946</v>
+        <v>2889</v>
       </c>
       <c r="F892" s="5"/>
       <c r="G892" s="5" t="s">
-        <v>2989</v>
+        <v>2958</v>
       </c>
       <c r="H892" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I892" s="5" t="s">
         <v>744</v>
       </c>
       <c r="J892" s="5" t="s">
-        <v>1098</v>
+        <v>1124</v>
       </c>
       <c r="K892" s="5" t="s">
-        <v>1099</v>
+        <v>2910</v>
       </c>
       <c r="L892" s="5"/>
       <c r="M892" s="15">
-        <v>1693.3</v>
+        <v>5083.8175999999994</v>
       </c>
     </row>
     <row r="893" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -58924,10 +58921,10 @@
       </c>
       <c r="F893" s="5"/>
       <c r="G893" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H893" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I893" s="5" t="s">
         <v>744</v>
@@ -58940,7 +58937,7 @@
       </c>
       <c r="L893" s="5"/>
       <c r="M893" s="15">
-        <v>5083.8175999999994</v>
+        <v>4617.7883999999995</v>
       </c>
     </row>
     <row r="894" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -58959,10 +58956,10 @@
       </c>
       <c r="F894" s="5"/>
       <c r="G894" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H894" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I894" s="5" t="s">
         <v>744</v>
@@ -58975,7 +58972,7 @@
       </c>
       <c r="L894" s="5"/>
       <c r="M894" s="15">
-        <v>4617.7883999999995</v>
+        <v>3186.0472</v>
       </c>
     </row>
     <row r="895" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -58994,10 +58991,10 @@
       </c>
       <c r="F895" s="5"/>
       <c r="G895" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H895" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I895" s="5" t="s">
         <v>744</v>
@@ -59010,7 +59007,7 @@
       </c>
       <c r="L895" s="5"/>
       <c r="M895" s="15">
-        <v>3186.0472</v>
+        <v>3401.5623999999998</v>
       </c>
     </row>
     <row r="896" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59029,10 +59026,10 @@
       </c>
       <c r="F896" s="5"/>
       <c r="G896" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="H896" s="5" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="I896" s="5" t="s">
         <v>744</v>
@@ -59045,7 +59042,7 @@
       </c>
       <c r="L896" s="5"/>
       <c r="M896" s="15">
-        <v>3401.5623999999998</v>
+        <v>9756.83</v>
       </c>
     </row>
     <row r="897" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59053,9 +59050,7 @@
         <v>2866</v>
       </c>
       <c r="B897" s="5"/>
-      <c r="C897" s="5" t="s">
-        <v>2889</v>
-      </c>
+      <c r="C897" s="5"/>
       <c r="D897" s="5" t="s">
         <v>520</v>
       </c>
@@ -59063,15 +59058,9 @@
         <v>2894</v>
       </c>
       <c r="F897" s="5"/>
-      <c r="G897" s="5" t="s">
-        <v>2959</v>
-      </c>
-      <c r="H897" s="5" t="s">
-        <v>2957</v>
-      </c>
-      <c r="I897" s="5" t="s">
-        <v>744</v>
-      </c>
+      <c r="G897" s="5"/>
+      <c r="H897" s="5"/>
+      <c r="I897" s="5"/>
       <c r="J897" s="5" t="s">
         <v>1124</v>
       </c>
@@ -59080,7 +59069,7 @@
       </c>
       <c r="L897" s="5"/>
       <c r="M897" s="15">
-        <v>9756.83</v>
+        <v>5471.3886000000002</v>
       </c>
     </row>
     <row r="898" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59088,7 +59077,9 @@
         <v>2867</v>
       </c>
       <c r="B898" s="5"/>
-      <c r="C898" s="5"/>
+      <c r="C898" t="s">
+        <v>3039</v>
+      </c>
       <c r="D898" s="5" t="s">
         <v>520</v>
       </c>
@@ -59115,9 +59106,7 @@
         <v>2868</v>
       </c>
       <c r="B899" s="5"/>
-      <c r="C899" t="s">
-        <v>3040</v>
-      </c>
+      <c r="C899" s="5"/>
       <c r="D899" s="5" t="s">
         <v>520</v>
       </c>
@@ -59129,14 +59118,14 @@
       <c r="H899" s="5"/>
       <c r="I899" s="5"/>
       <c r="J899" s="5" t="s">
-        <v>1124</v>
+        <v>2794</v>
       </c>
       <c r="K899" s="5" t="s">
         <v>2917</v>
       </c>
       <c r="L899" s="5"/>
       <c r="M899" s="15">
-        <v>5471.3886000000002</v>
+        <v>1365.6045599999998</v>
       </c>
     </row>
     <row r="900" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59163,7 +59152,7 @@
       </c>
       <c r="L900" s="5"/>
       <c r="M900" s="15">
-        <v>1365.6045599999998</v>
+        <v>1201.7320127999999</v>
       </c>
     </row>
     <row r="901" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59190,7 +59179,7 @@
       </c>
       <c r="L901" s="5"/>
       <c r="M901" s="15">
-        <v>1201.7320127999999</v>
+        <v>1775.2859279999998</v>
       </c>
     </row>
     <row r="902" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59213,11 +59202,11 @@
         <v>2794</v>
       </c>
       <c r="K902" s="5" t="s">
-        <v>2920</v>
+        <v>2917</v>
       </c>
       <c r="L902" s="5"/>
       <c r="M902" s="15">
-        <v>1775.2859279999998</v>
+        <v>2731.2091199999995</v>
       </c>
     </row>
     <row r="903" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59225,26 +59214,34 @@
         <v>2872</v>
       </c>
       <c r="B903" s="5"/>
-      <c r="C903" s="5"/>
+      <c r="C903" s="5" t="s">
+        <v>2942</v>
+      </c>
       <c r="D903" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E903" s="5" t="s">
-        <v>2900</v>
+        <v>1078</v>
       </c>
       <c r="F903" s="5"/>
-      <c r="G903" s="5"/>
-      <c r="H903" s="5"/>
-      <c r="I903" s="5"/>
+      <c r="G903" s="5" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H903" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I903" s="5" t="s">
+        <v>744</v>
+      </c>
       <c r="J903" s="5" t="s">
-        <v>2794</v>
+        <v>2795</v>
       </c>
       <c r="K903" s="5" t="s">
-        <v>2918</v>
+        <v>2856</v>
       </c>
       <c r="L903" s="5"/>
       <c r="M903" s="15">
-        <v>2731.2091199999995</v>
+        <v>1544.9101177499999</v>
       </c>
     </row>
     <row r="904" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59252,34 +59249,26 @@
         <v>2873</v>
       </c>
       <c r="B904" s="5"/>
-      <c r="C904" s="5" t="s">
-        <v>2943</v>
-      </c>
+      <c r="C904" s="5"/>
       <c r="D904" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E904" s="5" t="s">
-        <v>1078</v>
+        <v>2900</v>
       </c>
       <c r="F904" s="5"/>
-      <c r="G904" s="5" t="s">
-        <v>2953</v>
-      </c>
-      <c r="H904" s="5" t="s">
-        <v>2957</v>
-      </c>
-      <c r="I904" s="5" t="s">
-        <v>744</v>
-      </c>
+      <c r="G904" s="5"/>
+      <c r="H904" s="5"/>
+      <c r="I904" s="5"/>
       <c r="J904" s="5" t="s">
-        <v>2795</v>
+        <v>1152</v>
       </c>
       <c r="K904" s="5" t="s">
-        <v>2856</v>
+        <v>2920</v>
       </c>
       <c r="L904" s="5"/>
       <c r="M904" s="15">
-        <v>1544.9101177499999</v>
+        <v>2592.4323549599999</v>
       </c>
     </row>
     <row r="905" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59306,7 +59295,7 @@
       </c>
       <c r="L905" s="5"/>
       <c r="M905" s="15">
-        <v>2592.4323549599999</v>
+        <v>4146.8485356000001</v>
       </c>
     </row>
     <row r="906" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59333,7 +59322,7 @@
       </c>
       <c r="L906" s="5"/>
       <c r="M906" s="15">
-        <v>4146.8485356000001</v>
+        <v>1551.8080997999998</v>
       </c>
     </row>
     <row r="907" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59360,7 +59349,7 @@
       </c>
       <c r="L907" s="5"/>
       <c r="M907" s="15">
-        <v>1551.8080997999998</v>
+        <v>1549.2000189600001</v>
       </c>
     </row>
     <row r="908" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59387,7 +59376,7 @@
       </c>
       <c r="L908" s="5"/>
       <c r="M908" s="15">
-        <v>1549.2000189600001</v>
+        <v>2070.8161869599999</v>
       </c>
     </row>
     <row r="909" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59414,7 +59403,7 @@
       </c>
       <c r="L909" s="5"/>
       <c r="M909" s="15">
-        <v>2070.8161869599999</v>
+        <v>1073.2252656600001</v>
       </c>
     </row>
     <row r="910" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59441,7 +59430,7 @@
       </c>
       <c r="L910" s="5"/>
       <c r="M910" s="15">
-        <v>1073.2252656600001</v>
+        <v>2216.8687139999997</v>
       </c>
     </row>
     <row r="911" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59468,7 +59457,7 @@
       </c>
       <c r="L911" s="5"/>
       <c r="M911" s="15">
-        <v>2216.8687139999997</v>
+        <v>2412.4747769999999</v>
       </c>
     </row>
     <row r="912" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59495,7 +59484,7 @@
       </c>
       <c r="L912" s="5"/>
       <c r="M912" s="15">
-        <v>2412.4747769999999</v>
+        <v>1551.8080997999998</v>
       </c>
     </row>
     <row r="913" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -59515,122 +59504,130 @@
       <c r="H913" s="5"/>
       <c r="I913" s="5"/>
       <c r="J913" s="5" t="s">
-        <v>1152</v>
+        <v>2851</v>
       </c>
       <c r="K913" s="5" t="s">
         <v>2929</v>
       </c>
       <c r="L913" s="5"/>
       <c r="M913" s="15">
-        <v>1551.8080997999998</v>
+        <v>2034.3030551999998</v>
       </c>
     </row>
     <row r="914" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A914" s="5" t="s">
-        <v>2883</v>
+        <v>3028</v>
       </c>
       <c r="B914" s="5"/>
-      <c r="C914" s="5"/>
+      <c r="C914" s="19" t="s">
+        <v>3042</v>
+      </c>
       <c r="D914" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E914" s="5" t="s">
-        <v>2910</v>
+        <v>3029</v>
       </c>
       <c r="F914" s="5"/>
       <c r="G914" s="5"/>
       <c r="H914" s="5"/>
       <c r="I914" s="5"/>
-      <c r="J914" s="5" t="s">
-        <v>2851</v>
-      </c>
-      <c r="K914" s="5" t="s">
-        <v>2930</v>
-      </c>
+      <c r="K914" s="5"/>
       <c r="L914" s="5"/>
-      <c r="M914" s="15">
-        <v>2034.3030551999998</v>
-      </c>
+      <c r="M914" s="15"/>
     </row>
     <row r="915" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A915" s="5" t="s">
-        <v>3029</v>
+        <v>3031</v>
       </c>
       <c r="B915" s="5"/>
-      <c r="C915" s="19" t="s">
-        <v>3043</v>
+      <c r="C915" s="5" t="s">
+        <v>3037</v>
       </c>
       <c r="D915" s="5" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E915" s="5" t="s">
-        <v>3030</v>
+        <v>1259</v>
       </c>
       <c r="F915" s="5"/>
       <c r="G915" s="5"/>
       <c r="H915" s="5"/>
       <c r="I915" s="5"/>
-      <c r="K915" s="5"/>
+      <c r="J915" s="16" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K915" s="16" t="s">
+        <v>1292</v>
+      </c>
       <c r="L915" s="5"/>
       <c r="M915" s="15"/>
     </row>
     <row r="916" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A916" s="5" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="B916" s="5"/>
       <c r="C916" s="5" t="s">
-        <v>3038</v>
+        <v>3032</v>
       </c>
       <c r="D916" s="5" t="s">
-        <v>522</v>
+        <v>6</v>
       </c>
       <c r="E916" s="5" t="s">
-        <v>1259</v>
+        <v>329</v>
       </c>
       <c r="F916" s="5"/>
       <c r="G916" s="5"/>
       <c r="H916" s="5"/>
       <c r="I916" s="5"/>
-      <c r="J916" s="16" t="s">
-        <v>1115</v>
-      </c>
-      <c r="K916" s="16" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L916" s="5"/>
+      <c r="J916" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="K916" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="L916" s="22" t="s">
+        <v>361</v>
+      </c>
       <c r="M916" s="15"/>
+      <c r="N916" s="2" t="s">
+        <v>9392</v>
+      </c>
+      <c r="P916" s="2" t="e">
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="917" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A917" s="5" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="B917" s="5"/>
       <c r="C917" s="5" t="s">
-        <v>3033</v>
+        <v>3036</v>
       </c>
       <c r="D917" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E917" s="5" t="s">
-        <v>329</v>
+        <v>3034</v>
       </c>
       <c r="F917" s="5"/>
       <c r="G917" s="5"/>
       <c r="H917" s="5"/>
       <c r="I917" s="5"/>
-      <c r="J917" s="22" t="s">
-        <v>356</v>
+      <c r="J917" s="23" t="s">
+        <v>355</v>
       </c>
       <c r="K917" s="22" t="s">
-        <v>361</v>
+        <v>9397</v>
       </c>
       <c r="L917" s="22" t="s">
-        <v>361</v>
+        <v>9397</v>
       </c>
       <c r="M917" s="15"/>
       <c r="N917" s="2" t="s">
-        <v>9393</v>
+        <v>9391</v>
       </c>
       <c r="P917" s="2" t="e">
         <v>#N/A</v>
@@ -59638,72 +59635,54 @@
     </row>
     <row r="918" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A918" s="5" t="s">
-        <v>3036</v>
+        <v>1209</v>
       </c>
       <c r="B918" s="5"/>
       <c r="C918" s="5" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="D918" s="5" t="s">
-        <v>6</v>
+        <v>522</v>
       </c>
       <c r="E918" s="5" t="s">
-        <v>3035</v>
+        <v>1259</v>
       </c>
       <c r="F918" s="5"/>
       <c r="G918" s="5"/>
       <c r="H918" s="5"/>
       <c r="I918" s="5"/>
-      <c r="J918" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="K918" s="22" t="s">
-        <v>9398</v>
-      </c>
-      <c r="L918" s="22" t="s">
-        <v>9398</v>
-      </c>
+      <c r="J918" s="16" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K918" s="16" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L918" s="5"/>
       <c r="M918" s="15"/>
-      <c r="N918" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P918" s="2" t="e">
+    </row>
+    <row r="919" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A919" s="2" t="s">
+        <v>3046</v>
+      </c>
+      <c r="C919" s="2" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D919" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N919" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="P919" s="2" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="919" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A919" s="5" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B919" s="5"/>
-      <c r="C919" s="5" t="s">
-        <v>3039</v>
-      </c>
-      <c r="D919" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="E919" s="5" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F919" s="5"/>
-      <c r="G919" s="5"/>
-      <c r="H919" s="5"/>
-      <c r="I919" s="5"/>
-      <c r="J919" s="16" t="s">
-        <v>1115</v>
-      </c>
-      <c r="K919" s="16" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L919" s="5"/>
-      <c r="M919" s="15"/>
     </row>
     <row r="920" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A920" s="2" t="s">
+        <v>3048</v>
+      </c>
+      <c r="C920" s="2" t="s">
         <v>3047</v>
-      </c>
-      <c r="C920" s="2" t="s">
-        <v>3046</v>
       </c>
       <c r="D920" s="2" t="s">
         <v>6</v>
@@ -59720,13 +59699,13 @@
         <v>3049</v>
       </c>
       <c r="C921" s="2" t="s">
-        <v>3048</v>
+        <v>3050</v>
       </c>
       <c r="D921" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N921" s="2" t="s">
-        <v>9393</v>
+        <v>9391</v>
       </c>
       <c r="P921" s="2" t="e">
         <v>#N/A</v>
@@ -59734,10 +59713,10 @@
     </row>
     <row r="922" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A922" s="2" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="C922" s="2" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="D922" s="2" t="s">
         <v>6</v>
@@ -59751,7 +59730,7 @@
     </row>
     <row r="923" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A923" s="2" t="s">
-        <v>3052</v>
+        <v>3054</v>
       </c>
       <c r="C923" s="2" t="s">
         <v>3053</v>
@@ -59760,7 +59739,7 @@
         <v>6</v>
       </c>
       <c r="N923" s="2" t="s">
-        <v>9393</v>
+        <v>9391</v>
       </c>
       <c r="P923" s="2" t="e">
         <v>#N/A</v>
@@ -59768,19 +59747,19 @@
     </row>
     <row r="924" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A924" s="2" t="s">
+        <v>5134</v>
+      </c>
+      <c r="C924" s="2" t="s">
+        <v>7214</v>
+      </c>
+      <c r="D924" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E924" s="2" t="s">
         <v>3055</v>
       </c>
-      <c r="C924" s="2" t="s">
-        <v>3054</v>
-      </c>
-      <c r="D924" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="N924" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P924" s="2" t="e">
-        <v>#N/A</v>
+      <c r="J924" s="5" t="s">
+        <v>2644</v>
       </c>
     </row>
     <row r="925" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -64605,7 +64584,7 @@
         <v>2643</v>
       </c>
       <c r="E1208" s="2" t="s">
-        <v>3339</v>
+        <v>3230</v>
       </c>
       <c r="J1208" s="5" t="s">
         <v>2644</v>
@@ -64622,7 +64601,7 @@
         <v>2643</v>
       </c>
       <c r="E1209" s="2" t="s">
-        <v>3231</v>
+        <v>3339</v>
       </c>
       <c r="J1209" s="5" t="s">
         <v>2644</v>
@@ -71167,7 +71146,7 @@
         <v>2643</v>
       </c>
       <c r="E1594" s="2" t="s">
-        <v>3724</v>
+        <v>3713</v>
       </c>
       <c r="J1594" s="5" t="s">
         <v>2644</v>
@@ -71184,7 +71163,7 @@
         <v>2643</v>
       </c>
       <c r="E1595" s="2" t="s">
-        <v>3714</v>
+        <v>3724</v>
       </c>
       <c r="J1595" s="5" t="s">
         <v>2644</v>
@@ -74805,7 +74784,7 @@
         <v>2643</v>
       </c>
       <c r="E1808" s="2" t="s">
-        <v>3937</v>
+        <v>3244</v>
       </c>
       <c r="J1808" s="5" t="s">
         <v>2644</v>
@@ -74822,7 +74801,7 @@
         <v>2643</v>
       </c>
       <c r="E1809" s="2" t="s">
-        <v>3245</v>
+        <v>3937</v>
       </c>
       <c r="J1809" s="5" t="s">
         <v>2644</v>
@@ -75088,13 +75067,13 @@
         <v>6035</v>
       </c>
       <c r="C1825" s="2" t="s">
-        <v>8115</v>
+        <v>7831</v>
       </c>
       <c r="D1825" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E1825" s="2" t="s">
-        <v>3953</v>
+        <v>3671</v>
       </c>
       <c r="J1825" s="5" t="s">
         <v>2644</v>
@@ -75105,13 +75084,13 @@
         <v>6036</v>
       </c>
       <c r="C1826" s="2" t="s">
-        <v>7832</v>
+        <v>8115</v>
       </c>
       <c r="D1826" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E1826" s="2" t="s">
-        <v>3672</v>
+        <v>3953</v>
       </c>
       <c r="J1826" s="5" t="s">
         <v>2644</v>
@@ -85016,7 +84995,7 @@
         <v>6619</v>
       </c>
       <c r="C2409" s="2" t="s">
-        <v>8698</v>
+        <v>8625</v>
       </c>
       <c r="D2409" s="2" t="s">
         <v>2643</v>
@@ -85033,7 +85012,7 @@
         <v>6620</v>
       </c>
       <c r="C2410" s="2" t="s">
-        <v>8626</v>
+        <v>8698</v>
       </c>
       <c r="D2410" s="2" t="s">
         <v>2643</v>
@@ -85727,10 +85706,10 @@
     </row>
     <row r="2451" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2451" s="2" t="s">
-        <v>6661</v>
+        <v>5398</v>
       </c>
       <c r="C2451" s="2" t="s">
-        <v>8739</v>
+        <v>7478</v>
       </c>
       <c r="D2451" s="2" t="s">
         <v>2643</v>
@@ -85744,10 +85723,10 @@
     </row>
     <row r="2452" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2452" s="2" t="s">
-        <v>5399</v>
+        <v>6661</v>
       </c>
       <c r="C2452" s="2" t="s">
-        <v>7479</v>
+        <v>8739</v>
       </c>
       <c r="D2452" s="2" t="s">
         <v>2643</v>
@@ -94705,8 +94684,8 @@
       <c r="A2979" s="2" t="s">
         <v>7188</v>
       </c>
-      <c r="C2979" s="2" t="s">
-        <v>9266</v>
+      <c r="C2979" s="2">
+        <v>0</v>
       </c>
       <c r="D2979" s="2" t="s">
         <v>2643</v>
@@ -94722,8 +94701,8 @@
       <c r="A2980" s="2" t="s">
         <v>7189</v>
       </c>
-      <c r="C2980" s="2">
-        <v>0</v>
+      <c r="C2980" s="2" t="s">
+        <v>9266</v>
       </c>
       <c r="D2980" s="2" t="s">
         <v>2643</v>
@@ -95008,8 +94987,8 @@
       </c>
     </row>
     <row r="2997" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2997" s="2" t="s">
-        <v>7206</v>
+      <c r="A2997" s="2">
+        <v>0</v>
       </c>
       <c r="C2997" s="2" t="s">
         <v>9283</v>
@@ -95042,8 +95021,8 @@
       </c>
     </row>
     <row r="2999" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2999" s="2">
-        <v>0</v>
+      <c r="A2999" s="2" t="s">
+        <v>7206</v>
       </c>
       <c r="C2999" s="2" t="s">
         <v>9285</v>
@@ -95179,99 +95158,99 @@
     </row>
     <row r="3007" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3007" s="2" t="s">
-        <v>7214</v>
-      </c>
-      <c r="C3007" s="2" t="s">
         <v>9293</v>
       </c>
-      <c r="D3007" s="2" t="s">
-        <v>2643</v>
+      <c r="D3007" s="5" t="s">
+        <v>520</v>
       </c>
       <c r="E3007" s="2" t="s">
-        <v>5134</v>
-      </c>
-      <c r="J3007" s="5" t="s">
-        <v>2644</v>
+        <v>9294</v>
+      </c>
+      <c r="G3007" s="2" t="s">
+        <v>2952</v>
+      </c>
+      <c r="J3007" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K3007" s="2" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="3008" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3008" s="2" t="s">
-        <v>9294</v>
+        <v>2866</v>
+      </c>
+      <c r="C3008" s="2" t="s">
+        <v>9295</v>
       </c>
       <c r="D3008" s="5" t="s">
         <v>520</v>
       </c>
       <c r="E3008" s="2" t="s">
-        <v>9295</v>
-      </c>
-      <c r="G3008" s="2" t="s">
-        <v>2953</v>
+        <v>2894</v>
       </c>
       <c r="J3008" s="2" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="K3008" s="2" t="s">
-        <v>1097</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="3009" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3009" s="2" t="s">
-        <v>2867</v>
-      </c>
-      <c r="C3009" s="2" t="s">
         <v>9296</v>
       </c>
       <c r="D3009" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="E3009" s="2" t="s">
-        <v>2895</v>
-      </c>
-      <c r="J3009" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="K3009" s="2" t="s">
-        <v>2916</v>
+        <v>6</v>
+      </c>
+      <c r="E3009" s="21" t="s">
+        <v>9297</v>
+      </c>
+      <c r="J3009" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="K3009" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="L3009" s="2" t="s">
+        <v>9395</v>
+      </c>
+      <c r="N3009" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="P3009" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="3010" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3010" s="2" t="s">
-        <v>9297</v>
-      </c>
-      <c r="D3010" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3010" s="21" t="s">
         <v>9298</v>
       </c>
-      <c r="J3010" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="K3010" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="L3010" s="2" t="s">
-        <v>9396</v>
-      </c>
-      <c r="N3010" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P3010" s="2">
-        <v>20</v>
+      <c r="C3010" s="2" t="s">
+        <v>9299</v>
+      </c>
+      <c r="D3010" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E3010" s="2" t="s">
+        <v>9300</v>
+      </c>
+      <c r="J3010" s="5" t="s">
+        <v>2644</v>
       </c>
     </row>
     <row r="3011" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3011" s="2" t="s">
-        <v>9299</v>
+        <v>9301</v>
       </c>
       <c r="C3011" s="2" t="s">
-        <v>9300</v>
+        <v>9302</v>
       </c>
       <c r="D3011" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3011" s="2" t="s">
-        <v>9301</v>
+        <v>9303</v>
       </c>
       <c r="J3011" s="5" t="s">
         <v>2644</v>
@@ -95279,16 +95258,16 @@
     </row>
     <row r="3012" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3012" s="2" t="s">
-        <v>9302</v>
+        <v>9304</v>
       </c>
       <c r="C3012" s="2" t="s">
-        <v>9303</v>
+        <v>9305</v>
       </c>
       <c r="D3012" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3012" s="2" t="s">
-        <v>9304</v>
+        <v>9306</v>
       </c>
       <c r="J3012" s="5" t="s">
         <v>2644</v>
@@ -95296,16 +95275,16 @@
     </row>
     <row r="3013" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3013" s="2" t="s">
-        <v>9305</v>
+        <v>9307</v>
       </c>
       <c r="C3013" s="2" t="s">
-        <v>9306</v>
+        <v>9308</v>
       </c>
       <c r="D3013" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3013" s="2" t="s">
-        <v>9307</v>
+        <v>9309</v>
       </c>
       <c r="J3013" s="5" t="s">
         <v>2644</v>
@@ -95313,16 +95292,16 @@
     </row>
     <row r="3014" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3014" s="2" t="s">
-        <v>9308</v>
+        <v>9310</v>
       </c>
       <c r="C3014" s="2" t="s">
-        <v>9309</v>
+        <v>9311</v>
       </c>
       <c r="D3014" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3014" s="2" t="s">
-        <v>9310</v>
+        <v>9312</v>
       </c>
       <c r="J3014" s="5" t="s">
         <v>2644</v>
@@ -95330,16 +95309,16 @@
     </row>
     <row r="3015" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3015" s="2" t="s">
-        <v>9311</v>
+        <v>9313</v>
       </c>
       <c r="C3015" s="2" t="s">
-        <v>9312</v>
+        <v>9314</v>
       </c>
       <c r="D3015" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3015" s="2" t="s">
-        <v>9313</v>
+        <v>9315</v>
       </c>
       <c r="J3015" s="5" t="s">
         <v>2644</v>
@@ -95347,16 +95326,16 @@
     </row>
     <row r="3016" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3016" s="2" t="s">
-        <v>9314</v>
+        <v>9316</v>
       </c>
       <c r="C3016" s="2" t="s">
-        <v>9315</v>
+        <v>9317</v>
       </c>
       <c r="D3016" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3016" s="2" t="s">
-        <v>9316</v>
+        <v>9318</v>
       </c>
       <c r="J3016" s="5" t="s">
         <v>2644</v>
@@ -95364,16 +95343,16 @@
     </row>
     <row r="3017" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3017" s="2" t="s">
-        <v>9317</v>
+        <v>9319</v>
       </c>
       <c r="C3017" s="2" t="s">
-        <v>9318</v>
+        <v>9320</v>
       </c>
       <c r="D3017" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3017" s="2" t="s">
-        <v>9319</v>
+        <v>9321</v>
       </c>
       <c r="J3017" s="5" t="s">
         <v>2644</v>
@@ -95381,16 +95360,16 @@
     </row>
     <row r="3018" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3018" s="2" t="s">
-        <v>9320</v>
+        <v>9322</v>
       </c>
       <c r="C3018" s="2" t="s">
-        <v>9321</v>
+        <v>9323</v>
       </c>
       <c r="D3018" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3018" s="2" t="s">
-        <v>9322</v>
+        <v>9324</v>
       </c>
       <c r="J3018" s="5" t="s">
         <v>2644</v>
@@ -95398,16 +95377,16 @@
     </row>
     <row r="3019" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3019" s="2" t="s">
-        <v>9323</v>
+        <v>9325</v>
       </c>
       <c r="C3019" s="2" t="s">
-        <v>9324</v>
+        <v>9326</v>
       </c>
       <c r="D3019" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3019" s="2" t="s">
-        <v>9325</v>
+        <v>9327</v>
       </c>
       <c r="J3019" s="5" t="s">
         <v>2644</v>
@@ -95415,16 +95394,16 @@
     </row>
     <row r="3020" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3020" s="2" t="s">
-        <v>9326</v>
+        <v>9328</v>
       </c>
       <c r="C3020" s="2" t="s">
-        <v>9327</v>
+        <v>9329</v>
       </c>
       <c r="D3020" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3020" s="2" t="s">
-        <v>9328</v>
+        <v>9330</v>
       </c>
       <c r="J3020" s="5" t="s">
         <v>2644</v>
@@ -95432,16 +95411,16 @@
     </row>
     <row r="3021" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3021" s="2" t="s">
-        <v>9329</v>
+        <v>9331</v>
       </c>
       <c r="C3021" s="2" t="s">
-        <v>9330</v>
+        <v>9332</v>
       </c>
       <c r="D3021" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3021" s="2" t="s">
-        <v>9331</v>
+        <v>9333</v>
       </c>
       <c r="J3021" s="5" t="s">
         <v>2644</v>
@@ -95449,16 +95428,16 @@
     </row>
     <row r="3022" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3022" s="2" t="s">
-        <v>9332</v>
+        <v>9334</v>
       </c>
       <c r="C3022" s="2" t="s">
-        <v>9333</v>
+        <v>9335</v>
       </c>
       <c r="D3022" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3022" s="2" t="s">
-        <v>9334</v>
+        <v>9336</v>
       </c>
       <c r="J3022" s="5" t="s">
         <v>2644</v>
@@ -95466,16 +95445,16 @@
     </row>
     <row r="3023" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3023" s="2" t="s">
-        <v>9335</v>
+        <v>9337</v>
       </c>
       <c r="C3023" s="2" t="s">
-        <v>9336</v>
+        <v>9338</v>
       </c>
       <c r="D3023" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3023" s="2" t="s">
-        <v>9337</v>
+        <v>9339</v>
       </c>
       <c r="J3023" s="5" t="s">
         <v>2644</v>
@@ -95483,314 +95462,314 @@
     </row>
     <row r="3024" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3024" s="2" t="s">
-        <v>9338</v>
+        <v>9340</v>
       </c>
       <c r="C3024" s="2" t="s">
-        <v>9339</v>
+        <v>9341</v>
       </c>
       <c r="D3024" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3024" s="2" t="s">
-        <v>9340</v>
+        <v>9342</v>
       </c>
       <c r="J3024" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3025" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3025" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3025" s="2" t="s">
-        <v>9341</v>
+        <v>9343</v>
       </c>
       <c r="C3025" s="2" t="s">
-        <v>9342</v>
+        <v>9344</v>
       </c>
       <c r="D3025" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3025" s="2" t="s">
-        <v>9343</v>
+        <v>9345</v>
       </c>
       <c r="J3025" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3026" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3026" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3026" s="2" t="s">
-        <v>9344</v>
+        <v>9346</v>
       </c>
       <c r="C3026" s="2" t="s">
-        <v>9345</v>
+        <v>9347</v>
       </c>
       <c r="D3026" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3026" s="2" t="s">
-        <v>9346</v>
+        <v>9348</v>
       </c>
       <c r="J3026" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3027" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3027" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3027" s="2" t="s">
-        <v>9347</v>
+        <v>9349</v>
       </c>
       <c r="C3027" s="2" t="s">
-        <v>9348</v>
+        <v>9350</v>
       </c>
       <c r="D3027" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3027" s="2" t="s">
-        <v>9349</v>
+        <v>9351</v>
       </c>
       <c r="J3027" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3028" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3028" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3028" s="2" t="s">
-        <v>9350</v>
+        <v>9352</v>
       </c>
       <c r="C3028" s="2" t="s">
-        <v>9351</v>
+        <v>9353</v>
       </c>
       <c r="D3028" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3028" s="2" t="s">
-        <v>9352</v>
+        <v>9354</v>
       </c>
       <c r="J3028" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3029" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3029" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3029" s="2" t="s">
-        <v>9353</v>
+        <v>9355</v>
       </c>
       <c r="C3029" s="2" t="s">
-        <v>9354</v>
+        <v>9356</v>
       </c>
       <c r="D3029" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3029" s="2" t="s">
-        <v>9355</v>
+        <v>9357</v>
       </c>
       <c r="J3029" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3030" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3030" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3030" s="2" t="s">
-        <v>9356</v>
+        <v>9358</v>
       </c>
       <c r="C3030" s="2" t="s">
-        <v>9357</v>
+        <v>9359</v>
       </c>
       <c r="D3030" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3030" s="2" t="s">
-        <v>9358</v>
+        <v>9360</v>
       </c>
       <c r="J3030" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3031" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3031" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3031" s="2" t="s">
-        <v>9359</v>
+        <v>9361</v>
       </c>
       <c r="C3031" s="2" t="s">
-        <v>9360</v>
+        <v>9362</v>
       </c>
       <c r="D3031" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3031" s="2" t="s">
-        <v>9361</v>
+        <v>9363</v>
       </c>
       <c r="J3031" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3032" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3032" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3032" s="2" t="s">
-        <v>9362</v>
+        <v>9364</v>
       </c>
       <c r="C3032" s="2" t="s">
-        <v>9363</v>
+        <v>9365</v>
       </c>
       <c r="D3032" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3032" s="2" t="s">
-        <v>9364</v>
+        <v>9366</v>
       </c>
       <c r="J3032" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3033" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3033" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3033" s="2" t="s">
-        <v>9365</v>
+        <v>9367</v>
       </c>
       <c r="C3033" s="2" t="s">
-        <v>9366</v>
+        <v>9368</v>
       </c>
       <c r="D3033" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3033" s="2" t="s">
-        <v>9367</v>
+        <v>9369</v>
       </c>
       <c r="J3033" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3034" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3034" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3034" s="2" t="s">
-        <v>9368</v>
+        <v>9370</v>
       </c>
       <c r="C3034" s="2" t="s">
-        <v>9369</v>
+        <v>9371</v>
       </c>
       <c r="D3034" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3034" s="2" t="s">
-        <v>9370</v>
+        <v>9372</v>
       </c>
       <c r="J3034" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3035" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3035" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3035" s="2" t="s">
-        <v>9371</v>
+        <v>9373</v>
       </c>
       <c r="C3035" s="2" t="s">
-        <v>9372</v>
+        <v>9374</v>
       </c>
       <c r="D3035" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3035" s="2" t="s">
-        <v>9373</v>
+        <v>9375</v>
       </c>
       <c r="J3035" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3036" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3036" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3036" s="2" t="s">
-        <v>9374</v>
+        <v>9376</v>
       </c>
       <c r="C3036" s="2" t="s">
-        <v>9375</v>
+        <v>9377</v>
       </c>
       <c r="D3036" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3036" s="2" t="s">
-        <v>9376</v>
+        <v>9378</v>
       </c>
       <c r="J3036" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3037" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3037" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3037" s="2" t="s">
-        <v>9377</v>
+        <v>9379</v>
       </c>
       <c r="C3037" s="2" t="s">
-        <v>9378</v>
+        <v>9380</v>
       </c>
       <c r="D3037" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3037" s="2" t="s">
-        <v>9379</v>
+        <v>9381</v>
       </c>
       <c r="J3037" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3038" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3038" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3038" s="2" t="s">
-        <v>9380</v>
+        <v>9382</v>
       </c>
       <c r="C3038" s="2" t="s">
-        <v>9381</v>
+        <v>9383</v>
       </c>
       <c r="D3038" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3038" s="2" t="s">
-        <v>9382</v>
+        <v>9384</v>
       </c>
       <c r="J3038" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3039" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3039" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3039" s="2" t="s">
-        <v>9383</v>
+        <v>9385</v>
       </c>
       <c r="C3039" s="2" t="s">
-        <v>9384</v>
+        <v>9386</v>
       </c>
       <c r="D3039" s="2" t="s">
         <v>2643</v>
       </c>
       <c r="E3039" s="2" t="s">
-        <v>9385</v>
+        <v>9387</v>
       </c>
       <c r="J3039" s="5" t="s">
         <v>2644</v>
       </c>
     </row>
-    <row r="3040" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3040" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3040" s="2" t="s">
-        <v>9386</v>
+        <v>9389</v>
       </c>
       <c r="C3040" s="2" t="s">
-        <v>9387</v>
+        <v>9388</v>
       </c>
       <c r="D3040" s="2" t="s">
-        <v>2643</v>
+        <v>6</v>
       </c>
       <c r="E3040" s="2" t="s">
-        <v>9388</v>
-      </c>
-      <c r="J3040" s="5" t="s">
-        <v>2644</v>
-      </c>
-    </row>
-    <row r="3041" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9390</v>
+      </c>
+      <c r="N3040" s="2" t="s">
+        <v>9391</v>
+      </c>
+      <c r="P3040" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3041" s="2" t="s">
-        <v>9390</v>
+        <v>9436</v>
       </c>
       <c r="C3041" s="2" t="s">
-        <v>9389</v>
+        <v>9403</v>
       </c>
       <c r="D3041" s="2" t="s">
-        <v>6</v>
+        <v>2643</v>
       </c>
       <c r="E3041" s="2" t="s">
-        <v>9391</v>
-      </c>
-      <c r="N3041" s="2" t="s">
-        <v>9392</v>
-      </c>
-      <c r="P3041" s="2" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="3042" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9469</v>
+      </c>
+      <c r="J3041" s="2" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="3042" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3042" s="2" t="s">
         <v>9437</v>
       </c>
@@ -95807,7 +95786,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3043" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3043" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3043" s="2" t="s">
         <v>9438</v>
       </c>
@@ -95824,7 +95803,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3044" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3044" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3044" s="2" t="s">
         <v>9439</v>
       </c>
@@ -95841,7 +95820,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3045" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3045" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3045" s="2" t="s">
         <v>9440</v>
       </c>
@@ -95858,7 +95837,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3046" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3046" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3046" s="2" t="s">
         <v>9441</v>
       </c>
@@ -95875,7 +95854,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3047" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3047" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3047" s="2" t="s">
         <v>9442</v>
       </c>
@@ -95892,7 +95871,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3048" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3048" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3048" s="2" t="s">
         <v>9443</v>
       </c>
@@ -95909,7 +95888,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3049" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3049" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3049" s="2" t="s">
         <v>9444</v>
       </c>
@@ -95926,7 +95905,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3050" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3050" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3050" s="2" t="s">
         <v>9445</v>
       </c>
@@ -95943,7 +95922,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3051" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3051" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3051" s="2" t="s">
         <v>9446</v>
       </c>
@@ -95960,7 +95939,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3052" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3052" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3052" s="2" t="s">
         <v>9447</v>
       </c>
@@ -95977,7 +95956,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3053" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3053" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3053" s="2" t="s">
         <v>9448</v>
       </c>
@@ -95994,7 +95973,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3054" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3054" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3054" s="2" t="s">
         <v>9449</v>
       </c>
@@ -96011,7 +95990,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3055" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3055" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3055" s="2" t="s">
         <v>9450</v>
       </c>
@@ -96028,7 +96007,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3056" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3056" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3056" s="2" t="s">
         <v>9451</v>
       </c>
@@ -96334,25 +96313,8 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="3074" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3074" s="2" t="s">
-        <v>9469</v>
-      </c>
-      <c r="C3074" s="2" t="s">
-        <v>9436</v>
-      </c>
-      <c r="D3074" s="2" t="s">
-        <v>2643</v>
-      </c>
-      <c r="E3074" s="2" t="s">
-        <v>9502</v>
-      </c>
-      <c r="J3074" s="2" t="s">
-        <v>2644</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P3041" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
+  <autoFilter ref="A1:P3073" xr:uid="{3B2CFDDD-D63B-4FDB-9746-BFEFFD00084B}"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="41" priority="111"/>
   </conditionalFormatting>
@@ -96376,8 +96338,8 @@
     <cfRule type="duplicateValues" dxfId="34" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B95">
-    <cfRule type="duplicateValues" dxfId="33" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B125">
     <cfRule type="duplicateValues" dxfId="31" priority="78"/>
@@ -96397,9 +96359,9 @@
     <cfRule type="duplicateValues" dxfId="25" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E400">
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
     <cfRule type="duplicateValues" dxfId="21" priority="12"/>
     <cfRule type="duplicateValues" dxfId="20" priority="13"/>
     <cfRule type="duplicateValues" dxfId="19" priority="14"/>
@@ -96407,23 +96369,23 @@
     <cfRule type="duplicateValues" dxfId="17" priority="16" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E837:E840">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="23" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="24" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="23" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3010">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  <conditionalFormatting sqref="E3009">
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:I1">
